--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR3"/>
+  <dimension ref="A1:BR5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1303,8 +1303,436 @@
         <v>-1.75</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>4.315</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>3.555</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>1.495</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AI5" s="3" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="AJ5" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="AM5" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AN5" s="3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AP5" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ5" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR5" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS5" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT5" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AV5" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="AW5" s="3" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AX5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AY5" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA5" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="BB5" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BC5" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="BD5" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="BE5" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BF5" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BG5" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH5" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI5" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BJ5" s="3" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BK5" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL5" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BM5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN5" s="3" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BO5" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP5" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="BQ5" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BR5" s="3" t="n">
+        <v>1.805</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR3"/>
+  <autoFilter ref="A1:BR5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1306,433 +1306,647 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.61</v>
+        <v>2.495</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>3.015</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1.675</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AV4" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>2.165</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="AW4" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BH4" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>3.215</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2.745</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>2.665</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>2.715</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC4" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AD4" s="3" t="n">
-        <v>1.245</v>
-      </c>
-      <c r="AE4" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF4" s="3" t="n">
-        <v>2.075</v>
-      </c>
-      <c r="AG4" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH4" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AI4" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AJ4" s="3" t="n">
+      <c r="BI4" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="AK4" s="3" t="n">
-        <v>2.725</v>
-      </c>
-      <c r="AL4" s="3" t="n">
-        <v>2.255</v>
-      </c>
-      <c r="AM4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN4" s="3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>4.315</v>
-      </c>
-      <c r="AP4" s="3" t="n">
-        <v>2.615</v>
-      </c>
-      <c r="AQ4" s="3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AR4" s="3" t="n">
-        <v>2.915</v>
-      </c>
-      <c r="AS4" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT4" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU4" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AV4" s="3" t="n">
-        <v>2.905</v>
-      </c>
-      <c r="AW4" s="3" t="n">
-        <v>4.295</v>
-      </c>
-      <c r="AX4" s="3" t="n">
-        <v>2.795</v>
-      </c>
-      <c r="AY4" s="3" t="n">
-        <v>2.715</v>
-      </c>
-      <c r="AZ4" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BA4" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB4" s="3" t="n">
-        <v>2.405</v>
-      </c>
-      <c r="BC4" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BD4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BE4" s="3" t="n">
-        <v>2.825</v>
-      </c>
-      <c r="BF4" s="3" t="n">
-        <v>2.525</v>
-      </c>
-      <c r="BG4" s="3" t="n">
+      <c r="BJ4" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BM4" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="BH4" s="3" t="n">
-        <v>2.835</v>
-      </c>
-      <c r="BI4" s="3" t="n">
-        <v>4.275</v>
-      </c>
-      <c r="BJ4" s="3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BK4" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="BL4" s="3" t="n">
-        <v>3.555</v>
-      </c>
-      <c r="BM4" s="3" t="n">
-        <v>3.78</v>
-      </c>
       <c r="BN4" s="3" t="n">
-        <v>4.36</v>
+        <v>2.995</v>
       </c>
       <c r="BO4" s="3" t="n">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="BP4" s="3" t="n">
-        <v>2.525</v>
+        <v>2.21</v>
       </c>
       <c r="BQ4" s="3" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="BR4" s="3" t="n">
-        <v>1.495</v>
+        <v>-1.025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AI5" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ5" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AM5" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN5" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>4.315</v>
+      </c>
+      <c r="AP5" s="3" t="n">
         <v>2.615</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>2.975</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>1.935</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>2.765</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>3.285</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>2.795</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>2.755</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>2.665</v>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AC5" s="3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD5" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE5" s="3" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="AF5" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG5" s="3" t="n">
-        <v>1.315</v>
-      </c>
-      <c r="AH5" s="3" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="AI5" s="3" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="AJ5" s="3" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AK5" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AL5" s="3" t="n">
-        <v>2.005</v>
-      </c>
-      <c r="AM5" s="3" t="n">
-        <v>2.535</v>
-      </c>
-      <c r="AN5" s="3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>4.415</v>
-      </c>
-      <c r="AP5" s="3" t="n">
-        <v>2.66</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>2.56</v>
       </c>
       <c r="AR5" s="3" t="n">
-        <v>2.9</v>
+        <v>2.915</v>
       </c>
       <c r="AS5" s="3" t="n">
         <v>2.42</v>
       </c>
       <c r="AT5" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AV5" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AW5" s="3" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="AX5" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AY5" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BA5" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BB5" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="BC5" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BD5" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE5" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BF5" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BG5" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH5" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="BI5" s="3" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="BJ5" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BK5" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="BL5" s="3" t="n">
+        <v>3.555</v>
+      </c>
+      <c r="BM5" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BN5" s="3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BO5" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BP5" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BQ5" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BR5" s="3" t="n">
+        <v>1.495</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL6" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="AM6" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AP6" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR6" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS6" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT6" s="3" t="n">
         <v>2.495</v>
       </c>
-      <c r="AU5" s="3" t="n">
+      <c r="AU6" s="3" t="n">
         <v>2.775</v>
       </c>
-      <c r="AV5" s="3" t="n">
+      <c r="AV6" s="3" t="n">
         <v>2.975</v>
       </c>
-      <c r="AW5" s="3" t="n">
+      <c r="AW6" s="3" t="n">
         <v>4.32</v>
       </c>
-      <c r="AX5" s="3" t="n">
+      <c r="AX6" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="AY5" s="3" t="n">
+      <c r="AY6" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="AZ5" s="3" t="n">
+      <c r="AZ6" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="BA5" s="3" t="n">
+      <c r="BA6" s="3" t="n">
         <v>2.515</v>
       </c>
-      <c r="BB5" s="3" t="n">
+      <c r="BB6" s="3" t="n">
         <v>2.375</v>
       </c>
-      <c r="BC5" s="3" t="n">
+      <c r="BC6" s="3" t="n">
         <v>2.965</v>
       </c>
-      <c r="BD5" s="3" t="n">
+      <c r="BD6" s="3" t="n">
         <v>2.785</v>
       </c>
-      <c r="BE5" s="3" t="n">
+      <c r="BE6" s="3" t="n">
         <v>2.82</v>
       </c>
-      <c r="BF5" s="3" t="n">
+      <c r="BF6" s="3" t="n">
         <v>2.51</v>
       </c>
-      <c r="BG5" s="3" t="n">
+      <c r="BG6" s="3" t="n">
         <v>2.83</v>
       </c>
-      <c r="BH5" s="3" t="n">
+      <c r="BH6" s="3" t="n">
         <v>2.84</v>
       </c>
-      <c r="BI5" s="3" t="n">
+      <c r="BI6" s="3" t="n">
         <v>4.38</v>
       </c>
-      <c r="BJ5" s="3" t="n">
+      <c r="BJ6" s="3" t="n">
         <v>4.44</v>
       </c>
-      <c r="BK5" s="3" t="n">
+      <c r="BK6" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="BL5" s="3" t="n">
+      <c r="BL6" s="3" t="n">
         <v>3.76</v>
       </c>
-      <c r="BM5" s="3" t="n">
+      <c r="BM6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="BN5" s="3" t="n">
+      <c r="BN6" s="3" t="n">
         <v>4.45</v>
       </c>
-      <c r="BO5" s="3" t="n">
+      <c r="BO6" s="3" t="n">
         <v>2.46</v>
       </c>
-      <c r="BP5" s="3" t="n">
+      <c r="BP6" s="3" t="n">
         <v>2.515</v>
       </c>
-      <c r="BQ5" s="3" t="n">
+      <c r="BQ6" s="3" t="n">
         <v>2.825</v>
       </c>
-      <c r="BR5" s="3" t="n">
+      <c r="BR6" s="3" t="n">
         <v>1.805</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR5"/>
+  <autoFilter ref="A1:BR6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR6"/>
+  <dimension ref="A1:BR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -878,1075 +878,433 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2.86</v>
+        <v>2.825</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2.27</v>
+        <v>2.305</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.295</v>
+        <v>2.01</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2.715</v>
+        <v>2.625</v>
       </c>
       <c r="F2" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>1.655</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>-1.695</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
         <v>2.84</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>2.605</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>-2.455</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>2.585</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>3.085</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>2.515</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>1.425</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>1.805</v>
-      </c>
-      <c r="X2" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="Z2" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA2" s="3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AC2" s="3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD2" s="3" t="n">
-        <v>1.345</v>
-      </c>
-      <c r="AE2" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF2" s="3" t="n">
-        <v>1.635</v>
-      </c>
-      <c r="AG2" s="3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH2" s="3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AI2" s="3" t="n">
-        <v>-2.455</v>
-      </c>
-      <c r="AJ2" s="3" t="n">
-        <v>2.885</v>
-      </c>
       <c r="AK2" s="3" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>1.375</v>
+        <v>1.61</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>2.425</v>
+        <v>2.65</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>3.33</v>
+        <v>3.005</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>2.395</v>
+        <v>2.375</v>
       </c>
       <c r="AQ2" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AR2" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AS2" s="3" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="AT2" s="3" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="AU2" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW2" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AX2" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AY2" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AZ2" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BA2" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB2" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="BC2" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="BD2" s="3" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="BE2" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="BF2" s="3" t="n">
         <v>1.99</v>
       </c>
-      <c r="AR2" s="3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AS2" s="3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT2" s="3" t="n">
-        <v>1.925</v>
-      </c>
-      <c r="AU2" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AV2" s="3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AW2" s="3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AX2" s="3" t="n">
-        <v>2.755</v>
-      </c>
-      <c r="AY2" s="3" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="AZ2" s="3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="BA2" s="3" t="n">
-        <v>1.905</v>
-      </c>
-      <c r="BB2" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BC2" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD2" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BE2" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BF2" s="3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BG2" s="3" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BH2" s="3" t="n">
-        <v>2.815</v>
+        <v>2.745</v>
       </c>
       <c r="BI2" s="3" t="n">
-        <v>3.285</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" s="3" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="BK2" s="3" t="n">
         <v>1.875</v>
       </c>
       <c r="BL2" s="3" t="n">
-        <v>3.115</v>
+        <v>2.9</v>
       </c>
       <c r="BM2" s="3" t="n">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="BN2" s="3" t="n">
-        <v>3.37</v>
+        <v>2.96</v>
       </c>
       <c r="BO2" s="3" t="n">
         <v>1.905</v>
       </c>
       <c r="BP2" s="3" t="n">
-        <v>1.965</v>
+        <v>1.945</v>
       </c>
       <c r="BQ2" s="3" t="n">
-        <v>2.69</v>
+        <v>2.565</v>
       </c>
       <c r="BR2" s="3" t="n">
-        <v>-2.375</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2.825</v>
+        <v>2.73</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.305</v>
+        <v>2.33</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.01</v>
+        <v>2.495</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2.625</v>
+        <v>2.68</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.475</v>
+        <v>1.57</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.505</v>
+        <v>1.61</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2.635</v>
+        <v>2.68</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.62</v>
+        <v>2.665</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.04</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.865</v>
+        <v>1.98</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>2.655</v>
+        <v>2.74</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>3.01</v>
+        <v>3.015</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>2.66</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>2.965</v>
+        <v>2.945</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>2.565</v>
+        <v>2.695</v>
       </c>
       <c r="S3" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>1.675</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AA3" s="3" t="n">
         <v>2.59</v>
       </c>
-      <c r="T3" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>2.565</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="AA3" s="3" t="n">
+      <c r="AB3" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="AE3" s="3" t="n">
         <v>2.51</v>
       </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.535</v>
-      </c>
-      <c r="AC3" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD3" s="3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE3" s="3" t="n">
-        <v>2.425</v>
-      </c>
       <c r="AF3" s="3" t="n">
-        <v>1.655</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>1.425</v>
+        <v>1.43</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>2.32</v>
+        <v>2.365</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>-1.695</v>
+        <v>-1.03</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>2.62</v>
+        <v>2.645</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>1.44</v>
+        <v>1.545</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AN3" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AQ3" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR3" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AS3" s="3" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU3" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AV3" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW3" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AX3" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AY3" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="AO3" s="3" t="n">
-        <v>3.005</v>
-      </c>
-      <c r="AP3" s="3" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="AQ3" s="3" t="n">
+      <c r="BA3" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BB3" s="3" t="n">
         <v>1.96</v>
       </c>
-      <c r="AR3" s="3" t="n">
-        <v>2.745</v>
-      </c>
-      <c r="AS3" s="3" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="AT3" s="3" t="n">
-        <v>1.915</v>
-      </c>
-      <c r="AU3" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AV3" s="3" t="n">
+      <c r="BC3" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BD3" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE3" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="BF3" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG3" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BH3" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="AW3" s="3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AX3" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AY3" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AZ3" s="3" t="n">
-        <v>2.645</v>
-      </c>
-      <c r="BA3" s="3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BB3" s="3" t="n">
-        <v>1.865</v>
-      </c>
-      <c r="BC3" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="BD3" s="3" t="n">
-        <v>1.985</v>
-      </c>
-      <c r="BE3" s="3" t="n">
-        <v>2.685</v>
-      </c>
-      <c r="BF3" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BG3" s="3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH3" s="3" t="n">
-        <v>2.745</v>
-      </c>
       <c r="BI3" s="3" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BJ3" s="3" t="n">
-        <v>2.95</v>
+        <v>2.945</v>
       </c>
       <c r="BK3" s="3" t="n">
-        <v>1.875</v>
+        <v>2.1</v>
       </c>
       <c r="BL3" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="BM3" s="3" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="BN3" s="3" t="n">
-        <v>2.96</v>
+        <v>2.995</v>
       </c>
       <c r="BO3" s="3" t="n">
-        <v>1.905</v>
+        <v>2.09</v>
       </c>
       <c r="BP3" s="3" t="n">
-        <v>1.945</v>
+        <v>2.21</v>
       </c>
       <c r="BQ3" s="3" t="n">
-        <v>2.565</v>
+        <v>2.66</v>
       </c>
       <c r="BR3" s="3" t="n">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>2.665</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>3.015</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>2.945</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>2.695</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2.685</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1.675</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>2.615</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>2.685</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC4" s="3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD4" s="3" t="n">
-        <v>1.355</v>
-      </c>
-      <c r="AE4" s="3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AF4" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG4" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH4" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AI4" s="3" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="AJ4" s="3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AK4" s="3" t="n">
-        <v>2.645</v>
-      </c>
-      <c r="AL4" s="3" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="AM4" s="3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AN4" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>2.975</v>
-      </c>
-      <c r="AP4" s="3" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="AQ4" s="3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AR4" s="3" t="n">
-        <v>2.775</v>
-      </c>
-      <c r="AS4" s="3" t="n">
-        <v>2.025</v>
-      </c>
-      <c r="AT4" s="3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU4" s="3" t="n">
-        <v>2.605</v>
-      </c>
-      <c r="AV4" s="3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW4" s="3" t="n">
-        <v>2.945</v>
-      </c>
-      <c r="AX4" s="3" t="n">
-        <v>2.755</v>
-      </c>
-      <c r="AY4" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AZ4" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BA4" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BB4" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BC4" s="3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BD4" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BE4" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="BF4" s="3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BG4" s="3" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BH4" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI4" s="3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BJ4" s="3" t="n">
-        <v>2.945</v>
-      </c>
-      <c r="BK4" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BL4" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BM4" s="3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BN4" s="3" t="n">
-        <v>2.995</v>
-      </c>
-      <c r="BO4" s="3" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BP4" s="3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BQ4" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BR4" s="3" t="n">
         <v>-1.025</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>2.165</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>3.215</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>2.745</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>2.665</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>2.715</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC5" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AD5" s="3" t="n">
-        <v>1.245</v>
-      </c>
-      <c r="AE5" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF5" s="3" t="n">
-        <v>2.075</v>
-      </c>
-      <c r="AG5" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH5" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AI5" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AJ5" s="3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AK5" s="3" t="n">
-        <v>2.725</v>
-      </c>
-      <c r="AL5" s="3" t="n">
-        <v>2.255</v>
-      </c>
-      <c r="AM5" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AN5" s="3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>4.315</v>
-      </c>
-      <c r="AP5" s="3" t="n">
-        <v>2.615</v>
-      </c>
-      <c r="AQ5" s="3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AR5" s="3" t="n">
-        <v>2.915</v>
-      </c>
-      <c r="AS5" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT5" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU5" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AV5" s="3" t="n">
-        <v>2.905</v>
-      </c>
-      <c r="AW5" s="3" t="n">
-        <v>4.295</v>
-      </c>
-      <c r="AX5" s="3" t="n">
-        <v>2.795</v>
-      </c>
-      <c r="AY5" s="3" t="n">
-        <v>2.715</v>
-      </c>
-      <c r="AZ5" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BA5" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB5" s="3" t="n">
-        <v>2.405</v>
-      </c>
-      <c r="BC5" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BD5" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BE5" s="3" t="n">
-        <v>2.825</v>
-      </c>
-      <c r="BF5" s="3" t="n">
-        <v>2.525</v>
-      </c>
-      <c r="BG5" s="3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH5" s="3" t="n">
-        <v>2.835</v>
-      </c>
-      <c r="BI5" s="3" t="n">
-        <v>4.275</v>
-      </c>
-      <c r="BJ5" s="3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BK5" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="BL5" s="3" t="n">
-        <v>3.555</v>
-      </c>
-      <c r="BM5" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BN5" s="3" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="BO5" s="3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BP5" s="3" t="n">
-        <v>2.525</v>
-      </c>
-      <c r="BQ5" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BR5" s="3" t="n">
-        <v>1.495</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>2.615</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>2.975</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>1.935</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>2.765</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>3.285</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>2.795</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>2.755</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>2.665</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE6" s="3" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="AF6" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG6" s="3" t="n">
-        <v>1.315</v>
-      </c>
-      <c r="AH6" s="3" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="AI6" s="3" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AL6" s="3" t="n">
-        <v>2.005</v>
-      </c>
-      <c r="AM6" s="3" t="n">
-        <v>2.535</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>4.415</v>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AQ6" s="3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AS6" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="AU6" s="3" t="n">
-        <v>2.775</v>
-      </c>
-      <c r="AV6" s="3" t="n">
-        <v>2.975</v>
-      </c>
-      <c r="AW6" s="3" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="AX6" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AY6" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AZ6" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BA6" s="3" t="n">
-        <v>2.515</v>
-      </c>
-      <c r="BB6" s="3" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="BC6" s="3" t="n">
-        <v>2.965</v>
-      </c>
-      <c r="BD6" s="3" t="n">
-        <v>2.785</v>
-      </c>
-      <c r="BE6" s="3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BF6" s="3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BG6" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BH6" s="3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI6" s="3" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BJ6" s="3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="BK6" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BL6" s="3" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="BM6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN6" s="3" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BO6" s="3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BP6" s="3" t="n">
-        <v>2.515</v>
-      </c>
-      <c r="BQ6" s="3" t="n">
-        <v>2.825</v>
-      </c>
-      <c r="BR6" s="3" t="n">
-        <v>1.805</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR6"/>
+  <autoFilter ref="A1:BR3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR3"/>
+  <dimension ref="A1:BR5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -878,433 +878,861 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2.825</v>
+        <v>3.035</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2.305</v>
+        <v>2.46</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.01</v>
+        <v>2.175</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2.625</v>
+        <v>2.8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.7</v>
+        <v>2.965</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.475</v>
+        <v>1.5</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1.505</v>
+        <v>1.5</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>2.635</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.62</v>
+        <v>2.575</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.865</v>
+        <v>2.06</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>2.655</v>
+        <v>2.73</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>2.6</v>
+        <v>2.535</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>3.01</v>
+        <v>3.555</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2.66</v>
+        <v>2.835</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>2.965</v>
+        <v>3.34</v>
       </c>
       <c r="R2" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB2" s="3" t="n">
         <v>2.565</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X2" s="3" t="n">
-        <v>2.565</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Z2" s="3" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="AA2" s="3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.535</v>
       </c>
       <c r="AC2" s="3" t="n">
         <v>1.49</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>2.425</v>
+        <v>2.655</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>1.655</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>1.425</v>
+        <v>1.495</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>-1.695</v>
+        <v>-1.8</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>2.84</v>
+        <v>3.03</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>2.62</v>
+        <v>2.605</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>1.61</v>
+        <v>1.415</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>2.65</v>
+        <v>2.505</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>3.005</v>
+        <v>3.41</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>2.375</v>
+        <v>2.545</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AR2" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS2" s="3" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="AT2" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AU2" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AW2" s="3" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AX2" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AY2" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AZ2" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="BA2" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BB2" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BC2" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="BD2" s="3" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="BE2" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF2" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG2" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="BH2" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BI2" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BJ2" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK2" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL2" s="3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BM2" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BN2" s="3" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="BO2" s="3" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="BP2" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BQ2" s="3" t="n">
         <v>2.745</v>
       </c>
-      <c r="AS2" s="3" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="AT2" s="3" t="n">
-        <v>1.915</v>
-      </c>
-      <c r="AU2" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AV2" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AW2" s="3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AX2" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AY2" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AZ2" s="3" t="n">
-        <v>2.645</v>
-      </c>
-      <c r="BA2" s="3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BB2" s="3" t="n">
-        <v>1.865</v>
-      </c>
-      <c r="BC2" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="BD2" s="3" t="n">
-        <v>1.985</v>
-      </c>
-      <c r="BE2" s="3" t="n">
-        <v>2.685</v>
-      </c>
-      <c r="BF2" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BG2" s="3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH2" s="3" t="n">
-        <v>2.745</v>
-      </c>
-      <c r="BI2" s="3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ2" s="3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BK2" s="3" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="BL2" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BM2" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BN2" s="3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BO2" s="3" t="n">
-        <v>1.905</v>
-      </c>
-      <c r="BP2" s="3" t="n">
-        <v>1.945</v>
-      </c>
-      <c r="BQ2" s="3" t="n">
-        <v>2.565</v>
-      </c>
       <c r="BR2" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-2.455</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P3" s="3" t="n">
         <v>2.73</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>2.495</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>2.665</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>3.015</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="Q3" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z3" s="3" t="n">
         <v>2.66</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>2.945</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>2.695</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>2.685</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>1.675</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>2.615</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>2.685</v>
-      </c>
       <c r="AA3" s="3" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>1.355</v>
+        <v>1.345</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>1.79</v>
+        <v>1.635</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>2.365</v>
+        <v>2.34</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>-1.03</v>
+        <v>-2.455</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>2.85</v>
+        <v>2.885</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>2.645</v>
+        <v>2.64</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>1.545</v>
+        <v>1.24</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1.72</v>
+        <v>1.375</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>2.72</v>
+        <v>2.425</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>2.975</v>
+        <v>3.33</v>
       </c>
       <c r="AP3" s="3" t="n">
         <v>2.395</v>
       </c>
       <c r="AQ3" s="3" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>2.775</v>
+        <v>2.87</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>2.025</v>
+        <v>1.86</v>
       </c>
       <c r="AT3" s="3" t="n">
-        <v>2.12</v>
+        <v>1.925</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>2.605</v>
+        <v>2.735</v>
       </c>
       <c r="AV3" s="3" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="AW3" s="3" t="n">
-        <v>2.945</v>
+        <v>3.32</v>
       </c>
       <c r="AX3" s="3" t="n">
         <v>2.755</v>
       </c>
       <c r="AY3" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BA3" s="3" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="BB3" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BC3" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD3" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE3" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BF3" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG3" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BH3" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="BI3" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="BJ3" s="3" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BK3" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BL3" s="3" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="BM3" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN3" s="3" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BO3" s="3" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="BP3" s="3" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="BQ3" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BR3" s="3" t="n">
+        <v>-2.375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="AZ3" s="3" t="n">
+      <c r="O4" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1.655</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>-1.695</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN4" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="BA3" s="3" t="n">
+      <c r="AO4" s="3" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>3.015</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>1.675</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AI5" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="AJ5" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="AM5" s="3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN5" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="AP5" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AQ5" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR5" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AS5" s="3" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="AT5" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AV5" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW5" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AX5" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AY5" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BA5" s="3" t="n">
         <v>2.15</v>
       </c>
-      <c r="BB3" s="3" t="n">
+      <c r="BB5" s="3" t="n">
         <v>1.96</v>
       </c>
-      <c r="BC3" s="3" t="n">
+      <c r="BC5" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="BD3" s="3" t="n">
+      <c r="BD5" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="BE3" s="3" t="n">
+      <c r="BE5" s="3" t="n">
         <v>2.735</v>
       </c>
-      <c r="BF3" s="3" t="n">
+      <c r="BF5" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="BG3" s="3" t="n">
+      <c r="BG5" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="BH3" s="3" t="n">
+      <c r="BH5" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="BI3" s="3" t="n">
+      <c r="BI5" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="BJ3" s="3" t="n">
+      <c r="BJ5" s="3" t="n">
         <v>2.945</v>
       </c>
-      <c r="BK3" s="3" t="n">
+      <c r="BK5" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="BL3" s="3" t="n">
+      <c r="BL5" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="BM3" s="3" t="n">
+      <c r="BM5" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="BN3" s="3" t="n">
+      <c r="BN5" s="3" t="n">
         <v>2.995</v>
       </c>
-      <c r="BO3" s="3" t="n">
+      <c r="BO5" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="BP3" s="3" t="n">
+      <c r="BP5" s="3" t="n">
         <v>2.21</v>
       </c>
-      <c r="BQ3" s="3" t="n">
+      <c r="BQ5" s="3" t="n">
         <v>2.66</v>
       </c>
-      <c r="BR3" s="3" t="n">
+      <c r="BR5" s="3" t="n">
         <v>-1.025</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR3"/>
+  <autoFilter ref="A1:BR5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1731,8 +1731,864 @@
         <v>-1.025</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-0.345</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AC6" s="3" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>-0.335</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="AL6" s="3" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="AM6" s="3" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>3.065</v>
+      </c>
+      <c r="AP6" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AR6" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AS6" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AT6" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="AU6" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AV6" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AW6" s="3" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="AX6" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AY6" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AZ6" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BA6" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="BB6" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BC6" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="BD6" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BE6" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BF6" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG6" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH6" s="3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI6" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BJ6" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK6" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="BL6" s="3" t="n">
+        <v>2.995</v>
+      </c>
+      <c r="BM6" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="BN6" s="3" t="n">
+        <v>3.095</v>
+      </c>
+      <c r="BO6" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BP6" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BQ6" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="BR6" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="AH7" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AI7" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AJ7" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK7" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AL7" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM7" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN7" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>3.065</v>
+      </c>
+      <c r="AP7" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AQ7" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AR7" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AS7" s="3" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="AT7" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU7" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AV7" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AW7" s="3" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AX7" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AY7" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AZ7" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="BA7" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="BB7" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BC7" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BD7" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BE7" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="BF7" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG7" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BH7" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI7" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BJ7" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK7" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL7" s="3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BM7" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN7" s="3" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="BO7" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BP7" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BQ7" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="BR7" s="3" t="n">
+        <v>-1.025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AC8" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="AH8" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AI8" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AL8" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM8" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>3.065</v>
+      </c>
+      <c r="AP8" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AQ8" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AR8" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AS8" s="3" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="AT8" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU8" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AV8" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AW8" s="3" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AX8" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AY8" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AZ8" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="BA8" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="BB8" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BC8" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BD8" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BE8" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="BF8" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG8" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BH8" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI8" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BJ8" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK8" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL8" s="3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BM8" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN8" s="3" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="BO8" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BP8" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BQ8" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="BR8" s="3" t="n">
+        <v>-1.025</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AC9" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="AH9" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AI9" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AJ9" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK9" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AL9" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM9" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN9" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>3.065</v>
+      </c>
+      <c r="AP9" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AQ9" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AR9" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AS9" s="3" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="AT9" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU9" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AV9" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AW9" s="3" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AX9" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AY9" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AZ9" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="BA9" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="BB9" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BC9" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BD9" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BE9" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="BF9" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG9" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BH9" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI9" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BJ9" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK9" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL9" s="3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BM9" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN9" s="3" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="BO9" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BP9" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BQ9" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="BR9" s="3" t="n">
+        <v>-1.025</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR5"/>
+  <autoFilter ref="A1:BR9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR9"/>
+  <dimension ref="A1:BR11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2587,8 +2587,436 @@
         <v>-1.025</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC10" s="3" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH10" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AL10" s="3" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AM10" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AP10" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AQ10" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AR10" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="AS10" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="AT10" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="AV10" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AW10" s="3" t="n">
+        <v>3.535</v>
+      </c>
+      <c r="AX10" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AY10" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AZ10" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BA10" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB10" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC10" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BD10" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE10" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BF10" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG10" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BH10" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI10" s="3" t="n">
+        <v>3.435</v>
+      </c>
+      <c r="BJ10" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="BK10" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL10" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BM10" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="BN10" s="3" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BO10" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BP10" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BQ10" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BR10" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB11" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC11" s="3" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AE11" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AF11" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG11" s="3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH11" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>-1.005</v>
+      </c>
+      <c r="AJ11" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AL11" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AM11" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN11" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AO11" s="3" t="n">
+        <v>3.595</v>
+      </c>
+      <c r="AP11" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AQ11" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="AR11" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AS11" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AT11" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AV11" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="AW11" s="3" t="n">
+        <v>3.555</v>
+      </c>
+      <c r="AX11" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AY11" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AZ11" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA11" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB11" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="BC11" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BD11" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BE11" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="BF11" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BG11" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BH11" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="BI11" s="3" t="n">
+        <v>3.505</v>
+      </c>
+      <c r="BJ11" s="3" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="BK11" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BL11" s="3" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BM11" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BN11" s="3" t="n">
+        <v>3.645</v>
+      </c>
+      <c r="BO11" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="BP11" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BQ11" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BR11" s="3" t="n">
+        <v>-1.025</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR9"/>
+  <autoFilter ref="A1:BR11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR11"/>
+  <dimension ref="A1:BR13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3015,8 +3015,436 @@
         <v>-1.025</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2.935</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>3.255</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>2.895</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA12" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AB12" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="AC12" s="3" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AF12" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG12" s="3" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AH12" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>-1.175</v>
+      </c>
+      <c r="AJ12" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM12" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN12" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO12" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AP12" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AQ12" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AR12" s="3" t="n">
+        <v>2.985</v>
+      </c>
+      <c r="AS12" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AT12" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV12" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AW12" s="3" t="n">
+        <v>3.915</v>
+      </c>
+      <c r="AX12" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="AY12" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AZ12" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="BA12" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="BB12" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC12" s="3" t="n">
+        <v>3.205</v>
+      </c>
+      <c r="BD12" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE12" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="BF12" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG12" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="BH12" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI12" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="BJ12" s="3" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BK12" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BL12" s="3" t="n">
+        <v>3.505</v>
+      </c>
+      <c r="BM12" s="3" t="n">
+        <v>3.765</v>
+      </c>
+      <c r="BN12" s="3" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BO12" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BP12" s="3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BQ12" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BR12" s="3" t="n">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>-0.955</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AC13" s="3" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="AE13" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="AG13" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH13" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AI13" s="3" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AJ13" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AL13" s="3" t="n">
+        <v>1.595</v>
+      </c>
+      <c r="AM13" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN13" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO13" s="3" t="n">
+        <v>3.865</v>
+      </c>
+      <c r="AP13" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AQ13" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AR13" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="AS13" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AT13" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AV13" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AW13" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX13" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AY13" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="AZ13" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BA13" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB13" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BC13" s="3" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="BD13" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="BE13" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BF13" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BG13" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="BH13" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="BI13" s="3" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="BJ13" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="BK13" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="BL13" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BM13" s="3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BN13" s="3" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="BO13" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="BP13" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BQ13" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="BR13" s="3" t="n">
+        <v>-0.955</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR11"/>
+  <autoFilter ref="A1:BR13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR13"/>
+  <dimension ref="A1:BR15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3443,8 +3443,436 @@
         <v>-0.955</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>-0.635</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AC14" s="3" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE14" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AF14" s="3" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="AG14" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH14" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AJ14" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AL14" s="3" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="AM14" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN14" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AO14" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AP14" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AQ14" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR14" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="AS14" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT14" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AU14" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV14" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW14" s="3" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="AX14" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AY14" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AZ14" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BA14" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="BB14" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="BC14" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BD14" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BE14" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BF14" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BG14" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BH14" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="BI14" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BJ14" s="3" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="BK14" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BL14" s="3" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="BM14" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BN14" s="3" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="BO14" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BP14" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BQ14" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BR14" s="3" t="n">
+        <v>-0.525</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AC15" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AE15" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AF15" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AG15" s="3" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="AH15" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ15" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AL15" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AM15" s="3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AN15" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="AO15" s="3" t="n">
+        <v>3.575</v>
+      </c>
+      <c r="AP15" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ15" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AR15" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AS15" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AV15" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="AW15" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AX15" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AY15" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AZ15" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BA15" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="BB15" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BC15" s="3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BD15" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="BE15" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BF15" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="BG15" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BH15" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BI15" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ15" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BK15" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL15" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BM15" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="BN15" s="3" t="n">
+        <v>3.595</v>
+      </c>
+      <c r="BO15" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BP15" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="BQ15" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="BR15" s="3" t="n">
+        <v>0.255</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR13"/>
+  <autoFilter ref="A1:BR15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR15"/>
+  <dimension ref="A1:BR17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3446,7 +3446,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -3660,219 +3660,647 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2.7</v>
+        <v>2.725</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2.585</v>
+        <v>2.46</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2.625</v>
+        <v>2.65</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2.22</v>
+        <v>1.61</v>
       </c>
       <c r="I15" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>-0.635</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>2.655</v>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>2.745</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>2.665</v>
-      </c>
       <c r="N15" s="3" t="n">
-        <v>2.71</v>
+        <v>2.675</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>3.84</v>
+        <v>3.905</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.61</v>
+        <v>2.605</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>3.055</v>
+        <v>3.08</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>2.735</v>
+        <v>2.7</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>2.755</v>
+        <v>2.925</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>2.645</v>
+        <v>2.655</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>2.475</v>
+        <v>1.71</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>2.045</v>
+        <v>2.28</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>2.64</v>
+        <v>2.595</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>2.62</v>
+        <v>2.605</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>2.665</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>2.565</v>
+        <v>2.47</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>2.29</v>
+        <v>1.645</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>1.375</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>2.615</v>
+        <v>2.515</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>2.225</v>
+        <v>1.725</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>1.465</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AJ15" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>2.59</v>
       </c>
-      <c r="AI15" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ15" s="3" t="n">
-        <v>2.795</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>2.61</v>
-      </c>
       <c r="AL15" s="3" t="n">
-        <v>2.8</v>
+        <v>1.605</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>3.27</v>
+        <v>1.84</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>3.565</v>
+        <v>2.79</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>3.575</v>
+        <v>3.67</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>2.6</v>
+        <v>2.535</v>
       </c>
       <c r="AQ15" s="3" t="n">
-        <v>2.295</v>
+        <v>2.38</v>
       </c>
       <c r="AR15" s="3" t="n">
-        <v>2.795</v>
+        <v>2.715</v>
       </c>
       <c r="AS15" s="3" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="AT15" s="3" t="n">
-        <v>2.21</v>
+        <v>2.415</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>2.595</v>
+        <v>2.63</v>
       </c>
       <c r="AV15" s="3" t="n">
-        <v>2.825</v>
+        <v>2.75</v>
       </c>
       <c r="AW15" s="3" t="n">
-        <v>3.53</v>
+        <v>3.615</v>
       </c>
       <c r="AX15" s="3" t="n">
-        <v>2.71</v>
+        <v>2.745</v>
       </c>
       <c r="AY15" s="3" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AZ15" s="3" t="n">
         <v>2.635</v>
       </c>
       <c r="BA15" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="BB15" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="BC15" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BD15" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BE15" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BF15" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BG15" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BH15" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="BI15" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BJ15" s="3" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="BK15" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BL15" s="3" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="BM15" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BN15" s="3" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="BO15" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BP15" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BQ15" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BR15" s="3" t="n">
+        <v>-0.525</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>-0.635</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AC16" s="3" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE16" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AF16" s="3" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="AG16" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH16" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AJ16" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="AM16" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN16" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AO16" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AP16" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AQ16" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR16" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="AS16" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT16" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV16" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW16" s="3" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="AX16" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AY16" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AZ16" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BA16" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="BB16" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="BC16" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BD16" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BE16" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BF16" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BG16" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BH16" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="BI16" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BJ16" s="3" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="BK16" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BL16" s="3" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="BM16" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BN16" s="3" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="BO16" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BP16" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BQ16" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BR16" s="3" t="n">
+        <v>-0.525</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB17" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AC17" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AE17" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AF17" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AG17" s="3" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="AH17" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ17" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AM17" s="3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AN17" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="AO17" s="3" t="n">
+        <v>3.575</v>
+      </c>
+      <c r="AP17" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ17" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AR17" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AS17" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AU17" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AV17" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="AW17" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AX17" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AY17" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AZ17" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BA17" s="3" t="n">
         <v>2.305</v>
       </c>
-      <c r="BB15" s="3" t="n">
+      <c r="BB17" s="3" t="n">
         <v>2.08</v>
       </c>
-      <c r="BC15" s="3" t="n">
+      <c r="BC17" s="3" t="n">
         <v>2.89</v>
       </c>
-      <c r="BD15" s="3" t="n">
+      <c r="BD17" s="3" t="n">
         <v>2.445</v>
       </c>
-      <c r="BE15" s="3" t="n">
+      <c r="BE17" s="3" t="n">
         <v>2.66</v>
       </c>
-      <c r="BF15" s="3" t="n">
+      <c r="BF17" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="BG15" s="3" t="n">
+      <c r="BG17" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="BH15" s="3" t="n">
+      <c r="BH17" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="BI15" s="3" t="n">
+      <c r="BI17" s="3" t="n">
         <v>3.55</v>
       </c>
-      <c r="BJ15" s="3" t="n">
+      <c r="BJ17" s="3" t="n">
         <v>3.55</v>
       </c>
-      <c r="BK15" s="3" t="n">
+      <c r="BK17" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="BL15" s="3" t="n">
+      <c r="BL17" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="BM15" s="3" t="n">
+      <c r="BM17" s="3" t="n">
         <v>3.275</v>
       </c>
-      <c r="BN15" s="3" t="n">
+      <c r="BN17" s="3" t="n">
         <v>3.595</v>
       </c>
-      <c r="BO15" s="3" t="n">
+      <c r="BO17" s="3" t="n">
         <v>2.195</v>
       </c>
-      <c r="BP15" s="3" t="n">
+      <c r="BP17" s="3" t="n">
         <v>2.265</v>
       </c>
-      <c r="BQ15" s="3" t="n">
+      <c r="BQ17" s="3" t="n">
         <v>2.595</v>
       </c>
-      <c r="BR15" s="3" t="n">
+      <c r="BR17" s="3" t="n">
         <v>0.255</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR15"/>
+  <autoFilter ref="A1:BR17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR17"/>
+  <dimension ref="A1:BR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4299,8 +4299,436 @@
         <v>0.255</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA18" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC18" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE18" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AF18" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG18" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH18" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AI18" s="3" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="AJ18" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>2.145</v>
+      </c>
+      <c r="AM18" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="AN18" s="3" t="n">
+        <v>3.575</v>
+      </c>
+      <c r="AO18" s="3" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="AP18" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AQ18" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AR18" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS18" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT18" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AU18" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AV18" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AW18" s="3" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="AX18" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AY18" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AZ18" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="BA18" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB18" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="BC18" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD18" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BE18" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BF18" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG18" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BH18" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="BI18" s="3" t="n">
+        <v>3.785</v>
+      </c>
+      <c r="BJ18" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BK18" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL18" s="3" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="BM18" s="3" t="n">
+        <v>3.635</v>
+      </c>
+      <c r="BN18" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BO18" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP18" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="BQ18" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="BR18" s="3" t="n">
+        <v>0.695</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>4.355</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>3.315</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AA19" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AB19" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC19" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD19" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AF19" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AG19" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AH19" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AI19" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ19" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AL19" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AM19" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="AN19" s="3" t="n">
+        <v>3.585</v>
+      </c>
+      <c r="AO19" s="3" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="AP19" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AQ19" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AR19" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AS19" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT19" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="AU19" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AV19" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AW19" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AX19" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AY19" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AZ19" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BA19" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB19" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BC19" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD19" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="BE19" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BF19" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BG19" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BH19" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BI19" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="BJ19" s="3" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="BK19" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="BL19" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BM19" s="3" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="BN19" s="3" t="n">
+        <v>3.945</v>
+      </c>
+      <c r="BO19" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BP19" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BQ19" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BR19" s="3" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR17"/>
+  <autoFilter ref="A1:BR19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR19"/>
+  <dimension ref="A1:BR23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4727,8 +4727,864 @@
         <v>1.66</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>4.205</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA20" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AB20" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC20" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="AD20" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE20" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF20" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG20" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH20" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI20" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ20" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AL20" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM20" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AN20" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="AO20" s="3" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="AP20" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AQ20" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AR20" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS20" s="3" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="AT20" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU20" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AV20" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AW20" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AX20" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AY20" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AZ20" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BA20" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB20" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BC20" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD20" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BE20" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="BF20" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="BG20" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BH20" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="BI20" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BJ20" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BK20" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL20" s="3" t="n">
+        <v>3.485</v>
+      </c>
+      <c r="BM20" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BN20" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BO20" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BP20" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BQ20" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BR20" s="3" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>4.205</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA21" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC21" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE21" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF21" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG21" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH21" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI21" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ21" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AL21" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM21" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AN21" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="AO21" s="3" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="AP21" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AQ21" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AR21" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS21" s="3" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="AT21" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU21" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AV21" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AW21" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AX21" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AY21" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AZ21" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BA21" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB21" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BC21" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD21" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BE21" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="BF21" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="BG21" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BH21" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="BI21" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BJ21" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BK21" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL21" s="3" t="n">
+        <v>3.485</v>
+      </c>
+      <c r="BM21" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BN21" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BO21" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BP21" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BQ21" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BR21" s="3" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>4.205</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA22" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AB22" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC22" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="AD22" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE22" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF22" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG22" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH22" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ22" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AL22" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM22" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AN22" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="AO22" s="3" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="AP22" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AQ22" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AR22" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS22" s="3" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="AT22" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU22" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AV22" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AW22" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AX22" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AY22" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AZ22" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BA22" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB22" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BC22" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD22" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BE22" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="BF22" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="BG22" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BH22" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="BI22" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BJ22" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BK22" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL22" s="3" t="n">
+        <v>3.485</v>
+      </c>
+      <c r="BM22" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BN22" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BO22" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BP22" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BQ22" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BR22" s="3" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>4.205</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC23" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="AD23" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE23" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF23" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG23" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH23" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ23" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM23" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="AN23" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="AO23" s="3" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="AP23" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AQ23" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AR23" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS23" s="3" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="AT23" s="3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU23" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AV23" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AW23" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AX23" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AY23" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AZ23" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BA23" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB23" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BC23" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD23" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BE23" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="BF23" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="BG23" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BH23" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="BI23" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BJ23" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BK23" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL23" s="3" t="n">
+        <v>3.485</v>
+      </c>
+      <c r="BM23" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BN23" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BO23" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BP23" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BQ23" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BR23" s="3" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR19"/>
+  <autoFilter ref="A1:BR23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR23"/>
+  <dimension ref="A1:BR25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5583,8 +5583,436 @@
         <v>1.85</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>4.435</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>3.155</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC24" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="AD24" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE24" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF24" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG24" s="3" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="AH24" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="AJ24" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AL24" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="AM24" s="3" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="AN24" s="3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AO24" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AP24" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AQ24" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AR24" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AS24" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT24" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU24" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV24" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AW24" s="3" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AX24" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AY24" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AZ24" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="BA24" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="BB24" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BC24" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BD24" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BE24" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BF24" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="BG24" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH24" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="BJ24" s="3" t="n">
+        <v>4.405</v>
+      </c>
+      <c r="BK24" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BL24" s="3" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="BM24" s="3" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BN24" s="3" t="n">
+        <v>4.505</v>
+      </c>
+      <c r="BO24" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="BP24" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BQ24" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BR24" s="3" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>2.155</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC25" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD25" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE25" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF25" s="3" t="n">
+        <v>2.095</v>
+      </c>
+      <c r="AG25" s="3" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="AH25" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ25" s="3" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AL25" s="3" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="AM25" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AN25" s="3" t="n">
+        <v>3.295</v>
+      </c>
+      <c r="AO25" s="3" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AP25" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AQ25" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AR25" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AS25" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT25" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AU25" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AV25" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AW25" s="3" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AX25" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AY25" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AZ25" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="BA25" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BB25" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BC25" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="BD25" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BE25" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF25" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="BG25" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BH25" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="BI25" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ25" s="3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BK25" s="3" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="BL25" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BM25" s="3" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="BN25" s="3" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="BO25" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="BP25" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BQ25" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BR25" s="3" t="n">
+        <v>1.415</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR23"/>
+  <autoFilter ref="A1:BR25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR25"/>
+  <dimension ref="A1:BR27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6011,8 +6011,436 @@
         <v>1.415</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC26" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AD26" s="3" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="AE26" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF26" s="3" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="AG26" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH26" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AI26" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ26" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AK26" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AL26" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AM26" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN26" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AO26" s="3" t="n">
+        <v>4.315</v>
+      </c>
+      <c r="AP26" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AQ26" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR26" s="3" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="AS26" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT26" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU26" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AV26" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="AW26" s="3" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="AX26" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AY26" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="AZ26" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BA26" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BB26" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="BC26" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BD26" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE26" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BF26" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BG26" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH26" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="BI26" s="3" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="BJ26" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BK26" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="BL26" s="3" t="n">
+        <v>3.555</v>
+      </c>
+      <c r="BM26" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BN26" s="3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BO26" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BP26" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BQ26" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BR26" s="3" t="n">
+        <v>1.495</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC27" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD27" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE27" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AF27" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG27" s="3" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="AH27" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="AJ27" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK27" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL27" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="AM27" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AN27" s="3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AO27" s="3" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AP27" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ27" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR27" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS27" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT27" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AU27" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AV27" s="3" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="AW27" s="3" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AX27" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AY27" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AZ27" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA27" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="BB27" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BC27" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="BD27" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="BE27" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BF27" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BG27" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH27" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI27" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BJ27" s="3" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BK27" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL27" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BM27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN27" s="3" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BO27" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP27" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="BQ27" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BR27" s="3" t="n">
+        <v>1.805</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR25"/>
+  <autoFilter ref="A1:BR27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR27"/>
+  <dimension ref="A1:BR30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6439,8 +6439,650 @@
         <v>1.805</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2.6608</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2.8612</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3.0276</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1.3722</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>2.7652</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>2.8518</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>1.4801</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>2.5998</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>2.8201</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>4.6675</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>2.7584</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>3.2829</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>2.7806</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>1.4478</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>2.8389</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>2.5829</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>2.7398</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>2.7313</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>2.7713</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>2.6682</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>2.6783</v>
+      </c>
+      <c r="AC28" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD28" s="3" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="AE28" s="3" t="n">
+        <v>2.5694</v>
+      </c>
+      <c r="AF28" s="3" t="n">
+        <v>1.7617</v>
+      </c>
+      <c r="AG28" s="3" t="n">
+        <v>1.2532</v>
+      </c>
+      <c r="AH28" s="3" t="n">
+        <v>2.6648</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>1.4488</v>
+      </c>
+      <c r="AJ28" s="3" t="n">
+        <v>3.0011</v>
+      </c>
+      <c r="AK28" s="3" t="n">
+        <v>2.7717</v>
+      </c>
+      <c r="AL28" s="3" t="n">
+        <v>1.5449</v>
+      </c>
+      <c r="AM28" s="3" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="AN28" s="3" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="AO28" s="3" t="n">
+        <v>4.513</v>
+      </c>
+      <c r="AP28" s="3" t="n">
+        <v>2.6357</v>
+      </c>
+      <c r="AQ28" s="3" t="n">
+        <v>2.6937</v>
+      </c>
+      <c r="AR28" s="3" t="n">
+        <v>2.9394</v>
+      </c>
+      <c r="AS28" s="3" t="n">
+        <v>2.6104</v>
+      </c>
+      <c r="AT28" s="3" t="n">
+        <v>2.7079</v>
+      </c>
+      <c r="AU28" s="3" t="n">
+        <v>2.7638</v>
+      </c>
+      <c r="AV28" s="3" t="n">
+        <v>2.9832</v>
+      </c>
+      <c r="AW28" s="3" t="n">
+        <v>4.3928</v>
+      </c>
+      <c r="AX28" s="3" t="n">
+        <v>2.9072</v>
+      </c>
+      <c r="AY28" s="3" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="AZ28" s="3" t="n">
+        <v>2.977</v>
+      </c>
+      <c r="BA28" s="3" t="n">
+        <v>2.6507</v>
+      </c>
+      <c r="BB28" s="3" t="n">
+        <v>2.5267</v>
+      </c>
+      <c r="BC28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD28" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE28" s="3" t="n">
+        <v>2.8675</v>
+      </c>
+      <c r="BF28" s="3" t="n">
+        <v>2.7079</v>
+      </c>
+      <c r="BG28" s="3" t="n">
+        <v>2.7353</v>
+      </c>
+      <c r="BH28" s="3" t="n">
+        <v>2.9536</v>
+      </c>
+      <c r="BI28" s="3" t="n">
+        <v>4.4519</v>
+      </c>
+      <c r="BJ28" s="3" t="n">
+        <v>4.5175</v>
+      </c>
+      <c r="BK28" s="3" t="n">
+        <v>2.6401</v>
+      </c>
+      <c r="BL28" s="3" t="n">
+        <v>4.5175</v>
+      </c>
+      <c r="BM28" s="3" t="n">
+        <v>4.5712</v>
+      </c>
+      <c r="BN28" s="3" t="n">
+        <v>4.5712</v>
+      </c>
+      <c r="BO28" s="3" t="n">
+        <v>2.6579</v>
+      </c>
+      <c r="BP28" s="3" t="n">
+        <v>2.7475</v>
+      </c>
+      <c r="BQ28" s="3" t="n">
+        <v>2.8448</v>
+      </c>
+      <c r="BR28" s="3" t="n">
+        <v>1.477</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2.6608</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2.8612</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>3.0276</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1.3722</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>2.7652</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>2.8518</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>1.4801</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>2.5998</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>2.8201</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>4.6675</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>2.7584</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>3.2829</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>2.7806</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>1.4478</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>2.8389</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>2.5829</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>2.7398</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>2.7313</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>2.7713</v>
+      </c>
+      <c r="AA29" s="3" t="n">
+        <v>2.6682</v>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>2.6783</v>
+      </c>
+      <c r="AC29" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD29" s="3" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="AE29" s="3" t="n">
+        <v>2.5694</v>
+      </c>
+      <c r="AF29" s="3" t="n">
+        <v>1.7617</v>
+      </c>
+      <c r="AG29" s="3" t="n">
+        <v>1.2532</v>
+      </c>
+      <c r="AH29" s="3" t="n">
+        <v>2.6648</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>1.4488</v>
+      </c>
+      <c r="AJ29" s="3" t="n">
+        <v>3.0011</v>
+      </c>
+      <c r="AK29" s="3" t="n">
+        <v>2.7717</v>
+      </c>
+      <c r="AL29" s="3" t="n">
+        <v>1.5449</v>
+      </c>
+      <c r="AM29" s="3" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="AN29" s="3" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="AO29" s="3" t="n">
+        <v>4.513</v>
+      </c>
+      <c r="AP29" s="3" t="n">
+        <v>2.6357</v>
+      </c>
+      <c r="AQ29" s="3" t="n">
+        <v>2.6937</v>
+      </c>
+      <c r="AR29" s="3" t="n">
+        <v>2.9394</v>
+      </c>
+      <c r="AS29" s="3" t="n">
+        <v>2.6104</v>
+      </c>
+      <c r="AT29" s="3" t="n">
+        <v>2.7079</v>
+      </c>
+      <c r="AU29" s="3" t="n">
+        <v>2.7638</v>
+      </c>
+      <c r="AV29" s="3" t="n">
+        <v>2.9832</v>
+      </c>
+      <c r="AW29" s="3" t="n">
+        <v>4.3928</v>
+      </c>
+      <c r="AX29" s="3" t="n">
+        <v>2.9072</v>
+      </c>
+      <c r="AY29" s="3" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="AZ29" s="3" t="n">
+        <v>2.977</v>
+      </c>
+      <c r="BA29" s="3" t="n">
+        <v>2.6507</v>
+      </c>
+      <c r="BB29" s="3" t="n">
+        <v>2.5267</v>
+      </c>
+      <c r="BC29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD29" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE29" s="3" t="n">
+        <v>2.8675</v>
+      </c>
+      <c r="BF29" s="3" t="n">
+        <v>2.7079</v>
+      </c>
+      <c r="BG29" s="3" t="n">
+        <v>2.7353</v>
+      </c>
+      <c r="BH29" s="3" t="n">
+        <v>2.9536</v>
+      </c>
+      <c r="BI29" s="3" t="n">
+        <v>4.4519</v>
+      </c>
+      <c r="BJ29" s="3" t="n">
+        <v>4.5175</v>
+      </c>
+      <c r="BK29" s="3" t="n">
+        <v>2.6401</v>
+      </c>
+      <c r="BL29" s="3" t="n">
+        <v>4.5175</v>
+      </c>
+      <c r="BM29" s="3" t="n">
+        <v>4.5712</v>
+      </c>
+      <c r="BN29" s="3" t="n">
+        <v>4.5712</v>
+      </c>
+      <c r="BO29" s="3" t="n">
+        <v>2.6579</v>
+      </c>
+      <c r="BP29" s="3" t="n">
+        <v>2.7475</v>
+      </c>
+      <c r="BQ29" s="3" t="n">
+        <v>2.8448</v>
+      </c>
+      <c r="BR29" s="3" t="n">
+        <v>1.477</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2.6608</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2.8612</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>3.0276</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1.3722</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>2.7652</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2.8518</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>1.4801</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>2.5998</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>2.8201</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>4.6675</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>2.7584</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>3.2829</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>2.7806</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>1.4478</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>2.8389</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>2.5829</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>2.7398</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>2.7313</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>2.7713</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>2.6682</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>2.6783</v>
+      </c>
+      <c r="AC30" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD30" s="3" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="AE30" s="3" t="n">
+        <v>2.5694</v>
+      </c>
+      <c r="AF30" s="3" t="n">
+        <v>1.7617</v>
+      </c>
+      <c r="AG30" s="3" t="n">
+        <v>1.2532</v>
+      </c>
+      <c r="AH30" s="3" t="n">
+        <v>2.6648</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>1.4488</v>
+      </c>
+      <c r="AJ30" s="3" t="n">
+        <v>3.0011</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>2.7717</v>
+      </c>
+      <c r="AL30" s="3" t="n">
+        <v>1.5449</v>
+      </c>
+      <c r="AM30" s="3" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="AN30" s="3" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="AO30" s="3" t="n">
+        <v>4.513</v>
+      </c>
+      <c r="AP30" s="3" t="n">
+        <v>2.6357</v>
+      </c>
+      <c r="AQ30" s="3" t="n">
+        <v>2.6937</v>
+      </c>
+      <c r="AR30" s="3" t="n">
+        <v>2.9394</v>
+      </c>
+      <c r="AS30" s="3" t="n">
+        <v>2.6104</v>
+      </c>
+      <c r="AT30" s="3" t="n">
+        <v>2.7079</v>
+      </c>
+      <c r="AU30" s="3" t="n">
+        <v>2.7638</v>
+      </c>
+      <c r="AV30" s="3" t="n">
+        <v>2.9832</v>
+      </c>
+      <c r="AW30" s="3" t="n">
+        <v>4.3928</v>
+      </c>
+      <c r="AX30" s="3" t="n">
+        <v>2.9072</v>
+      </c>
+      <c r="AY30" s="3" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="AZ30" s="3" t="n">
+        <v>2.977</v>
+      </c>
+      <c r="BA30" s="3" t="n">
+        <v>2.6507</v>
+      </c>
+      <c r="BB30" s="3" t="n">
+        <v>2.5267</v>
+      </c>
+      <c r="BC30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD30" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE30" s="3" t="n">
+        <v>2.8675</v>
+      </c>
+      <c r="BF30" s="3" t="n">
+        <v>2.7079</v>
+      </c>
+      <c r="BG30" s="3" t="n">
+        <v>2.7353</v>
+      </c>
+      <c r="BH30" s="3" t="n">
+        <v>2.9536</v>
+      </c>
+      <c r="BI30" s="3" t="n">
+        <v>4.4519</v>
+      </c>
+      <c r="BJ30" s="3" t="n">
+        <v>4.5175</v>
+      </c>
+      <c r="BK30" s="3" t="n">
+        <v>2.6401</v>
+      </c>
+      <c r="BL30" s="3" t="n">
+        <v>4.5175</v>
+      </c>
+      <c r="BM30" s="3" t="n">
+        <v>4.5712</v>
+      </c>
+      <c r="BN30" s="3" t="n">
+        <v>4.5712</v>
+      </c>
+      <c r="BO30" s="3" t="n">
+        <v>2.6579</v>
+      </c>
+      <c r="BP30" s="3" t="n">
+        <v>2.7475</v>
+      </c>
+      <c r="BQ30" s="3" t="n">
+        <v>2.8448</v>
+      </c>
+      <c r="BR30" s="3" t="n">
+        <v>1.477</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR27"/>
+  <autoFilter ref="A1:BR30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR30"/>
+  <dimension ref="A1:BR31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6449,208 +6449,208 @@
         <v>2.825</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2.6608</v>
+        <v>2.665</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.8612</v>
+        <v>2.86</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>3.0276</v>
+        <v>3.025</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.3722</v>
+        <v>1.37</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.3685</v>
+        <v>1.365</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.7652</v>
+        <v>2.765</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.8518</v>
+        <v>2.85</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1.4801</v>
+        <v>1.465</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2.5998</v>
+        <v>2.6</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>2.8201</v>
+        <v>2.87</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2.85</v>
+        <v>2.845</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>4.6675</v>
+        <v>4.68</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>2.7584</v>
+        <v>2.76</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>3.2829</v>
+        <v>3.285</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2.81</v>
+        <v>2.805</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.85</v>
+        <v>2.865</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>2.7806</v>
+        <v>2.785</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.4478</v>
+        <v>1.565</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>2.8389</v>
+        <v>2.84</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>2.5829</v>
+        <v>2.585</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>2.7398</v>
+        <v>2.74</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>2.7313</v>
+        <v>2.73</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2.7713</v>
+        <v>2.785</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>2.6682</v>
+        <v>2.67</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>2.6783</v>
+        <v>2.68</v>
       </c>
       <c r="AC28" s="3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>1.617</v>
+        <v>1.205</v>
       </c>
       <c r="AE28" s="3" t="n">
-        <v>2.5694</v>
+        <v>2.565</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>1.7617</v>
+        <v>1.76</v>
       </c>
       <c r="AG28" s="3" t="n">
-        <v>1.2532</v>
+        <v>1.255</v>
       </c>
       <c r="AH28" s="3" t="n">
-        <v>2.6648</v>
+        <v>2.665</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>1.4488</v>
+        <v>1.47</v>
       </c>
       <c r="AJ28" s="3" t="n">
-        <v>3.0011</v>
+        <v>3</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>2.7717</v>
+        <v>2.77</v>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>1.5449</v>
+        <v>1.545</v>
       </c>
       <c r="AM28" s="3" t="n">
-        <v>1.8094</v>
+        <v>1.81</v>
       </c>
       <c r="AN28" s="3" t="n">
-        <v>2.768</v>
+        <v>2.77</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>4.513</v>
+        <v>4.515</v>
       </c>
       <c r="AP28" s="3" t="n">
-        <v>2.6357</v>
+        <v>2.635</v>
       </c>
       <c r="AQ28" s="3" t="n">
-        <v>2.6937</v>
+        <v>2.695</v>
       </c>
       <c r="AR28" s="3" t="n">
-        <v>2.9394</v>
+        <v>2.94</v>
       </c>
       <c r="AS28" s="3" t="n">
-        <v>2.6104</v>
+        <v>2.61</v>
       </c>
       <c r="AT28" s="3" t="n">
-        <v>2.7079</v>
+        <v>2.71</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>2.7638</v>
+        <v>2.765</v>
       </c>
       <c r="AV28" s="3" t="n">
-        <v>2.9832</v>
+        <v>2.985</v>
       </c>
       <c r="AW28" s="3" t="n">
-        <v>4.3928</v>
+        <v>4.395</v>
       </c>
       <c r="AX28" s="3" t="n">
-        <v>2.9072</v>
+        <v>2.9</v>
       </c>
       <c r="AY28" s="3" t="n">
-        <v>2.723</v>
+        <v>2.725</v>
       </c>
       <c r="AZ28" s="3" t="n">
-        <v>2.977</v>
+        <v>2.835</v>
       </c>
       <c r="BA28" s="3" t="n">
-        <v>2.6507</v>
+        <v>2.65</v>
       </c>
       <c r="BB28" s="3" t="n">
-        <v>2.5267</v>
+        <v>2.53</v>
       </c>
       <c r="BC28" s="3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BD28" s="3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BE28" s="3" t="n">
-        <v>2.8675</v>
+        <v>2.87</v>
       </c>
       <c r="BF28" s="3" t="n">
-        <v>2.7079</v>
+        <v>2.705</v>
       </c>
       <c r="BG28" s="3" t="n">
-        <v>2.7353</v>
+        <v>2.69</v>
       </c>
       <c r="BH28" s="3" t="n">
-        <v>2.9536</v>
+        <v>2.95</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>4.4519</v>
+        <v>4.46</v>
       </c>
       <c r="BJ28" s="3" t="n">
-        <v>4.5175</v>
+        <v>4.515</v>
       </c>
       <c r="BK28" s="3" t="n">
-        <v>2.6401</v>
+        <v>2.64</v>
       </c>
       <c r="BL28" s="3" t="n">
-        <v>4.5175</v>
+        <v>3.945</v>
       </c>
       <c r="BM28" s="3" t="n">
-        <v>4.5712</v>
+        <v>3.575</v>
       </c>
       <c r="BN28" s="3" t="n">
-        <v>4.5712</v>
+        <v>4.575</v>
       </c>
       <c r="BO28" s="3" t="n">
-        <v>2.6579</v>
+        <v>2.675</v>
       </c>
       <c r="BP28" s="3" t="n">
-        <v>2.7475</v>
+        <v>2.75</v>
       </c>
       <c r="BQ28" s="3" t="n">
-        <v>2.8448</v>
+        <v>2.845</v>
       </c>
       <c r="BR28" s="3" t="n">
-        <v>1.477</v>
+        <v>1.505</v>
       </c>
     </row>
     <row r="29">
@@ -6663,208 +6663,208 @@
         <v>2.825</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.6608</v>
+        <v>2.665</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.8612</v>
+        <v>2.86</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.0276</v>
+        <v>3.025</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.3722</v>
+        <v>1.37</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.3685</v>
+        <v>1.365</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.7652</v>
+        <v>2.765</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.8518</v>
+        <v>2.85</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.4801</v>
+        <v>1.465</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.5998</v>
+        <v>2.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.8201</v>
+        <v>2.87</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.85</v>
+        <v>2.845</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.6675</v>
+        <v>4.68</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.7584</v>
+        <v>2.76</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.2829</v>
+        <v>3.285</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.81</v>
+        <v>2.805</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>2.85</v>
+        <v>2.865</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>2.7806</v>
+        <v>2.785</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>1.4478</v>
+        <v>1.565</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>2.8389</v>
+        <v>2.84</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>2.5829</v>
+        <v>2.585</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>2.7398</v>
+        <v>2.74</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.7313</v>
+        <v>2.73</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>2.7713</v>
+        <v>2.785</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>2.6682</v>
+        <v>2.67</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>2.6783</v>
+        <v>2.68</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>1.617</v>
+        <v>1.205</v>
       </c>
       <c r="AE29" s="3" t="n">
-        <v>2.5694</v>
+        <v>2.565</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>1.7617</v>
+        <v>1.76</v>
       </c>
       <c r="AG29" s="3" t="n">
-        <v>1.2532</v>
+        <v>1.255</v>
       </c>
       <c r="AH29" s="3" t="n">
-        <v>2.6648</v>
+        <v>2.665</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>1.4488</v>
+        <v>1.47</v>
       </c>
       <c r="AJ29" s="3" t="n">
-        <v>3.0011</v>
+        <v>3</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>2.7717</v>
+        <v>2.77</v>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>1.5449</v>
+        <v>1.545</v>
       </c>
       <c r="AM29" s="3" t="n">
-        <v>1.8094</v>
+        <v>1.81</v>
       </c>
       <c r="AN29" s="3" t="n">
-        <v>2.768</v>
+        <v>2.77</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>4.513</v>
+        <v>4.515</v>
       </c>
       <c r="AP29" s="3" t="n">
-        <v>2.6357</v>
+        <v>2.635</v>
       </c>
       <c r="AQ29" s="3" t="n">
-        <v>2.6937</v>
+        <v>2.695</v>
       </c>
       <c r="AR29" s="3" t="n">
-        <v>2.9394</v>
+        <v>2.94</v>
       </c>
       <c r="AS29" s="3" t="n">
-        <v>2.6104</v>
+        <v>2.61</v>
       </c>
       <c r="AT29" s="3" t="n">
-        <v>2.7079</v>
+        <v>2.71</v>
       </c>
       <c r="AU29" s="3" t="n">
-        <v>2.7638</v>
+        <v>2.765</v>
       </c>
       <c r="AV29" s="3" t="n">
-        <v>2.9832</v>
+        <v>2.985</v>
       </c>
       <c r="AW29" s="3" t="n">
-        <v>4.3928</v>
+        <v>4.395</v>
       </c>
       <c r="AX29" s="3" t="n">
-        <v>2.9072</v>
+        <v>2.9</v>
       </c>
       <c r="AY29" s="3" t="n">
-        <v>2.723</v>
+        <v>2.725</v>
       </c>
       <c r="AZ29" s="3" t="n">
-        <v>2.977</v>
+        <v>2.835</v>
       </c>
       <c r="BA29" s="3" t="n">
-        <v>2.6507</v>
+        <v>2.65</v>
       </c>
       <c r="BB29" s="3" t="n">
-        <v>2.5267</v>
+        <v>2.53</v>
       </c>
       <c r="BC29" s="3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BD29" s="3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BE29" s="3" t="n">
-        <v>2.8675</v>
+        <v>2.87</v>
       </c>
       <c r="BF29" s="3" t="n">
-        <v>2.7079</v>
+        <v>2.705</v>
       </c>
       <c r="BG29" s="3" t="n">
-        <v>2.7353</v>
+        <v>2.69</v>
       </c>
       <c r="BH29" s="3" t="n">
-        <v>2.9536</v>
+        <v>2.95</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>4.4519</v>
+        <v>4.46</v>
       </c>
       <c r="BJ29" s="3" t="n">
-        <v>4.5175</v>
+        <v>4.515</v>
       </c>
       <c r="BK29" s="3" t="n">
-        <v>2.6401</v>
+        <v>2.64</v>
       </c>
       <c r="BL29" s="3" t="n">
-        <v>4.5175</v>
+        <v>3.945</v>
       </c>
       <c r="BM29" s="3" t="n">
-        <v>4.5712</v>
+        <v>3.575</v>
       </c>
       <c r="BN29" s="3" t="n">
-        <v>4.5712</v>
+        <v>4.575</v>
       </c>
       <c r="BO29" s="3" t="n">
-        <v>2.6579</v>
+        <v>2.675</v>
       </c>
       <c r="BP29" s="3" t="n">
-        <v>2.7475</v>
+        <v>2.75</v>
       </c>
       <c r="BQ29" s="3" t="n">
-        <v>2.8448</v>
+        <v>2.845</v>
       </c>
       <c r="BR29" s="3" t="n">
-        <v>1.477</v>
+        <v>1.505</v>
       </c>
     </row>
     <row r="30">
@@ -6877,212 +6877,426 @@
         <v>2.825</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.6608</v>
+        <v>2.665</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC30" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD30" s="3" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="AE30" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AF30" s="3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG30" s="3" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="AH30" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AL30" s="3" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="AM30" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN30" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO30" s="3" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="AP30" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AQ30" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="AR30" s="3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS30" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AT30" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU30" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="AV30" s="3" t="n">
+        <v>2.985</v>
+      </c>
+      <c r="AW30" s="3" t="n">
+        <v>4.395</v>
+      </c>
+      <c r="AX30" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AY30" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="AZ30" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="BA30" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB30" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BC30" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD30" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BE30" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BF30" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="BG30" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BH30" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI30" s="3" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="BJ30" s="3" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="BK30" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BL30" s="3" t="n">
+        <v>3.945</v>
+      </c>
+      <c r="BM30" s="3" t="n">
+        <v>3.575</v>
+      </c>
+      <c r="BN30" s="3" t="n">
+        <v>4.575</v>
+      </c>
+      <c r="BO30" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="BP30" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BQ30" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="BR30" s="3" t="n">
+        <v>1.505</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2.9877</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2.9245</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>3.0141</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>1.1806</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>1.1258</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>2.8442</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>2.8861</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>2.8671</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>2.8526</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>4.8622</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>2.7449</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>3.3506</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>2.9811</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>3.2385</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>2.7587</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>1.0976</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>2.8274</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>2.8824</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>2.6834</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>2.749</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>2.7859</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>2.7981</v>
+      </c>
+      <c r="AB31" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>2.8612</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>3.0276</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1.3722</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>1.3685</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>2.7652</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>2.8518</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>1.4801</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>2.5998</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>2.8201</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>4.6675</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>2.7584</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>3.2829</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>2.7806</v>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>1.4478</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>2.8389</v>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v>2.5829</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>2.7398</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>2.7313</v>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v>2.7713</v>
-      </c>
-      <c r="AA30" s="3" t="n">
-        <v>2.6682</v>
-      </c>
-      <c r="AB30" s="3" t="n">
-        <v>2.6783</v>
-      </c>
-      <c r="AC30" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD30" s="3" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="AE30" s="3" t="n">
-        <v>2.5694</v>
-      </c>
-      <c r="AF30" s="3" t="n">
-        <v>1.7617</v>
-      </c>
-      <c r="AG30" s="3" t="n">
-        <v>1.2532</v>
-      </c>
-      <c r="AH30" s="3" t="n">
-        <v>2.6648</v>
-      </c>
-      <c r="AI30" s="3" t="n">
-        <v>1.4488</v>
-      </c>
-      <c r="AJ30" s="3" t="n">
-        <v>3.0011</v>
-      </c>
-      <c r="AK30" s="3" t="n">
-        <v>2.7717</v>
-      </c>
-      <c r="AL30" s="3" t="n">
-        <v>1.5449</v>
-      </c>
-      <c r="AM30" s="3" t="n">
-        <v>1.8094</v>
-      </c>
-      <c r="AN30" s="3" t="n">
-        <v>2.768</v>
-      </c>
-      <c r="AO30" s="3" t="n">
-        <v>4.513</v>
-      </c>
-      <c r="AP30" s="3" t="n">
-        <v>2.6357</v>
-      </c>
-      <c r="AQ30" s="3" t="n">
-        <v>2.6937</v>
-      </c>
-      <c r="AR30" s="3" t="n">
-        <v>2.9394</v>
-      </c>
-      <c r="AS30" s="3" t="n">
-        <v>2.6104</v>
-      </c>
-      <c r="AT30" s="3" t="n">
-        <v>2.7079</v>
-      </c>
-      <c r="AU30" s="3" t="n">
-        <v>2.7638</v>
-      </c>
-      <c r="AV30" s="3" t="n">
-        <v>2.9832</v>
-      </c>
-      <c r="AW30" s="3" t="n">
-        <v>4.3928</v>
-      </c>
-      <c r="AX30" s="3" t="n">
-        <v>2.9072</v>
-      </c>
-      <c r="AY30" s="3" t="n">
-        <v>2.723</v>
-      </c>
-      <c r="AZ30" s="3" t="n">
-        <v>2.977</v>
-      </c>
-      <c r="BA30" s="3" t="n">
-        <v>2.6507</v>
-      </c>
-      <c r="BB30" s="3" t="n">
-        <v>2.5267</v>
-      </c>
-      <c r="BC30" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD30" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE30" s="3" t="n">
-        <v>2.8675</v>
-      </c>
-      <c r="BF30" s="3" t="n">
-        <v>2.7079</v>
-      </c>
-      <c r="BG30" s="3" t="n">
-        <v>2.7353</v>
-      </c>
-      <c r="BH30" s="3" t="n">
-        <v>2.9536</v>
-      </c>
-      <c r="BI30" s="3" t="n">
-        <v>4.4519</v>
-      </c>
-      <c r="BJ30" s="3" t="n">
-        <v>4.5175</v>
-      </c>
-      <c r="BK30" s="3" t="n">
-        <v>2.6401</v>
-      </c>
-      <c r="BL30" s="3" t="n">
-        <v>4.5175</v>
-      </c>
-      <c r="BM30" s="3" t="n">
-        <v>4.5712</v>
-      </c>
-      <c r="BN30" s="3" t="n">
-        <v>4.5712</v>
-      </c>
-      <c r="BO30" s="3" t="n">
-        <v>2.6579</v>
-      </c>
-      <c r="BP30" s="3" t="n">
-        <v>2.7475</v>
-      </c>
-      <c r="BQ30" s="3" t="n">
-        <v>2.8448</v>
-      </c>
-      <c r="BR30" s="3" t="n">
-        <v>1.477</v>
+      <c r="AC31" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD31" s="3" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AE31" s="3" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="AF31" s="3" t="n">
+        <v>1.4014</v>
+      </c>
+      <c r="AG31" s="3" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="AH31" s="3" t="n">
+        <v>2.5749</v>
+      </c>
+      <c r="AI31" s="3" t="n">
+        <v>1.1612</v>
+      </c>
+      <c r="AJ31" s="3" t="n">
+        <v>2.9786</v>
+      </c>
+      <c r="AK31" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AL31" s="3" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="AM31" s="3" t="n">
+        <v>1.5328</v>
+      </c>
+      <c r="AN31" s="3" t="n">
+        <v>2.6287</v>
+      </c>
+      <c r="AO31" s="3" t="n">
+        <v>4.7218</v>
+      </c>
+      <c r="AP31" s="3" t="n">
+        <v>2.5552</v>
+      </c>
+      <c r="AQ31" s="3" t="n">
+        <v>2.8959</v>
+      </c>
+      <c r="AR31" s="3" t="n">
+        <v>3.0041</v>
+      </c>
+      <c r="AS31" s="3" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="AT31" s="3" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="AU31" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV31" s="3" t="n">
+        <v>2.9761</v>
+      </c>
+      <c r="AW31" s="3" t="n">
+        <v>4.3944</v>
+      </c>
+      <c r="AX31" s="3" t="n">
+        <v>2.9021</v>
+      </c>
+      <c r="AY31" s="3" t="n">
+        <v>2.7479</v>
+      </c>
+      <c r="AZ31" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="BA31" s="3" t="n">
+        <v>2.8583</v>
+      </c>
+      <c r="BB31" s="3" t="n">
+        <v>2.8392</v>
+      </c>
+      <c r="BC31" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="BD31" s="3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BE31" s="3" t="n">
+        <v>2.8918</v>
+      </c>
+      <c r="BF31" s="3" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="BG31" s="3" t="n">
+        <v>2.7567</v>
+      </c>
+      <c r="BH31" s="3" t="n">
+        <v>2.8672</v>
+      </c>
+      <c r="BI31" s="3" t="n">
+        <v>4.6793</v>
+      </c>
+      <c r="BJ31" s="3" t="n">
+        <v>4.7122</v>
+      </c>
+      <c r="BK31" s="3" t="n">
+        <v>2.9815</v>
+      </c>
+      <c r="BL31" s="3" t="n">
+        <v>4.7122</v>
+      </c>
+      <c r="BM31" s="3" t="n">
+        <v>4.8453</v>
+      </c>
+      <c r="BN31" s="3" t="n">
+        <v>4.8453</v>
+      </c>
+      <c r="BO31" s="3" t="n">
+        <v>2.963</v>
+      </c>
+      <c r="BP31" s="3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BQ31" s="3" t="n">
+        <v>2.8885</v>
+      </c>
+      <c r="BR31" s="3" t="n">
+        <v>1.2726</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR30"/>
+  <autoFilter ref="A1:BR31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -7088,211 +7088,211 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>2.9877</v>
+        <v>2.99</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>2.525</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2.9245</v>
+        <v>2.925</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3.0141</v>
+        <v>3.015</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.1806</v>
+        <v>1.18</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.1258</v>
+        <v>1.13</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.8442</v>
+        <v>2.87</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.8861</v>
+        <v>2.885</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.2125</v>
+        <v>1.19</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2.8671</v>
+        <v>2.865</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>2.8526</v>
+        <v>2.855</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>2.83</v>
+        <v>2.845</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>4.8622</v>
+        <v>4.735</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.7449</v>
+        <v>2.745</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>3.3506</v>
+        <v>3.35</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>2.9811</v>
+        <v>2.98</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>3.2385</v>
+        <v>3.235</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>2.7587</v>
+        <v>2.765</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.0976</v>
+        <v>1.275</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>2.8274</v>
+        <v>2.825</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>2.8824</v>
+        <v>2.885</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>2.6834</v>
+        <v>2.685</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2.749</v>
+        <v>2.75</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>2.7859</v>
+        <v>2.785</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>2.7981</v>
+        <v>2.8</v>
       </c>
       <c r="AB31" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="AC31" s="3" t="n">
-        <v>1.15</v>
+        <v>1.155</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>1.667</v>
+        <v>1.08</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>2.632</v>
+        <v>2.58</v>
       </c>
       <c r="AF31" s="3" t="n">
-        <v>1.4014</v>
+        <v>1.4</v>
       </c>
       <c r="AG31" s="3" t="n">
-        <v>1.136</v>
+        <v>1.135</v>
       </c>
       <c r="AH31" s="3" t="n">
-        <v>2.5749</v>
+        <v>2.575</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>1.1612</v>
+        <v>1.19</v>
       </c>
       <c r="AJ31" s="3" t="n">
-        <v>2.9786</v>
+        <v>2.955</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>2.84</v>
+        <v>2.865</v>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>1.266</v>
+        <v>1.26</v>
       </c>
       <c r="AM31" s="3" t="n">
-        <v>1.5328</v>
+        <v>1.53</v>
       </c>
       <c r="AN31" s="3" t="n">
-        <v>2.6287</v>
+        <v>2.63</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>4.7218</v>
+        <v>4.72</v>
       </c>
       <c r="AP31" s="3" t="n">
-        <v>2.5552</v>
+        <v>2.555</v>
       </c>
       <c r="AQ31" s="3" t="n">
-        <v>2.8959</v>
+        <v>2.895</v>
       </c>
       <c r="AR31" s="3" t="n">
-        <v>3.0041</v>
+        <v>3.005</v>
       </c>
       <c r="AS31" s="3" t="n">
-        <v>2.859</v>
+        <v>2.86</v>
       </c>
       <c r="AT31" s="3" t="n">
-        <v>3.013</v>
+        <v>3.015</v>
       </c>
       <c r="AU31" s="3" t="n">
         <v>2.77</v>
       </c>
       <c r="AV31" s="3" t="n">
-        <v>2.9761</v>
+        <v>2.975</v>
       </c>
       <c r="AW31" s="3" t="n">
-        <v>4.3944</v>
+        <v>4.395</v>
       </c>
       <c r="AX31" s="3" t="n">
-        <v>2.9021</v>
+        <v>2.9</v>
       </c>
       <c r="AY31" s="3" t="n">
-        <v>2.7479</v>
+        <v>2.75</v>
       </c>
       <c r="AZ31" s="3" t="n">
-        <v>2.875</v>
+        <v>2.895</v>
       </c>
       <c r="BA31" s="3" t="n">
-        <v>2.8583</v>
+        <v>2.86</v>
       </c>
       <c r="BB31" s="3" t="n">
-        <v>2.8392</v>
+        <v>2.84</v>
       </c>
       <c r="BC31" s="3" t="n">
-        <v>3.61</v>
+        <v>3.595</v>
       </c>
       <c r="BD31" s="3" t="n">
-        <v>3.41</v>
+        <v>3.23</v>
       </c>
       <c r="BE31" s="3" t="n">
-        <v>2.8918</v>
+        <v>2.895</v>
       </c>
       <c r="BF31" s="3" t="n">
-        <v>3.013</v>
+        <v>3</v>
       </c>
       <c r="BG31" s="3" t="n">
-        <v>2.7567</v>
+        <v>2.755</v>
       </c>
       <c r="BH31" s="3" t="n">
-        <v>2.8672</v>
+        <v>2.865</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>4.6793</v>
+        <v>4.675</v>
       </c>
       <c r="BJ31" s="3" t="n">
-        <v>4.7122</v>
+        <v>4.71</v>
       </c>
       <c r="BK31" s="3" t="n">
-        <v>2.9815</v>
+        <v>2.985</v>
       </c>
       <c r="BL31" s="3" t="n">
-        <v>4.7122</v>
+        <v>4.14</v>
       </c>
       <c r="BM31" s="3" t="n">
-        <v>4.8453</v>
+        <v>4.315</v>
       </c>
       <c r="BN31" s="3" t="n">
-        <v>4.8453</v>
+        <v>4.84</v>
       </c>
       <c r="BO31" s="3" t="n">
-        <v>2.963</v>
+        <v>3.04</v>
       </c>
       <c r="BP31" s="3" t="n">
         <v>3.12</v>
       </c>
       <c r="BQ31" s="3" t="n">
-        <v>2.8885</v>
+        <v>2.89</v>
       </c>
       <c r="BR31" s="3" t="n">
-        <v>1.2726</v>
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR31"/>
+  <dimension ref="A1:BR32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7295,8 +7295,222 @@
         <v>1.27</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2.935</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>4.615</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>3.035</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>4.085</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AC32" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AD32" s="3" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="AE32" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF32" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AG32" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AH32" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AI32" s="3" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="AJ32" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AK32" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AL32" s="3" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="AM32" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN32" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO32" s="3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AP32" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AQ32" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AR32" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AS32" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT32" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU32" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AV32" s="3" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="AW32" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX32" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AY32" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AZ32" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BA32" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="BB32" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="BC32" s="3" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BD32" s="3" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="BE32" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BF32" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BG32" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="BH32" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BI32" s="3" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="BJ32" s="3" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="BK32" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BL32" s="3" t="n">
+        <v>3.725</v>
+      </c>
+      <c r="BM32" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BN32" s="3" t="n">
+        <v>4.815</v>
+      </c>
+      <c r="BO32" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BP32" s="3" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="BQ32" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="BR32" s="3" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR31"/>
+  <autoFilter ref="A1:BR32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR32"/>
+  <dimension ref="A1:BR34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7509,8 +7509,436 @@
         <v>0.77</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>5.135</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>4.395</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>3.325</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>11.555</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="AC33" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AD33" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AE33" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="AF33" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AG33" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AH33" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AI33" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AJ33" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL33" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM33" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AN33" s="3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO33" s="3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AP33" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AQ33" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AR33" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AS33" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT33" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU33" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV33" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="AW33" s="3" t="n">
+        <v>4.065</v>
+      </c>
+      <c r="AX33" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AY33" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="AZ33" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BA33" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BB33" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="BC33" s="3" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="BD33" s="3" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="BE33" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF33" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="BG33" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BH33" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="BI33" s="3" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="BJ33" s="3" t="n">
+        <v>4.395</v>
+      </c>
+      <c r="BK33" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BL33" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BM33" s="3" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BN33" s="3" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="BO33" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="BP33" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BQ33" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="BR33" s="3" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2.7533</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2.5586</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2.6947</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2.8003</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.9094</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>2.6845</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>2.7269</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.6589</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>2.5139</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>2.6571</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>3.9813</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2.6091</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>3.2798</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>3.0585</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>7.2224</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>2.5976</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>0.9868</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>2.7072</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>2.5723</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>2.6024</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>2.6363</v>
+      </c>
+      <c r="AA34" s="3" t="n">
+        <v>2.6348</v>
+      </c>
+      <c r="AB34" s="3" t="n">
+        <v>2.6958</v>
+      </c>
+      <c r="AC34" s="3" t="n">
+        <v>1.0685</v>
+      </c>
+      <c r="AD34" s="3" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="AE34" s="3" t="n">
+        <v>2.4613</v>
+      </c>
+      <c r="AF34" s="3" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="AG34" s="3" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="AH34" s="3" t="n">
+        <v>2.5369</v>
+      </c>
+      <c r="AI34" s="3" t="n">
+        <v>0.6542</v>
+      </c>
+      <c r="AJ34" s="3" t="n">
+        <v>2.7829</v>
+      </c>
+      <c r="AK34" s="3" t="n">
+        <v>2.6347</v>
+      </c>
+      <c r="AL34" s="3" t="n">
+        <v>0.8772</v>
+      </c>
+      <c r="AM34" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AN34" s="3" t="n">
+        <v>1.8838</v>
+      </c>
+      <c r="AO34" s="3" t="n">
+        <v>3.7614</v>
+      </c>
+      <c r="AP34" s="3" t="n">
+        <v>2.4996</v>
+      </c>
+      <c r="AQ34" s="3" t="n">
+        <v>2.6041</v>
+      </c>
+      <c r="AR34" s="3" t="n">
+        <v>2.7104</v>
+      </c>
+      <c r="AS34" s="3" t="n">
+        <v>2.5091</v>
+      </c>
+      <c r="AT34" s="3" t="n">
+        <v>2.6535</v>
+      </c>
+      <c r="AU34" s="3" t="n">
+        <v>2.6033</v>
+      </c>
+      <c r="AV34" s="3" t="n">
+        <v>2.7805</v>
+      </c>
+      <c r="AW34" s="3" t="n">
+        <v>3.8149</v>
+      </c>
+      <c r="AX34" s="3" t="n">
+        <v>2.7203</v>
+      </c>
+      <c r="AY34" s="3" t="n">
+        <v>2.5893</v>
+      </c>
+      <c r="AZ34" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="BA34" s="3" t="n">
+        <v>2.5972</v>
+      </c>
+      <c r="BB34" s="3" t="n">
+        <v>2.4352</v>
+      </c>
+      <c r="BC34" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD34" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE34" s="3" t="n">
+        <v>2.7004</v>
+      </c>
+      <c r="BF34" s="3" t="n">
+        <v>2.6535</v>
+      </c>
+      <c r="BG34" s="3" t="n">
+        <v>2.5931</v>
+      </c>
+      <c r="BH34" s="3" t="n">
+        <v>2.6992</v>
+      </c>
+      <c r="BI34" s="3" t="n">
+        <v>3.8323</v>
+      </c>
+      <c r="BJ34" s="3" t="n">
+        <v>3.8313</v>
+      </c>
+      <c r="BK34" s="3" t="n">
+        <v>2.6083</v>
+      </c>
+      <c r="BL34" s="3" t="n">
+        <v>3.8313</v>
+      </c>
+      <c r="BM34" s="3" t="n">
+        <v>3.9164</v>
+      </c>
+      <c r="BN34" s="3" t="n">
+        <v>3.9164</v>
+      </c>
+      <c r="BO34" s="3" t="n">
+        <v>2.6035</v>
+      </c>
+      <c r="BP34" s="3" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="BQ34" s="3" t="n">
+        <v>2.6691</v>
+      </c>
+      <c r="BR34" s="3" t="n">
+        <v>0.6198</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR32"/>
+  <autoFilter ref="A1:BR34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR34"/>
+  <dimension ref="A1:BR37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7730,215 +7730,857 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2.7533</v>
+        <v>2.755</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.5586</v>
+        <v>2.56</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3.5</v>
+        <v>3.515</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2.6947</v>
+        <v>2.695</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2.8003</v>
+        <v>2.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9094</v>
+        <v>0.91</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.9206</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.6845</v>
+        <v>2.685</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>2.7269</v>
+        <v>2.725</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.6589</v>
+        <v>0.655</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>2.5139</v>
+        <v>2.515</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>2.6571</v>
+        <v>2.72</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>2.74</v>
+        <v>2.745</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>3.9813</v>
+        <v>4.01</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>2.6091</v>
+        <v>2.61</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3.2798</v>
+        <v>3.28</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>3.0585</v>
+        <v>3.06</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>7.2224</v>
+        <v>7.22</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>2.5976</v>
+        <v>2.605</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>0.9868</v>
+        <v>0.99</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2.7072</v>
+        <v>2.705</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>2.5723</v>
+        <v>2.57</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>2.6024</v>
+        <v>2.6</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>2.6363</v>
+        <v>2.635</v>
       </c>
       <c r="AA34" s="3" t="n">
-        <v>2.6348</v>
+        <v>2.635</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>2.6958</v>
+        <v>2.695</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>1.0685</v>
+        <v>0.96</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>1.572</v>
+        <v>0.965</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>2.4613</v>
+        <v>2.46</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>1.249</v>
+        <v>1.25</v>
       </c>
       <c r="AG34" s="3" t="n">
-        <v>1.0054</v>
+        <v>1.005</v>
       </c>
       <c r="AH34" s="3" t="n">
-        <v>2.5369</v>
+        <v>2.535</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>0.6542</v>
+        <v>0.66</v>
       </c>
       <c r="AJ34" s="3" t="n">
-        <v>2.7829</v>
+        <v>2.785</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>2.6347</v>
+        <v>2.635</v>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>0.8772</v>
+        <v>0.875</v>
       </c>
       <c r="AM34" s="3" t="n">
         <v>0.9350000000000001</v>
       </c>
       <c r="AN34" s="3" t="n">
-        <v>1.8838</v>
+        <v>1.885</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>3.7614</v>
+        <v>3.76</v>
       </c>
       <c r="AP34" s="3" t="n">
-        <v>2.4996</v>
+        <v>2.5</v>
       </c>
       <c r="AQ34" s="3" t="n">
-        <v>2.6041</v>
+        <v>2.605</v>
       </c>
       <c r="AR34" s="3" t="n">
-        <v>2.7104</v>
+        <v>2.71</v>
       </c>
       <c r="AS34" s="3" t="n">
-        <v>2.5091</v>
+        <v>2.51</v>
       </c>
       <c r="AT34" s="3" t="n">
-        <v>2.6535</v>
+        <v>2.655</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>2.6033</v>
+        <v>2.605</v>
       </c>
       <c r="AV34" s="3" t="n">
-        <v>2.7805</v>
+        <v>2.78</v>
       </c>
       <c r="AW34" s="3" t="n">
-        <v>3.8149</v>
+        <v>3.815</v>
       </c>
       <c r="AX34" s="3" t="n">
-        <v>2.7203</v>
+        <v>2.72</v>
       </c>
       <c r="AY34" s="3" t="n">
-        <v>2.5893</v>
+        <v>2.59</v>
       </c>
       <c r="AZ34" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="BA34" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BB34" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC34" s="3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BD34" s="3" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="BE34" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BF34" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BG34" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="BH34" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI34" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BJ34" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BK34" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BL34" s="3" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="BM34" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BN34" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BO34" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BP34" s="3" t="n">
         <v>2.755</v>
       </c>
-      <c r="BA34" s="3" t="n">
-        <v>2.5972</v>
-      </c>
-      <c r="BB34" s="3" t="n">
-        <v>2.4352</v>
-      </c>
-      <c r="BC34" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD34" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE34" s="3" t="n">
-        <v>2.7004</v>
-      </c>
-      <c r="BF34" s="3" t="n">
-        <v>2.6535</v>
-      </c>
-      <c r="BG34" s="3" t="n">
-        <v>2.5931</v>
-      </c>
-      <c r="BH34" s="3" t="n">
-        <v>2.6992</v>
-      </c>
-      <c r="BI34" s="3" t="n">
-        <v>3.8323</v>
-      </c>
-      <c r="BJ34" s="3" t="n">
-        <v>3.8313</v>
-      </c>
-      <c r="BK34" s="3" t="n">
-        <v>2.6083</v>
-      </c>
-      <c r="BL34" s="3" t="n">
-        <v>3.8313</v>
-      </c>
-      <c r="BM34" s="3" t="n">
-        <v>3.9164</v>
-      </c>
-      <c r="BN34" s="3" t="n">
-        <v>3.9164</v>
-      </c>
-      <c r="BO34" s="3" t="n">
-        <v>2.6035</v>
-      </c>
-      <c r="BP34" s="3" t="n">
-        <v>2.734</v>
-      </c>
       <c r="BQ34" s="3" t="n">
-        <v>2.6691</v>
+        <v>2.67</v>
       </c>
       <c r="BR34" s="3" t="n">
-        <v>0.6198</v>
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AB35" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="AC35" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AD35" s="3" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="AE35" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF35" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG35" s="3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="AH35" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AI35" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ35" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AK35" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AL35" s="3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AM35" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AN35" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="AO35" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AP35" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ35" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AR35" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AS35" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT35" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AU35" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AV35" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW35" s="3" t="n">
+        <v>3.815</v>
+      </c>
+      <c r="AX35" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AY35" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AZ35" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="BA35" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BB35" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC35" s="3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BD35" s="3" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="BE35" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BF35" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BG35" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="BH35" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI35" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BJ35" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BK35" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BL35" s="3" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="BM35" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BN35" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BO35" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BP35" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="BQ35" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BR35" s="3" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AA36" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AB36" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="AC36" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AD36" s="3" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="AE36" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF36" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG36" s="3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="AH36" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AI36" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ36" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AL36" s="3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AM36" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AN36" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="AO36" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AP36" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ36" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AR36" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AS36" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT36" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AU36" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AV36" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW36" s="3" t="n">
+        <v>3.815</v>
+      </c>
+      <c r="AX36" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AY36" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AZ36" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="BA36" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BB36" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC36" s="3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BD36" s="3" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="BE36" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BF36" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BG36" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="BH36" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI36" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BJ36" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BK36" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BL36" s="3" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="BM36" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BN36" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BO36" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BP36" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="BQ36" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BR36" s="3" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AA37" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AB37" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="AC37" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AD37" s="3" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="AE37" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF37" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG37" s="3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="AH37" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AI37" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ37" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AL37" s="3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AM37" s="3" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AN37" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="AO37" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AP37" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ37" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AR37" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AS37" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT37" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AU37" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AV37" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW37" s="3" t="n">
+        <v>3.815</v>
+      </c>
+      <c r="AX37" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AY37" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AZ37" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="BA37" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BB37" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC37" s="3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BD37" s="3" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="BE37" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BF37" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BG37" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="BH37" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI37" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BJ37" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BK37" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BL37" s="3" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="BM37" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BN37" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BO37" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="BP37" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="BQ37" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BR37" s="3" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR34"/>
+  <autoFilter ref="A1:BR37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR37"/>
+  <dimension ref="A1:BR40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8579,8 +8579,650 @@
         <v>0.62</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AA38" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AB38" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC38" s="3" t="n">
+        <v>1.685</v>
+      </c>
+      <c r="AD38" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE38" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AF38" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG38" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH38" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AI38" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ38" s="3" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AL38" s="3" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="AM38" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="AN38" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="AO38" s="3" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AP38" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ38" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AR38" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="AS38" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AT38" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AU38" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV38" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="AW38" s="3" t="n">
+        <v>3.885</v>
+      </c>
+      <c r="AX38" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AY38" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AZ38" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BA38" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="BB38" s="3" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="BC38" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="BD38" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE38" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BF38" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="BG38" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH38" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="BI38" s="3" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BJ38" s="3" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="BK38" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BL38" s="3" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="BM38" s="3" t="n">
+        <v>3.645</v>
+      </c>
+      <c r="BN38" s="3" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="BO38" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BP38" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="BQ38" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="BR38" s="3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2.7442</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2.6527</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2.6325</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2.6782</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2.7693</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1.6658</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>1.6836</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>2.7455</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>2.7923</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>1.7755</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>2.2837</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>2.6865</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>4.0446</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>2.6639</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>3.1278</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>2.8177</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>2.6714</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>1.6844</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>2.7461</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>2.2288</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>2.6407</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>2.6644</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>2.6644</v>
+      </c>
+      <c r="AA39" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB39" s="3" t="n">
+        <v>2.7888</v>
+      </c>
+      <c r="AC39" s="3" t="n">
+        <v>1.7348</v>
+      </c>
+      <c r="AD39" s="3" t="n">
+        <v>1.6005</v>
+      </c>
+      <c r="AE39" s="3" t="n">
+        <v>2.6431</v>
+      </c>
+      <c r="AF39" s="3" t="n">
+        <v>1.8095</v>
+      </c>
+      <c r="AG39" s="3" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="AH39" s="3" t="n">
+        <v>2.6262</v>
+      </c>
+      <c r="AI39" s="3" t="n">
+        <v>1.7768</v>
+      </c>
+      <c r="AJ39" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>2.7017</v>
+      </c>
+      <c r="AL39" s="3" t="n">
+        <v>1.7887</v>
+      </c>
+      <c r="AM39" s="3" t="n">
+        <v>2.0309</v>
+      </c>
+      <c r="AN39" s="3" t="n">
+        <v>2.9679</v>
+      </c>
+      <c r="AO39" s="3" t="n">
+        <v>3.9122</v>
+      </c>
+      <c r="AP39" s="3" t="n">
+        <v>2.5678</v>
+      </c>
+      <c r="AQ39" s="3" t="n">
+        <v>2.3671</v>
+      </c>
+      <c r="AR39" s="3" t="n">
+        <v>2.7196</v>
+      </c>
+      <c r="AS39" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT39" s="3" t="n">
+        <v>2.3147</v>
+      </c>
+      <c r="AU39" s="3" t="n">
+        <v>2.6657</v>
+      </c>
+      <c r="AV39" s="3" t="n">
+        <v>2.7898</v>
+      </c>
+      <c r="AW39" s="3" t="n">
+        <v>3.8297</v>
+      </c>
+      <c r="AX39" s="3" t="n">
+        <v>2.7447</v>
+      </c>
+      <c r="AY39" s="3" t="n">
+        <v>2.6498</v>
+      </c>
+      <c r="AZ39" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BA39" s="3" t="n">
+        <v>2.4578</v>
+      </c>
+      <c r="BB39" s="3" t="n">
+        <v>2.2277</v>
+      </c>
+      <c r="BC39" s="3" t="n">
+        <v>2.8325</v>
+      </c>
+      <c r="BD39" s="3" t="n">
+        <v>2.6325</v>
+      </c>
+      <c r="BE39" s="3" t="n">
+        <v>2.7214</v>
+      </c>
+      <c r="BF39" s="3" t="n">
+        <v>2.3147</v>
+      </c>
+      <c r="BG39" s="3" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="BH39" s="3" t="n">
+        <v>2.8124</v>
+      </c>
+      <c r="BI39" s="3" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="BJ39" s="3" t="n">
+        <v>3.8946</v>
+      </c>
+      <c r="BK39" s="3" t="n">
+        <v>2.3084</v>
+      </c>
+      <c r="BL39" s="3" t="n">
+        <v>3.8946</v>
+      </c>
+      <c r="BM39" s="3" t="n">
+        <v>4.0188</v>
+      </c>
+      <c r="BN39" s="3" t="n">
+        <v>4.0188</v>
+      </c>
+      <c r="BO39" s="3" t="n">
+        <v>2.2647</v>
+      </c>
+      <c r="BP39" s="3" t="n">
+        <v>2.3147</v>
+      </c>
+      <c r="BQ39" s="3" t="n">
+        <v>2.709</v>
+      </c>
+      <c r="BR39" s="3" t="n">
+        <v>1.7553</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2.8285</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2.6245</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>3.2205</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2.7275</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2.8005</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>2.7695</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>4.2675</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>3.2675</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>3.1325</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>3.2125</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>2.737</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>2.3815</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>2.5665</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>2.6955</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA40" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="AB40" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC40" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD40" s="3" t="n">
+        <v>1.6005</v>
+      </c>
+      <c r="AE40" s="3" t="n">
+        <v>2.4595</v>
+      </c>
+      <c r="AF40" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG40" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH40" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AI40" s="3" t="n">
+        <v>1.2755</v>
+      </c>
+      <c r="AJ40" s="3" t="n">
+        <v>2.8005</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AL40" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM40" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AN40" s="3" t="n">
+        <v>3.832</v>
+      </c>
+      <c r="AO40" s="3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AP40" s="3" t="n">
+        <v>2.4335</v>
+      </c>
+      <c r="AQ40" s="3" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="AR40" s="3" t="n">
+        <v>2.8025</v>
+      </c>
+      <c r="AS40" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AT40" s="3" t="n">
+        <v>2.5895</v>
+      </c>
+      <c r="AU40" s="3" t="n">
+        <v>2.6415</v>
+      </c>
+      <c r="AV40" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AW40" s="3" t="n">
+        <v>4.046</v>
+      </c>
+      <c r="AX40" s="3" t="n">
+        <v>2.7395</v>
+      </c>
+      <c r="AY40" s="3" t="n">
+        <v>2.6455</v>
+      </c>
+      <c r="AZ40" s="3" t="n">
+        <v>2.7835</v>
+      </c>
+      <c r="BA40" s="3" t="n">
+        <v>2.686</v>
+      </c>
+      <c r="BB40" s="3" t="n">
+        <v>2.3465</v>
+      </c>
+      <c r="BC40" s="3" t="n">
+        <v>3.2725</v>
+      </c>
+      <c r="BD40" s="3" t="n">
+        <v>3.2205</v>
+      </c>
+      <c r="BE40" s="3" t="n">
+        <v>2.7625</v>
+      </c>
+      <c r="BF40" s="3" t="n">
+        <v>2.4827</v>
+      </c>
+      <c r="BG40" s="3" t="n">
+        <v>2.7025</v>
+      </c>
+      <c r="BH40" s="3" t="n">
+        <v>3.153</v>
+      </c>
+      <c r="BI40" s="3" t="n">
+        <v>4.095</v>
+      </c>
+      <c r="BJ40" s="3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BK40" s="3" t="n">
+        <v>2.4745</v>
+      </c>
+      <c r="BL40" s="3" t="n">
+        <v>4.0025</v>
+      </c>
+      <c r="BM40" s="3" t="n">
+        <v>3.5095</v>
+      </c>
+      <c r="BN40" s="3" t="n">
+        <v>4.378</v>
+      </c>
+      <c r="BO40" s="3" t="n">
+        <v>2.5275</v>
+      </c>
+      <c r="BP40" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BQ40" s="3" t="n">
+        <v>2.7795</v>
+      </c>
+      <c r="BR40" s="3" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR37"/>
+  <autoFilter ref="A1:BR40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -8800,211 +8800,211 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>2.7442</v>
+        <v>2.745</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2.6527</v>
+        <v>2.655</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2.6325</v>
+        <v>2.615</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2.6782</v>
+        <v>2.68</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2.7693</v>
+        <v>2.77</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1.6658</v>
+        <v>1.665</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.6836</v>
+        <v>1.685</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.7455</v>
+        <v>2.75</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>2.7923</v>
+        <v>2.79</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.7755</v>
+        <v>1.775</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>2.2837</v>
+        <v>2.285</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>2.6865</v>
+        <v>2.655</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>2.805</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>4.0446</v>
+        <v>4.035</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.6639</v>
+        <v>2.665</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>3.1278</v>
+        <v>3.13</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>2.81</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>2.8177</v>
+        <v>2.82</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>2.6714</v>
+        <v>2.675</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>1.6844</v>
+        <v>1.925</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>2.7461</v>
+        <v>2.745</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>2.2288</v>
+        <v>2.23</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>2.6407</v>
+        <v>2.64</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>2.6644</v>
+        <v>2.665</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>2.6644</v>
+        <v>2.665</v>
       </c>
       <c r="AA39" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="AB39" s="3" t="n">
-        <v>2.7888</v>
+        <v>2.79</v>
       </c>
       <c r="AC39" s="3" t="n">
-        <v>1.7348</v>
+        <v>1.745</v>
       </c>
       <c r="AD39" s="3" t="n">
-        <v>1.6005</v>
+        <v>1.29</v>
       </c>
       <c r="AE39" s="3" t="n">
-        <v>2.6431</v>
+        <v>2.645</v>
       </c>
       <c r="AF39" s="3" t="n">
-        <v>1.8095</v>
+        <v>1.81</v>
       </c>
       <c r="AG39" s="3" t="n">
-        <v>1.339</v>
+        <v>1.34</v>
       </c>
       <c r="AH39" s="3" t="n">
-        <v>2.6262</v>
+        <v>2.63</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>1.7768</v>
+        <v>1.775</v>
       </c>
       <c r="AJ39" s="3" t="n">
         <v>2.82</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>2.7017</v>
+        <v>2.7</v>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>1.7887</v>
+        <v>1.795</v>
       </c>
       <c r="AM39" s="3" t="n">
-        <v>2.0309</v>
+        <v>2.03</v>
       </c>
       <c r="AN39" s="3" t="n">
-        <v>2.9679</v>
+        <v>2.97</v>
       </c>
       <c r="AO39" s="3" t="n">
-        <v>3.9122</v>
+        <v>3.91</v>
       </c>
       <c r="AP39" s="3" t="n">
-        <v>2.5678</v>
+        <v>2.57</v>
       </c>
       <c r="AQ39" s="3" t="n">
-        <v>2.3671</v>
+        <v>2.365</v>
       </c>
       <c r="AR39" s="3" t="n">
-        <v>2.7196</v>
+        <v>2.72</v>
       </c>
       <c r="AS39" s="3" t="n">
         <v>2.26</v>
       </c>
       <c r="AT39" s="3" t="n">
-        <v>2.3147</v>
+        <v>2.315</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>2.6657</v>
+        <v>2.665</v>
       </c>
       <c r="AV39" s="3" t="n">
-        <v>2.7898</v>
+        <v>2.79</v>
       </c>
       <c r="AW39" s="3" t="n">
-        <v>3.8297</v>
+        <v>3.83</v>
       </c>
       <c r="AX39" s="3" t="n">
-        <v>2.7447</v>
+        <v>2.745</v>
       </c>
       <c r="AY39" s="3" t="n">
-        <v>2.6498</v>
+        <v>2.65</v>
       </c>
       <c r="AZ39" s="3" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BA39" s="3" t="n">
-        <v>2.4578</v>
+        <v>2.455</v>
       </c>
       <c r="BB39" s="3" t="n">
-        <v>2.2277</v>
+        <v>2.23</v>
       </c>
       <c r="BC39" s="3" t="n">
-        <v>2.8325</v>
+        <v>2.695</v>
       </c>
       <c r="BD39" s="3" t="n">
-        <v>2.6325</v>
+        <v>2.555</v>
       </c>
       <c r="BE39" s="3" t="n">
-        <v>2.7214</v>
+        <v>2.72</v>
       </c>
       <c r="BF39" s="3" t="n">
-        <v>2.3147</v>
+        <v>2.35</v>
       </c>
       <c r="BG39" s="3" t="n">
-        <v>2.662</v>
+        <v>2.66</v>
       </c>
       <c r="BH39" s="3" t="n">
-        <v>2.8124</v>
+        <v>2.81</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>3.853</v>
+        <v>3.855</v>
       </c>
       <c r="BJ39" s="3" t="n">
-        <v>3.8946</v>
+        <v>3.895</v>
       </c>
       <c r="BK39" s="3" t="n">
-        <v>2.3084</v>
+        <v>2.31</v>
       </c>
       <c r="BL39" s="3" t="n">
-        <v>3.8946</v>
+        <v>3.45</v>
       </c>
       <c r="BM39" s="3" t="n">
-        <v>4.0188</v>
+        <v>3.49</v>
       </c>
       <c r="BN39" s="3" t="n">
-        <v>4.0188</v>
+        <v>4.015</v>
       </c>
       <c r="BO39" s="3" t="n">
-        <v>2.2647</v>
+        <v>2.29</v>
       </c>
       <c r="BP39" s="3" t="n">
-        <v>2.3147</v>
+        <v>2.37</v>
       </c>
       <c r="BQ39" s="3" t="n">
-        <v>2.709</v>
+        <v>2.71</v>
       </c>
       <c r="BR39" s="3" t="n">
-        <v>1.7553</v>
+        <v>1.755</v>
       </c>
     </row>
     <row r="40">
@@ -9014,211 +9014,211 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>2.8285</v>
+        <v>2.7743</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2.6245</v>
+        <v>2.6196</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>3.2205</v>
+        <v>3.1</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2.7275</v>
+        <v>2.7136</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2.8005</v>
+        <v>2.78</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2.235</v>
+        <v>2.1839</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>2.225</v>
+        <v>2.2007</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.79</v>
+        <v>2.7953</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>2.74</v>
+        <v>2.8289</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1.6</v>
+        <v>1.7416</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>2.415</v>
+        <v>2.4765</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>2.7695</v>
+        <v>2.705</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>4.2675</v>
+        <v>4.283</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.7</v>
+        <v>2.7372</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>3.2675</v>
+        <v>3.3026</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>3.1325</v>
+        <v>2.82</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>3.2125</v>
+        <v>3.02</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>2.737</v>
+        <v>2.6827</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>2.47</v>
+        <v>2.1769</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>2.8</v>
+        <v>2.8123</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>2.3815</v>
+        <v>2.4461</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>2.5665</v>
+        <v>2.6481</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>2.6955</v>
+        <v>2.6825</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2.7</v>
+        <v>2.722</v>
       </c>
       <c r="AA40" s="3" t="n">
-        <v>2.805</v>
+        <v>2.7611</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7992</v>
       </c>
       <c r="AC40" s="3" t="n">
-        <v>2.28</v>
+        <v>2.1886</v>
       </c>
       <c r="AD40" s="3" t="n">
-        <v>1.6005</v>
+        <v>1.563</v>
       </c>
       <c r="AE40" s="3" t="n">
-        <v>2.4595</v>
+        <v>2.6342</v>
       </c>
       <c r="AF40" s="3" t="n">
-        <v>2.2</v>
+        <v>2.0642</v>
       </c>
       <c r="AG40" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7797</v>
       </c>
       <c r="AH40" s="3" t="n">
-        <v>2.61</v>
+        <v>2.6519</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>1.2755</v>
+        <v>1.7642</v>
       </c>
       <c r="AJ40" s="3" t="n">
-        <v>2.8005</v>
+        <v>2.8447</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>2.735</v>
+        <v>2.75</v>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>2.35</v>
+        <v>2.0045</v>
       </c>
       <c r="AM40" s="3" t="n">
-        <v>3.01</v>
+        <v>2.2681</v>
       </c>
       <c r="AN40" s="3" t="n">
-        <v>3.832</v>
+        <v>3.0764</v>
       </c>
       <c r="AO40" s="3" t="n">
-        <v>4.05</v>
+        <v>4.1121</v>
       </c>
       <c r="AP40" s="3" t="n">
-        <v>2.4335</v>
+        <v>2.6357</v>
       </c>
       <c r="AQ40" s="3" t="n">
-        <v>2.504</v>
+        <v>2.5315</v>
       </c>
       <c r="AR40" s="3" t="n">
-        <v>2.8025</v>
+        <v>2.8242</v>
       </c>
       <c r="AS40" s="3" t="n">
-        <v>2.489</v>
+        <v>2.4714</v>
       </c>
       <c r="AT40" s="3" t="n">
-        <v>2.5895</v>
+        <v>2.5663</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>2.6415</v>
+        <v>2.6741</v>
       </c>
       <c r="AV40" s="3" t="n">
-        <v>2.885</v>
+        <v>2.8315</v>
       </c>
       <c r="AW40" s="3" t="n">
-        <v>4.046</v>
+        <v>4.0482</v>
       </c>
       <c r="AX40" s="3" t="n">
-        <v>2.7395</v>
+        <v>2.7556</v>
       </c>
       <c r="AY40" s="3" t="n">
-        <v>2.6455</v>
+        <v>2.6839</v>
       </c>
       <c r="AZ40" s="3" t="n">
-        <v>2.7835</v>
+        <v>2.68</v>
       </c>
       <c r="BA40" s="3" t="n">
-        <v>2.686</v>
+        <v>2.6072</v>
       </c>
       <c r="BB40" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.3983</v>
       </c>
       <c r="BC40" s="3" t="n">
-        <v>3.2725</v>
+        <v>3.3</v>
       </c>
       <c r="BD40" s="3" t="n">
-        <v>3.2205</v>
+        <v>3.1</v>
       </c>
       <c r="BE40" s="3" t="n">
-        <v>2.7625</v>
+        <v>2.789</v>
       </c>
       <c r="BF40" s="3" t="n">
-        <v>2.4827</v>
+        <v>2.5663</v>
       </c>
       <c r="BG40" s="3" t="n">
-        <v>2.7025</v>
+        <v>2.7035</v>
       </c>
       <c r="BH40" s="3" t="n">
-        <v>3.153</v>
+        <v>2.7732</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>4.095</v>
+        <v>4.0941</v>
       </c>
       <c r="BJ40" s="3" t="n">
-        <v>4.12</v>
+        <v>4.133</v>
       </c>
       <c r="BK40" s="3" t="n">
-        <v>2.4745</v>
+        <v>2.531</v>
       </c>
       <c r="BL40" s="3" t="n">
-        <v>4.0025</v>
+        <v>4.133</v>
       </c>
       <c r="BM40" s="3" t="n">
-        <v>3.5095</v>
+        <v>4.2232</v>
       </c>
       <c r="BN40" s="3" t="n">
-        <v>4.378</v>
+        <v>4.2232</v>
       </c>
       <c r="BO40" s="3" t="n">
-        <v>2.5275</v>
+        <v>2.5163</v>
       </c>
       <c r="BP40" s="3" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="BQ40" s="3" t="n">
-        <v>2.7795</v>
+        <v>2.7786</v>
       </c>
       <c r="BR40" s="3" t="n">
-        <v>1.56</v>
+        <v>1.7289</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR40"/>
+  <dimension ref="A1:BR41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9014,215 +9014,429 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>2.7743</v>
+        <v>2.775</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2.6196</v>
+        <v>2.62</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2.7136</v>
+        <v>2.715</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>2.78</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2.1839</v>
+        <v>2.185</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>2.2007</v>
+        <v>2.21</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.7953</v>
+        <v>2.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>2.8289</v>
+        <v>2.83</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1.7416</v>
+        <v>1.755</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>2.4765</v>
+        <v>2.475</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>2.705</v>
+        <v>2.71</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.75</v>
+        <v>2.825</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>4.283</v>
+        <v>4.215</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.7372</v>
+        <v>2.735</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>3.3026</v>
+        <v>3.305</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>2.82</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>3.02</v>
+        <v>3.015</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>2.6827</v>
+        <v>2.69</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>2.1769</v>
+        <v>2.295</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>2.8123</v>
+        <v>2.81</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>2.4461</v>
+        <v>2.445</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>2.6481</v>
+        <v>2.65</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>2.6825</v>
+        <v>2.68</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2.722</v>
+        <v>2.72</v>
       </c>
       <c r="AA40" s="3" t="n">
-        <v>2.7611</v>
+        <v>2.765</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>2.7992</v>
+        <v>2.8</v>
       </c>
       <c r="AC40" s="3" t="n">
-        <v>2.1886</v>
+        <v>2.21</v>
       </c>
       <c r="AD40" s="3" t="n">
-        <v>1.563</v>
+        <v>1.715</v>
       </c>
       <c r="AE40" s="3" t="n">
-        <v>2.6342</v>
+        <v>2.635</v>
       </c>
       <c r="AF40" s="3" t="n">
-        <v>2.0642</v>
+        <v>2.065</v>
       </c>
       <c r="AG40" s="3" t="n">
-        <v>1.7797</v>
+        <v>1.78</v>
       </c>
       <c r="AH40" s="3" t="n">
-        <v>2.6519</v>
+        <v>2.65</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>1.7642</v>
+        <v>1.76</v>
       </c>
       <c r="AJ40" s="3" t="n">
-        <v>2.8447</v>
+        <v>2.845</v>
       </c>
       <c r="AK40" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL40" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="AM40" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AN40" s="3" t="n">
+        <v>3.075</v>
+      </c>
+      <c r="AO40" s="3" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AP40" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AQ40" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AR40" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="AS40" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT40" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AU40" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AV40" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AW40" s="3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AX40" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AY40" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AZ40" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="BA40" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="BB40" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC40" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BD40" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BE40" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BF40" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG40" s="3" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="BH40" s="3" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="BI40" s="3" t="n">
+        <v>4.095</v>
+      </c>
+      <c r="BJ40" s="3" t="n">
+        <v>4.135</v>
+      </c>
+      <c r="BK40" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL40" s="3" t="n">
+        <v>3.595</v>
+      </c>
+      <c r="BM40" s="3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BN40" s="3" t="n">
+        <v>4.225</v>
+      </c>
+      <c r="BO40" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP40" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BQ40" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BR40" s="3" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2.6876</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2.5206</v>
+      </c>
+      <c r="D41" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="AL40" s="3" t="n">
-        <v>2.0045</v>
-      </c>
-      <c r="AM40" s="3" t="n">
-        <v>2.2681</v>
-      </c>
-      <c r="AN40" s="3" t="n">
-        <v>3.0764</v>
-      </c>
-      <c r="AO40" s="3" t="n">
-        <v>4.1121</v>
-      </c>
-      <c r="AP40" s="3" t="n">
-        <v>2.6357</v>
-      </c>
-      <c r="AQ40" s="3" t="n">
-        <v>2.5315</v>
-      </c>
-      <c r="AR40" s="3" t="n">
-        <v>2.8242</v>
-      </c>
-      <c r="AS40" s="3" t="n">
-        <v>2.4714</v>
-      </c>
-      <c r="AT40" s="3" t="n">
-        <v>2.5663</v>
-      </c>
-      <c r="AU40" s="3" t="n">
-        <v>2.6741</v>
-      </c>
-      <c r="AV40" s="3" t="n">
-        <v>2.8315</v>
-      </c>
-      <c r="AW40" s="3" t="n">
-        <v>4.0482</v>
-      </c>
-      <c r="AX40" s="3" t="n">
-        <v>2.7556</v>
-      </c>
-      <c r="AY40" s="3" t="n">
-        <v>2.6839</v>
-      </c>
-      <c r="AZ40" s="3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BA40" s="3" t="n">
-        <v>2.6072</v>
-      </c>
-      <c r="BB40" s="3" t="n">
-        <v>2.3983</v>
-      </c>
-      <c r="BC40" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE40" s="3" t="n">
-        <v>2.789</v>
-      </c>
-      <c r="BF40" s="3" t="n">
-        <v>2.5663</v>
-      </c>
-      <c r="BG40" s="3" t="n">
+      <c r="E41" s="3" t="n">
+        <v>2.6182</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2.7063</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>1.9414</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>1.9893</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>2.7003</v>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>2.7035</v>
       </c>
-      <c r="BH40" s="3" t="n">
-        <v>2.7732</v>
-      </c>
-      <c r="BI40" s="3" t="n">
-        <v>4.0941</v>
-      </c>
-      <c r="BJ40" s="3" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="BK40" s="3" t="n">
-        <v>2.531</v>
-      </c>
-      <c r="BL40" s="3" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="BM40" s="3" t="n">
-        <v>4.2232</v>
-      </c>
-      <c r="BN40" s="3" t="n">
-        <v>4.2232</v>
-      </c>
-      <c r="BO40" s="3" t="n">
-        <v>2.5163</v>
-      </c>
-      <c r="BP40" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BQ40" s="3" t="n">
-        <v>2.7786</v>
-      </c>
-      <c r="BR40" s="3" t="n">
-        <v>1.7289</v>
+      <c r="K41" s="3" t="n">
+        <v>1.5458</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>2.3959</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>4.0281</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>2.6038</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>3.1451</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>2.7213</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>2.8395</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>2.5674</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>1.9074</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>2.6923</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>2.3638</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>2.5461</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>2.5299</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>2.6551</v>
+      </c>
+      <c r="AA41" s="3" t="n">
+        <v>2.6843</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>2.6817</v>
+      </c>
+      <c r="AC41" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD41" s="3" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="AE41" s="3" t="n">
+        <v>2.5531</v>
+      </c>
+      <c r="AF41" s="3" t="n">
+        <v>2.2049</v>
+      </c>
+      <c r="AG41" s="3" t="n">
+        <v>1.901</v>
+      </c>
+      <c r="AH41" s="3" t="n">
+        <v>2.5466</v>
+      </c>
+      <c r="AI41" s="3" t="n">
+        <v>1.5551</v>
+      </c>
+      <c r="AJ41" s="3" t="n">
+        <v>2.7843</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AL41" s="3" t="n">
+        <v>1.8772</v>
+      </c>
+      <c r="AM41" s="3" t="n">
+        <v>2.0072</v>
+      </c>
+      <c r="AN41" s="3" t="n">
+        <v>2.8981</v>
+      </c>
+      <c r="AO41" s="3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AP41" s="3" t="n">
+        <v>2.5302</v>
+      </c>
+      <c r="AQ41" s="3" t="n">
+        <v>2.4778</v>
+      </c>
+      <c r="AR41" s="3" t="n">
+        <v>2.6992</v>
+      </c>
+      <c r="AS41" s="3" t="n">
+        <v>2.4199</v>
+      </c>
+      <c r="AT41" s="3" t="n">
+        <v>2.5295</v>
+      </c>
+      <c r="AU41" s="3" t="n">
+        <v>2.5443</v>
+      </c>
+      <c r="AV41" s="3" t="n">
+        <v>2.7321</v>
+      </c>
+      <c r="AW41" s="3" t="n">
+        <v>3.707</v>
+      </c>
+      <c r="AX41" s="3" t="n">
+        <v>2.7176</v>
+      </c>
+      <c r="AY41" s="3" t="n">
+        <v>2.5801</v>
+      </c>
+      <c r="AZ41" s="3" t="n">
+        <v>2.6201</v>
+      </c>
+      <c r="BA41" s="3" t="n">
+        <v>2.5144</v>
+      </c>
+      <c r="BB41" s="3" t="n">
+        <v>2.3375</v>
+      </c>
+      <c r="BC41" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BD41" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE41" s="3" t="n">
+        <v>2.7354</v>
+      </c>
+      <c r="BF41" s="3" t="n">
+        <v>2.5295</v>
+      </c>
+      <c r="BG41" s="3" t="n">
+        <v>2.5624</v>
+      </c>
+      <c r="BH41" s="3" t="n">
+        <v>2.7641</v>
+      </c>
+      <c r="BI41" s="3" t="n">
+        <v>3.8474</v>
+      </c>
+      <c r="BJ41" s="3" t="n">
+        <v>3.8781</v>
+      </c>
+      <c r="BK41" s="3" t="n">
+        <v>2.4924</v>
+      </c>
+      <c r="BL41" s="3" t="n">
+        <v>3.8781</v>
+      </c>
+      <c r="BM41" s="3" t="n">
+        <v>3.9917</v>
+      </c>
+      <c r="BN41" s="3" t="n">
+        <v>3.9917</v>
+      </c>
+      <c r="BO41" s="3" t="n">
+        <v>2.4795</v>
+      </c>
+      <c r="BP41" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BQ41" s="3" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="BR41" s="3" t="n">
+        <v>1.5428</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR40"/>
+  <autoFilter ref="A1:BR41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -9228,211 +9228,211 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>2.6876</v>
+        <v>2.69</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2.5206</v>
+        <v>2.52</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2.75</v>
+        <v>2.755</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.6182</v>
+        <v>2.62</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.7063</v>
+        <v>2.705</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.9414</v>
+        <v>1.94</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.9893</v>
+        <v>1.985</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.7003</v>
+        <v>2.695</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2.7035</v>
+        <v>2.705</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.5458</v>
+        <v>1.55</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>2.3959</v>
+        <v>2.395</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>2.67</v>
+        <v>2.695</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>2.67</v>
+        <v>2.715</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>4.0281</v>
+        <v>4.01</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>2.6038</v>
+        <v>2.605</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>3.1451</v>
+        <v>3.145</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>2.7213</v>
+        <v>2.72</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>2.8395</v>
+        <v>2.84</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>2.5674</v>
+        <v>2.56</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1.9074</v>
+        <v>2.025</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>2.6923</v>
+        <v>2.69</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>2.3638</v>
+        <v>2.365</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>2.5461</v>
+        <v>2.545</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>2.5299</v>
+        <v>2.53</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6551</v>
+        <v>2.66</v>
       </c>
       <c r="AA41" s="3" t="n">
-        <v>2.6843</v>
+        <v>2.685</v>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>2.6817</v>
+        <v>2.68</v>
       </c>
       <c r="AC41" s="3" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AD41" s="3" t="n">
-        <v>1.328</v>
+        <v>1.865</v>
       </c>
       <c r="AE41" s="3" t="n">
-        <v>2.5531</v>
+        <v>2.55</v>
       </c>
       <c r="AF41" s="3" t="n">
-        <v>2.2049</v>
+        <v>2.205</v>
       </c>
       <c r="AG41" s="3" t="n">
-        <v>1.901</v>
+        <v>1.905</v>
       </c>
       <c r="AH41" s="3" t="n">
-        <v>2.5466</v>
+        <v>2.545</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>1.5551</v>
+        <v>1.555</v>
       </c>
       <c r="AJ41" s="3" t="n">
-        <v>2.7843</v>
+        <v>2.785</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>2.65</v>
+        <v>2.635</v>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>1.8772</v>
+        <v>1.9</v>
       </c>
       <c r="AM41" s="3" t="n">
-        <v>2.0072</v>
+        <v>2.005</v>
       </c>
       <c r="AN41" s="3" t="n">
-        <v>2.8981</v>
+        <v>2.9</v>
       </c>
       <c r="AO41" s="3" t="n">
         <v>3.85</v>
       </c>
       <c r="AP41" s="3" t="n">
-        <v>2.5302</v>
+        <v>2.53</v>
       </c>
       <c r="AQ41" s="3" t="n">
-        <v>2.4778</v>
+        <v>2.48</v>
       </c>
       <c r="AR41" s="3" t="n">
-        <v>2.6992</v>
+        <v>2.7</v>
       </c>
       <c r="AS41" s="3" t="n">
-        <v>2.4199</v>
+        <v>2.42</v>
       </c>
       <c r="AT41" s="3" t="n">
-        <v>2.5295</v>
+        <v>2.53</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>2.5443</v>
+        <v>2.56</v>
       </c>
       <c r="AV41" s="3" t="n">
-        <v>2.7321</v>
+        <v>2.73</v>
       </c>
       <c r="AW41" s="3" t="n">
-        <v>3.707</v>
+        <v>3.705</v>
       </c>
       <c r="AX41" s="3" t="n">
-        <v>2.7176</v>
+        <v>2.72</v>
       </c>
       <c r="AY41" s="3" t="n">
-        <v>2.5801</v>
+        <v>2.58</v>
       </c>
       <c r="AZ41" s="3" t="n">
-        <v>2.6201</v>
+        <v>2.665</v>
       </c>
       <c r="BA41" s="3" t="n">
-        <v>2.5144</v>
+        <v>2.515</v>
       </c>
       <c r="BB41" s="3" t="n">
-        <v>2.3375</v>
+        <v>2.335</v>
       </c>
       <c r="BC41" s="3" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="BD41" s="3" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="BE41" s="3" t="n">
-        <v>2.7354</v>
+        <v>2.735</v>
       </c>
       <c r="BF41" s="3" t="n">
-        <v>2.5295</v>
+        <v>2.545</v>
       </c>
       <c r="BG41" s="3" t="n">
-        <v>2.5624</v>
+        <v>2.56</v>
       </c>
       <c r="BH41" s="3" t="n">
-        <v>2.7641</v>
+        <v>2.765</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>3.8474</v>
+        <v>3.845</v>
       </c>
       <c r="BJ41" s="3" t="n">
-        <v>3.8781</v>
+        <v>3.88</v>
       </c>
       <c r="BK41" s="3" t="n">
-        <v>2.4924</v>
+        <v>2.49</v>
       </c>
       <c r="BL41" s="3" t="n">
-        <v>3.8781</v>
+        <v>3.39</v>
       </c>
       <c r="BM41" s="3" t="n">
-        <v>3.9917</v>
+        <v>3.71</v>
       </c>
       <c r="BN41" s="3" t="n">
-        <v>3.9917</v>
+        <v>3.99</v>
       </c>
       <c r="BO41" s="3" t="n">
-        <v>2.4795</v>
+        <v>2.51</v>
       </c>
       <c r="BP41" s="3" t="n">
-        <v>2.61</v>
+        <v>2.645</v>
       </c>
       <c r="BQ41" s="3" t="n">
-        <v>2.691</v>
+        <v>2.69</v>
       </c>
       <c r="BR41" s="3" t="n">
-        <v>1.5428</v>
+        <v>1.535</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR41"/>
+  <dimension ref="A1:BR44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9435,8 +9435,650 @@
         <v>1.535</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>3.705</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AA42" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="AC42" s="3" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="AD42" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE42" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF42" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AG42" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH42" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI42" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="AJ42" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="AK42" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="AL42" s="3" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="AM42" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN42" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="AO42" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AP42" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AQ42" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AR42" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS42" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT42" s="3" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="AU42" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AV42" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AW42" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AX42" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AY42" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AZ42" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="BA42" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="BB42" s="3" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="BC42" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BD42" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BE42" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="BF42" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BG42" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BH42" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BI42" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ42" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BK42" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL42" s="3" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="BM42" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN42" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BO42" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BP42" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="BQ42" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR42" s="3" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>3.705</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="AC43" s="3" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="AD43" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE43" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF43" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AG43" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH43" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI43" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="AJ43" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="AK43" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="AL43" s="3" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="AM43" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN43" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="AO43" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AP43" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AQ43" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AR43" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS43" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT43" s="3" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="AU43" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AV43" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AW43" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AX43" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AY43" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AZ43" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="BA43" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="BB43" s="3" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="BC43" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BD43" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BE43" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="BF43" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BG43" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BH43" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BI43" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ43" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BK43" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL43" s="3" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="BM43" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN43" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BO43" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BP43" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="BQ43" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR43" s="3" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>3.705</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AA44" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB44" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="AC44" s="3" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="AD44" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE44" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF44" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AG44" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH44" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI44" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="AJ44" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="AK44" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="AL44" s="3" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="AM44" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN44" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="AO44" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AP44" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AQ44" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AR44" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS44" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT44" s="3" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="AU44" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AV44" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AW44" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AX44" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AY44" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AZ44" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="BA44" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="BB44" s="3" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="BC44" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BD44" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="BE44" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="BF44" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="BG44" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BH44" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="BI44" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ44" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BK44" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL44" s="3" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="BM44" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN44" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BO44" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BP44" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="BQ44" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR44" s="3" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR41"/>
+  <autoFilter ref="A1:BR44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR44"/>
+  <dimension ref="A1:BR46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10077,8 +10077,436 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AC45" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD45" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AE45" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF45" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="AG45" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH45" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI45" s="3" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="AJ45" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL45" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AM45" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AN45" s="3" t="n">
+        <v>3.345</v>
+      </c>
+      <c r="AO45" s="3" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AP45" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AQ45" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="AR45" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS45" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT45" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU45" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AV45" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AW45" s="3" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="AX45" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="AY45" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="AZ45" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="BA45" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB45" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BC45" s="3" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="BD45" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="BE45" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF45" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG45" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BH45" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="BI45" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BJ45" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BK45" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="BL45" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BM45" s="3" t="n">
+        <v>3.485</v>
+      </c>
+      <c r="BN45" s="3" t="n">
+        <v>3.635</v>
+      </c>
+      <c r="BO45" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP45" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="BQ45" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BR45" s="3" t="n">
+        <v>1.715</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>2.5918</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2.5635</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3.2385</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2.5694</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2.6625</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>2.3919</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>2.3766</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.6682</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>2.6435</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1.7782</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>2.391</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>3.789</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>2.3459</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>2.7697</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>2.8665</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>3.4885</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>2.4641</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>2.6106</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>2.3984</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>2.533</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>2.3674</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>2.5257</v>
+      </c>
+      <c r="AA46" s="3" t="n">
+        <v>2.6626</v>
+      </c>
+      <c r="AB46" s="3" t="n">
+        <v>2.6517</v>
+      </c>
+      <c r="AC46" s="3" t="n">
+        <v>2.4975</v>
+      </c>
+      <c r="AD46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE46" s="3" t="n">
+        <v>2.5288</v>
+      </c>
+      <c r="AF46" s="3" t="n">
+        <v>2.6689</v>
+      </c>
+      <c r="AG46" s="3" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="AH46" s="3" t="n">
+        <v>2.5137</v>
+      </c>
+      <c r="AI46" s="3" t="n">
+        <v>1.7829</v>
+      </c>
+      <c r="AJ46" s="3" t="n">
+        <v>2.6764</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>2.5705</v>
+      </c>
+      <c r="AL46" s="3" t="n">
+        <v>2.4357</v>
+      </c>
+      <c r="AM46" s="3" t="n">
+        <v>2.7228</v>
+      </c>
+      <c r="AN46" s="3" t="n">
+        <v>3.6401</v>
+      </c>
+      <c r="AO46" s="3" t="n">
+        <v>3.6085</v>
+      </c>
+      <c r="AP46" s="3" t="n">
+        <v>2.424</v>
+      </c>
+      <c r="AQ46" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="AR46" s="3" t="n">
+        <v>2.6336</v>
+      </c>
+      <c r="AS46" s="3" t="n">
+        <v>2.4562</v>
+      </c>
+      <c r="AT46" s="3" t="n">
+        <v>2.5774</v>
+      </c>
+      <c r="AU46" s="3" t="n">
+        <v>2.4041</v>
+      </c>
+      <c r="AV46" s="3" t="n">
+        <v>2.6008</v>
+      </c>
+      <c r="AW46" s="3" t="n">
+        <v>3.6171</v>
+      </c>
+      <c r="AX46" s="3" t="n">
+        <v>2.5543</v>
+      </c>
+      <c r="AY46" s="3" t="n">
+        <v>2.3762</v>
+      </c>
+      <c r="AZ46" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="BA46" s="3" t="n">
+        <v>2.4929</v>
+      </c>
+      <c r="BB46" s="3" t="n">
+        <v>2.3897</v>
+      </c>
+      <c r="BC46" s="3" t="n">
+        <v>3.4385</v>
+      </c>
+      <c r="BD46" s="3" t="n">
+        <v>3.2385</v>
+      </c>
+      <c r="BE46" s="3" t="n">
+        <v>2.5767</v>
+      </c>
+      <c r="BF46" s="3" t="n">
+        <v>2.5774</v>
+      </c>
+      <c r="BG46" s="3" t="n">
+        <v>2.3926</v>
+      </c>
+      <c r="BH46" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI46" s="3" t="n">
+        <v>3.5646</v>
+      </c>
+      <c r="BJ46" s="3" t="n">
+        <v>3.639</v>
+      </c>
+      <c r="BK46" s="3" t="n">
+        <v>2.4929</v>
+      </c>
+      <c r="BL46" s="3" t="n">
+        <v>3.639</v>
+      </c>
+      <c r="BM46" s="3" t="n">
+        <v>3.7877</v>
+      </c>
+      <c r="BN46" s="3" t="n">
+        <v>3.7877</v>
+      </c>
+      <c r="BO46" s="3" t="n">
+        <v>2.5274</v>
+      </c>
+      <c r="BP46" s="3" t="n">
+        <v>2.7313</v>
+      </c>
+      <c r="BQ46" s="3" t="n">
+        <v>2.6002</v>
+      </c>
+      <c r="BR46" s="3" t="n">
+        <v>1.8001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR44"/>
+  <autoFilter ref="A1:BR46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10298,211 +10298,211 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2.5918</v>
+        <v>2.59</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2.5635</v>
+        <v>2.565</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3.2385</v>
+        <v>3.415</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2.5694</v>
+        <v>2.57</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>2.6625</v>
+        <v>2.665</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2.3919</v>
+        <v>2.39</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>2.3766</v>
+        <v>2.375</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.6682</v>
+        <v>2.67</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2.6435</v>
+        <v>2.645</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.7782</v>
+        <v>1.78</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>2.391</v>
+        <v>2.39</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>2.572</v>
+        <v>2.485</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2.68</v>
+        <v>2.675</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>3.789</v>
+        <v>3.65</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.3459</v>
+        <v>2.345</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>2.7697</v>
+        <v>2.77</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>2.8665</v>
+        <v>2.865</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>3.4885</v>
+        <v>3.505</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>2.406</v>
+        <v>2.415</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>2.4641</v>
+        <v>2.745</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>2.6106</v>
+        <v>2.61</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>2.3984</v>
+        <v>2.4</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>2.533</v>
+        <v>2.535</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>2.3674</v>
+        <v>2.365</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2.5257</v>
+        <v>2.525</v>
       </c>
       <c r="AA46" s="3" t="n">
-        <v>2.6626</v>
+        <v>2.665</v>
       </c>
       <c r="AB46" s="3" t="n">
-        <v>2.6517</v>
+        <v>2.65</v>
       </c>
       <c r="AC46" s="3" t="n">
-        <v>2.4975</v>
+        <v>2.48</v>
       </c>
       <c r="AD46" s="3" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AE46" s="3" t="n">
-        <v>2.5288</v>
+        <v>2.53</v>
       </c>
       <c r="AF46" s="3" t="n">
-        <v>2.6689</v>
+        <v>2.67</v>
       </c>
       <c r="AG46" s="3" t="n">
-        <v>2.432</v>
+        <v>2.43</v>
       </c>
       <c r="AH46" s="3" t="n">
-        <v>2.5137</v>
+        <v>2.515</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>1.7829</v>
+        <v>1.78</v>
       </c>
       <c r="AJ46" s="3" t="n">
-        <v>2.6764</v>
+        <v>2.675</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>2.5705</v>
+        <v>2.57</v>
       </c>
       <c r="AL46" s="3" t="n">
-        <v>2.4357</v>
+        <v>2.43</v>
       </c>
       <c r="AM46" s="3" t="n">
-        <v>2.7228</v>
+        <v>2.72</v>
       </c>
       <c r="AN46" s="3" t="n">
-        <v>3.6401</v>
+        <v>3.64</v>
       </c>
       <c r="AO46" s="3" t="n">
-        <v>3.6085</v>
+        <v>3.61</v>
       </c>
       <c r="AP46" s="3" t="n">
-        <v>2.424</v>
+        <v>2.425</v>
       </c>
       <c r="AQ46" s="3" t="n">
-        <v>2.458</v>
+        <v>2.46</v>
       </c>
       <c r="AR46" s="3" t="n">
-        <v>2.6336</v>
+        <v>2.635</v>
       </c>
       <c r="AS46" s="3" t="n">
-        <v>2.4562</v>
+        <v>2.46</v>
       </c>
       <c r="AT46" s="3" t="n">
-        <v>2.5774</v>
+        <v>2.575</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>2.4041</v>
+        <v>2.405</v>
       </c>
       <c r="AV46" s="3" t="n">
-        <v>2.6008</v>
+        <v>2.6</v>
       </c>
       <c r="AW46" s="3" t="n">
-        <v>3.6171</v>
+        <v>3.615</v>
       </c>
       <c r="AX46" s="3" t="n">
-        <v>2.5543</v>
+        <v>2.555</v>
       </c>
       <c r="AY46" s="3" t="n">
-        <v>2.3762</v>
+        <v>2.375</v>
       </c>
       <c r="AZ46" s="3" t="n">
-        <v>2.597</v>
+        <v>2.56</v>
       </c>
       <c r="BA46" s="3" t="n">
-        <v>2.4929</v>
+        <v>2.495</v>
       </c>
       <c r="BB46" s="3" t="n">
-        <v>2.3897</v>
+        <v>2.39</v>
       </c>
       <c r="BC46" s="3" t="n">
-        <v>3.4385</v>
+        <v>3.35</v>
       </c>
       <c r="BD46" s="3" t="n">
-        <v>3.2385</v>
+        <v>3.16</v>
       </c>
       <c r="BE46" s="3" t="n">
-        <v>2.5767</v>
+        <v>2.575</v>
       </c>
       <c r="BF46" s="3" t="n">
-        <v>2.5774</v>
+        <v>2.545</v>
       </c>
       <c r="BG46" s="3" t="n">
-        <v>2.3926</v>
+        <v>2.395</v>
       </c>
       <c r="BH46" s="3" t="n">
         <v>2.54</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>3.5646</v>
+        <v>3.565</v>
       </c>
       <c r="BJ46" s="3" t="n">
-        <v>3.639</v>
+        <v>3.64</v>
       </c>
       <c r="BK46" s="3" t="n">
-        <v>2.4929</v>
+        <v>2.495</v>
       </c>
       <c r="BL46" s="3" t="n">
-        <v>3.639</v>
+        <v>3.04</v>
       </c>
       <c r="BM46" s="3" t="n">
-        <v>3.7877</v>
+        <v>3.315</v>
       </c>
       <c r="BN46" s="3" t="n">
-        <v>3.7877</v>
+        <v>3.79</v>
       </c>
       <c r="BO46" s="3" t="n">
-        <v>2.5274</v>
+        <v>2.54</v>
       </c>
       <c r="BP46" s="3" t="n">
-        <v>2.7313</v>
+        <v>2.735</v>
       </c>
       <c r="BQ46" s="3" t="n">
-        <v>2.6002</v>
+        <v>2.6</v>
       </c>
       <c r="BR46" s="3" t="n">
-        <v>1.8001</v>
+        <v>1.795</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR46"/>
+  <dimension ref="A1:BR47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10505,8 +10505,222 @@
         <v>1.795</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>1.685</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="Y47" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AA47" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AB47" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="AC47" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AD47" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AE47" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AF47" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AG47" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AH47" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI47" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ47" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AL47" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM47" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AN47" s="3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AO47" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AP47" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AQ47" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AR47" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AS47" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AT47" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AU47" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AV47" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AW47" s="3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AX47" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AY47" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AZ47" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="BA47" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BB47" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BC47" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BD47" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="BE47" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF47" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BG47" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BH47" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="BI47" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BJ47" s="3" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="BK47" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL47" s="3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BM47" s="3" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="BN47" s="3" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BO47" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BP47" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="BQ47" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="BR47" s="3" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR46"/>
+  <autoFilter ref="A1:BR47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR47"/>
+  <dimension ref="A1:BR51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10719,8 +10719,864 @@
         <v>1.71</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="Q48" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S48" s="3" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="U48" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y48" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Z48" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA48" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AB48" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AC48" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AD48" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="AE48" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF48" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG48" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AH48" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AI48" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ48" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AL48" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AM48" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="AN48" s="3" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AO48" s="3" t="n">
+        <v>3.575</v>
+      </c>
+      <c r="AP48" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="AQ48" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AR48" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AS48" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AT48" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU48" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV48" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AW48" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX48" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AY48" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ48" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="BA48" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="BB48" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BC48" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD48" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="BE48" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF48" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG48" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="BH48" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI48" s="3" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="BJ48" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="BK48" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="BL48" s="3" t="n">
+        <v>3.075</v>
+      </c>
+      <c r="BM48" s="3" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="BN48" s="3" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="BO48" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP48" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="BQ48" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BR48" s="3" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2.4455</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2.4028</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2.5064</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>2.4036</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>2.5457</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>2.5705</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>1.6637</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>2.0249</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>2.5087</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>3.7467</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>2.3363</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>2.7655</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>2.5773</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>2.3786</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>2.3965</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>2.5597</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>2.4316</v>
+      </c>
+      <c r="Y49" s="3" t="n">
+        <v>2.3464</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>2.4727</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>2.5204</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>2.5366</v>
+      </c>
+      <c r="AC49" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD49" s="3" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="AE49" s="3" t="n">
+        <v>2.4689</v>
+      </c>
+      <c r="AF49" s="3" t="n">
+        <v>2.7767</v>
+      </c>
+      <c r="AG49" s="3" t="n">
+        <v>2.4427</v>
+      </c>
+      <c r="AH49" s="3" t="n">
+        <v>2.4252</v>
+      </c>
+      <c r="AI49" s="3" t="n">
+        <v>1.7069</v>
+      </c>
+      <c r="AJ49" s="3" t="n">
+        <v>2.6136</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AL49" s="3" t="n">
+        <v>2.3796</v>
+      </c>
+      <c r="AM49" s="3" t="n">
+        <v>2.5569</v>
+      </c>
+      <c r="AN49" s="3" t="n">
+        <v>3.422</v>
+      </c>
+      <c r="AO49" s="3" t="n">
+        <v>3.5237</v>
+      </c>
+      <c r="AP49" s="3" t="n">
+        <v>2.4299</v>
+      </c>
+      <c r="AQ49" s="3" t="n">
+        <v>2.2076</v>
+      </c>
+      <c r="AR49" s="3" t="n">
+        <v>2.5808</v>
+      </c>
+      <c r="AS49" s="3" t="n">
+        <v>2.0152</v>
+      </c>
+      <c r="AT49" s="3" t="n">
+        <v>2.0802</v>
+      </c>
+      <c r="AU49" s="3" t="n">
+        <v>2.3773</v>
+      </c>
+      <c r="AV49" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AW49" s="3" t="n">
+        <v>3.5877</v>
+      </c>
+      <c r="AX49" s="3" t="n">
+        <v>2.5165</v>
+      </c>
+      <c r="AY49" s="3" t="n">
+        <v>2.3613</v>
+      </c>
+      <c r="AZ49" s="3" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="BA49" s="3" t="n">
+        <v>2.1714</v>
+      </c>
+      <c r="BB49" s="3" t="n">
+        <v>2.0326</v>
+      </c>
+      <c r="BC49" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD49" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE49" s="3" t="n">
+        <v>2.5076</v>
+      </c>
+      <c r="BF49" s="3" t="n">
+        <v>2.0802</v>
+      </c>
+      <c r="BG49" s="3" t="n">
+        <v>2.3972</v>
+      </c>
+      <c r="BH49" s="3" t="n">
+        <v>2.5487</v>
+      </c>
+      <c r="BI49" s="3" t="n">
+        <v>3.5403</v>
+      </c>
+      <c r="BJ49" s="3" t="n">
+        <v>3.5967</v>
+      </c>
+      <c r="BK49" s="3" t="n">
+        <v>2.0586</v>
+      </c>
+      <c r="BL49" s="3" t="n">
+        <v>3.5967</v>
+      </c>
+      <c r="BM49" s="3" t="n">
+        <v>3.7167</v>
+      </c>
+      <c r="BN49" s="3" t="n">
+        <v>3.7167</v>
+      </c>
+      <c r="BO49" s="3" t="n">
+        <v>2.0302</v>
+      </c>
+      <c r="BP49" s="3" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="BQ49" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="BR49" s="3" t="n">
+        <v>1.6384</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>2.4455</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2.4028</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2.5064</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>2.4036</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>2.5457</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>2.5705</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>1.6637</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>2.0249</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>2.5087</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>3.7467</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>2.3363</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>2.7655</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>2.5773</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>2.3786</v>
+      </c>
+      <c r="U50" s="3" t="n">
+        <v>2.3965</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>2.5597</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>2.4316</v>
+      </c>
+      <c r="Y50" s="3" t="n">
+        <v>2.3464</v>
+      </c>
+      <c r="Z50" s="3" t="n">
+        <v>2.4727</v>
+      </c>
+      <c r="AA50" s="3" t="n">
+        <v>2.5204</v>
+      </c>
+      <c r="AB50" s="3" t="n">
+        <v>2.5366</v>
+      </c>
+      <c r="AC50" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD50" s="3" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="AE50" s="3" t="n">
+        <v>2.4689</v>
+      </c>
+      <c r="AF50" s="3" t="n">
+        <v>2.7767</v>
+      </c>
+      <c r="AG50" s="3" t="n">
+        <v>2.4427</v>
+      </c>
+      <c r="AH50" s="3" t="n">
+        <v>2.4252</v>
+      </c>
+      <c r="AI50" s="3" t="n">
+        <v>1.7069</v>
+      </c>
+      <c r="AJ50" s="3" t="n">
+        <v>2.6136</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AL50" s="3" t="n">
+        <v>2.3796</v>
+      </c>
+      <c r="AM50" s="3" t="n">
+        <v>2.5569</v>
+      </c>
+      <c r="AN50" s="3" t="n">
+        <v>3.422</v>
+      </c>
+      <c r="AO50" s="3" t="n">
+        <v>3.5237</v>
+      </c>
+      <c r="AP50" s="3" t="n">
+        <v>2.4299</v>
+      </c>
+      <c r="AQ50" s="3" t="n">
+        <v>2.2076</v>
+      </c>
+      <c r="AR50" s="3" t="n">
+        <v>2.5808</v>
+      </c>
+      <c r="AS50" s="3" t="n">
+        <v>2.0152</v>
+      </c>
+      <c r="AT50" s="3" t="n">
+        <v>2.0802</v>
+      </c>
+      <c r="AU50" s="3" t="n">
+        <v>2.3773</v>
+      </c>
+      <c r="AV50" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AW50" s="3" t="n">
+        <v>3.5877</v>
+      </c>
+      <c r="AX50" s="3" t="n">
+        <v>2.5165</v>
+      </c>
+      <c r="AY50" s="3" t="n">
+        <v>2.3613</v>
+      </c>
+      <c r="AZ50" s="3" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="BA50" s="3" t="n">
+        <v>2.1714</v>
+      </c>
+      <c r="BB50" s="3" t="n">
+        <v>2.0326</v>
+      </c>
+      <c r="BC50" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD50" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE50" s="3" t="n">
+        <v>2.5076</v>
+      </c>
+      <c r="BF50" s="3" t="n">
+        <v>2.0802</v>
+      </c>
+      <c r="BG50" s="3" t="n">
+        <v>2.3972</v>
+      </c>
+      <c r="BH50" s="3" t="n">
+        <v>2.5487</v>
+      </c>
+      <c r="BI50" s="3" t="n">
+        <v>3.5403</v>
+      </c>
+      <c r="BJ50" s="3" t="n">
+        <v>3.5967</v>
+      </c>
+      <c r="BK50" s="3" t="n">
+        <v>2.0586</v>
+      </c>
+      <c r="BL50" s="3" t="n">
+        <v>3.5967</v>
+      </c>
+      <c r="BM50" s="3" t="n">
+        <v>3.7167</v>
+      </c>
+      <c r="BN50" s="3" t="n">
+        <v>3.7167</v>
+      </c>
+      <c r="BO50" s="3" t="n">
+        <v>2.0302</v>
+      </c>
+      <c r="BP50" s="3" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="BQ50" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="BR50" s="3" t="n">
+        <v>1.6384</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2.4455</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2.4028</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2.5064</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>2.4036</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>2.5457</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>2.5705</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>1.6637</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>2.0249</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>2.5087</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>3.7467</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>2.3363</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>2.7655</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>2.5773</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>2.3786</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>2.3965</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>2.5597</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>2.4316</v>
+      </c>
+      <c r="Y51" s="3" t="n">
+        <v>2.3464</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>2.4727</v>
+      </c>
+      <c r="AA51" s="3" t="n">
+        <v>2.5204</v>
+      </c>
+      <c r="AB51" s="3" t="n">
+        <v>2.5366</v>
+      </c>
+      <c r="AC51" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD51" s="3" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="AE51" s="3" t="n">
+        <v>2.4689</v>
+      </c>
+      <c r="AF51" s="3" t="n">
+        <v>2.7767</v>
+      </c>
+      <c r="AG51" s="3" t="n">
+        <v>2.4427</v>
+      </c>
+      <c r="AH51" s="3" t="n">
+        <v>2.4252</v>
+      </c>
+      <c r="AI51" s="3" t="n">
+        <v>1.7069</v>
+      </c>
+      <c r="AJ51" s="3" t="n">
+        <v>2.6136</v>
+      </c>
+      <c r="AK51" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AL51" s="3" t="n">
+        <v>2.3796</v>
+      </c>
+      <c r="AM51" s="3" t="n">
+        <v>2.5569</v>
+      </c>
+      <c r="AN51" s="3" t="n">
+        <v>3.422</v>
+      </c>
+      <c r="AO51" s="3" t="n">
+        <v>3.5237</v>
+      </c>
+      <c r="AP51" s="3" t="n">
+        <v>2.4299</v>
+      </c>
+      <c r="AQ51" s="3" t="n">
+        <v>2.2076</v>
+      </c>
+      <c r="AR51" s="3" t="n">
+        <v>2.5808</v>
+      </c>
+      <c r="AS51" s="3" t="n">
+        <v>2.0152</v>
+      </c>
+      <c r="AT51" s="3" t="n">
+        <v>2.0802</v>
+      </c>
+      <c r="AU51" s="3" t="n">
+        <v>2.3773</v>
+      </c>
+      <c r="AV51" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AW51" s="3" t="n">
+        <v>3.5877</v>
+      </c>
+      <c r="AX51" s="3" t="n">
+        <v>2.5165</v>
+      </c>
+      <c r="AY51" s="3" t="n">
+        <v>2.3613</v>
+      </c>
+      <c r="AZ51" s="3" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="BA51" s="3" t="n">
+        <v>2.1714</v>
+      </c>
+      <c r="BB51" s="3" t="n">
+        <v>2.0326</v>
+      </c>
+      <c r="BC51" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD51" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE51" s="3" t="n">
+        <v>2.5076</v>
+      </c>
+      <c r="BF51" s="3" t="n">
+        <v>2.0802</v>
+      </c>
+      <c r="BG51" s="3" t="n">
+        <v>2.3972</v>
+      </c>
+      <c r="BH51" s="3" t="n">
+        <v>2.5487</v>
+      </c>
+      <c r="BI51" s="3" t="n">
+        <v>3.5403</v>
+      </c>
+      <c r="BJ51" s="3" t="n">
+        <v>3.5967</v>
+      </c>
+      <c r="BK51" s="3" t="n">
+        <v>2.0586</v>
+      </c>
+      <c r="BL51" s="3" t="n">
+        <v>3.5967</v>
+      </c>
+      <c r="BM51" s="3" t="n">
+        <v>3.7167</v>
+      </c>
+      <c r="BN51" s="3" t="n">
+        <v>3.7167</v>
+      </c>
+      <c r="BO51" s="3" t="n">
+        <v>2.0302</v>
+      </c>
+      <c r="BP51" s="3" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="BQ51" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="BR51" s="3" t="n">
+        <v>1.6384</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR47"/>
+  <autoFilter ref="A1:BR51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10943,208 +10943,208 @@
         <v>2.55</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2.4455</v>
+        <v>2.445</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2.4028</v>
+        <v>2.405</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2.5064</v>
+        <v>2.505</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>2.38</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2.4036</v>
+        <v>2.405</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>2.5457</v>
+        <v>2.545</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>2.5705</v>
+        <v>2.57</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>1.6637</v>
+        <v>1.69</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2.0249</v>
+        <v>2.025</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>2.5087</v>
+        <v>2.51</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>2.58</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>3.7467</v>
+        <v>3.615</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>2.3363</v>
+        <v>2.335</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>2.7655</v>
+        <v>2.765</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>2.5773</v>
+        <v>2.575</v>
       </c>
       <c r="S49" s="3" t="n">
         <v>2.65</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>2.3786</v>
+        <v>2.39</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>2.3965</v>
+        <v>2.5</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>2.5597</v>
+        <v>2.56</v>
       </c>
       <c r="W49" s="3" t="n">
         <v>2.005</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>2.4316</v>
+        <v>2.43</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>2.3464</v>
+        <v>2.345</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>2.4727</v>
+        <v>2.475</v>
       </c>
       <c r="AA49" s="3" t="n">
-        <v>2.5204</v>
+        <v>2.52</v>
       </c>
       <c r="AB49" s="3" t="n">
-        <v>2.5366</v>
+        <v>2.535</v>
       </c>
       <c r="AC49" s="3" t="n">
-        <v>2.45</v>
+        <v>2.425</v>
       </c>
       <c r="AD49" s="3" t="n">
-        <v>2.304</v>
+        <v>2.42</v>
       </c>
       <c r="AE49" s="3" t="n">
-        <v>2.4689</v>
+        <v>2.455</v>
       </c>
       <c r="AF49" s="3" t="n">
-        <v>2.7767</v>
+        <v>2.775</v>
       </c>
       <c r="AG49" s="3" t="n">
-        <v>2.4427</v>
+        <v>2.445</v>
       </c>
       <c r="AH49" s="3" t="n">
-        <v>2.4252</v>
+        <v>2.425</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>1.7069</v>
+        <v>1.69</v>
       </c>
       <c r="AJ49" s="3" t="n">
-        <v>2.6136</v>
+        <v>2.615</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>2.48</v>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>2.3796</v>
+        <v>2.38</v>
       </c>
       <c r="AM49" s="3" t="n">
-        <v>2.5569</v>
+        <v>2.56</v>
       </c>
       <c r="AN49" s="3" t="n">
-        <v>3.422</v>
+        <v>3.42</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>3.5237</v>
+        <v>3.525</v>
       </c>
       <c r="AP49" s="3" t="n">
-        <v>2.4299</v>
+        <v>2.43</v>
       </c>
       <c r="AQ49" s="3" t="n">
-        <v>2.2076</v>
+        <v>2.21</v>
       </c>
       <c r="AR49" s="3" t="n">
-        <v>2.5808</v>
+        <v>2.58</v>
       </c>
       <c r="AS49" s="3" t="n">
-        <v>2.0152</v>
+        <v>2.015</v>
       </c>
       <c r="AT49" s="3" t="n">
-        <v>2.0802</v>
+        <v>2.08</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>2.3773</v>
+        <v>2.375</v>
       </c>
       <c r="AV49" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.575</v>
       </c>
       <c r="AW49" s="3" t="n">
-        <v>3.5877</v>
+        <v>3.59</v>
       </c>
       <c r="AX49" s="3" t="n">
-        <v>2.5165</v>
+        <v>2.515</v>
       </c>
       <c r="AY49" s="3" t="n">
-        <v>2.3613</v>
+        <v>2.36</v>
       </c>
       <c r="AZ49" s="3" t="n">
-        <v>2.601</v>
+        <v>2.495</v>
       </c>
       <c r="BA49" s="3" t="n">
-        <v>2.1714</v>
+        <v>2.17</v>
       </c>
       <c r="BB49" s="3" t="n">
-        <v>2.0326</v>
+        <v>2.035</v>
       </c>
       <c r="BC49" s="3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="BD49" s="3" t="n">
-        <v>2.22</v>
+        <v>2.245</v>
       </c>
       <c r="BE49" s="3" t="n">
-        <v>2.5076</v>
+        <v>2.51</v>
       </c>
       <c r="BF49" s="3" t="n">
-        <v>2.0802</v>
+        <v>2.12</v>
       </c>
       <c r="BG49" s="3" t="n">
-        <v>2.3972</v>
+        <v>2.395</v>
       </c>
       <c r="BH49" s="3" t="n">
-        <v>2.5487</v>
+        <v>2.55</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>3.5403</v>
+        <v>3.54</v>
       </c>
       <c r="BJ49" s="3" t="n">
-        <v>3.5967</v>
+        <v>3.595</v>
       </c>
       <c r="BK49" s="3" t="n">
-        <v>2.0586</v>
+        <v>2.06</v>
       </c>
       <c r="BL49" s="3" t="n">
-        <v>3.5967</v>
+        <v>3.185</v>
       </c>
       <c r="BM49" s="3" t="n">
-        <v>3.7167</v>
+        <v>3.16</v>
       </c>
       <c r="BN49" s="3" t="n">
-        <v>3.7167</v>
+        <v>3.715</v>
       </c>
       <c r="BO49" s="3" t="n">
-        <v>2.0302</v>
+        <v>2.055</v>
       </c>
       <c r="BP49" s="3" t="n">
-        <v>2.125</v>
+        <v>2.12</v>
       </c>
       <c r="BQ49" s="3" t="n">
         <v>2.445</v>
       </c>
       <c r="BR49" s="3" t="n">
-        <v>1.6384</v>
+        <v>1.655</v>
       </c>
     </row>
     <row r="50">
@@ -11157,208 +11157,208 @@
         <v>2.55</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2.4455</v>
+        <v>2.445</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2.4028</v>
+        <v>2.405</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2.5064</v>
+        <v>2.505</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>2.38</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>2.4036</v>
+        <v>2.405</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>2.5457</v>
+        <v>2.545</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2.5705</v>
+        <v>2.57</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>1.6637</v>
+        <v>1.69</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>2.0249</v>
+        <v>2.025</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>2.5087</v>
+        <v>2.51</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>2.58</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>3.7467</v>
+        <v>3.615</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>2.3363</v>
+        <v>2.335</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>2.7655</v>
+        <v>2.765</v>
       </c>
       <c r="R50" s="3" t="n">
-        <v>2.5773</v>
+        <v>2.575</v>
       </c>
       <c r="S50" s="3" t="n">
         <v>2.65</v>
       </c>
       <c r="T50" s="3" t="n">
-        <v>2.3786</v>
+        <v>2.39</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>2.3965</v>
+        <v>2.5</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>2.5597</v>
+        <v>2.56</v>
       </c>
       <c r="W50" s="3" t="n">
         <v>2.005</v>
       </c>
       <c r="X50" s="3" t="n">
-        <v>2.4316</v>
+        <v>2.43</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>2.3464</v>
+        <v>2.345</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>2.4727</v>
+        <v>2.475</v>
       </c>
       <c r="AA50" s="3" t="n">
-        <v>2.5204</v>
+        <v>2.52</v>
       </c>
       <c r="AB50" s="3" t="n">
-        <v>2.5366</v>
+        <v>2.535</v>
       </c>
       <c r="AC50" s="3" t="n">
-        <v>2.45</v>
+        <v>2.425</v>
       </c>
       <c r="AD50" s="3" t="n">
-        <v>2.304</v>
+        <v>2.42</v>
       </c>
       <c r="AE50" s="3" t="n">
-        <v>2.4689</v>
+        <v>2.455</v>
       </c>
       <c r="AF50" s="3" t="n">
-        <v>2.7767</v>
+        <v>2.775</v>
       </c>
       <c r="AG50" s="3" t="n">
-        <v>2.4427</v>
+        <v>2.445</v>
       </c>
       <c r="AH50" s="3" t="n">
-        <v>2.4252</v>
+        <v>2.425</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>1.7069</v>
+        <v>1.69</v>
       </c>
       <c r="AJ50" s="3" t="n">
-        <v>2.6136</v>
+        <v>2.615</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>2.48</v>
       </c>
       <c r="AL50" s="3" t="n">
-        <v>2.3796</v>
+        <v>2.38</v>
       </c>
       <c r="AM50" s="3" t="n">
-        <v>2.5569</v>
+        <v>2.56</v>
       </c>
       <c r="AN50" s="3" t="n">
-        <v>3.422</v>
+        <v>3.42</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>3.5237</v>
+        <v>3.525</v>
       </c>
       <c r="AP50" s="3" t="n">
-        <v>2.4299</v>
+        <v>2.43</v>
       </c>
       <c r="AQ50" s="3" t="n">
-        <v>2.2076</v>
+        <v>2.21</v>
       </c>
       <c r="AR50" s="3" t="n">
-        <v>2.5808</v>
+        <v>2.58</v>
       </c>
       <c r="AS50" s="3" t="n">
-        <v>2.0152</v>
+        <v>2.015</v>
       </c>
       <c r="AT50" s="3" t="n">
-        <v>2.0802</v>
+        <v>2.08</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>2.3773</v>
+        <v>2.375</v>
       </c>
       <c r="AV50" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.575</v>
       </c>
       <c r="AW50" s="3" t="n">
-        <v>3.5877</v>
+        <v>3.59</v>
       </c>
       <c r="AX50" s="3" t="n">
-        <v>2.5165</v>
+        <v>2.515</v>
       </c>
       <c r="AY50" s="3" t="n">
-        <v>2.3613</v>
+        <v>2.36</v>
       </c>
       <c r="AZ50" s="3" t="n">
-        <v>2.601</v>
+        <v>2.495</v>
       </c>
       <c r="BA50" s="3" t="n">
-        <v>2.1714</v>
+        <v>2.17</v>
       </c>
       <c r="BB50" s="3" t="n">
-        <v>2.0326</v>
+        <v>2.035</v>
       </c>
       <c r="BC50" s="3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="BD50" s="3" t="n">
-        <v>2.22</v>
+        <v>2.245</v>
       </c>
       <c r="BE50" s="3" t="n">
-        <v>2.5076</v>
+        <v>2.51</v>
       </c>
       <c r="BF50" s="3" t="n">
-        <v>2.0802</v>
+        <v>2.12</v>
       </c>
       <c r="BG50" s="3" t="n">
-        <v>2.3972</v>
+        <v>2.395</v>
       </c>
       <c r="BH50" s="3" t="n">
-        <v>2.5487</v>
+        <v>2.55</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>3.5403</v>
+        <v>3.54</v>
       </c>
       <c r="BJ50" s="3" t="n">
-        <v>3.5967</v>
+        <v>3.595</v>
       </c>
       <c r="BK50" s="3" t="n">
-        <v>2.0586</v>
+        <v>2.06</v>
       </c>
       <c r="BL50" s="3" t="n">
-        <v>3.5967</v>
+        <v>3.185</v>
       </c>
       <c r="BM50" s="3" t="n">
-        <v>3.7167</v>
+        <v>3.16</v>
       </c>
       <c r="BN50" s="3" t="n">
-        <v>3.7167</v>
+        <v>3.715</v>
       </c>
       <c r="BO50" s="3" t="n">
-        <v>2.0302</v>
+        <v>2.055</v>
       </c>
       <c r="BP50" s="3" t="n">
-        <v>2.125</v>
+        <v>2.12</v>
       </c>
       <c r="BQ50" s="3" t="n">
         <v>2.445</v>
       </c>
       <c r="BR50" s="3" t="n">
-        <v>1.6384</v>
+        <v>1.655</v>
       </c>
     </row>
     <row r="51">
@@ -11371,212 +11371,426 @@
         <v>2.55</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2.4455</v>
+        <v>2.445</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2.4028</v>
+        <v>2.405</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2.5064</v>
+        <v>2.505</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>2.38</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>2.4036</v>
+        <v>2.405</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2.5457</v>
+        <v>2.545</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2.5705</v>
+        <v>2.57</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>1.6637</v>
+        <v>1.69</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>2.0249</v>
+        <v>2.025</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>2.5087</v>
+        <v>2.51</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>2.58</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.7467</v>
+        <v>3.615</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>2.3363</v>
+        <v>2.335</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.7655</v>
+        <v>2.765</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>2.5773</v>
+        <v>2.575</v>
       </c>
       <c r="S51" s="3" t="n">
         <v>2.65</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>2.3786</v>
+        <v>2.39</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>2.3965</v>
+        <v>2.5</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.5597</v>
+        <v>2.56</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>2.005</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.4316</v>
+        <v>2.43</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>2.3464</v>
+        <v>2.345</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>2.4727</v>
+        <v>2.475</v>
       </c>
       <c r="AA51" s="3" t="n">
-        <v>2.5204</v>
+        <v>2.52</v>
       </c>
       <c r="AB51" s="3" t="n">
-        <v>2.5366</v>
+        <v>2.535</v>
       </c>
       <c r="AC51" s="3" t="n">
-        <v>2.45</v>
+        <v>2.425</v>
       </c>
       <c r="AD51" s="3" t="n">
-        <v>2.304</v>
+        <v>2.42</v>
       </c>
       <c r="AE51" s="3" t="n">
-        <v>2.4689</v>
+        <v>2.455</v>
       </c>
       <c r="AF51" s="3" t="n">
-        <v>2.7767</v>
+        <v>2.775</v>
       </c>
       <c r="AG51" s="3" t="n">
-        <v>2.4427</v>
+        <v>2.445</v>
       </c>
       <c r="AH51" s="3" t="n">
-        <v>2.4252</v>
+        <v>2.425</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>1.7069</v>
+        <v>1.69</v>
       </c>
       <c r="AJ51" s="3" t="n">
-        <v>2.6136</v>
+        <v>2.615</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>2.48</v>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>2.3796</v>
+        <v>2.38</v>
       </c>
       <c r="AM51" s="3" t="n">
-        <v>2.5569</v>
+        <v>2.56</v>
       </c>
       <c r="AN51" s="3" t="n">
-        <v>3.422</v>
+        <v>3.42</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>3.5237</v>
+        <v>3.525</v>
       </c>
       <c r="AP51" s="3" t="n">
-        <v>2.4299</v>
+        <v>2.43</v>
       </c>
       <c r="AQ51" s="3" t="n">
-        <v>2.2076</v>
+        <v>2.21</v>
       </c>
       <c r="AR51" s="3" t="n">
-        <v>2.5808</v>
+        <v>2.58</v>
       </c>
       <c r="AS51" s="3" t="n">
-        <v>2.0152</v>
+        <v>2.015</v>
       </c>
       <c r="AT51" s="3" t="n">
-        <v>2.0802</v>
+        <v>2.08</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>2.3773</v>
+        <v>2.375</v>
       </c>
       <c r="AV51" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.575</v>
       </c>
       <c r="AW51" s="3" t="n">
-        <v>3.5877</v>
+        <v>3.59</v>
       </c>
       <c r="AX51" s="3" t="n">
-        <v>2.5165</v>
+        <v>2.515</v>
       </c>
       <c r="AY51" s="3" t="n">
-        <v>2.3613</v>
+        <v>2.36</v>
       </c>
       <c r="AZ51" s="3" t="n">
-        <v>2.601</v>
+        <v>2.495</v>
       </c>
       <c r="BA51" s="3" t="n">
-        <v>2.1714</v>
+        <v>2.17</v>
       </c>
       <c r="BB51" s="3" t="n">
-        <v>2.0326</v>
+        <v>2.035</v>
       </c>
       <c r="BC51" s="3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="BD51" s="3" t="n">
-        <v>2.22</v>
+        <v>2.245</v>
       </c>
       <c r="BE51" s="3" t="n">
-        <v>2.5076</v>
+        <v>2.51</v>
       </c>
       <c r="BF51" s="3" t="n">
-        <v>2.0802</v>
+        <v>2.12</v>
       </c>
       <c r="BG51" s="3" t="n">
-        <v>2.3972</v>
+        <v>2.395</v>
       </c>
       <c r="BH51" s="3" t="n">
-        <v>2.5487</v>
+        <v>2.55</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>3.5403</v>
+        <v>3.54</v>
       </c>
       <c r="BJ51" s="3" t="n">
-        <v>3.5967</v>
+        <v>3.595</v>
       </c>
       <c r="BK51" s="3" t="n">
-        <v>2.0586</v>
+        <v>2.06</v>
       </c>
       <c r="BL51" s="3" t="n">
-        <v>3.5967</v>
+        <v>3.185</v>
       </c>
       <c r="BM51" s="3" t="n">
-        <v>3.7167</v>
+        <v>3.16</v>
       </c>
       <c r="BN51" s="3" t="n">
-        <v>3.7167</v>
+        <v>3.715</v>
       </c>
       <c r="BO51" s="3" t="n">
-        <v>2.0302</v>
+        <v>2.055</v>
       </c>
       <c r="BP51" s="3" t="n">
-        <v>2.125</v>
+        <v>2.12</v>
       </c>
       <c r="BQ51" s="3" t="n">
         <v>2.445</v>
       </c>
       <c r="BR51" s="3" t="n">
-        <v>1.6384</v>
+        <v>1.655</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2.4893</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>2.4684</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2.5522</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>2.4895</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>2.5823</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>2.5534</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>1.9827</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>2.0053</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>2.6031</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>3.8124</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>2.4148</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>2.7901</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>2.553</v>
+      </c>
+      <c r="S52" s="3" t="n">
+        <v>2.5819</v>
+      </c>
+      <c r="T52" s="3" t="n">
+        <v>2.443</v>
+      </c>
+      <c r="U52" s="3" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>2.5504</v>
+      </c>
+      <c r="W52" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="X52" s="3" t="n">
+        <v>2.5011</v>
+      </c>
+      <c r="Y52" s="3" t="n">
+        <v>2.4185</v>
+      </c>
+      <c r="Z52" s="3" t="n">
+        <v>2.5466</v>
+      </c>
+      <c r="AA52" s="3" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="AB52" s="3" t="n">
+        <v>2.5337</v>
+      </c>
+      <c r="AC52" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD52" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE52" s="3" t="n">
+        <v>2.3711</v>
+      </c>
+      <c r="AF52" s="3" t="n">
+        <v>2.9887</v>
+      </c>
+      <c r="AG52" s="3" t="n">
+        <v>2.6338</v>
+      </c>
+      <c r="AH52" s="3" t="n">
+        <v>2.4647</v>
+      </c>
+      <c r="AI52" s="3" t="n">
+        <v>1.9736</v>
+      </c>
+      <c r="AJ52" s="3" t="n">
+        <v>2.6374</v>
+      </c>
+      <c r="AK52" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AL52" s="3" t="n">
+        <v>2.5656</v>
+      </c>
+      <c r="AM52" s="3" t="n">
+        <v>2.8015</v>
+      </c>
+      <c r="AN52" s="3" t="n">
+        <v>3.6631</v>
+      </c>
+      <c r="AO52" s="3" t="n">
+        <v>3.6259</v>
+      </c>
+      <c r="AP52" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AQ52" s="3" t="n">
+        <v>2.1791</v>
+      </c>
+      <c r="AR52" s="3" t="n">
+        <v>2.5928</v>
+      </c>
+      <c r="AS52" s="3" t="n">
+        <v>2.0216</v>
+      </c>
+      <c r="AT52" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="AU52" s="3" t="n">
+        <v>2.4275</v>
+      </c>
+      <c r="AV52" s="3" t="n">
+        <v>2.5507</v>
+      </c>
+      <c r="AW52" s="3" t="n">
+        <v>3.6144</v>
+      </c>
+      <c r="AX52" s="3" t="n">
+        <v>2.5357</v>
+      </c>
+      <c r="AY52" s="3" t="n">
+        <v>2.419</v>
+      </c>
+      <c r="AZ52" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BA52" s="3" t="n">
+        <v>2.1545</v>
+      </c>
+      <c r="BB52" s="3" t="n">
+        <v>1.9889</v>
+      </c>
+      <c r="BC52" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD52" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE52" s="3" t="n">
+        <v>2.5806</v>
+      </c>
+      <c r="BF52" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BG52" s="3" t="n">
+        <v>2.3925</v>
+      </c>
+      <c r="BH52" s="3" t="n">
+        <v>2.5779</v>
+      </c>
+      <c r="BI52" s="3" t="n">
+        <v>3.6471</v>
+      </c>
+      <c r="BJ52" s="3" t="n">
+        <v>3.6624</v>
+      </c>
+      <c r="BK52" s="3" t="n">
+        <v>2.0568</v>
+      </c>
+      <c r="BL52" s="3" t="n">
+        <v>3.6624</v>
+      </c>
+      <c r="BM52" s="3" t="n">
+        <v>3.7813</v>
+      </c>
+      <c r="BN52" s="3" t="n">
+        <v>3.7813</v>
+      </c>
+      <c r="BO52" s="3" t="n">
+        <v>2.0295</v>
+      </c>
+      <c r="BP52" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ52" s="3" t="n">
+        <v>2.5158</v>
+      </c>
+      <c r="BR52" s="3" t="n">
+        <v>1.956</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR51"/>
+  <autoFilter ref="A1:BR52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -11585,208 +11585,208 @@
         <v>2.55</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2.4893</v>
+        <v>2.49</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2.22</v>
+        <v>2.235</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>2.4684</v>
+        <v>2.47</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2.5522</v>
+        <v>2.55</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2.4895</v>
+        <v>2.49</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>2.484</v>
+        <v>2.485</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>2.5823</v>
+        <v>2.59</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>2.5534</v>
+        <v>2.555</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>1.9827</v>
+        <v>1.975</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>2.0053</v>
+        <v>2.005</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>2.6031</v>
+        <v>2.55</v>
       </c>
       <c r="N52" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R52" s="3" t="n">
         <v>2.555</v>
       </c>
-      <c r="O52" s="3" t="n">
-        <v>3.8124</v>
-      </c>
-      <c r="P52" s="3" t="n">
-        <v>2.4148</v>
-      </c>
-      <c r="Q52" s="3" t="n">
-        <v>2.7901</v>
-      </c>
-      <c r="R52" s="3" t="n">
-        <v>2.553</v>
-      </c>
       <c r="S52" s="3" t="n">
-        <v>2.5819</v>
+        <v>2.58</v>
       </c>
       <c r="T52" s="3" t="n">
-        <v>2.443</v>
+        <v>2.45</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>2.542</v>
+        <v>2.785</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>2.5504</v>
+        <v>2.55</v>
       </c>
       <c r="W52" s="3" t="n">
         <v>1.975</v>
       </c>
       <c r="X52" s="3" t="n">
-        <v>2.5011</v>
+        <v>2.5</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>2.4185</v>
+        <v>2.42</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>2.5466</v>
+        <v>2.545</v>
       </c>
       <c r="AA52" s="3" t="n">
-        <v>2.531</v>
+        <v>2.53</v>
       </c>
       <c r="AB52" s="3" t="n">
-        <v>2.5337</v>
+        <v>2.535</v>
       </c>
       <c r="AC52" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AD52" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE52" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF52" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG52" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AH52" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="AI52" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AJ52" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AK52" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="AD52" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE52" s="3" t="n">
-        <v>2.3711</v>
-      </c>
-      <c r="AF52" s="3" t="n">
-        <v>2.9887</v>
-      </c>
-      <c r="AG52" s="3" t="n">
-        <v>2.6338</v>
-      </c>
-      <c r="AH52" s="3" t="n">
-        <v>2.4647</v>
-      </c>
-      <c r="AI52" s="3" t="n">
-        <v>1.9736</v>
-      </c>
-      <c r="AJ52" s="3" t="n">
-        <v>2.6374</v>
-      </c>
-      <c r="AK52" s="3" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AL52" s="3" t="n">
-        <v>2.5656</v>
+        <v>2.565</v>
       </c>
       <c r="AM52" s="3" t="n">
-        <v>2.8015</v>
+        <v>2.8</v>
       </c>
       <c r="AN52" s="3" t="n">
-        <v>3.6631</v>
+        <v>3.665</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>3.6259</v>
+        <v>3.625</v>
       </c>
       <c r="AP52" s="3" t="n">
         <v>2.505</v>
       </c>
       <c r="AQ52" s="3" t="n">
-        <v>2.1791</v>
+        <v>2.18</v>
       </c>
       <c r="AR52" s="3" t="n">
-        <v>2.5928</v>
+        <v>2.595</v>
       </c>
       <c r="AS52" s="3" t="n">
-        <v>2.0216</v>
+        <v>2.02</v>
       </c>
       <c r="AT52" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.08</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.43</v>
       </c>
       <c r="AV52" s="3" t="n">
-        <v>2.5507</v>
+        <v>2.545</v>
       </c>
       <c r="AW52" s="3" t="n">
-        <v>3.6144</v>
+        <v>3.615</v>
       </c>
       <c r="AX52" s="3" t="n">
-        <v>2.5357</v>
+        <v>2.535</v>
       </c>
       <c r="AY52" s="3" t="n">
-        <v>2.419</v>
+        <v>2.42</v>
       </c>
       <c r="AZ52" s="3" t="n">
-        <v>2.53</v>
+        <v>2.485</v>
       </c>
       <c r="BA52" s="3" t="n">
-        <v>2.1545</v>
+        <v>2.155</v>
       </c>
       <c r="BB52" s="3" t="n">
-        <v>1.9889</v>
+        <v>1.99</v>
       </c>
       <c r="BC52" s="3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BD52" s="3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BE52" s="3" t="n">
-        <v>2.5806</v>
+        <v>2.585</v>
       </c>
       <c r="BF52" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.09</v>
       </c>
       <c r="BG52" s="3" t="n">
-        <v>2.3925</v>
+        <v>2.395</v>
       </c>
       <c r="BH52" s="3" t="n">
-        <v>2.5779</v>
+        <v>2.58</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>3.6471</v>
+        <v>3.645</v>
       </c>
       <c r="BJ52" s="3" t="n">
-        <v>3.6624</v>
+        <v>3.66</v>
       </c>
       <c r="BK52" s="3" t="n">
-        <v>2.0568</v>
+        <v>2.055</v>
       </c>
       <c r="BL52" s="3" t="n">
-        <v>3.6624</v>
+        <v>3.025</v>
       </c>
       <c r="BM52" s="3" t="n">
-        <v>3.7813</v>
+        <v>3.3</v>
       </c>
       <c r="BN52" s="3" t="n">
-        <v>3.7813</v>
+        <v>3.785</v>
       </c>
       <c r="BO52" s="3" t="n">
-        <v>2.0295</v>
+        <v>2.055</v>
       </c>
       <c r="BP52" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.1</v>
       </c>
       <c r="BQ52" s="3" t="n">
-        <v>2.5158</v>
+        <v>2.515</v>
       </c>
       <c r="BR52" s="3" t="n">
-        <v>1.956</v>
+        <v>1.96</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR52"/>
+  <dimension ref="A1:BR62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11789,8 +11789,2148 @@
         <v>1.96</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S53" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="Y53" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA53" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC53" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD53" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE53" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF53" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG53" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH53" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AI53" s="3" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="AJ53" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AL53" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AM53" s="3" t="n">
+        <v>3.015</v>
+      </c>
+      <c r="AN53" s="3" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AO53" s="3" t="n">
+        <v>3.575</v>
+      </c>
+      <c r="AP53" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AQ53" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR53" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AS53" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT53" s="3" t="n">
+        <v>2.095</v>
+      </c>
+      <c r="AU53" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="AV53" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW53" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AX53" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AY53" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AZ53" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="BA53" s="3" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="BB53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC53" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BD53" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="BE53" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BF53" s="3" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="BG53" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH53" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI53" s="3" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BJ53" s="3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BK53" s="3" t="n">
+        <v>2.065</v>
+      </c>
+      <c r="BL53" s="3" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="BM53" s="3" t="n">
+        <v>3.435</v>
+      </c>
+      <c r="BN53" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="BO53" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BP53" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BQ53" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="BR53" s="3" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2.5465</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2.5327</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2.4928</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2.5367</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>2.5685</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>2.5238</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>2.5911</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>2.5739</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>2.4076</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>1.9983</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>2.6365</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>2.5725</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>2.5649</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>2.9432</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>2.5237</v>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>2.6148</v>
+      </c>
+      <c r="T54" s="3" t="n">
+        <v>2.5507</v>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>2.5843</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>2.5763</v>
+      </c>
+      <c r="W54" s="3" t="n">
+        <v>2.0287</v>
+      </c>
+      <c r="X54" s="3" t="n">
+        <v>2.5297</v>
+      </c>
+      <c r="Y54" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Z54" s="3" t="n">
+        <v>2.5537</v>
+      </c>
+      <c r="AA54" s="3" t="n">
+        <v>2.5534</v>
+      </c>
+      <c r="AB54" s="3" t="n">
+        <v>2.5553</v>
+      </c>
+      <c r="AC54" s="3" t="n">
+        <v>2.6589</v>
+      </c>
+      <c r="AD54" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE54" s="3" t="n">
+        <v>2.4481</v>
+      </c>
+      <c r="AF54" s="3" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="AG54" s="3" t="n">
+        <v>2.6497</v>
+      </c>
+      <c r="AH54" s="3" t="n">
+        <v>2.5057</v>
+      </c>
+      <c r="AI54" s="3" t="n">
+        <v>2.4215</v>
+      </c>
+      <c r="AJ54" s="3" t="n">
+        <v>2.6382</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>2.5446</v>
+      </c>
+      <c r="AL54" s="3" t="n">
+        <v>2.6479</v>
+      </c>
+      <c r="AM54" s="3" t="n">
+        <v>3.1378</v>
+      </c>
+      <c r="AN54" s="3" t="n">
+        <v>3.9719</v>
+      </c>
+      <c r="AO54" s="3" t="n">
+        <v>3.6248</v>
+      </c>
+      <c r="AP54" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ54" s="3" t="n">
+        <v>2.1761</v>
+      </c>
+      <c r="AR54" s="3" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="AS54" s="3" t="n">
+        <v>2.0017</v>
+      </c>
+      <c r="AT54" s="3" t="n">
+        <v>2.0822</v>
+      </c>
+      <c r="AU54" s="3" t="n">
+        <v>2.4887</v>
+      </c>
+      <c r="AV54" s="3" t="n">
+        <v>2.5853</v>
+      </c>
+      <c r="AW54" s="3" t="n">
+        <v>3.6554</v>
+      </c>
+      <c r="AX54" s="3" t="n">
+        <v>2.5586</v>
+      </c>
+      <c r="AY54" s="3" t="n">
+        <v>2.4923</v>
+      </c>
+      <c r="AZ54" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA54" s="3" t="n">
+        <v>2.0816</v>
+      </c>
+      <c r="BB54" s="3" t="n">
+        <v>2.0068</v>
+      </c>
+      <c r="BC54" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD54" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE54" s="3" t="n">
+        <v>2.564</v>
+      </c>
+      <c r="BF54" s="3" t="n">
+        <v>2.0822</v>
+      </c>
+      <c r="BG54" s="3" t="n">
+        <v>2.4498</v>
+      </c>
+      <c r="BH54" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI54" s="3" t="n">
+        <v>3.5955</v>
+      </c>
+      <c r="BJ54" s="3" t="n">
+        <v>3.638</v>
+      </c>
+      <c r="BK54" s="3" t="n">
+        <v>2.0553</v>
+      </c>
+      <c r="BL54" s="3" t="n">
+        <v>3.638</v>
+      </c>
+      <c r="BM54" s="3" t="n">
+        <v>3.7092</v>
+      </c>
+      <c r="BN54" s="3" t="n">
+        <v>3.7092</v>
+      </c>
+      <c r="BO54" s="3" t="n">
+        <v>2.0322</v>
+      </c>
+      <c r="BP54" s="3" t="n">
+        <v>2.0538</v>
+      </c>
+      <c r="BQ54" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BR54" s="3" t="n">
+        <v>2.4173</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W55" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X55" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y55" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z55" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA55" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB55" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC55" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD55" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE55" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF55" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG55" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH55" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI55" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ55" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK55" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL55" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM55" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN55" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO55" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP55" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ55" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR55" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS55" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT55" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU55" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV55" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW55" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX55" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY55" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ55" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA55" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB55" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC55" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD55" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE55" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF55" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG55" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH55" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI55" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ55" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK55" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL55" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM55" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN55" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO55" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP55" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ55" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR55" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y56" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z56" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA56" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB56" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC56" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD56" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE56" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF56" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG56" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH56" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI56" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ56" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL56" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM56" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN56" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO56" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP56" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ56" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR56" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS56" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT56" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU56" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV56" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW56" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX56" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY56" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ56" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA56" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB56" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC56" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD56" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE56" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF56" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG56" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH56" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI56" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ56" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK56" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL56" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM56" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN56" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO56" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP56" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ56" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR56" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S57" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T57" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V57" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W57" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X57" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y57" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z57" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA57" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB57" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC57" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD57" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE57" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF57" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG57" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH57" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI57" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ57" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK57" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL57" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM57" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN57" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO57" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP57" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ57" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR57" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS57" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT57" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU57" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV57" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW57" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX57" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY57" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ57" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA57" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB57" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC57" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD57" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE57" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF57" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG57" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH57" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI57" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ57" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK57" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL57" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM57" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN57" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO57" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP57" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ57" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR57" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q58" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S58" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T58" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U58" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W58" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X58" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y58" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z58" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA58" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC58" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD58" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE58" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF58" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG58" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH58" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI58" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ58" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL58" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM58" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN58" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO58" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP58" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ58" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR58" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS58" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT58" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU58" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV58" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW58" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX58" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY58" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ58" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA58" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB58" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC58" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD58" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE58" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF58" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG58" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH58" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI58" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ58" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK58" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL58" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM58" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN58" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO58" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP58" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ58" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR58" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S59" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T59" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V59" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W59" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X59" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y59" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z59" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA59" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB59" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC59" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD59" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE59" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF59" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG59" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH59" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI59" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ59" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL59" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM59" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN59" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO59" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP59" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ59" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR59" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS59" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT59" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU59" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV59" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW59" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX59" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY59" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ59" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA59" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB59" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC59" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD59" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE59" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF59" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG59" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH59" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI59" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ59" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK59" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL59" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM59" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN59" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO59" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP59" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ59" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR59" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q60" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S60" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T60" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W60" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X60" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y60" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z60" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA60" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC60" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD60" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE60" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF60" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG60" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH60" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI60" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ60" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK60" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL60" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM60" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN60" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO60" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP60" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ60" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR60" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS60" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT60" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU60" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV60" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW60" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX60" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY60" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ60" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA60" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB60" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC60" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD60" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE60" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF60" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG60" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH60" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI60" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ60" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK60" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL60" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM60" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN60" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO60" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP60" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ60" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR60" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y61" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z61" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA61" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC61" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD61" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE61" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF61" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG61" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH61" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI61" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ61" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK61" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL61" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM61" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN61" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO61" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP61" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ61" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR61" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS61" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT61" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU61" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV61" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW61" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX61" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY61" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ61" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA61" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB61" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC61" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD61" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE61" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF61" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG61" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH61" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI61" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ61" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK61" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL61" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM61" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN61" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO61" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP61" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ61" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR61" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>2.5455</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="S62" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W62" s="3" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="X62" s="3" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="Y62" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AA62" s="3" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="AC62" s="3" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="AD62" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE62" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF62" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG62" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH62" s="3" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="AI62" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="AJ62" s="3" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="AK62" s="3" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AL62" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM62" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="AN62" s="3" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="AO62" s="3" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="AP62" s="3" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="AQ62" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="AR62" s="3" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="AS62" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT62" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU62" s="3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AV62" s="3" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="AW62" s="3" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="AX62" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AY62" s="3" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AZ62" s="3" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="BA62" s="3" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="BB62" s="3" t="n">
+        <v>1.9535</v>
+      </c>
+      <c r="BC62" s="3" t="n">
+        <v>2.472</v>
+      </c>
+      <c r="BD62" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE62" s="3" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="BF62" s="3" t="n">
+        <v>2.0972</v>
+      </c>
+      <c r="BG62" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH62" s="3" t="n">
+        <v>2.7675</v>
+      </c>
+      <c r="BI62" s="3" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="BJ62" s="3" t="n">
+        <v>3.727</v>
+      </c>
+      <c r="BK62" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BL62" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BM62" s="3" t="n">
+        <v>2.9005</v>
+      </c>
+      <c r="BN62" s="3" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="BO62" s="3" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="BP62" s="3" t="n">
+        <v>2.5105</v>
+      </c>
+      <c r="BQ62" s="3" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="BR62" s="3" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BR52"/>
+  <autoFilter ref="A1:BR62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -12010,211 +12010,211 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2.5465</v>
+        <v>2.545</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2.5327</v>
+        <v>2.535</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2.15</v>
+        <v>2.175</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2.4928</v>
+        <v>2.495</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2.5367</v>
+        <v>2.535</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2.5685</v>
+        <v>2.57</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>2.5238</v>
+        <v>2.525</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2.5911</v>
+        <v>2.59</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2.5739</v>
+        <v>2.575</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2.4076</v>
+        <v>2.415</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>1.9983</v>
+        <v>2</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>2.6365</v>
+        <v>2.6</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>2.5725</v>
+        <v>2.58</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>3.788</v>
+        <v>3.755</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>2.5649</v>
+        <v>2.565</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>2.9432</v>
+        <v>2.945</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>2.5237</v>
+        <v>2.525</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>2.6148</v>
+        <v>2.615</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>2.5507</v>
+        <v>2.55</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>2.5843</v>
+        <v>3.075</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>2.5763</v>
+        <v>2.575</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>2.0287</v>
+        <v>2.03</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>2.5297</v>
+        <v>2.53</v>
       </c>
       <c r="Y54" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="Z54" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AA54" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AB54" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AC54" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD54" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AE54" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF54" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG54" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH54" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AI54" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AJ54" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL54" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AM54" s="3" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="AN54" s="3" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AO54" s="3" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AP54" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AQ54" s="3" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="AR54" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT54" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU54" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="Z54" s="3" t="n">
-        <v>2.5537</v>
-      </c>
-      <c r="AA54" s="3" t="n">
-        <v>2.5534</v>
-      </c>
-      <c r="AB54" s="3" t="n">
-        <v>2.5553</v>
-      </c>
-      <c r="AC54" s="3" t="n">
-        <v>2.6589</v>
-      </c>
-      <c r="AD54" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE54" s="3" t="n">
-        <v>2.4481</v>
-      </c>
-      <c r="AF54" s="3" t="n">
-        <v>3.158</v>
-      </c>
-      <c r="AG54" s="3" t="n">
-        <v>2.6497</v>
-      </c>
-      <c r="AH54" s="3" t="n">
-        <v>2.5057</v>
-      </c>
-      <c r="AI54" s="3" t="n">
-        <v>2.4215</v>
-      </c>
-      <c r="AJ54" s="3" t="n">
-        <v>2.6382</v>
-      </c>
-      <c r="AK54" s="3" t="n">
-        <v>2.5446</v>
-      </c>
-      <c r="AL54" s="3" t="n">
-        <v>2.6479</v>
-      </c>
-      <c r="AM54" s="3" t="n">
-        <v>3.1378</v>
-      </c>
-      <c r="AN54" s="3" t="n">
-        <v>3.9719</v>
-      </c>
-      <c r="AO54" s="3" t="n">
-        <v>3.6248</v>
-      </c>
-      <c r="AP54" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ54" s="3" t="n">
-        <v>2.1761</v>
-      </c>
-      <c r="AR54" s="3" t="n">
-        <v>2.591</v>
-      </c>
-      <c r="AS54" s="3" t="n">
-        <v>2.0017</v>
-      </c>
-      <c r="AT54" s="3" t="n">
-        <v>2.0822</v>
-      </c>
-      <c r="AU54" s="3" t="n">
-        <v>2.4887</v>
-      </c>
       <c r="AV54" s="3" t="n">
-        <v>2.5853</v>
+        <v>2.585</v>
       </c>
       <c r="AW54" s="3" t="n">
-        <v>3.6554</v>
+        <v>3.655</v>
       </c>
       <c r="AX54" s="3" t="n">
-        <v>2.5586</v>
+        <v>2.56</v>
       </c>
       <c r="AY54" s="3" t="n">
-        <v>2.4923</v>
+        <v>2.49</v>
       </c>
       <c r="AZ54" s="3" t="n">
-        <v>2.641</v>
+        <v>2.555</v>
       </c>
       <c r="BA54" s="3" t="n">
-        <v>2.0816</v>
+        <v>2.08</v>
       </c>
       <c r="BB54" s="3" t="n">
-        <v>2.0068</v>
+        <v>2.005</v>
       </c>
       <c r="BC54" s="3" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="BD54" s="3" t="n">
-        <v>2.15</v>
+        <v>2.205</v>
       </c>
       <c r="BE54" s="3" t="n">
-        <v>2.564</v>
+        <v>2.565</v>
       </c>
       <c r="BF54" s="3" t="n">
-        <v>2.0822</v>
+        <v>2.11</v>
       </c>
       <c r="BG54" s="3" t="n">
-        <v>2.4498</v>
+        <v>2.45</v>
       </c>
       <c r="BH54" s="3" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>3.5955</v>
+        <v>3.595</v>
       </c>
       <c r="BJ54" s="3" t="n">
-        <v>3.638</v>
+        <v>3.64</v>
       </c>
       <c r="BK54" s="3" t="n">
-        <v>2.0553</v>
+        <v>2.055</v>
       </c>
       <c r="BL54" s="3" t="n">
-        <v>3.638</v>
+        <v>3.2</v>
       </c>
       <c r="BM54" s="3" t="n">
-        <v>3.7092</v>
+        <v>2.965</v>
       </c>
       <c r="BN54" s="3" t="n">
-        <v>3.7092</v>
+        <v>3.71</v>
       </c>
       <c r="BO54" s="3" t="n">
-        <v>2.0322</v>
+        <v>2.055</v>
       </c>
       <c r="BP54" s="3" t="n">
-        <v>2.0538</v>
+        <v>2.055</v>
       </c>
       <c r="BQ54" s="3" t="n">
         <v>2.55</v>
       </c>
       <c r="BR54" s="3" t="n">
-        <v>2.4173</v>
+        <v>2.405</v>
       </c>
     </row>
     <row r="55">
@@ -12224,211 +12224,211 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2.619</v>
+        <v>2.595</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2.5455</v>
+        <v>2.49</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>2.577</v>
+        <v>2.475</v>
       </c>
       <c r="F55" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="N55" s="3" t="n">
         <v>2.58</v>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>2.689</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>2.639</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M55" s="3" t="n">
-        <v>2.574</v>
-      </c>
-      <c r="N55" s="3" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O55" s="3" t="n">
-        <v>3.846</v>
+        <v>3.705</v>
       </c>
       <c r="P55" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="W55" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X55" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y55" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="Z55" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AA55" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="Q55" s="3" t="n">
-        <v>2.882</v>
-      </c>
-      <c r="R55" s="3" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="S55" s="3" t="n">
+      <c r="AB55" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC55" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD55" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AE55" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AF55" s="3" t="n">
+        <v>3.185</v>
+      </c>
+      <c r="AG55" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AH55" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI55" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AJ55" s="3" t="n">
         <v>2.625</v>
       </c>
-      <c r="T55" s="3" t="n">
-        <v>2.577</v>
-      </c>
-      <c r="U55" s="3" t="n">
-        <v>3.119</v>
-      </c>
-      <c r="V55" s="3" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="W55" s="3" t="n">
-        <v>1.9885</v>
-      </c>
-      <c r="X55" s="3" t="n">
-        <v>2.539</v>
-      </c>
-      <c r="Y55" s="3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Z55" s="3" t="n">
-        <v>2.607</v>
-      </c>
-      <c r="AA55" s="3" t="n">
-        <v>2.689</v>
-      </c>
-      <c r="AB55" s="3" t="n">
-        <v>2.694</v>
-      </c>
-      <c r="AC55" s="3" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="AD55" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE55" s="3" t="n">
+      <c r="AK55" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="AL55" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AM55" s="3" t="n">
+        <v>3.205</v>
+      </c>
+      <c r="AN55" s="3" t="n">
+        <v>3.975</v>
+      </c>
+      <c r="AO55" s="3" t="n">
+        <v>3.545</v>
+      </c>
+      <c r="AP55" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AQ55" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AR55" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="AS55" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT55" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AU55" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AV55" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AW55" s="3" t="n">
+        <v>3.545</v>
+      </c>
+      <c r="AX55" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="AY55" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AZ55" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="BA55" s="3" t="n">
+        <v>2.035</v>
+      </c>
+      <c r="BB55" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BC55" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD55" s="3" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="BE55" s="3" t="n">
         <v>2.53</v>
       </c>
-      <c r="AF55" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG55" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH55" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="AI55" s="3" t="n">
-        <v>1.9055</v>
-      </c>
-      <c r="AJ55" s="3" t="n">
-        <v>2.687</v>
-      </c>
-      <c r="AK55" s="3" t="n">
-        <v>2.653</v>
-      </c>
-      <c r="AL55" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AM55" s="3" t="n">
-        <v>3.249</v>
-      </c>
-      <c r="AN55" s="3" t="n">
-        <v>3.999</v>
-      </c>
-      <c r="AO55" s="3" t="n">
-        <v>3.654</v>
-      </c>
-      <c r="AP55" s="3" t="n">
-        <v>2.479</v>
-      </c>
-      <c r="AQ55" s="3" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="AR55" s="3" t="n">
-        <v>2.669</v>
-      </c>
-      <c r="AS55" s="3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT55" s="3" t="n">
+      <c r="BF55" s="3" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="BG55" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH55" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI55" s="3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BJ55" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="BK55" s="3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL55" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="BM55" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BN55" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BO55" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BP55" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BQ55" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="BR55" s="3" t="n">
         <v>2.32</v>
-      </c>
-      <c r="AU55" s="3" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="AV55" s="3" t="n">
-        <v>2.682</v>
-      </c>
-      <c r="AW55" s="3" t="n">
-        <v>3.627</v>
-      </c>
-      <c r="AX55" s="3" t="n">
-        <v>2.597</v>
-      </c>
-      <c r="AY55" s="3" t="n">
-        <v>2.444</v>
-      </c>
-      <c r="AZ55" s="3" t="n">
-        <v>2.641</v>
-      </c>
-      <c r="BA55" s="3" t="n">
-        <v>2.458</v>
-      </c>
-      <c r="BB55" s="3" t="n">
-        <v>1.9535</v>
-      </c>
-      <c r="BC55" s="3" t="n">
-        <v>2.472</v>
-      </c>
-      <c r="BD55" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BE55" s="3" t="n">
-        <v>2.627</v>
-      </c>
-      <c r="BF55" s="3" t="n">
-        <v>2.0972</v>
-      </c>
-      <c r="BG55" s="3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BH55" s="3" t="n">
-        <v>2.7675</v>
-      </c>
-      <c r="BI55" s="3" t="n">
-        <v>3.702</v>
-      </c>
-      <c r="BJ55" s="3" t="n">
-        <v>3.727</v>
-      </c>
-      <c r="BK55" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BL55" s="3" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="BM55" s="3" t="n">
-        <v>2.9005</v>
-      </c>
-      <c r="BN55" s="3" t="n">
-        <v>3.769</v>
-      </c>
-      <c r="BO55" s="3" t="n">
-        <v>2.258</v>
-      </c>
-      <c r="BP55" s="3" t="n">
-        <v>2.5105</v>
-      </c>
-      <c r="BQ55" s="3" t="n">
-        <v>2.594</v>
-      </c>
-      <c r="BR55" s="3" t="n">
-        <v>2.19</v>
       </c>
     </row>
     <row r="56">

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -12866,211 +12866,211 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>2.619</v>
+        <v>2.59</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>2.5455</v>
+        <v>2.535</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>2.42</v>
+        <v>2.005</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>2.577</v>
+        <v>2.47</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>2.58</v>
+        <v>2.585</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>2.49</v>
+        <v>2.495</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>2.689</v>
+        <v>2.645</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>2.639</v>
+        <v>2.605</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>2.23</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>2.04</v>
+        <v>1.775</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>2.574</v>
+        <v>2.545</v>
       </c>
       <c r="N58" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="Q58" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="S58" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="T58" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="U58" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="W58" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X58" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y58" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="Z58" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AA58" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC58" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="AD58" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AE58" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AF58" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AG58" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="AH58" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AI58" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="AJ58" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AL58" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AM58" s="3" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="AN58" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AO58" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="AP58" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AQ58" s="3" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="AR58" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AS58" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT58" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AU58" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AV58" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="O58" s="3" t="n">
-        <v>3.846</v>
-      </c>
-      <c r="P58" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q58" s="3" t="n">
-        <v>2.882</v>
-      </c>
-      <c r="R58" s="3" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="S58" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="T58" s="3" t="n">
-        <v>2.577</v>
-      </c>
-      <c r="U58" s="3" t="n">
-        <v>3.119</v>
-      </c>
-      <c r="V58" s="3" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="W58" s="3" t="n">
-        <v>1.9885</v>
-      </c>
-      <c r="X58" s="3" t="n">
-        <v>2.539</v>
-      </c>
-      <c r="Y58" s="3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Z58" s="3" t="n">
-        <v>2.607</v>
-      </c>
-      <c r="AA58" s="3" t="n">
-        <v>2.689</v>
-      </c>
-      <c r="AB58" s="3" t="n">
-        <v>2.694</v>
-      </c>
-      <c r="AC58" s="3" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="AD58" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE58" s="3" t="n">
+      <c r="AW58" s="3" t="n">
+        <v>3.605</v>
+      </c>
+      <c r="AX58" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AY58" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="AZ58" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BA58" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB58" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BC58" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD58" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE58" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="BF58" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG58" s="3" t="n">
         <v>2.53</v>
       </c>
-      <c r="AF58" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG58" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH58" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="AI58" s="3" t="n">
-        <v>1.9055</v>
-      </c>
-      <c r="AJ58" s="3" t="n">
-        <v>2.687</v>
-      </c>
-      <c r="AK58" s="3" t="n">
-        <v>2.653</v>
-      </c>
-      <c r="AL58" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AM58" s="3" t="n">
-        <v>3.249</v>
-      </c>
-      <c r="AN58" s="3" t="n">
-        <v>3.999</v>
-      </c>
-      <c r="AO58" s="3" t="n">
-        <v>3.654</v>
-      </c>
-      <c r="AP58" s="3" t="n">
-        <v>2.479</v>
-      </c>
-      <c r="AQ58" s="3" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="AR58" s="3" t="n">
-        <v>2.669</v>
-      </c>
-      <c r="AS58" s="3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT58" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU58" s="3" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="AV58" s="3" t="n">
-        <v>2.682</v>
-      </c>
-      <c r="AW58" s="3" t="n">
-        <v>3.627</v>
-      </c>
-      <c r="AX58" s="3" t="n">
-        <v>2.597</v>
-      </c>
-      <c r="AY58" s="3" t="n">
-        <v>2.444</v>
-      </c>
-      <c r="AZ58" s="3" t="n">
-        <v>2.641</v>
-      </c>
-      <c r="BA58" s="3" t="n">
-        <v>2.458</v>
-      </c>
-      <c r="BB58" s="3" t="n">
-        <v>1.9535</v>
-      </c>
-      <c r="BC58" s="3" t="n">
-        <v>2.472</v>
-      </c>
-      <c r="BD58" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BE58" s="3" t="n">
-        <v>2.627</v>
-      </c>
-      <c r="BF58" s="3" t="n">
-        <v>2.0972</v>
-      </c>
-      <c r="BG58" s="3" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BH58" s="3" t="n">
-        <v>2.7675</v>
+        <v>2.53</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>3.702</v>
+        <v>3.63</v>
       </c>
       <c r="BJ58" s="3" t="n">
-        <v>3.727</v>
+        <v>3.63</v>
       </c>
       <c r="BK58" s="3" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="BL58" s="3" t="n">
-        <v>3.74</v>
+        <v>3.07</v>
       </c>
       <c r="BM58" s="3" t="n">
-        <v>2.9005</v>
+        <v>3.055</v>
       </c>
       <c r="BN58" s="3" t="n">
-        <v>3.769</v>
+        <v>3.7</v>
       </c>
       <c r="BO58" s="3" t="n">
-        <v>2.258</v>
+        <v>1.88</v>
       </c>
       <c r="BP58" s="3" t="n">
-        <v>2.5105</v>
+        <v>2</v>
       </c>
       <c r="BQ58" s="3" t="n">
-        <v>2.594</v>
+        <v>2.555</v>
       </c>
       <c r="BR58" s="3" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="59">
@@ -13080,211 +13080,211 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>2.619</v>
+        <v>2.5</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>2.5455</v>
+        <v>2.455</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2.42</v>
+        <v>2.315</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>2.577</v>
+        <v>2.395</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>2.58</v>
+        <v>2.385</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>2.49</v>
+        <v>2.455</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>2.689</v>
+        <v>2.56</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>2.639</v>
+        <v>2.575</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>2.23</v>
+        <v>1.965</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>2.04</v>
+        <v>1.995</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>2.574</v>
+        <v>2.5</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>3.846</v>
+        <v>3.835</v>
       </c>
       <c r="P59" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="R59" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="Q59" s="3" t="n">
-        <v>2.882</v>
-      </c>
-      <c r="R59" s="3" t="n">
-        <v>2.545</v>
-      </c>
       <c r="S59" s="3" t="n">
-        <v>2.625</v>
+        <v>2.575</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>2.577</v>
+        <v>2.47</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>3.119</v>
+        <v>3.115</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>1.9885</v>
+        <v>2</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>2.539</v>
+        <v>2.455</v>
       </c>
       <c r="Y59" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="Z59" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AA59" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AB59" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AC59" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AD59" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AE59" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AF59" s="3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AG59" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AH59" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="AI59" s="3" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="AJ59" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AL59" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="AM59" s="3" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="AN59" s="3" t="n">
+        <v>4.225</v>
+      </c>
+      <c r="AO59" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AP59" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AQ59" s="3" t="n">
+        <v>2.145</v>
+      </c>
+      <c r="AR59" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AS59" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT59" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="AU59" s="3" t="n">
         <v>2.43</v>
       </c>
-      <c r="Z59" s="3" t="n">
-        <v>2.607</v>
-      </c>
-      <c r="AA59" s="3" t="n">
-        <v>2.689</v>
-      </c>
-      <c r="AB59" s="3" t="n">
-        <v>2.694</v>
-      </c>
-      <c r="AC59" s="3" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="AD59" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE59" s="3" t="n">
+      <c r="AV59" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AW59" s="3" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="AX59" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AY59" s="3" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="AZ59" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BA59" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB59" s="3" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="BC59" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD59" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE59" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="BF59" s="3" t="n">
+        <v>2.095</v>
+      </c>
+      <c r="BG59" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BH59" s="3" t="n">
         <v>2.53</v>
       </c>
-      <c r="AF59" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG59" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH59" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="AI59" s="3" t="n">
-        <v>1.9055</v>
-      </c>
-      <c r="AJ59" s="3" t="n">
-        <v>2.687</v>
-      </c>
-      <c r="AK59" s="3" t="n">
-        <v>2.653</v>
-      </c>
-      <c r="AL59" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AM59" s="3" t="n">
-        <v>3.249</v>
-      </c>
-      <c r="AN59" s="3" t="n">
-        <v>3.999</v>
-      </c>
-      <c r="AO59" s="3" t="n">
-        <v>3.654</v>
-      </c>
-      <c r="AP59" s="3" t="n">
-        <v>2.479</v>
-      </c>
-      <c r="AQ59" s="3" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="AR59" s="3" t="n">
-        <v>2.669</v>
-      </c>
-      <c r="AS59" s="3" t="n">
+      <c r="BI59" s="3" t="n">
+        <v>3.745</v>
+      </c>
+      <c r="BJ59" s="3" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="BK59" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL59" s="3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BM59" s="3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BN59" s="3" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BO59" s="3" t="n">
         <v>2.08</v>
       </c>
-      <c r="AT59" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU59" s="3" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="AV59" s="3" t="n">
-        <v>2.682</v>
-      </c>
-      <c r="AW59" s="3" t="n">
-        <v>3.627</v>
-      </c>
-      <c r="AX59" s="3" t="n">
-        <v>2.597</v>
-      </c>
-      <c r="AY59" s="3" t="n">
-        <v>2.444</v>
-      </c>
-      <c r="AZ59" s="3" t="n">
-        <v>2.641</v>
-      </c>
-      <c r="BA59" s="3" t="n">
-        <v>2.458</v>
-      </c>
-      <c r="BB59" s="3" t="n">
-        <v>1.9535</v>
-      </c>
-      <c r="BC59" s="3" t="n">
-        <v>2.472</v>
-      </c>
-      <c r="BD59" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BE59" s="3" t="n">
-        <v>2.627</v>
-      </c>
-      <c r="BF59" s="3" t="n">
-        <v>2.0972</v>
-      </c>
-      <c r="BG59" s="3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BH59" s="3" t="n">
-        <v>2.7675</v>
-      </c>
-      <c r="BI59" s="3" t="n">
-        <v>3.702</v>
-      </c>
-      <c r="BJ59" s="3" t="n">
-        <v>3.727</v>
-      </c>
-      <c r="BK59" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BL59" s="3" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="BM59" s="3" t="n">
-        <v>2.9005</v>
-      </c>
-      <c r="BN59" s="3" t="n">
-        <v>3.769</v>
-      </c>
-      <c r="BO59" s="3" t="n">
-        <v>2.258</v>
-      </c>
       <c r="BP59" s="3" t="n">
-        <v>2.5105</v>
+        <v>2.14</v>
       </c>
       <c r="BQ59" s="3" t="n">
-        <v>2.594</v>
+        <v>2.5</v>
       </c>
       <c r="BR59" s="3" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="60">

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -13294,211 +13294,211 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>2.619</v>
+        <v>2.405</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>2.5455</v>
+        <v>2.385</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q60" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S60" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="T60" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W60" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X60" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="Y60" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Z60" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AA60" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AC60" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AD60" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="AE60" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AF60" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AG60" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AH60" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI60" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ60" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AK60" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AL60" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM60" s="3" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="AN60" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AO60" s="3" t="n">
+        <v>3.545</v>
+      </c>
+      <c r="AP60" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AQ60" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AR60" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AS60" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT60" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AU60" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AV60" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AW60" s="3" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="AX60" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="E60" s="3" t="n">
-        <v>2.577</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>2.689</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>2.639</v>
-      </c>
-      <c r="K60" s="3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M60" s="3" t="n">
-        <v>2.574</v>
-      </c>
-      <c r="N60" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O60" s="3" t="n">
-        <v>3.846</v>
-      </c>
-      <c r="P60" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q60" s="3" t="n">
-        <v>2.882</v>
-      </c>
-      <c r="R60" s="3" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="S60" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="T60" s="3" t="n">
-        <v>2.577</v>
-      </c>
-      <c r="U60" s="3" t="n">
-        <v>3.119</v>
-      </c>
-      <c r="V60" s="3" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="W60" s="3" t="n">
-        <v>1.9885</v>
-      </c>
-      <c r="X60" s="3" t="n">
-        <v>2.539</v>
-      </c>
-      <c r="Y60" s="3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Z60" s="3" t="n">
-        <v>2.607</v>
-      </c>
-      <c r="AA60" s="3" t="n">
-        <v>2.689</v>
-      </c>
-      <c r="AB60" s="3" t="n">
-        <v>2.694</v>
-      </c>
-      <c r="AC60" s="3" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="AD60" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE60" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AF60" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG60" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH60" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="AI60" s="3" t="n">
-        <v>1.9055</v>
-      </c>
-      <c r="AJ60" s="3" t="n">
-        <v>2.687</v>
-      </c>
-      <c r="AK60" s="3" t="n">
-        <v>2.653</v>
-      </c>
-      <c r="AL60" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AM60" s="3" t="n">
-        <v>3.249</v>
-      </c>
-      <c r="AN60" s="3" t="n">
-        <v>3.999</v>
-      </c>
-      <c r="AO60" s="3" t="n">
-        <v>3.654</v>
-      </c>
-      <c r="AP60" s="3" t="n">
-        <v>2.479</v>
-      </c>
-      <c r="AQ60" s="3" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="AR60" s="3" t="n">
-        <v>2.669</v>
-      </c>
-      <c r="AS60" s="3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT60" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU60" s="3" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="AV60" s="3" t="n">
-        <v>2.682</v>
-      </c>
-      <c r="AW60" s="3" t="n">
-        <v>3.627</v>
-      </c>
-      <c r="AX60" s="3" t="n">
-        <v>2.597</v>
-      </c>
       <c r="AY60" s="3" t="n">
-        <v>2.444</v>
+        <v>2.365</v>
       </c>
       <c r="AZ60" s="3" t="n">
-        <v>2.641</v>
+        <v>2.44</v>
       </c>
       <c r="BA60" s="3" t="n">
-        <v>2.458</v>
+        <v>2.105</v>
       </c>
       <c r="BB60" s="3" t="n">
-        <v>1.9535</v>
+        <v>1.915</v>
       </c>
       <c r="BC60" s="3" t="n">
-        <v>2.472</v>
+        <v>2.44</v>
       </c>
       <c r="BD60" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE60" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="BE60" s="3" t="n">
-        <v>2.627</v>
-      </c>
       <c r="BF60" s="3" t="n">
-        <v>2.0972</v>
+        <v>2.05</v>
       </c>
       <c r="BG60" s="3" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="BH60" s="3" t="n">
-        <v>2.7675</v>
+        <v>2.45</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>3.702</v>
+        <v>3.515</v>
       </c>
       <c r="BJ60" s="3" t="n">
-        <v>3.727</v>
+        <v>3.585</v>
       </c>
       <c r="BK60" s="3" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="BL60" s="3" t="n">
-        <v>3.74</v>
+        <v>2.78</v>
       </c>
       <c r="BM60" s="3" t="n">
-        <v>2.9005</v>
+        <v>3.225</v>
       </c>
       <c r="BN60" s="3" t="n">
-        <v>3.769</v>
+        <v>3.69</v>
       </c>
       <c r="BO60" s="3" t="n">
-        <v>2.258</v>
+        <v>2</v>
       </c>
       <c r="BP60" s="3" t="n">
-        <v>2.5105</v>
+        <v>2.085</v>
       </c>
       <c r="BQ60" s="3" t="n">
-        <v>2.594</v>
+        <v>2.42</v>
       </c>
       <c r="BR60" s="3" t="n">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="61">
@@ -13508,211 +13508,211 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>2.619</v>
+        <v>2.4097</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2.5455</v>
+        <v>2.3626</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2.577</v>
+        <v>2.2976</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2.58</v>
+        <v>2.3927</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2.49</v>
+        <v>2.4087</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>2.49</v>
+        <v>2.3664</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>2.689</v>
+        <v>2.4577</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2.639</v>
+        <v>2.4486</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>2.23</v>
+        <v>1.6664</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>2.04</v>
+        <v>1.8481</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>2.574</v>
+        <v>2.3946</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>3.846</v>
+        <v>3.6834</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>2.54</v>
+        <v>2.3032</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>2.882</v>
+        <v>2.5542</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>2.545</v>
+        <v>2.4942</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>2.625</v>
+        <v>2.5331</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>2.577</v>
+        <v>2.3473</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>3.119</v>
+        <v>2.4016</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.67</v>
+        <v>2.4379</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.9885</v>
+        <v>1.8417</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>2.539</v>
+        <v>2.3856</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.43</v>
+        <v>2.3215</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>2.607</v>
+        <v>2.3723</v>
       </c>
       <c r="AA61" s="3" t="n">
-        <v>2.689</v>
+        <v>2.4196</v>
       </c>
       <c r="AB61" s="3" t="n">
-        <v>2.694</v>
+        <v>2.4479</v>
       </c>
       <c r="AC61" s="3" t="n">
-        <v>2.663</v>
+        <v>2.3868</v>
       </c>
       <c r="AD61" s="3" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AE61" s="3" t="n">
-        <v>2.53</v>
+        <v>2.3018</v>
       </c>
       <c r="AF61" s="3" t="n">
-        <v>3.2</v>
+        <v>3.1517</v>
       </c>
       <c r="AG61" s="3" t="n">
-        <v>2.64</v>
+        <v>2.4611</v>
       </c>
       <c r="AH61" s="3" t="n">
-        <v>2.532</v>
+        <v>2.3422</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.6201</v>
       </c>
       <c r="AJ61" s="3" t="n">
-        <v>2.687</v>
+        <v>2.4595</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>2.653</v>
+        <v>2.4</v>
       </c>
       <c r="AL61" s="3" t="n">
-        <v>2.73</v>
+        <v>2.4186</v>
       </c>
       <c r="AM61" s="3" t="n">
-        <v>3.249</v>
+        <v>3.0618</v>
       </c>
       <c r="AN61" s="3" t="n">
-        <v>3.999</v>
+        <v>3.8515</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>3.654</v>
+        <v>3.4958</v>
       </c>
       <c r="AP61" s="3" t="n">
-        <v>2.479</v>
+        <v>2.3982</v>
       </c>
       <c r="AQ61" s="3" t="n">
-        <v>2.123</v>
+        <v>1.9983</v>
       </c>
       <c r="AR61" s="3" t="n">
-        <v>2.669</v>
+        <v>2.3531</v>
       </c>
       <c r="AS61" s="3" t="n">
-        <v>2.08</v>
+        <v>1.8937</v>
       </c>
       <c r="AT61" s="3" t="n">
-        <v>2.32</v>
+        <v>1.952</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>2.449</v>
+        <v>2.34</v>
       </c>
       <c r="AV61" s="3" t="n">
-        <v>2.682</v>
+        <v>2.3866</v>
       </c>
       <c r="AW61" s="3" t="n">
-        <v>3.627</v>
+        <v>3.4859</v>
       </c>
       <c r="AX61" s="3" t="n">
-        <v>2.597</v>
+        <v>2.3744</v>
       </c>
       <c r="AY61" s="3" t="n">
+        <v>2.3334</v>
+      </c>
+      <c r="AZ61" s="3" t="n">
         <v>2.444</v>
       </c>
-      <c r="AZ61" s="3" t="n">
-        <v>2.641</v>
-      </c>
       <c r="BA61" s="3" t="n">
-        <v>2.458</v>
+        <v>1.9579</v>
       </c>
       <c r="BB61" s="3" t="n">
-        <v>1.9535</v>
+        <v>1.8062</v>
       </c>
       <c r="BC61" s="3" t="n">
-        <v>2.472</v>
+        <v>2.35</v>
       </c>
       <c r="BD61" s="3" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="BE61" s="3" t="n">
-        <v>2.627</v>
+        <v>2.3931</v>
       </c>
       <c r="BF61" s="3" t="n">
-        <v>2.0972</v>
+        <v>1.952</v>
       </c>
       <c r="BG61" s="3" t="n">
-        <v>2.46</v>
+        <v>2.3409</v>
       </c>
       <c r="BH61" s="3" t="n">
-        <v>2.7675</v>
+        <v>2.3938</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>3.702</v>
+        <v>3.4982</v>
       </c>
       <c r="BJ61" s="3" t="n">
-        <v>3.727</v>
+        <v>3.5334</v>
       </c>
       <c r="BK61" s="3" t="n">
-        <v>2.29</v>
+        <v>1.8827</v>
       </c>
       <c r="BL61" s="3" t="n">
-        <v>3.74</v>
+        <v>3.5334</v>
       </c>
       <c r="BM61" s="3" t="n">
-        <v>2.9005</v>
+        <v>3.6087</v>
       </c>
       <c r="BN61" s="3" t="n">
-        <v>3.769</v>
+        <v>3.6087</v>
       </c>
       <c r="BO61" s="3" t="n">
-        <v>2.258</v>
+        <v>1.902</v>
       </c>
       <c r="BP61" s="3" t="n">
-        <v>2.5105</v>
+        <v>1.9427</v>
       </c>
       <c r="BQ61" s="3" t="n">
-        <v>2.594</v>
+        <v>2.3965</v>
       </c>
       <c r="BR61" s="3" t="n">
-        <v>2.19</v>
+        <v>1.5785</v>
       </c>
     </row>
     <row r="62">
@@ -13722,211 +13722,211 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>2.619</v>
+        <v>2.362</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2.5455</v>
+        <v>2.3635</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>2.42</v>
+        <v>2.163</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>2.577</v>
+        <v>2.32</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2.58</v>
+        <v>2.323</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>2.49</v>
+        <v>2.3025</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>2.49</v>
+        <v>2.3025</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>2.689</v>
+        <v>2.432</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>2.639</v>
+        <v>2.382</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>2.23</v>
+        <v>1.973</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>2.574</v>
+        <v>2.38</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>2.6</v>
+        <v>2.475</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>3.846</v>
+        <v>3.62</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="Q62" s="3" t="n">
-        <v>2.882</v>
+        <v>2.625</v>
       </c>
       <c r="R62" s="3" t="n">
-        <v>2.545</v>
+        <v>2.288</v>
       </c>
       <c r="S62" s="3" t="n">
-        <v>2.625</v>
+        <v>2.368</v>
       </c>
       <c r="T62" s="3" t="n">
-        <v>2.577</v>
+        <v>2.387</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>3.119</v>
+        <v>3.33</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>2.67</v>
+        <v>2.375</v>
       </c>
       <c r="W62" s="3" t="n">
-        <v>1.9885</v>
+        <v>1.8385</v>
       </c>
       <c r="X62" s="3" t="n">
-        <v>2.539</v>
+        <v>2.35</v>
       </c>
       <c r="Y62" s="3" t="n">
+        <v>2.173</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA62" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC62" s="3" t="n">
+        <v>2.426</v>
+      </c>
+      <c r="AD62" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE62" s="3" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="AF62" s="3" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="AG62" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AH62" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI62" s="3" t="n">
+        <v>1.6485</v>
+      </c>
+      <c r="AJ62" s="3" t="n">
         <v>2.43</v>
       </c>
-      <c r="Z62" s="3" t="n">
-        <v>2.607</v>
-      </c>
-      <c r="AA62" s="3" t="n">
-        <v>2.689</v>
-      </c>
-      <c r="AB62" s="3" t="n">
-        <v>2.694</v>
-      </c>
-      <c r="AC62" s="3" t="n">
-        <v>2.663</v>
-      </c>
-      <c r="AD62" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE62" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AF62" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG62" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH62" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="AI62" s="3" t="n">
-        <v>1.9055</v>
-      </c>
-      <c r="AJ62" s="3" t="n">
-        <v>2.687</v>
-      </c>
       <c r="AK62" s="3" t="n">
-        <v>2.653</v>
+        <v>2.3535</v>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="AM62" s="3" t="n">
-        <v>3.249</v>
+        <v>3.46</v>
       </c>
       <c r="AN62" s="3" t="n">
-        <v>3.999</v>
+        <v>4.1</v>
       </c>
       <c r="AO62" s="3" t="n">
-        <v>3.654</v>
+        <v>3.45</v>
       </c>
       <c r="AP62" s="3" t="n">
-        <v>2.479</v>
+        <v>2.32</v>
       </c>
       <c r="AQ62" s="3" t="n">
-        <v>2.123</v>
+        <v>1.973</v>
       </c>
       <c r="AR62" s="3" t="n">
-        <v>2.669</v>
+        <v>2.412</v>
       </c>
       <c r="AS62" s="3" t="n">
-        <v>2.08</v>
+        <v>1.7725</v>
       </c>
       <c r="AT62" s="3" t="n">
-        <v>2.32</v>
+        <v>2.0275</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>2.449</v>
+        <v>2.24</v>
       </c>
       <c r="AV62" s="3" t="n">
-        <v>2.682</v>
+        <v>2.425</v>
       </c>
       <c r="AW62" s="3" t="n">
-        <v>3.627</v>
+        <v>3.45</v>
       </c>
       <c r="AX62" s="3" t="n">
-        <v>2.597</v>
+        <v>2.4</v>
       </c>
       <c r="AY62" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AZ62" s="3" t="n">
         <v>2.444</v>
       </c>
-      <c r="AZ62" s="3" t="n">
-        <v>2.641</v>
-      </c>
       <c r="BA62" s="3" t="n">
-        <v>2.458</v>
+        <v>2.1625</v>
       </c>
       <c r="BB62" s="3" t="n">
-        <v>1.9535</v>
+        <v>1.8035</v>
       </c>
       <c r="BC62" s="3" t="n">
-        <v>2.472</v>
+        <v>2.215</v>
       </c>
       <c r="BD62" s="3" t="n">
-        <v>2.42</v>
+        <v>2.163</v>
       </c>
       <c r="BE62" s="3" t="n">
-        <v>2.627</v>
+        <v>2.37</v>
       </c>
       <c r="BF62" s="3" t="n">
-        <v>2.0972</v>
+        <v>1.8402</v>
       </c>
       <c r="BG62" s="3" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="BH62" s="3" t="n">
-        <v>2.7675</v>
+        <v>2.6255</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>3.702</v>
+        <v>3.525</v>
       </c>
       <c r="BJ62" s="3" t="n">
-        <v>3.727</v>
+        <v>3.55</v>
       </c>
       <c r="BK62" s="3" t="n">
-        <v>2.29</v>
+        <v>2.033</v>
       </c>
       <c r="BL62" s="3" t="n">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="BM62" s="3" t="n">
-        <v>2.9005</v>
+        <v>2.6435</v>
       </c>
       <c r="BN62" s="3" t="n">
-        <v>3.769</v>
+        <v>3.512</v>
       </c>
       <c r="BO62" s="3" t="n">
-        <v>2.258</v>
+        <v>2.001</v>
       </c>
       <c r="BP62" s="3" t="n">
-        <v>2.5105</v>
+        <v>2.2535</v>
       </c>
       <c r="BQ62" s="3" t="n">
-        <v>2.594</v>
+        <v>2.38</v>
       </c>
       <c r="BR62" s="3" t="n">
-        <v>2.19</v>
+        <v>1.933</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR62"/>
+  <dimension ref="A1:BR93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13508,211 +13508,211 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>2.4097</v>
+        <v>2.41</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2.3626</v>
+        <v>2.365</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>2.15</v>
+        <v>2.085</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2.2976</v>
+        <v>2.3</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2.3927</v>
+        <v>2.395</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2.4087</v>
+        <v>2.41</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>2.3664</v>
+        <v>2.365</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>2.4577</v>
+        <v>2.45</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2.4486</v>
+        <v>2.45</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>1.6664</v>
+        <v>1.64</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.8481</v>
+        <v>1.85</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>2.3946</v>
+        <v>2.405</v>
       </c>
       <c r="N61" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="Y61" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="Z61" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA61" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="AC61" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD61" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="O61" s="3" t="n">
-        <v>3.6834</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>2.3032</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>2.5542</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>2.4942</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>2.5331</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>2.3473</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>2.4016</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>2.4379</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>1.8417</v>
-      </c>
-      <c r="X61" s="3" t="n">
-        <v>2.3856</v>
-      </c>
-      <c r="Y61" s="3" t="n">
-        <v>2.3215</v>
-      </c>
-      <c r="Z61" s="3" t="n">
-        <v>2.3723</v>
-      </c>
-      <c r="AA61" s="3" t="n">
-        <v>2.4196</v>
-      </c>
-      <c r="AB61" s="3" t="n">
-        <v>2.4479</v>
-      </c>
-      <c r="AC61" s="3" t="n">
-        <v>2.3868</v>
-      </c>
-      <c r="AD61" s="3" t="n">
+      <c r="AE61" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="AE61" s="3" t="n">
-        <v>2.3018</v>
-      </c>
       <c r="AF61" s="3" t="n">
-        <v>3.1517</v>
+        <v>3.15</v>
       </c>
       <c r="AG61" s="3" t="n">
-        <v>2.4611</v>
+        <v>2.46</v>
       </c>
       <c r="AH61" s="3" t="n">
-        <v>2.3422</v>
+        <v>2.34</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>1.6201</v>
+        <v>1.645</v>
       </c>
       <c r="AJ61" s="3" t="n">
-        <v>2.4595</v>
+        <v>2.46</v>
       </c>
       <c r="AK61" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AL61" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AM61" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AN61" s="3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AO61" s="3" t="n">
+        <v>3.495</v>
+      </c>
+      <c r="AP61" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="AL61" s="3" t="n">
-        <v>2.4186</v>
-      </c>
-      <c r="AM61" s="3" t="n">
-        <v>3.0618</v>
-      </c>
-      <c r="AN61" s="3" t="n">
-        <v>3.8515</v>
-      </c>
-      <c r="AO61" s="3" t="n">
-        <v>3.4958</v>
-      </c>
-      <c r="AP61" s="3" t="n">
-        <v>2.3982</v>
-      </c>
       <c r="AQ61" s="3" t="n">
-        <v>1.9983</v>
+        <v>2</v>
       </c>
       <c r="AR61" s="3" t="n">
-        <v>2.3531</v>
+        <v>2.355</v>
       </c>
       <c r="AS61" s="3" t="n">
-        <v>1.8937</v>
+        <v>1.895</v>
       </c>
       <c r="AT61" s="3" t="n">
-        <v>1.952</v>
+        <v>1.95</v>
       </c>
       <c r="AU61" s="3" t="n">
         <v>2.34</v>
       </c>
       <c r="AV61" s="3" t="n">
-        <v>2.3866</v>
+        <v>2.385</v>
       </c>
       <c r="AW61" s="3" t="n">
-        <v>3.4859</v>
+        <v>3.485</v>
       </c>
       <c r="AX61" s="3" t="n">
-        <v>2.3744</v>
+        <v>2.375</v>
       </c>
       <c r="AY61" s="3" t="n">
-        <v>2.3334</v>
+        <v>2.335</v>
       </c>
       <c r="AZ61" s="3" t="n">
-        <v>2.444</v>
+        <v>2.375</v>
       </c>
       <c r="BA61" s="3" t="n">
-        <v>1.9579</v>
+        <v>1.965</v>
       </c>
       <c r="BB61" s="3" t="n">
-        <v>1.8062</v>
+        <v>1.805</v>
       </c>
       <c r="BC61" s="3" t="n">
-        <v>2.35</v>
+        <v>2.445</v>
       </c>
       <c r="BD61" s="3" t="n">
-        <v>2.15</v>
+        <v>2.065</v>
       </c>
       <c r="BE61" s="3" t="n">
-        <v>2.3931</v>
+        <v>2.395</v>
       </c>
       <c r="BF61" s="3" t="n">
-        <v>1.952</v>
+        <v>1.955</v>
       </c>
       <c r="BG61" s="3" t="n">
-        <v>2.3409</v>
+        <v>2.34</v>
       </c>
       <c r="BH61" s="3" t="n">
-        <v>2.3938</v>
+        <v>2.385</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>3.4982</v>
+        <v>3.5</v>
       </c>
       <c r="BJ61" s="3" t="n">
-        <v>3.5334</v>
+        <v>3.535</v>
       </c>
       <c r="BK61" s="3" t="n">
-        <v>1.8827</v>
+        <v>1.885</v>
       </c>
       <c r="BL61" s="3" t="n">
-        <v>3.5334</v>
+        <v>2.7</v>
       </c>
       <c r="BM61" s="3" t="n">
-        <v>3.6087</v>
+        <v>3.35</v>
       </c>
       <c r="BN61" s="3" t="n">
-        <v>3.6087</v>
+        <v>3.615</v>
       </c>
       <c r="BO61" s="3" t="n">
-        <v>1.902</v>
+        <v>1.905</v>
       </c>
       <c r="BP61" s="3" t="n">
-        <v>1.9427</v>
+        <v>1.945</v>
       </c>
       <c r="BQ61" s="3" t="n">
-        <v>2.3965</v>
+        <v>2.395</v>
       </c>
       <c r="BR61" s="3" t="n">
-        <v>1.5785</v>
+        <v>1.615</v>
       </c>
     </row>
     <row r="62">
@@ -13722,215 +13722,6849 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3727</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2.3635</v>
+        <v>2.3924</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>2.163</v>
+        <v>2.12</v>
       </c>
       <c r="E62" s="3" t="n">
+        <v>2.3453</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>2.4098</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>2.4122</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>2.3948</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>2.434</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>1.8325</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>1.7728</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>2.4011</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>3.6106</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>2.3502</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>2.6375</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>2.4783</v>
+      </c>
+      <c r="S62" s="3" t="n">
+        <v>2.4984</v>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>2.3568</v>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>2.4515</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>2.4347</v>
+      </c>
+      <c r="W62" s="3" t="n">
+        <v>1.7491</v>
+      </c>
+      <c r="X62" s="3" t="n">
+        <v>2.3977</v>
+      </c>
+      <c r="Y62" s="3" t="n">
+        <v>2.3292</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>2.4039</v>
+      </c>
+      <c r="AA62" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>2.3865</v>
+      </c>
+      <c r="AC62" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD62" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE62" s="3" t="n">
+        <v>2.3439</v>
+      </c>
+      <c r="AF62" s="3" t="n">
+        <v>3.1466</v>
+      </c>
+      <c r="AG62" s="3" t="n">
+        <v>2.5169</v>
+      </c>
+      <c r="AH62" s="3" t="n">
+        <v>2.3872</v>
+      </c>
+      <c r="AI62" s="3" t="n">
+        <v>1.8519</v>
+      </c>
+      <c r="AJ62" s="3" t="n">
+        <v>2.4587</v>
+      </c>
+      <c r="AK62" s="3" t="n">
+        <v>2.3966</v>
+      </c>
+      <c r="AL62" s="3" t="n">
+        <v>2.5222</v>
+      </c>
+      <c r="AM62" s="3" t="n">
+        <v>2.9336</v>
+      </c>
+      <c r="AN62" s="3" t="n">
+        <v>3.7939</v>
+      </c>
+      <c r="AO62" s="3" t="n">
+        <v>3.4301</v>
+      </c>
+      <c r="AP62" s="3" t="n">
+        <v>2.3992</v>
+      </c>
+      <c r="AQ62" s="3" t="n">
+        <v>1.9626</v>
+      </c>
+      <c r="AR62" s="3" t="n">
+        <v>2.3962</v>
+      </c>
+      <c r="AS62" s="3" t="n">
+        <v>1.7958</v>
+      </c>
+      <c r="AT62" s="3" t="n">
+        <v>1.8472</v>
+      </c>
+      <c r="AU62" s="3" t="n">
+        <v>2.3431</v>
+      </c>
+      <c r="AV62" s="3" t="n">
+        <v>2.4372</v>
+      </c>
+      <c r="AW62" s="3" t="n">
+        <v>3.4006</v>
+      </c>
+      <c r="AX62" s="3" t="n">
+        <v>2.4049</v>
+      </c>
+      <c r="AY62" s="3" t="n">
+        <v>2.3413</v>
+      </c>
+      <c r="AZ62" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA62" s="3" t="n">
+        <v>1.8997</v>
+      </c>
+      <c r="BB62" s="3" t="n">
+        <v>1.7588</v>
+      </c>
+      <c r="BC62" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="F62" s="3" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>2.3025</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>2.3025</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>2.432</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>2.382</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>1.973</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="M62" s="3" t="n">
+      <c r="BD62" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE62" s="3" t="n">
+        <v>2.4077</v>
+      </c>
+      <c r="BF62" s="3" t="n">
+        <v>1.8472</v>
+      </c>
+      <c r="BG62" s="3" t="n">
+        <v>2.3549</v>
+      </c>
+      <c r="BH62" s="3" t="n">
+        <v>2.4275</v>
+      </c>
+      <c r="BI62" s="3" t="n">
+        <v>3.3876</v>
+      </c>
+      <c r="BJ62" s="3" t="n">
+        <v>3.4606</v>
+      </c>
+      <c r="BK62" s="3" t="n">
+        <v>1.7933</v>
+      </c>
+      <c r="BL62" s="3" t="n">
+        <v>3.4606</v>
+      </c>
+      <c r="BM62" s="3" t="n">
+        <v>3.5394</v>
+      </c>
+      <c r="BN62" s="3" t="n">
+        <v>3.5394</v>
+      </c>
+      <c r="BO62" s="3" t="n">
+        <v>1.7972</v>
+      </c>
+      <c r="BP62" s="3" t="n">
+        <v>1.8831</v>
+      </c>
+      <c r="BQ62" s="3" t="n">
+        <v>2.3927</v>
+      </c>
+      <c r="BR62" s="3" t="n">
+        <v>1.7085</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S63" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T63" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W63" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X63" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y63" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z63" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA63" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB63" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC63" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD63" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE63" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF63" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG63" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH63" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI63" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ63" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK63" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL63" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM63" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN63" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO63" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP63" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ63" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR63" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS63" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT63" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU63" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV63" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW63" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX63" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY63" s="3" t="n">
         <v>2.38</v>
       </c>
-      <c r="N62" s="3" t="n">
-        <v>2.475</v>
-      </c>
-      <c r="O62" s="3" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P62" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q62" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="R62" s="3" t="n">
-        <v>2.288</v>
-      </c>
-      <c r="S62" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="T62" s="3" t="n">
-        <v>2.387</v>
-      </c>
-      <c r="U62" s="3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="V62" s="3" t="n">
+      <c r="AZ63" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA63" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB63" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC63" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD63" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE63" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF63" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG63" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH63" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI63" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ63" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK63" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL63" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM63" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN63" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO63" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP63" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ63" s="3" t="n">
         <v>2.375</v>
       </c>
-      <c r="W62" s="3" t="n">
-        <v>1.8385</v>
-      </c>
-      <c r="X62" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y62" s="3" t="n">
-        <v>2.173</v>
-      </c>
-      <c r="Z62" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA62" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB62" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC62" s="3" t="n">
-        <v>2.426</v>
-      </c>
-      <c r="AD62" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE62" s="3" t="n">
-        <v>2.273</v>
-      </c>
-      <c r="AF62" s="3" t="n">
-        <v>3.003</v>
-      </c>
-      <c r="AG62" s="3" t="n">
+      <c r="BR63" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T64" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W64" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X64" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y64" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z64" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA64" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB64" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC64" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD64" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE64" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF64" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG64" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH64" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI64" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ64" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK64" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL64" s="3" t="n">
         <v>2.383</v>
       </c>
-      <c r="AH62" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI62" s="3" t="n">
-        <v>1.6485</v>
-      </c>
-      <c r="AJ62" s="3" t="n">
+      <c r="AM64" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN64" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO64" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP64" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ64" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR64" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS64" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT64" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU64" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV64" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW64" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX64" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY64" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ64" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA64" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB64" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC64" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD64" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE64" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF64" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG64" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH64" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI64" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ64" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK64" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL64" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM64" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN64" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO64" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP64" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ64" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR64" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S65" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T65" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U65" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W65" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X65" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y65" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z65" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA65" s="3" t="n">
         <v>2.43</v>
       </c>
-      <c r="AK62" s="3" t="n">
-        <v>2.3535</v>
-      </c>
-      <c r="AL62" s="3" t="n">
+      <c r="AB65" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC65" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD65" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE65" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF65" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG65" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH65" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI65" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ65" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK65" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL65" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM65" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN65" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO65" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP65" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ65" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR65" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS65" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT65" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU65" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV65" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW65" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX65" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY65" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ65" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="AM62" s="3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AN62" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO62" s="3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AP62" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AQ62" s="3" t="n">
-        <v>1.973</v>
-      </c>
-      <c r="AR62" s="3" t="n">
-        <v>2.412</v>
-      </c>
-      <c r="AS62" s="3" t="n">
-        <v>1.7725</v>
-      </c>
-      <c r="AT62" s="3" t="n">
-        <v>2.0275</v>
-      </c>
-      <c r="AU62" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV62" s="3" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="AW62" s="3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX62" s="3" t="n">
+      <c r="BA65" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB65" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC65" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD65" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE65" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF65" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG65" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="AY62" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ62" s="3" t="n">
-        <v>2.444</v>
-      </c>
-      <c r="BA62" s="3" t="n">
-        <v>2.1625</v>
-      </c>
-      <c r="BB62" s="3" t="n">
-        <v>1.8035</v>
-      </c>
-      <c r="BC62" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="BD62" s="3" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="BE62" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="BF62" s="3" t="n">
-        <v>1.8402</v>
-      </c>
-      <c r="BG62" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BH62" s="3" t="n">
-        <v>2.6255</v>
-      </c>
-      <c r="BI62" s="3" t="n">
-        <v>3.525</v>
-      </c>
-      <c r="BJ62" s="3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BK62" s="3" t="n">
-        <v>2.033</v>
-      </c>
-      <c r="BL62" s="3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BM62" s="3" t="n">
-        <v>2.6435</v>
-      </c>
-      <c r="BN62" s="3" t="n">
-        <v>3.512</v>
-      </c>
-      <c r="BO62" s="3" t="n">
-        <v>2.001</v>
-      </c>
-      <c r="BP62" s="3" t="n">
-        <v>2.2535</v>
-      </c>
-      <c r="BQ62" s="3" t="n">
+      <c r="BH65" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI65" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ65" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK65" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL65" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM65" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN65" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO65" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP65" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ65" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR65" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y66" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z66" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA66" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB66" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC66" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD66" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE66" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF66" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG66" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH66" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI66" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ66" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK66" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL66" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM66" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN66" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO66" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP66" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ66" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR66" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS66" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT66" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU66" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV66" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW66" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX66" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY66" s="3" t="n">
         <v>2.38</v>
       </c>
-      <c r="BR62" s="3" t="n">
-        <v>1.933</v>
+      <c r="AZ66" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA66" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB66" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC66" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD66" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE66" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF66" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG66" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH66" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI66" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ66" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK66" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL66" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM66" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN66" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO66" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP66" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ66" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR66" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S67" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T67" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W67" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X67" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y67" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA67" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC67" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD67" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE67" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF67" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG67" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH67" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI67" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ67" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK67" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL67" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM67" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN67" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO67" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP67" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ67" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR67" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS67" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT67" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU67" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV67" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW67" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX67" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY67" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ67" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA67" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB67" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC67" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD67" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE67" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF67" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG67" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH67" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI67" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ67" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK67" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL67" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM67" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN67" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO67" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP67" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ67" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR67" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S68" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T68" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U68" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W68" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X68" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y68" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA68" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC68" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD68" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE68" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF68" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG68" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH68" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI68" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ68" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK68" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL68" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM68" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN68" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO68" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP68" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ68" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR68" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS68" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT68" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU68" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV68" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW68" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX68" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY68" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ68" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA68" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB68" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC68" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD68" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE68" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF68" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG68" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH68" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI68" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ68" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK68" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL68" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM68" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN68" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO68" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP68" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ68" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR68" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S69" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T69" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W69" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y69" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA69" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC69" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD69" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE69" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF69" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG69" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH69" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI69" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ69" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK69" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL69" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM69" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN69" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO69" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP69" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ69" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR69" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS69" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT69" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU69" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV69" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW69" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX69" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY69" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ69" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA69" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB69" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC69" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD69" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE69" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF69" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG69" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH69" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI69" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ69" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK69" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL69" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM69" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN69" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO69" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP69" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ69" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR69" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q70" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S70" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T70" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W70" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y70" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z70" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA70" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC70" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD70" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE70" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF70" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG70" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH70" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI70" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ70" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK70" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL70" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM70" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN70" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO70" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP70" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ70" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR70" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS70" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT70" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU70" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV70" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW70" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX70" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY70" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ70" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA70" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB70" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC70" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD70" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE70" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF70" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG70" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH70" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI70" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ70" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK70" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL70" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM70" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN70" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO70" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP70" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ70" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR70" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W71" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA71" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC71" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD71" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE71" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF71" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG71" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH71" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI71" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ71" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK71" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL71" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM71" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN71" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO71" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP71" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ71" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR71" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS71" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT71" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU71" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV71" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW71" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX71" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY71" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ71" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA71" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB71" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC71" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD71" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE71" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF71" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG71" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH71" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI71" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ71" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK71" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL71" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM71" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN71" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO71" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP71" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ71" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR71" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S72" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T72" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U72" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V72" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W72" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y72" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA72" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC72" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD72" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE72" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF72" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG72" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH72" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI72" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ72" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK72" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL72" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM72" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN72" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO72" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP72" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ72" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR72" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS72" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT72" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU72" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV72" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW72" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX72" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY72" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ72" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA72" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB72" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC72" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD72" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE72" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF72" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG72" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH72" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI72" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ72" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK72" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL72" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM72" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN72" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO72" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP72" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ72" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR72" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S73" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T73" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V73" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W73" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y73" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z73" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA73" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC73" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD73" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE73" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF73" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG73" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH73" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI73" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ73" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK73" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL73" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM73" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN73" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO73" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP73" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ73" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR73" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS73" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT73" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU73" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV73" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW73" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX73" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY73" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ73" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA73" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB73" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC73" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD73" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE73" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF73" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG73" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH73" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI73" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ73" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK73" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL73" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM73" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN73" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO73" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP73" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ73" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR73" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S74" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T74" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y74" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC74" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD74" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE74" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF74" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG74" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH74" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI74" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ74" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK74" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL74" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM74" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN74" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO74" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP74" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ74" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR74" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS74" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT74" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU74" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV74" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW74" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX74" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY74" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ74" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA74" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB74" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC74" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD74" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE74" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF74" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG74" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH74" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI74" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ74" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK74" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL74" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM74" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN74" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO74" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP74" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ74" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR74" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S75" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC75" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD75" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE75" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF75" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG75" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH75" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI75" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ75" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL75" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM75" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN75" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO75" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP75" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ75" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR75" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS75" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT75" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU75" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV75" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW75" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX75" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY75" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ75" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA75" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB75" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC75" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD75" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE75" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF75" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG75" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH75" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI75" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ75" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK75" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL75" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM75" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN75" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO75" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP75" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ75" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR75" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA76" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC76" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD76" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE76" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF76" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG76" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH76" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI76" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ76" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL76" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM76" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN76" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO76" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP76" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ76" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR76" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS76" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT76" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU76" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV76" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW76" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX76" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY76" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ76" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA76" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB76" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC76" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD76" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE76" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF76" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG76" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH76" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI76" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ76" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK76" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL76" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM76" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN76" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO76" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP76" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ76" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR76" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S77" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA77" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC77" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD77" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE77" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF77" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG77" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH77" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI77" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ77" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK77" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL77" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM77" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN77" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO77" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP77" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ77" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR77" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS77" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT77" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU77" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV77" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW77" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX77" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY77" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ77" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA77" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB77" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC77" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD77" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE77" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF77" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG77" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH77" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI77" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ77" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK77" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL77" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM77" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN77" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO77" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP77" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ77" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR77" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S78" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA78" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC78" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD78" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE78" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF78" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG78" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH78" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI78" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ78" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK78" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL78" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM78" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN78" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO78" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP78" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ78" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR78" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS78" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT78" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU78" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV78" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW78" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX78" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY78" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ78" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA78" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB78" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC78" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD78" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE78" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF78" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG78" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH78" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI78" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ78" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK78" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL78" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM78" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN78" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO78" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP78" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ78" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR78" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA79" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD79" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE79" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF79" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG79" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH79" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI79" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ79" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK79" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL79" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM79" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN79" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO79" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP79" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ79" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR79" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS79" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT79" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU79" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV79" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW79" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX79" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY79" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ79" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA79" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB79" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC79" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD79" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE79" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF79" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG79" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH79" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI79" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ79" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK79" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL79" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM79" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN79" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO79" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP79" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ79" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR79" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD80" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE80" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF80" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG80" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH80" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI80" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ80" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK80" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL80" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM80" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN80" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO80" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP80" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ80" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR80" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS80" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT80" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU80" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV80" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW80" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX80" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY80" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ80" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA80" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB80" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC80" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD80" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE80" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF80" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG80" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH80" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI80" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ80" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK80" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL80" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM80" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN80" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO80" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP80" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ80" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR80" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S81" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA81" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD81" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE81" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF81" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG81" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH81" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI81" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ81" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK81" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL81" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM81" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN81" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO81" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP81" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ81" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR81" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS81" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT81" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU81" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV81" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW81" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX81" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY81" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ81" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA81" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB81" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC81" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD81" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE81" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF81" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG81" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH81" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI81" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ81" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK81" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL81" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM81" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN81" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO81" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP81" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ81" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR81" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S82" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA82" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD82" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE82" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF82" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG82" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH82" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI82" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ82" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK82" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL82" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM82" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN82" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO82" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP82" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ82" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR82" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS82" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT82" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU82" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV82" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW82" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX82" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY82" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ82" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA82" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB82" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC82" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD82" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE82" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF82" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG82" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH82" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI82" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ82" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK82" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL82" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM82" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN82" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO82" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP82" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ82" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR82" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S83" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA83" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC83" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD83" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE83" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF83" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG83" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH83" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI83" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ83" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK83" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL83" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM83" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN83" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO83" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP83" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ83" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR83" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS83" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT83" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU83" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV83" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW83" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX83" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY83" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ83" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA83" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB83" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC83" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD83" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE83" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF83" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG83" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH83" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI83" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ83" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK83" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL83" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM83" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN83" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO83" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP83" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ83" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR83" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA84" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB84" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC84" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD84" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE84" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF84" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG84" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH84" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI84" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ84" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK84" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL84" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM84" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN84" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO84" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP84" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ84" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR84" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS84" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT84" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU84" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV84" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW84" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX84" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY84" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ84" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA84" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB84" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC84" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD84" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE84" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF84" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG84" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH84" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI84" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ84" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK84" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL84" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM84" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN84" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO84" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP84" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ84" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR84" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S85" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T85" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W85" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y85" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA85" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC85" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD85" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE85" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF85" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG85" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH85" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI85" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ85" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK85" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL85" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM85" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN85" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO85" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP85" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ85" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR85" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS85" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT85" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU85" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV85" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW85" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX85" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY85" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ85" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA85" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB85" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC85" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD85" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE85" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF85" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG85" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH85" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI85" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ85" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK85" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL85" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM85" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN85" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO85" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP85" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ85" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR85" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y86" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z86" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA86" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC86" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD86" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE86" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF86" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG86" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH86" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI86" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ86" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK86" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL86" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM86" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN86" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO86" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP86" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ86" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR86" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS86" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT86" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU86" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV86" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW86" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX86" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY86" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ86" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA86" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB86" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC86" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD86" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE86" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF86" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG86" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH86" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI86" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ86" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK86" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL86" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM86" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN86" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO86" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP86" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ86" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR86" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S87" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T87" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W87" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y87" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA87" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB87" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC87" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD87" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE87" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF87" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG87" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH87" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI87" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ87" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK87" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL87" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM87" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN87" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO87" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP87" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ87" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR87" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS87" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT87" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU87" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV87" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW87" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX87" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY87" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ87" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA87" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB87" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC87" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD87" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE87" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF87" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG87" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH87" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI87" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ87" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK87" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL87" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM87" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN87" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO87" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP87" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ87" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR87" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q88" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S88" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T88" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W88" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y88" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z88" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA88" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB88" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC88" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD88" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE88" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF88" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG88" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH88" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI88" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ88" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK88" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL88" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM88" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN88" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO88" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP88" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ88" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR88" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS88" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT88" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU88" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV88" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW88" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX88" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY88" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ88" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA88" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB88" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC88" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD88" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE88" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF88" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG88" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH88" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI88" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ88" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK88" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL88" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM88" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN88" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO88" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP88" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ88" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR88" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S89" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T89" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W89" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y89" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA89" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB89" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC89" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD89" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE89" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF89" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG89" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH89" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI89" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ89" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK89" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL89" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM89" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN89" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO89" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP89" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ89" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR89" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS89" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT89" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU89" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV89" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW89" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX89" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY89" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ89" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA89" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB89" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC89" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD89" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE89" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF89" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG89" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH89" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI89" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ89" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK89" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL89" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM89" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN89" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO89" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP89" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ89" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR89" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q90" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S90" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W90" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y90" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z90" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA90" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC90" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD90" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE90" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF90" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG90" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH90" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI90" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ90" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK90" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL90" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM90" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN90" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO90" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP90" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ90" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR90" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS90" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT90" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU90" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV90" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW90" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX90" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY90" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ90" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA90" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB90" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC90" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD90" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE90" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF90" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG90" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH90" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI90" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ90" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK90" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL90" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM90" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN90" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO90" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP90" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ90" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR90" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y91" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA91" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB91" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC91" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD91" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE91" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF91" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG91" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH91" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI91" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ91" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK91" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL91" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM91" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN91" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO91" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP91" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ91" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR91" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS91" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT91" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU91" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV91" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW91" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX91" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY91" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ91" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA91" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB91" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC91" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD91" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE91" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF91" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG91" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH91" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI91" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ91" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK91" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL91" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM91" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN91" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO91" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP91" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ91" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR91" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q92" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S92" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W92" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y92" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z92" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA92" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB92" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC92" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD92" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE92" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF92" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG92" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH92" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI92" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ92" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK92" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL92" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM92" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN92" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO92" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP92" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ92" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR92" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS92" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT92" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU92" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV92" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW92" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX92" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY92" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ92" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA92" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB92" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC92" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD92" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE92" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF92" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG92" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH92" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI92" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ92" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK92" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL92" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM92" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN92" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO92" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP92" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ92" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR92" s="3" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="Q93" s="3" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>2.5025</v>
+      </c>
+      <c r="S93" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>2.4225</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="Y93" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AA93" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB93" s="3" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="AC93" s="3" t="n">
+        <v>2.4625</v>
+      </c>
+      <c r="AD93" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE93" s="3" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="AF93" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG93" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="AH93" s="3" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="AI93" s="3" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="AJ93" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="AK93" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL93" s="3" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="AM93" s="3" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="AN93" s="3" t="n">
+        <v>3.7495</v>
+      </c>
+      <c r="AO93" s="3" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="AP93" s="3" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="AQ93" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR93" s="3" t="n">
+        <v>2.4105</v>
+      </c>
+      <c r="AS93" s="3" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="AT93" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AU93" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV93" s="3" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="AW93" s="3" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="AX93" s="3" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="AY93" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ93" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA93" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB93" s="3" t="n">
+        <v>1.847</v>
+      </c>
+      <c r="BC93" s="3" t="n">
+        <v>2.4475</v>
+      </c>
+      <c r="BD93" s="3" t="n">
+        <v>2.3855</v>
+      </c>
+      <c r="BE93" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF93" s="3" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="BG93" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH93" s="3" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="BI93" s="3" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="BJ93" s="3" t="n">
+        <v>3.544</v>
+      </c>
+      <c r="BK93" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL93" s="3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BM93" s="3" t="n">
+        <v>3.1125</v>
+      </c>
+      <c r="BN93" s="3" t="n">
+        <v>3.6955</v>
+      </c>
+      <c r="BO93" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BP93" s="3" t="n">
+        <v>2.0795</v>
+      </c>
+      <c r="BQ93" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BR93" s="3" t="n">
+        <v>1.73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BR62"/>
+  <autoFilter ref="A1:BR93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -13722,211 +13722,211 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>2.3727</v>
+        <v>2.375</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2.3924</v>
+        <v>2.39</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>2.3453</v>
+        <v>2.345</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2.4098</v>
+        <v>2.41</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>2.4122</v>
+        <v>2.41</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>2.3948</v>
+        <v>2.395</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>2.429</v>
+        <v>2.43</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>2.434</v>
+        <v>2.435</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>1.8325</v>
+        <v>1.845</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>1.7728</v>
+        <v>1.77</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>2.4011</v>
+        <v>2.415</v>
       </c>
       <c r="N62" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>3.545</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R62" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="O62" s="3" t="n">
-        <v>3.6106</v>
-      </c>
-      <c r="P62" s="3" t="n">
-        <v>2.3502</v>
-      </c>
-      <c r="Q62" s="3" t="n">
-        <v>2.6375</v>
-      </c>
-      <c r="R62" s="3" t="n">
-        <v>2.4783</v>
-      </c>
       <c r="S62" s="3" t="n">
-        <v>2.4984</v>
+        <v>2.5</v>
       </c>
       <c r="T62" s="3" t="n">
-        <v>2.3568</v>
+        <v>2.365</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>2.4515</v>
+        <v>2.745</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>2.4347</v>
+        <v>2.435</v>
       </c>
       <c r="W62" s="3" t="n">
-        <v>1.7491</v>
+        <v>1.75</v>
       </c>
       <c r="X62" s="3" t="n">
-        <v>2.3977</v>
+        <v>2.4</v>
       </c>
       <c r="Y62" s="3" t="n">
-        <v>2.3292</v>
+        <v>2.33</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>2.4039</v>
+        <v>2.405</v>
       </c>
       <c r="AA62" s="3" t="n">
-        <v>2.41</v>
+        <v>2.405</v>
       </c>
       <c r="AB62" s="3" t="n">
-        <v>2.3865</v>
+        <v>2.385</v>
       </c>
       <c r="AC62" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="AD62" s="3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AE62" s="3" t="n">
-        <v>2.3439</v>
+        <v>2.345</v>
       </c>
       <c r="AF62" s="3" t="n">
-        <v>3.1466</v>
+        <v>3.145</v>
       </c>
       <c r="AG62" s="3" t="n">
-        <v>2.5169</v>
+        <v>2.515</v>
       </c>
       <c r="AH62" s="3" t="n">
-        <v>2.3872</v>
+        <v>2.39</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>1.8519</v>
+        <v>1.85</v>
       </c>
       <c r="AJ62" s="3" t="n">
-        <v>2.4587</v>
+        <v>2.46</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>2.3966</v>
+        <v>2.4</v>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>2.5222</v>
+        <v>2.52</v>
       </c>
       <c r="AM62" s="3" t="n">
-        <v>2.9336</v>
+        <v>2.93</v>
       </c>
       <c r="AN62" s="3" t="n">
-        <v>3.7939</v>
+        <v>3.795</v>
       </c>
       <c r="AO62" s="3" t="n">
-        <v>3.4301</v>
+        <v>3.43</v>
       </c>
       <c r="AP62" s="3" t="n">
-        <v>2.3992</v>
+        <v>2.4</v>
       </c>
       <c r="AQ62" s="3" t="n">
-        <v>1.9626</v>
+        <v>1.965</v>
       </c>
       <c r="AR62" s="3" t="n">
-        <v>2.3962</v>
+        <v>2.395</v>
       </c>
       <c r="AS62" s="3" t="n">
-        <v>1.7958</v>
+        <v>1.795</v>
       </c>
       <c r="AT62" s="3" t="n">
-        <v>1.8472</v>
+        <v>1.845</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>2.3431</v>
+        <v>2.345</v>
       </c>
       <c r="AV62" s="3" t="n">
-        <v>2.4372</v>
+        <v>2.435</v>
       </c>
       <c r="AW62" s="3" t="n">
-        <v>3.4006</v>
+        <v>3.4</v>
       </c>
       <c r="AX62" s="3" t="n">
-        <v>2.4049</v>
+        <v>2.405</v>
       </c>
       <c r="AY62" s="3" t="n">
-        <v>2.3413</v>
+        <v>2.34</v>
       </c>
       <c r="AZ62" s="3" t="n">
-        <v>2.4</v>
+        <v>2.385</v>
       </c>
       <c r="BA62" s="3" t="n">
-        <v>1.8997</v>
+        <v>1.895</v>
       </c>
       <c r="BB62" s="3" t="n">
-        <v>1.7588</v>
+        <v>1.76</v>
       </c>
       <c r="BC62" s="3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BD62" s="3" t="n">
         <v>2.12</v>
       </c>
       <c r="BE62" s="3" t="n">
-        <v>2.4077</v>
+        <v>2.41</v>
       </c>
       <c r="BF62" s="3" t="n">
-        <v>1.8472</v>
+        <v>1.845</v>
       </c>
       <c r="BG62" s="3" t="n">
-        <v>2.3549</v>
+        <v>2.355</v>
       </c>
       <c r="BH62" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.43</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>3.3876</v>
+        <v>3.39</v>
       </c>
       <c r="BJ62" s="3" t="n">
-        <v>3.4606</v>
+        <v>3.46</v>
       </c>
       <c r="BK62" s="3" t="n">
-        <v>1.7933</v>
+        <v>1.795</v>
       </c>
       <c r="BL62" s="3" t="n">
-        <v>3.4606</v>
+        <v>2.905</v>
       </c>
       <c r="BM62" s="3" t="n">
-        <v>3.5394</v>
+        <v>2.835</v>
       </c>
       <c r="BN62" s="3" t="n">
-        <v>3.5394</v>
+        <v>3.55</v>
       </c>
       <c r="BO62" s="3" t="n">
-        <v>1.7972</v>
+        <v>1.82</v>
       </c>
       <c r="BP62" s="3" t="n">
-        <v>1.8831</v>
+        <v>1.88</v>
       </c>
       <c r="BQ62" s="3" t="n">
-        <v>2.3927</v>
+        <v>2.395</v>
       </c>
       <c r="BR62" s="3" t="n">
-        <v>1.7085</v>
+        <v>1.745</v>
       </c>
     </row>
     <row r="63">
@@ -13936,211 +13936,211 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>2.47</v>
+        <v>2.4413</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>2.332</v>
+        <v>2.2903</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3402</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>2.51</v>
+        <v>2.4489</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>2.309</v>
+        <v>2.3292</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>2.31</v>
+        <v>2.3049</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>2.471</v>
+        <v>2.3892</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>2.471</v>
+        <v>2.427</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.8079</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>1.848</v>
+        <v>1.7039</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3564</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>2.465</v>
+        <v>2.48</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>3.73</v>
+        <v>3.3385</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>2.399</v>
+        <v>2.205</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>2.722</v>
+        <v>2.5874</v>
       </c>
       <c r="R63" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.5043</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>2.57</v>
+        <v>2.6392</v>
       </c>
       <c r="T63" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.2724</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>2.745</v>
+        <v>2.4546</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>2.445</v>
+        <v>2.4088</v>
       </c>
       <c r="W63" s="3" t="n">
-        <v>1.95</v>
+        <v>1.6936</v>
       </c>
       <c r="X63" s="3" t="n">
-        <v>2.365</v>
+        <v>2.327</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>2.39</v>
+        <v>2.2683</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>2.399</v>
+        <v>2.3379</v>
       </c>
       <c r="AA63" s="3" t="n">
-        <v>2.43</v>
+        <v>2.353</v>
       </c>
       <c r="AB63" s="3" t="n">
-        <v>2.451</v>
+        <v>2.3182</v>
       </c>
       <c r="AC63" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3713</v>
       </c>
       <c r="AD63" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE63" s="3" t="n">
-        <v>2.282</v>
+        <v>2.2349</v>
       </c>
       <c r="AF63" s="3" t="n">
-        <v>3.2</v>
+        <v>3.1306</v>
       </c>
       <c r="AG63" s="3" t="n">
-        <v>2.665</v>
+        <v>2.4406</v>
       </c>
       <c r="AH63" s="3" t="n">
-        <v>2.321</v>
+        <v>2.2794</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>1.818</v>
+        <v>1.8339</v>
       </c>
       <c r="AJ63" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.4511</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>2.415</v>
+        <v>2.386</v>
       </c>
       <c r="AL63" s="3" t="n">
-        <v>2.383</v>
+        <v>2.3956</v>
       </c>
       <c r="AM63" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.7917</v>
       </c>
       <c r="AN63" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.6702</v>
       </c>
       <c r="AO63" s="3" t="n">
-        <v>3.528</v>
+        <v>3.1802</v>
       </c>
       <c r="AP63" s="3" t="n">
-        <v>2.344</v>
+        <v>2.2916</v>
       </c>
       <c r="AQ63" s="3" t="n">
-        <v>1.99</v>
+        <v>1.8242</v>
       </c>
       <c r="AR63" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4158</v>
       </c>
       <c r="AS63" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.74</v>
       </c>
       <c r="AT63" s="3" t="n">
-        <v>2.008</v>
+        <v>1.8141</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>2.34</v>
+        <v>2.3649</v>
       </c>
       <c r="AV63" s="3" t="n">
-        <v>2.516</v>
+        <v>2.3836</v>
       </c>
       <c r="AW63" s="3" t="n">
-        <v>3.478</v>
+        <v>3.1632</v>
       </c>
       <c r="AX63" s="3" t="n">
-        <v>2.374</v>
+        <v>2.3768</v>
       </c>
       <c r="AY63" s="3" t="n">
-        <v>2.38</v>
+        <v>2.2271</v>
       </c>
       <c r="AZ63" s="3" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BA63" s="3" t="n">
-        <v>2.12</v>
+        <v>1.9095</v>
       </c>
       <c r="BB63" s="3" t="n">
-        <v>1.847</v>
+        <v>1.6625</v>
       </c>
       <c r="BC63" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.68</v>
       </c>
       <c r="BD63" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.48</v>
       </c>
       <c r="BE63" s="3" t="n">
-        <v>2.45</v>
+        <v>2.3794</v>
       </c>
       <c r="BF63" s="3" t="n">
-        <v>1.963</v>
+        <v>1.8141</v>
       </c>
       <c r="BG63" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2528</v>
       </c>
       <c r="BH63" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.3807</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>3.465</v>
+        <v>3.129</v>
       </c>
       <c r="BJ63" s="3" t="n">
-        <v>3.544</v>
+        <v>3.1885</v>
       </c>
       <c r="BK63" s="3" t="n">
-        <v>1.91</v>
+        <v>1.7132</v>
       </c>
       <c r="BL63" s="3" t="n">
-        <v>3.08</v>
+        <v>3.1885</v>
       </c>
       <c r="BM63" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.2504</v>
       </c>
       <c r="BN63" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.2504</v>
       </c>
       <c r="BO63" s="3" t="n">
-        <v>1.99</v>
+        <v>1.7641</v>
       </c>
       <c r="BP63" s="3" t="n">
-        <v>2.0795</v>
+        <v>1.8446</v>
       </c>
       <c r="BQ63" s="3" t="n">
-        <v>2.375</v>
+        <v>2.3825</v>
       </c>
       <c r="BR63" s="3" t="n">
-        <v>1.73</v>
+        <v>1.8104</v>
       </c>
     </row>
     <row r="64">
@@ -14150,211 +14150,211 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>2.47</v>
+        <v>2.4413</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>2.332</v>
+        <v>2.2903</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3402</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2.51</v>
+        <v>2.4489</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>2.309</v>
+        <v>2.3292</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>2.31</v>
+        <v>2.3049</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>2.471</v>
+        <v>2.3892</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>2.471</v>
+        <v>2.427</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.8079</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>1.848</v>
+        <v>1.7039</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3564</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>2.465</v>
+        <v>2.48</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>3.73</v>
+        <v>3.3385</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>2.399</v>
+        <v>2.205</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>2.722</v>
+        <v>2.5874</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.5043</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>2.57</v>
+        <v>2.6392</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.2724</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>2.745</v>
+        <v>2.4546</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>2.445</v>
+        <v>2.4088</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>1.95</v>
+        <v>1.6936</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>2.365</v>
+        <v>2.327</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>2.39</v>
+        <v>2.2683</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>2.399</v>
+        <v>2.3379</v>
       </c>
       <c r="AA64" s="3" t="n">
-        <v>2.43</v>
+        <v>2.353</v>
       </c>
       <c r="AB64" s="3" t="n">
-        <v>2.451</v>
+        <v>2.3182</v>
       </c>
       <c r="AC64" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3713</v>
       </c>
       <c r="AD64" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE64" s="3" t="n">
-        <v>2.282</v>
+        <v>2.2349</v>
       </c>
       <c r="AF64" s="3" t="n">
-        <v>3.2</v>
+        <v>3.1306</v>
       </c>
       <c r="AG64" s="3" t="n">
-        <v>2.665</v>
+        <v>2.4406</v>
       </c>
       <c r="AH64" s="3" t="n">
-        <v>2.321</v>
+        <v>2.2794</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>1.818</v>
+        <v>1.8339</v>
       </c>
       <c r="AJ64" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.4511</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>2.415</v>
+        <v>2.386</v>
       </c>
       <c r="AL64" s="3" t="n">
-        <v>2.383</v>
+        <v>2.3956</v>
       </c>
       <c r="AM64" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.7917</v>
       </c>
       <c r="AN64" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.6702</v>
       </c>
       <c r="AO64" s="3" t="n">
-        <v>3.528</v>
+        <v>3.1802</v>
       </c>
       <c r="AP64" s="3" t="n">
-        <v>2.344</v>
+        <v>2.2916</v>
       </c>
       <c r="AQ64" s="3" t="n">
-        <v>1.99</v>
+        <v>1.8242</v>
       </c>
       <c r="AR64" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4158</v>
       </c>
       <c r="AS64" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.74</v>
       </c>
       <c r="AT64" s="3" t="n">
-        <v>2.008</v>
+        <v>1.8141</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>2.34</v>
+        <v>2.3649</v>
       </c>
       <c r="AV64" s="3" t="n">
-        <v>2.516</v>
+        <v>2.3836</v>
       </c>
       <c r="AW64" s="3" t="n">
-        <v>3.478</v>
+        <v>3.1632</v>
       </c>
       <c r="AX64" s="3" t="n">
-        <v>2.374</v>
+        <v>2.3768</v>
       </c>
       <c r="AY64" s="3" t="n">
-        <v>2.38</v>
+        <v>2.2271</v>
       </c>
       <c r="AZ64" s="3" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BA64" s="3" t="n">
-        <v>2.12</v>
+        <v>1.9095</v>
       </c>
       <c r="BB64" s="3" t="n">
-        <v>1.847</v>
+        <v>1.6625</v>
       </c>
       <c r="BC64" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.68</v>
       </c>
       <c r="BD64" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.48</v>
       </c>
       <c r="BE64" s="3" t="n">
-        <v>2.45</v>
+        <v>2.3794</v>
       </c>
       <c r="BF64" s="3" t="n">
-        <v>1.963</v>
+        <v>1.8141</v>
       </c>
       <c r="BG64" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2528</v>
       </c>
       <c r="BH64" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.3807</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>3.465</v>
+        <v>3.129</v>
       </c>
       <c r="BJ64" s="3" t="n">
-        <v>3.544</v>
+        <v>3.1885</v>
       </c>
       <c r="BK64" s="3" t="n">
-        <v>1.91</v>
+        <v>1.7132</v>
       </c>
       <c r="BL64" s="3" t="n">
-        <v>3.08</v>
+        <v>3.1885</v>
       </c>
       <c r="BM64" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.2504</v>
       </c>
       <c r="BN64" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.2504</v>
       </c>
       <c r="BO64" s="3" t="n">
-        <v>1.99</v>
+        <v>1.7641</v>
       </c>
       <c r="BP64" s="3" t="n">
-        <v>2.0795</v>
+        <v>1.8446</v>
       </c>
       <c r="BQ64" s="3" t="n">
-        <v>2.375</v>
+        <v>2.3825</v>
       </c>
       <c r="BR64" s="3" t="n">
-        <v>1.73</v>
+        <v>1.8104</v>
       </c>
     </row>
     <row r="65">
@@ -14364,211 +14364,211 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>2.47</v>
+        <v>2.4413</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>2.332</v>
+        <v>2.2903</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3402</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2.51</v>
+        <v>2.4489</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.309</v>
+        <v>2.3292</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>2.31</v>
+        <v>2.3049</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>2.471</v>
+        <v>2.3892</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>2.471</v>
+        <v>2.427</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.8079</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>1.848</v>
+        <v>1.7039</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3564</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>2.465</v>
+        <v>2.48</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>3.73</v>
+        <v>3.3385</v>
       </c>
       <c r="P65" s="3" t="n">
-        <v>2.399</v>
+        <v>2.205</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>2.722</v>
+        <v>2.5874</v>
       </c>
       <c r="R65" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.5043</v>
       </c>
       <c r="S65" s="3" t="n">
-        <v>2.57</v>
+        <v>2.6392</v>
       </c>
       <c r="T65" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.2724</v>
       </c>
       <c r="U65" s="3" t="n">
-        <v>2.745</v>
+        <v>2.4546</v>
       </c>
       <c r="V65" s="3" t="n">
-        <v>2.445</v>
+        <v>2.4088</v>
       </c>
       <c r="W65" s="3" t="n">
-        <v>1.95</v>
+        <v>1.6936</v>
       </c>
       <c r="X65" s="3" t="n">
-        <v>2.365</v>
+        <v>2.327</v>
       </c>
       <c r="Y65" s="3" t="n">
-        <v>2.39</v>
+        <v>2.2683</v>
       </c>
       <c r="Z65" s="3" t="n">
-        <v>2.399</v>
+        <v>2.3379</v>
       </c>
       <c r="AA65" s="3" t="n">
-        <v>2.43</v>
+        <v>2.353</v>
       </c>
       <c r="AB65" s="3" t="n">
-        <v>2.451</v>
+        <v>2.3182</v>
       </c>
       <c r="AC65" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.3713</v>
       </c>
       <c r="AD65" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE65" s="3" t="n">
-        <v>2.282</v>
+        <v>2.2349</v>
       </c>
       <c r="AF65" s="3" t="n">
-        <v>3.2</v>
+        <v>3.1306</v>
       </c>
       <c r="AG65" s="3" t="n">
-        <v>2.665</v>
+        <v>2.4406</v>
       </c>
       <c r="AH65" s="3" t="n">
-        <v>2.321</v>
+        <v>2.2794</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>1.818</v>
+        <v>1.8339</v>
       </c>
       <c r="AJ65" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.4511</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>2.415</v>
+        <v>2.386</v>
       </c>
       <c r="AL65" s="3" t="n">
-        <v>2.383</v>
+        <v>2.3956</v>
       </c>
       <c r="AM65" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.7917</v>
       </c>
       <c r="AN65" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.6702</v>
       </c>
       <c r="AO65" s="3" t="n">
-        <v>3.528</v>
+        <v>3.1802</v>
       </c>
       <c r="AP65" s="3" t="n">
-        <v>2.344</v>
+        <v>2.2916</v>
       </c>
       <c r="AQ65" s="3" t="n">
-        <v>1.99</v>
+        <v>1.8242</v>
       </c>
       <c r="AR65" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4158</v>
       </c>
       <c r="AS65" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.74</v>
       </c>
       <c r="AT65" s="3" t="n">
-        <v>2.008</v>
+        <v>1.8141</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>2.34</v>
+        <v>2.3649</v>
       </c>
       <c r="AV65" s="3" t="n">
-        <v>2.516</v>
+        <v>2.3836</v>
       </c>
       <c r="AW65" s="3" t="n">
-        <v>3.478</v>
+        <v>3.1632</v>
       </c>
       <c r="AX65" s="3" t="n">
-        <v>2.374</v>
+        <v>2.3768</v>
       </c>
       <c r="AY65" s="3" t="n">
-        <v>2.38</v>
+        <v>2.2271</v>
       </c>
       <c r="AZ65" s="3" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BA65" s="3" t="n">
-        <v>2.12</v>
+        <v>1.9095</v>
       </c>
       <c r="BB65" s="3" t="n">
-        <v>1.847</v>
+        <v>1.6625</v>
       </c>
       <c r="BC65" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.68</v>
       </c>
       <c r="BD65" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.48</v>
       </c>
       <c r="BE65" s="3" t="n">
-        <v>2.45</v>
+        <v>2.3794</v>
       </c>
       <c r="BF65" s="3" t="n">
-        <v>1.963</v>
+        <v>1.8141</v>
       </c>
       <c r="BG65" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2528</v>
       </c>
       <c r="BH65" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.3807</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>3.465</v>
+        <v>3.129</v>
       </c>
       <c r="BJ65" s="3" t="n">
-        <v>3.544</v>
+        <v>3.1885</v>
       </c>
       <c r="BK65" s="3" t="n">
-        <v>1.91</v>
+        <v>1.7132</v>
       </c>
       <c r="BL65" s="3" t="n">
-        <v>3.08</v>
+        <v>3.1885</v>
       </c>
       <c r="BM65" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.2504</v>
       </c>
       <c r="BN65" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.2504</v>
       </c>
       <c r="BO65" s="3" t="n">
-        <v>1.99</v>
+        <v>1.7641</v>
       </c>
       <c r="BP65" s="3" t="n">
-        <v>2.0795</v>
+        <v>1.8446</v>
       </c>
       <c r="BQ65" s="3" t="n">
-        <v>2.375</v>
+        <v>2.3825</v>
       </c>
       <c r="BR65" s="3" t="n">
-        <v>1.73</v>
+        <v>1.8104</v>
       </c>
     </row>
     <row r="66">
@@ -14578,211 +14578,211 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA66" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB66" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC66" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD66" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE66" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF66" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG66" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH66" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ66" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL66" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM66" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN66" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO66" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP66" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ66" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR66" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS66" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT66" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV66" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW66" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX66" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY66" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA66" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB66" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC66" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD66" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE66" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF66" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH66" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ66" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK66" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL66" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM66" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN66" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO66" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP66" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ66" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR66" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="67">
@@ -14792,211 +14792,211 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V67" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W67" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X67" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y67" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z67" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA67" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB67" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC67" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD67" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE67" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF67" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG67" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH67" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ67" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL67" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM67" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN67" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP67" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ67" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR67" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS67" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT67" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV67" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW67" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX67" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY67" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ67" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA67" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB67" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC67" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD67" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE67" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF67" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG67" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH67" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ67" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK67" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL67" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM67" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN67" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO67" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP67" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ67" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR67" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="68">
@@ -15006,211 +15006,211 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X68" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA68" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB68" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC68" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD68" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE68" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF68" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG68" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH68" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ68" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM68" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN68" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO68" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP68" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ68" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR68" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS68" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT68" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV68" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW68" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX68" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY68" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ68" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA68" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB68" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC68" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD68" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE68" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF68" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG68" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH68" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ68" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK68" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL68" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM68" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN68" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO68" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP68" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ68" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR68" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="69">
@@ -15220,211 +15220,211 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA69" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB69" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC69" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD69" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE69" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF69" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG69" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH69" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ69" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM69" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN69" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP69" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ69" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR69" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS69" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT69" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV69" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW69" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX69" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY69" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ69" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA69" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB69" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC69" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD69" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE69" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF69" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG69" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH69" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ69" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK69" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL69" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM69" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN69" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO69" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP69" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ69" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR69" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="70">
@@ -15434,211 +15434,211 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T70" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X70" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z70" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA70" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB70" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC70" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD70" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE70" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF70" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG70" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH70" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ70" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM70" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN70" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP70" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ70" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR70" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS70" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT70" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV70" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW70" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX70" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY70" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ70" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA70" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB70" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC70" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD70" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE70" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF70" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG70" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH70" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ70" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK70" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL70" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM70" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN70" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO70" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP70" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ70" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR70" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="71">
@@ -15648,211 +15648,211 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA71" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB71" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC71" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD71" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE71" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF71" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG71" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH71" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ71" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL71" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN71" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP71" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ71" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR71" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS71" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT71" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV71" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW71" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX71" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY71" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA71" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB71" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC71" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD71" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE71" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF71" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH71" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ71" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK71" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL71" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM71" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN71" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO71" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP71" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ71" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR71" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="72">
@@ -15862,211 +15862,211 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y72" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z72" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA72" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB72" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC72" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD72" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE72" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF72" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG72" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH72" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ72" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL72" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN72" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP72" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ72" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR72" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS72" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT72" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV72" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW72" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX72" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY72" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ72" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA72" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB72" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC72" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD72" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE72" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF72" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG72" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH72" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ72" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK72" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL72" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM72" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN72" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO72" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP72" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ72" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR72" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="73">
@@ -16076,211 +16076,211 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X73" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA73" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB73" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC73" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD73" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE73" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF73" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG73" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH73" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ73" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL73" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM73" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN73" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO73" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP73" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ73" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR73" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS73" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT73" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV73" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW73" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX73" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY73" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ73" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA73" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB73" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC73" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD73" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE73" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF73" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG73" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH73" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ73" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK73" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL73" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM73" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN73" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO73" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP73" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ73" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR73" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="74">
@@ -16290,211 +16290,211 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA74" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB74" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC74" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD74" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE74" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF74" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG74" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH74" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ74" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL74" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM74" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN74" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO74" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP74" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ74" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR74" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS74" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT74" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV74" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW74" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX74" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY74" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ74" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA74" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB74" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC74" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD74" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE74" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF74" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG74" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH74" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL74" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM74" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN74" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO74" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP74" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR74" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="75">
@@ -16504,211 +16504,211 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T75" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X75" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y75" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z75" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA75" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB75" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC75" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD75" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE75" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF75" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG75" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH75" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ75" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL75" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM75" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN75" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO75" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP75" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ75" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR75" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS75" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT75" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV75" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW75" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX75" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY75" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ75" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA75" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB75" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC75" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD75" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE75" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF75" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG75" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH75" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL75" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM75" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN75" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO75" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP75" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR75" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="76">
@@ -16718,211 +16718,211 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA76" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB76" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC76" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD76" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE76" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF76" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG76" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH76" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ76" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL76" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM76" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN76" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO76" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP76" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ76" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR76" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS76" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT76" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV76" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW76" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX76" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY76" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ76" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA76" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB76" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC76" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD76" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE76" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF76" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG76" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH76" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL76" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM76" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN76" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO76" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP76" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR76" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="77">
@@ -16932,211 +16932,211 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q77" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R77" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S77" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T77" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X77" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y77" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z77" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA77" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB77" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC77" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD77" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE77" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF77" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG77" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH77" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ77" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL77" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM77" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN77" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO77" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP77" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ77" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR77" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS77" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT77" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV77" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW77" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX77" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY77" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ77" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA77" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB77" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC77" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD77" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE77" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF77" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG77" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH77" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL77" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM77" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN77" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO77" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP77" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR77" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="78">
@@ -17146,211 +17146,211 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X78" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y78" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA78" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB78" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC78" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD78" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE78" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF78" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG78" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH78" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ78" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL78" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM78" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN78" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO78" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP78" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ78" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR78" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS78" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT78" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV78" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW78" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX78" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY78" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ78" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA78" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB78" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC78" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD78" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE78" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF78" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG78" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH78" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL78" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM78" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN78" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO78" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP78" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR78" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="79">
@@ -17360,211 +17360,211 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA79" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB79" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC79" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD79" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE79" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF79" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG79" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH79" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ79" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL79" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM79" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN79" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO79" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP79" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ79" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR79" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS79" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT79" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV79" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW79" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX79" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY79" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ79" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA79" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB79" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC79" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD79" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE79" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF79" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG79" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH79" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL79" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM79" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN79" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO79" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP79" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR79" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="80">
@@ -17574,211 +17574,211 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T80" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X80" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y80" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z80" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA80" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB80" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC80" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD80" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE80" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF80" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG80" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH80" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ80" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK80" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL80" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM80" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN80" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO80" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP80" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ80" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR80" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS80" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT80" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV80" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW80" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX80" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY80" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ80" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA80" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB80" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC80" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD80" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE80" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF80" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG80" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH80" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL80" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM80" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN80" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO80" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP80" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR80" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="81">
@@ -17788,211 +17788,211 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P81" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R81" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S81" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T81" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X81" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA81" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB81" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC81" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD81" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE81" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF81" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG81" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH81" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ81" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL81" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM81" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN81" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO81" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP81" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ81" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR81" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS81" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT81" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV81" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW81" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX81" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY81" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ81" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA81" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB81" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC81" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD81" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE81" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF81" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG81" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH81" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL81" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM81" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN81" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO81" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP81" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR81" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="82">
@@ -18002,211 +18002,211 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P82" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R82" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S82" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T82" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U82" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W82" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X82" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y82" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA82" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB82" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC82" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD82" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE82" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF82" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG82" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH82" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ82" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK82" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL82" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM82" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN82" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO82" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP82" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ82" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR82" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS82" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT82" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV82" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW82" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX82" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY82" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ82" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA82" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB82" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC82" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD82" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE82" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF82" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG82" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH82" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL82" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM82" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN82" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO82" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP82" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR82" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="83">
@@ -18216,211 +18216,211 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P83" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W83" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X83" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y83" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA83" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB83" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC83" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD83" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE83" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF83" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG83" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH83" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ83" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK83" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM83" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN83" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO83" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP83" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ83" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR83" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS83" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT83" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV83" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW83" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX83" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY83" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ83" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA83" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB83" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC83" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD83" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE83" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF83" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG83" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH83" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL83" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM83" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN83" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO83" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP83" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR83" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="84">
@@ -18430,211 +18430,211 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA84" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB84" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC84" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD84" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE84" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF84" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG84" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH84" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ84" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL84" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM84" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN84" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO84" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP84" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ84" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR84" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS84" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT84" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV84" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW84" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX84" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY84" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ84" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA84" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB84" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC84" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD84" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE84" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF84" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG84" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH84" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL84" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM84" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN84" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO84" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP84" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR84" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="85">
@@ -18644,211 +18644,211 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X85" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA85" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB85" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC85" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD85" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE85" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF85" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG85" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH85" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ85" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK85" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM85" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN85" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO85" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP85" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ85" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR85" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS85" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT85" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV85" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW85" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX85" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY85" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ85" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA85" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB85" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC85" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD85" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE85" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF85" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG85" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH85" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL85" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM85" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN85" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO85" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP85" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR85" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="86">
@@ -18858,211 +18858,211 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA86" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB86" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC86" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD86" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE86" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF86" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG86" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH86" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ86" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK86" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM86" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN86" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO86" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP86" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ86" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR86" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS86" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT86" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV86" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW86" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX86" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY86" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA86" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB86" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC86" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD86" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE86" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF86" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH86" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL86" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM86" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN86" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO86" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP86" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR86" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="87">
@@ -19072,211 +19072,211 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P87" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W87" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X87" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z87" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA87" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB87" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC87" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD87" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE87" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF87" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG87" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH87" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ87" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK87" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM87" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN87" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO87" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP87" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ87" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR87" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS87" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT87" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV87" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW87" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX87" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY87" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ87" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA87" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB87" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC87" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD87" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE87" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF87" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG87" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH87" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ87" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK87" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL87" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM87" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN87" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO87" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP87" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ87" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR87" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="88">
@@ -19286,211 +19286,211 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W88" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X88" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y88" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA88" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB88" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC88" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD88" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE88" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF88" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG88" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH88" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ88" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK88" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM88" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN88" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO88" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP88" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ88" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR88" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS88" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT88" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV88" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW88" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX88" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY88" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ88" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA88" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB88" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC88" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD88" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE88" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF88" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG88" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH88" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ88" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK88" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL88" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM88" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN88" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO88" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP88" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ88" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR88" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="89">
@@ -19500,211 +19500,211 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA89" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB89" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC89" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD89" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE89" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF89" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG89" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH89" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI89" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ89" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK89" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL89" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM89" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN89" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO89" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP89" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ89" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR89" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS89" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT89" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV89" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW89" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX89" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY89" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ89" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA89" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB89" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC89" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD89" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE89" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF89" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG89" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH89" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ89" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK89" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL89" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM89" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN89" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO89" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP89" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ89" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR89" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="90">
@@ -19714,211 +19714,211 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA90" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB90" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC90" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD90" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE90" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF90" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG90" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH90" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI90" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ90" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK90" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL90" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM90" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN90" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO90" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP90" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ90" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR90" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS90" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT90" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV90" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW90" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX90" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY90" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ90" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA90" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB90" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC90" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD90" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE90" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF90" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG90" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH90" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ90" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK90" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL90" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM90" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN90" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO90" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP90" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ90" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR90" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="91">
@@ -19928,211 +19928,211 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA91" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB91" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC91" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD91" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE91" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF91" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG91" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH91" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI91" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ91" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK91" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL91" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM91" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN91" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO91" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP91" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ91" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR91" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS91" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT91" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV91" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW91" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX91" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY91" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ91" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA91" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB91" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC91" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD91" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE91" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF91" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG91" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH91" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ91" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK91" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL91" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM91" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN91" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO91" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP91" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ91" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR91" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="92">
@@ -20142,211 +20142,211 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W92" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X92" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA92" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB92" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC92" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD92" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE92" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF92" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG92" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH92" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI92" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ92" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK92" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL92" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM92" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN92" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO92" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP92" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ92" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR92" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS92" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT92" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV92" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW92" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX92" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY92" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ92" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA92" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB92" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC92" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD92" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE92" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF92" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG92" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH92" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ92" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK92" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL92" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM92" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN92" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO92" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP92" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ92" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR92" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="93">
@@ -20356,211 +20356,211 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>2.47</v>
+        <v>2.465</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.332</v>
+        <v>2.348</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2.51</v>
+        <v>2.505</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2.309</v>
+        <v>2.304</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.31</v>
+        <v>2.305</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>2.471</v>
+        <v>2.466</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>1.7555</v>
+        <v>1.7505</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>1.848</v>
+        <v>1.865</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>2.465</v>
+        <v>2.5</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>3.73</v>
+        <v>3.725</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>2.399</v>
+        <v>2.34</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>2.722</v>
+        <v>2.717</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>2.5025</v>
+        <v>2.4975</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>2.57</v>
+        <v>2.565</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>2.4225</v>
+        <v>2.3635</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>2.745</v>
+        <v>2.6475</v>
       </c>
       <c r="V93" s="3" t="n">
-        <v>2.445</v>
+        <v>2.44</v>
       </c>
       <c r="W93" s="3" t="n">
-        <v>1.95</v>
+        <v>1.967</v>
       </c>
       <c r="X93" s="3" t="n">
-        <v>2.365</v>
+        <v>2.397</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>2.39</v>
+        <v>2.385</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>2.399</v>
+        <v>2.394</v>
       </c>
       <c r="AA93" s="3" t="n">
-        <v>2.43</v>
+        <v>2.425</v>
       </c>
       <c r="AB93" s="3" t="n">
-        <v>2.451</v>
+        <v>2.446</v>
       </c>
       <c r="AC93" s="3" t="n">
-        <v>2.4625</v>
+        <v>2.45</v>
       </c>
       <c r="AD93" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="AE93" s="3" t="n">
-        <v>2.282</v>
+        <v>2.277</v>
       </c>
       <c r="AF93" s="3" t="n">
-        <v>3.2</v>
+        <v>3.195</v>
       </c>
       <c r="AG93" s="3" t="n">
-        <v>2.665</v>
+        <v>2.6</v>
       </c>
       <c r="AH93" s="3" t="n">
-        <v>2.321</v>
+        <v>2.337</v>
       </c>
       <c r="AI93" s="3" t="n">
-        <v>1.818</v>
+        <v>1.813</v>
       </c>
       <c r="AJ93" s="3" t="n">
-        <v>2.5755</v>
+        <v>2.5705</v>
       </c>
       <c r="AK93" s="3" t="n">
         <v>2.415</v>
       </c>
       <c r="AL93" s="3" t="n">
-        <v>2.383</v>
+        <v>2.378</v>
       </c>
       <c r="AM93" s="3" t="n">
-        <v>2.9175</v>
+        <v>2.82</v>
       </c>
       <c r="AN93" s="3" t="n">
-        <v>3.7495</v>
+        <v>3.652</v>
       </c>
       <c r="AO93" s="3" t="n">
-        <v>3.528</v>
+        <v>3.523</v>
       </c>
       <c r="AP93" s="3" t="n">
-        <v>2.344</v>
+        <v>2.339</v>
       </c>
       <c r="AQ93" s="3" t="n">
-        <v>1.99</v>
+        <v>2.007</v>
       </c>
       <c r="AR93" s="3" t="n">
-        <v>2.4105</v>
+        <v>2.4055</v>
       </c>
       <c r="AS93" s="3" t="n">
-        <v>1.8775</v>
+        <v>1.8945</v>
       </c>
       <c r="AT93" s="3" t="n">
-        <v>2.008</v>
+        <v>2.003</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>2.34</v>
+        <v>2.335</v>
       </c>
       <c r="AV93" s="3" t="n">
-        <v>2.516</v>
+        <v>2.511</v>
       </c>
       <c r="AW93" s="3" t="n">
-        <v>3.478</v>
+        <v>3.473</v>
       </c>
       <c r="AX93" s="3" t="n">
-        <v>2.374</v>
+        <v>2.369</v>
       </c>
       <c r="AY93" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="AZ93" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BA93" s="3" t="n">
-        <v>2.12</v>
+        <v>2.112</v>
       </c>
       <c r="BB93" s="3" t="n">
-        <v>1.847</v>
+        <v>1.864</v>
       </c>
       <c r="BC93" s="3" t="n">
-        <v>2.4475</v>
+        <v>2.4425</v>
       </c>
       <c r="BD93" s="3" t="n">
-        <v>2.3855</v>
+        <v>2.3805</v>
       </c>
       <c r="BE93" s="3" t="n">
-        <v>2.45</v>
+        <v>2.445</v>
       </c>
       <c r="BF93" s="3" t="n">
-        <v>1.963</v>
+        <v>1.958</v>
       </c>
       <c r="BG93" s="3" t="n">
-        <v>2.4</v>
+        <v>2.395</v>
       </c>
       <c r="BH93" s="3" t="n">
-        <v>2.4575</v>
+        <v>2.4525</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>3.465</v>
+        <v>3.475</v>
       </c>
       <c r="BJ93" s="3" t="n">
-        <v>3.544</v>
+        <v>3.5</v>
       </c>
       <c r="BK93" s="3" t="n">
-        <v>1.91</v>
+        <v>1.905</v>
       </c>
       <c r="BL93" s="3" t="n">
-        <v>3.08</v>
+        <v>3.0755</v>
       </c>
       <c r="BM93" s="3" t="n">
-        <v>3.1125</v>
+        <v>3.1075</v>
       </c>
       <c r="BN93" s="3" t="n">
-        <v>3.6955</v>
+        <v>3.6905</v>
       </c>
       <c r="BO93" s="3" t="n">
-        <v>1.99</v>
+        <v>1.985</v>
       </c>
       <c r="BP93" s="3" t="n">
-        <v>2.0795</v>
+        <v>2.0745</v>
       </c>
       <c r="BQ93" s="3" t="n">
-        <v>2.375</v>
+        <v>2.37</v>
       </c>
       <c r="BR93" s="3" t="n">
-        <v>1.73</v>
+        <v>1.725</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -14578,211 +14578,211 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>2.4233</v>
+        <v>2.425</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2.348</v>
+        <v>2.35</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2.3935</v>
+        <v>2.395</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.4682</v>
+        <v>2.47</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2.3075</v>
+        <v>2.31</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2.3102</v>
+        <v>2.31</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.4614</v>
+        <v>2.465</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.4759</v>
+        <v>2.475</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>2.1186</v>
+        <v>2.115</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.9074</v>
+        <v>1.905</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>2.4053</v>
+        <v>2.465</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.545</v>
+        <v>2.54</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.5604</v>
+        <v>3.375</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>2.3598</v>
+        <v>2.36</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>2.8021</v>
+        <v>2.8</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>2.7109</v>
+        <v>2.71</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.9229</v>
+        <v>2.9</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.3595</v>
+        <v>2.365</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.4235</v>
+        <v>2.775</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.4431</v>
+        <v>2.445</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.8323</v>
+        <v>1.83</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.3458</v>
+        <v>2.345</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.3372</v>
+        <v>2.335</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.3834</v>
+        <v>2.385</v>
       </c>
       <c r="AA66" s="3" t="n">
-        <v>2.4326</v>
+        <v>2.435</v>
       </c>
       <c r="AB66" s="3" t="n">
-        <v>2.4065</v>
+        <v>2.405</v>
       </c>
       <c r="AC66" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="AD66" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AE66" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="AF66" s="3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG66" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH66" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI66" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ66" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK66" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AL66" s="3" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="AM66" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AN66" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AO66" s="3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AP66" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ66" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AR66" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS66" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT66" s="3" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AU66" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AV66" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="AW66" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AX66" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="AD66" s="3" t="n">
-        <v>2.441</v>
-      </c>
-      <c r="AE66" s="3" t="n">
-        <v>2.3036</v>
-      </c>
-      <c r="AF66" s="3" t="n">
-        <v>3.1111</v>
-      </c>
-      <c r="AG66" s="3" t="n">
-        <v>2.5525</v>
-      </c>
-      <c r="AH66" s="3" t="n">
-        <v>2.2781</v>
-      </c>
-      <c r="AI66" s="3" t="n">
-        <v>2.1148</v>
-      </c>
-      <c r="AJ66" s="3" t="n">
-        <v>2.4799</v>
-      </c>
-      <c r="AK66" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AL66" s="3" t="n">
-        <v>2.3338</v>
-      </c>
-      <c r="AM66" s="3" t="n">
-        <v>2.7781</v>
-      </c>
-      <c r="AN66" s="3" t="n">
-        <v>3.668</v>
-      </c>
-      <c r="AO66" s="3" t="n">
-        <v>3.3103</v>
-      </c>
-      <c r="AP66" s="3" t="n">
-        <v>2.3416</v>
-      </c>
-      <c r="AQ66" s="3" t="n">
-        <v>2.0217</v>
-      </c>
-      <c r="AR66" s="3" t="n">
-        <v>2.4997</v>
-      </c>
-      <c r="AS66" s="3" t="n">
-        <v>2.0098</v>
-      </c>
-      <c r="AT66" s="3" t="n">
-        <v>2.1235</v>
-      </c>
-      <c r="AU66" s="3" t="n">
-        <v>2.3493</v>
-      </c>
-      <c r="AV66" s="3" t="n">
-        <v>2.4574</v>
-      </c>
-      <c r="AW66" s="3" t="n">
-        <v>3.1999</v>
-      </c>
-      <c r="AX66" s="3" t="n">
-        <v>2.4008</v>
-      </c>
       <c r="AY66" s="3" t="n">
-        <v>2.348</v>
+        <v>2.35</v>
       </c>
       <c r="AZ66" s="3" t="n">
-        <v>2.366</v>
+        <v>2.41</v>
       </c>
       <c r="BA66" s="3" t="n">
-        <v>2.1597</v>
+        <v>2.165</v>
       </c>
       <c r="BB66" s="3" t="n">
-        <v>1.7172</v>
+        <v>1.715</v>
       </c>
       <c r="BC66" s="3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BD66" s="3" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="BE66" s="3" t="n">
-        <v>2.4386</v>
+        <v>2.44</v>
       </c>
       <c r="BF66" s="3" t="n">
-        <v>2.1235</v>
+        <v>2.125</v>
       </c>
       <c r="BG66" s="3" t="n">
-        <v>2.3572</v>
+        <v>2.355</v>
       </c>
       <c r="BH66" s="3" t="n">
-        <v>2.4032</v>
+        <v>2.405</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>3.3639</v>
+        <v>3.365</v>
       </c>
       <c r="BJ66" s="3" t="n">
-        <v>3.4104</v>
+        <v>3.41</v>
       </c>
       <c r="BK66" s="3" t="n">
-        <v>1.8195</v>
+        <v>1.82</v>
       </c>
       <c r="BL66" s="3" t="n">
-        <v>3.4104</v>
+        <v>3.055</v>
       </c>
       <c r="BM66" s="3" t="n">
-        <v>3.4641</v>
+        <v>2.92</v>
       </c>
       <c r="BN66" s="3" t="n">
-        <v>3.4641</v>
+        <v>3.47</v>
       </c>
       <c r="BO66" s="3" t="n">
-        <v>2.0735</v>
+        <v>2.135</v>
       </c>
       <c r="BP66" s="3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BQ66" s="3" t="n">
-        <v>2.4062</v>
+        <v>2.405</v>
       </c>
       <c r="BR66" s="3" t="n">
-        <v>2.1184</v>
+        <v>2.105</v>
       </c>
     </row>
     <row r="67">
@@ -14792,211 +14792,211 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>2.43</v>
+        <v>2.4129</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2.289</v>
+        <v>2.3228</v>
       </c>
       <c r="D67" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>2.3047</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>2.4066</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>2.2815</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>2.2922</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>2.3992</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>2.4005</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>2.0073</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>1.9269</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>2.3474</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>2.4825</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>3.3766</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>2.7268</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>2.5885</v>
+      </c>
+      <c r="S67" s="3" t="n">
+        <v>2.7031</v>
+      </c>
+      <c r="T67" s="3" t="n">
+        <v>2.2732</v>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>2.4002</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>2.3801</v>
+      </c>
+      <c r="W67" s="3" t="n">
+        <v>1.9065</v>
+      </c>
+      <c r="X67" s="3" t="n">
+        <v>2.3148</v>
+      </c>
+      <c r="Y67" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>2.3144</v>
+      </c>
+      <c r="AA67" s="3" t="n">
+        <v>2.3734</v>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>2.3559</v>
+      </c>
+      <c r="AC67" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="AD67" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E67" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M67" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N67" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O67" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P67" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q67" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R67" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S67" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T67" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U67" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V67" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W67" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X67" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y67" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z67" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA67" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB67" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC67" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD67" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE67" s="3" t="n">
-        <v>2.25</v>
+        <v>2.2475</v>
       </c>
       <c r="AF67" s="3" t="n">
-        <v>3.03</v>
+        <v>2.9037</v>
       </c>
       <c r="AG67" s="3" t="n">
-        <v>2.55</v>
+        <v>2.4797</v>
       </c>
       <c r="AH67" s="3" t="n">
-        <v>2.278</v>
+        <v>2.2282</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>1.938</v>
+        <v>2.0287</v>
       </c>
       <c r="AJ67" s="3" t="n">
-        <v>2.52</v>
+        <v>2.4076</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>2.379</v>
+        <v>2.34</v>
       </c>
       <c r="AL67" s="3" t="n">
-        <v>2.275</v>
+        <v>2.2558</v>
       </c>
       <c r="AM67" s="3" t="n">
-        <v>2.678</v>
+        <v>2.7823</v>
       </c>
       <c r="AN67" s="3" t="n">
-        <v>3.51</v>
+        <v>3.6787</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>3.48</v>
+        <v>3.2083</v>
       </c>
       <c r="AP67" s="3" t="n">
-        <v>2.3</v>
+        <v>2.3072</v>
       </c>
       <c r="AQ67" s="3" t="n">
-        <v>2.02</v>
+        <v>2.035</v>
       </c>
       <c r="AR67" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.4021</v>
       </c>
       <c r="AS67" s="3" t="n">
-        <v>1.9055</v>
+        <v>2.012</v>
       </c>
       <c r="AT67" s="3" t="n">
-        <v>2.014</v>
+        <v>2.12</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>2.3</v>
+        <v>2.2752</v>
       </c>
       <c r="AV67" s="3" t="n">
-        <v>2.48</v>
+        <v>2.3903</v>
       </c>
       <c r="AW67" s="3" t="n">
-        <v>3.43</v>
+        <v>3.1826</v>
       </c>
       <c r="AX67" s="3" t="n">
-        <v>2.34</v>
+        <v>2.3442</v>
       </c>
       <c r="AY67" s="3" t="n">
-        <v>2.33</v>
+        <v>2.2698</v>
       </c>
       <c r="AZ67" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA67" s="3" t="n">
-        <v>2.123</v>
+        <v>2.1436</v>
       </c>
       <c r="BB67" s="3" t="n">
-        <v>1.877</v>
+        <v>1.8641</v>
       </c>
       <c r="BC67" s="3" t="n">
-        <v>2.3975</v>
+        <v>3.05</v>
       </c>
       <c r="BD67" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.85</v>
       </c>
       <c r="BE67" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3448</v>
       </c>
       <c r="BF67" s="3" t="n">
-        <v>1.969</v>
+        <v>2.12</v>
       </c>
       <c r="BG67" s="3" t="n">
-        <v>2.35</v>
+        <v>2.2662</v>
       </c>
       <c r="BH67" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3855</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>3.433</v>
+        <v>3.1971</v>
       </c>
       <c r="BJ67" s="3" t="n">
-        <v>3.458</v>
+        <v>3.2266</v>
       </c>
       <c r="BK67" s="3" t="n">
-        <v>1.85</v>
+        <v>1.9769</v>
       </c>
       <c r="BL67" s="3" t="n">
-        <v>3.0865</v>
+        <v>3.2266</v>
       </c>
       <c r="BM67" s="3" t="n">
-        <v>3.067</v>
+        <v>3.3376</v>
       </c>
       <c r="BN67" s="3" t="n">
-        <v>3.65</v>
+        <v>3.3376</v>
       </c>
       <c r="BO67" s="3" t="n">
-        <v>1.996</v>
+        <v>2.07</v>
       </c>
       <c r="BP67" s="3" t="n">
-        <v>2.0855</v>
+        <v>2.1937</v>
       </c>
       <c r="BQ67" s="3" t="n">
-        <v>2.381</v>
+        <v>2.3137</v>
       </c>
       <c r="BR67" s="3" t="n">
-        <v>1.85</v>
+        <v>2.0128</v>
       </c>
     </row>
     <row r="68">
@@ -15006,211 +15006,211 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D68" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S68" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T68" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U68" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W68" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X68" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y68" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA68" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC68" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD68" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E68" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M68" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N68" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O68" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P68" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q68" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R68" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S68" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T68" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U68" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V68" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W68" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X68" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y68" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z68" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA68" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB68" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC68" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD68" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE68" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF68" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG68" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH68" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ68" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM68" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN68" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO68" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP68" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ68" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR68" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS68" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT68" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV68" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW68" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX68" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY68" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ68" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA68" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB68" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC68" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD68" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE68" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF68" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG68" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH68" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ68" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK68" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL68" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM68" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN68" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO68" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP68" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ68" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR68" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="69">
@@ -15220,211 +15220,211 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D69" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S69" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T69" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W69" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y69" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA69" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC69" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD69" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E69" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O69" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q69" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R69" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S69" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T69" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U69" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V69" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W69" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X69" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y69" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z69" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA69" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB69" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC69" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD69" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE69" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF69" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG69" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH69" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ69" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM69" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN69" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP69" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ69" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR69" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS69" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT69" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV69" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW69" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX69" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY69" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ69" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA69" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB69" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC69" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD69" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE69" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF69" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG69" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH69" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ69" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK69" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL69" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM69" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN69" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO69" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP69" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ69" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR69" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="70">
@@ -15434,211 +15434,211 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D70" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q70" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S70" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T70" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W70" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y70" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z70" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA70" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC70" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD70" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E70" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M70" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N70" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O70" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P70" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q70" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R70" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S70" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T70" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U70" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V70" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W70" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X70" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y70" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z70" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA70" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB70" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC70" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD70" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE70" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF70" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG70" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH70" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ70" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM70" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN70" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP70" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ70" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR70" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS70" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT70" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV70" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW70" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX70" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY70" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ70" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA70" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB70" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC70" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD70" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE70" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF70" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG70" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH70" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ70" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK70" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL70" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM70" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN70" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO70" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP70" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ70" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR70" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="71">
@@ -15648,211 +15648,211 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D71" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W71" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA71" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC71" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD71" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E71" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R71" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S71" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T71" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U71" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V71" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W71" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X71" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y71" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z71" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA71" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB71" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC71" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD71" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE71" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF71" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG71" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH71" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ71" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL71" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN71" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP71" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ71" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR71" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS71" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT71" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV71" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW71" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX71" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY71" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ71" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA71" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB71" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC71" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD71" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF71" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG71" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH71" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ71" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK71" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL71" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM71" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN71" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO71" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP71" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ71" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR71" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="72">
@@ -15862,211 +15862,211 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D72" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S72" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T72" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U72" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V72" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W72" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y72" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA72" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC72" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD72" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E72" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M72" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N72" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O72" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P72" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q72" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R72" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S72" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T72" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U72" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V72" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W72" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X72" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y72" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z72" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA72" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB72" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC72" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD72" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE72" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF72" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG72" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH72" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ72" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL72" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN72" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP72" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ72" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR72" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS72" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT72" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV72" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW72" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX72" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY72" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ72" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA72" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB72" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC72" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD72" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE72" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF72" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG72" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH72" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ72" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK72" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL72" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM72" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN72" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO72" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP72" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ72" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR72" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="73">
@@ -16076,211 +16076,211 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D73" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S73" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T73" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V73" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W73" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y73" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z73" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA73" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC73" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD73" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N73" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O73" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P73" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q73" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R73" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S73" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T73" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U73" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V73" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W73" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X73" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y73" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z73" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA73" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB73" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC73" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD73" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE73" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF73" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG73" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH73" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ73" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL73" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM73" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN73" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO73" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP73" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ73" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR73" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS73" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT73" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV73" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW73" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX73" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY73" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ73" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA73" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB73" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC73" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD73" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE73" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF73" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG73" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH73" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ73" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK73" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL73" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM73" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN73" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO73" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP73" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ73" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR73" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="74">
@@ -16290,211 +16290,211 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D74" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S74" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T74" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y74" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC74" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD74" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E74" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N74" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O74" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P74" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q74" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R74" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S74" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T74" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U74" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V74" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W74" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X74" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y74" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z74" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA74" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB74" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC74" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD74" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE74" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF74" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG74" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH74" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ74" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL74" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM74" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN74" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO74" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP74" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ74" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR74" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS74" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT74" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV74" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW74" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX74" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY74" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ74" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA74" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB74" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC74" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD74" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE74" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF74" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG74" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH74" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL74" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM74" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN74" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO74" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP74" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR74" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="75">
@@ -16504,211 +16504,211 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D75" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S75" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC75" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD75" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E75" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J75" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M75" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N75" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O75" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P75" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q75" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R75" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S75" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T75" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U75" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V75" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W75" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X75" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y75" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z75" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA75" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB75" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC75" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD75" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE75" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF75" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG75" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH75" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ75" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL75" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM75" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN75" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO75" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP75" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ75" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR75" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS75" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT75" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV75" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW75" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX75" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY75" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ75" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA75" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB75" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC75" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD75" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE75" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF75" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG75" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH75" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL75" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM75" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN75" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO75" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP75" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR75" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="76">
@@ -16718,211 +16718,211 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D76" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA76" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC76" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD76" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E76" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z76" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA76" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB76" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC76" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD76" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE76" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF76" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG76" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH76" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ76" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL76" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM76" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN76" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO76" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP76" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ76" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR76" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS76" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT76" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV76" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW76" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX76" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY76" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ76" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA76" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB76" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC76" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD76" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE76" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF76" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH76" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL76" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM76" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN76" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO76" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP76" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR76" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="77">
@@ -16932,211 +16932,211 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D77" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S77" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA77" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC77" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD77" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E77" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M77" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N77" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O77" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P77" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q77" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R77" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S77" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T77" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U77" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V77" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W77" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X77" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y77" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z77" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA77" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB77" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC77" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD77" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE77" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF77" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG77" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH77" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ77" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL77" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM77" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN77" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO77" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP77" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ77" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR77" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS77" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT77" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV77" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW77" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX77" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY77" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ77" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA77" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB77" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC77" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD77" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE77" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF77" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG77" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH77" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL77" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM77" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN77" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO77" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP77" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR77" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="78">
@@ -17146,211 +17146,211 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D78" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S78" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA78" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC78" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD78" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E78" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N78" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O78" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P78" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q78" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R78" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S78" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T78" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U78" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V78" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W78" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X78" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y78" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z78" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA78" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB78" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC78" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD78" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE78" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF78" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG78" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH78" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ78" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL78" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM78" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN78" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO78" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP78" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ78" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR78" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS78" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT78" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV78" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW78" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX78" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY78" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ78" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA78" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB78" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC78" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD78" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE78" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF78" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG78" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH78" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL78" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM78" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN78" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO78" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP78" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR78" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="79">
@@ -17360,211 +17360,211 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D79" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA79" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD79" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E79" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H79" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T79" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U79" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V79" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W79" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X79" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y79" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z79" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA79" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB79" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC79" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD79" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE79" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF79" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG79" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH79" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ79" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL79" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM79" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN79" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO79" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP79" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ79" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR79" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS79" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT79" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV79" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW79" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX79" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY79" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ79" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA79" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB79" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC79" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD79" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE79" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF79" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG79" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH79" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL79" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM79" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN79" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO79" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP79" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR79" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="80">
@@ -17574,211 +17574,211 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D80" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD80" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E80" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H80" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N80" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O80" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P80" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q80" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R80" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S80" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T80" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U80" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V80" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W80" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X80" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y80" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z80" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA80" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB80" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC80" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD80" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE80" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF80" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG80" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH80" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ80" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL80" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM80" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN80" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO80" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP80" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ80" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR80" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS80" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT80" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV80" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW80" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX80" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY80" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ80" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA80" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB80" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC80" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD80" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE80" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF80" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG80" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH80" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL80" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM80" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN80" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO80" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP80" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR80" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="81">
@@ -17788,211 +17788,211 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D81" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S81" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA81" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD81" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E81" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M81" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N81" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O81" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P81" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q81" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R81" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S81" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T81" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U81" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V81" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W81" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X81" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y81" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z81" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA81" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB81" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC81" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD81" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE81" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF81" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG81" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH81" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ81" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL81" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM81" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN81" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO81" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP81" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ81" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR81" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS81" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT81" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV81" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW81" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX81" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY81" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ81" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA81" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB81" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC81" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD81" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE81" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF81" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG81" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH81" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL81" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM81" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN81" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO81" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP81" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR81" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="82">
@@ -18002,211 +18002,211 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D82" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S82" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA82" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD82" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E82" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N82" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O82" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P82" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q82" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R82" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S82" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T82" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U82" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V82" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W82" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X82" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y82" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z82" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA82" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB82" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC82" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD82" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE82" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF82" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG82" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH82" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ82" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL82" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM82" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN82" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO82" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP82" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ82" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR82" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS82" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT82" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV82" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW82" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX82" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY82" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ82" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA82" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB82" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC82" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD82" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE82" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF82" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG82" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH82" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL82" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM82" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN82" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO82" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP82" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR82" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="83">
@@ -18216,211 +18216,211 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D83" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S83" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA83" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC83" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD83" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E83" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N83" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O83" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P83" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q83" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R83" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S83" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T83" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U83" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V83" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W83" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X83" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y83" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z83" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA83" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB83" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC83" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD83" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE83" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF83" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG83" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH83" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ83" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM83" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN83" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO83" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP83" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ83" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR83" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS83" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT83" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV83" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW83" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX83" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY83" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ83" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA83" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB83" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC83" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD83" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE83" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF83" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG83" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH83" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL83" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM83" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN83" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO83" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP83" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR83" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="84">
@@ -18430,211 +18430,211 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D84" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA84" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB84" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC84" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD84" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E84" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N84" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O84" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q84" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R84" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S84" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T84" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U84" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V84" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W84" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X84" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y84" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z84" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA84" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB84" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC84" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD84" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE84" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF84" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG84" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH84" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ84" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL84" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM84" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN84" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO84" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP84" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ84" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR84" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS84" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT84" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV84" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW84" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX84" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY84" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ84" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA84" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB84" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC84" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD84" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE84" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF84" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG84" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH84" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL84" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM84" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN84" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO84" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP84" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR84" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="85">
@@ -18644,211 +18644,211 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D85" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S85" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T85" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W85" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y85" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA85" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC85" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD85" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E85" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M85" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N85" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O85" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P85" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q85" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R85" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S85" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T85" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U85" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V85" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W85" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X85" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y85" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z85" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA85" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB85" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC85" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD85" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE85" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF85" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG85" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH85" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ85" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM85" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN85" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO85" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP85" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ85" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR85" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS85" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT85" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV85" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW85" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX85" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY85" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ85" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA85" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB85" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC85" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD85" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE85" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF85" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG85" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH85" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL85" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM85" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN85" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO85" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP85" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR85" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="86">
@@ -18858,211 +18858,211 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D86" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y86" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z86" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA86" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC86" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD86" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E86" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T86" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U86" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V86" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W86" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X86" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y86" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z86" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA86" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB86" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC86" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD86" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE86" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF86" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG86" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH86" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ86" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM86" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN86" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO86" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP86" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ86" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR86" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS86" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT86" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV86" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW86" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX86" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY86" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ86" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA86" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB86" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC86" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD86" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF86" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG86" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH86" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL86" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM86" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN86" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO86" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP86" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR86" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="87">
@@ -19072,211 +19072,211 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D87" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S87" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T87" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W87" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y87" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA87" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB87" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC87" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD87" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N87" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O87" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q87" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R87" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S87" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T87" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U87" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V87" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W87" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X87" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y87" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z87" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA87" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB87" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC87" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD87" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE87" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF87" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG87" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH87" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ87" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM87" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN87" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO87" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP87" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ87" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR87" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS87" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT87" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV87" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW87" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX87" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY87" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ87" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA87" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB87" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC87" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD87" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE87" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF87" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG87" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH87" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ87" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK87" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL87" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM87" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN87" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO87" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP87" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ87" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR87" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="88">
@@ -19286,211 +19286,211 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D88" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q88" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S88" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T88" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W88" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y88" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z88" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA88" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB88" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC88" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD88" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E88" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N88" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O88" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P88" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q88" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R88" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S88" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T88" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U88" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V88" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W88" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X88" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y88" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z88" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA88" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB88" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC88" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD88" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE88" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF88" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG88" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH88" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ88" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM88" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN88" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO88" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP88" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ88" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR88" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS88" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT88" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV88" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW88" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX88" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY88" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ88" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA88" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB88" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC88" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD88" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE88" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF88" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG88" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH88" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ88" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK88" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL88" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM88" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN88" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO88" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP88" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ88" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR88" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="89">
@@ -19500,211 +19500,211 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D89" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S89" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T89" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W89" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y89" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA89" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB89" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC89" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD89" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E89" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N89" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O89" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P89" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q89" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R89" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S89" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T89" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U89" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V89" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W89" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X89" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y89" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z89" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA89" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB89" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC89" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD89" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE89" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF89" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG89" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH89" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI89" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ89" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL89" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM89" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN89" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO89" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP89" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ89" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR89" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS89" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT89" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV89" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW89" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX89" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY89" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ89" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA89" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB89" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC89" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD89" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE89" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF89" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG89" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH89" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ89" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK89" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL89" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM89" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN89" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO89" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP89" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ89" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR89" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="90">
@@ -19714,211 +19714,211 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D90" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q90" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S90" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W90" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y90" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z90" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA90" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC90" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD90" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E90" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M90" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N90" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O90" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P90" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q90" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R90" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S90" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T90" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U90" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V90" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W90" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X90" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y90" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z90" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA90" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB90" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC90" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD90" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE90" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF90" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG90" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH90" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI90" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ90" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL90" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM90" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN90" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO90" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP90" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ90" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR90" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS90" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT90" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV90" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW90" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX90" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY90" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ90" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA90" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB90" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC90" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD90" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE90" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF90" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG90" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH90" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ90" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK90" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL90" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM90" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN90" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO90" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP90" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ90" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR90" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="91">
@@ -19928,211 +19928,211 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D91" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y91" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA91" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB91" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC91" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD91" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E91" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U91" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X91" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y91" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z91" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA91" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB91" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC91" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD91" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE91" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF91" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG91" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH91" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI91" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ91" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL91" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM91" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN91" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO91" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP91" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ91" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR91" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS91" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT91" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV91" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW91" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX91" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY91" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ91" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA91" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB91" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC91" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD91" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE91" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF91" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG91" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH91" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ91" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK91" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL91" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM91" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN91" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO91" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP91" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ91" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR91" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="92">
@@ -20142,211 +20142,211 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D92" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q92" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S92" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W92" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y92" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z92" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA92" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB92" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC92" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD92" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M92" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N92" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O92" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P92" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q92" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R92" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S92" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T92" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U92" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V92" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W92" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X92" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y92" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z92" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA92" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB92" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC92" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD92" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE92" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF92" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG92" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH92" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI92" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ92" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL92" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM92" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN92" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO92" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP92" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ92" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR92" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS92" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT92" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV92" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW92" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX92" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY92" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ92" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA92" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB92" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC92" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD92" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE92" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF92" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG92" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH92" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ92" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK92" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL92" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM92" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN92" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO92" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP92" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ92" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR92" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="93">
@@ -20356,211 +20356,211 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>2.43</v>
+        <v>2.327</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.289</v>
+        <v>2.246</v>
       </c>
       <c r="D93" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q93" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="S93" s="3" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>2.3235</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>2.4775</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Y93" s="3" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA93" s="3" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AB93" s="3" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="AC93" s="3" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="AD93" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="E93" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>2.243</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>2.428</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>1.878</v>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N93" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O93" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P93" s="3" t="n">
-        <v>2.353</v>
-      </c>
-      <c r="Q93" s="3" t="n">
-        <v>2.728</v>
-      </c>
-      <c r="R93" s="3" t="n">
-        <v>2.4525</v>
-      </c>
-      <c r="S93" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T93" s="3" t="n">
-        <v>2.3765</v>
-      </c>
-      <c r="U93" s="3" t="n">
-        <v>2.5055</v>
-      </c>
-      <c r="V93" s="3" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="W93" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X93" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y93" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z93" s="3" t="n">
-        <v>2.368</v>
-      </c>
-      <c r="AA93" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB93" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC93" s="3" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="AD93" s="3" t="n">
-        <v>2.441</v>
-      </c>
       <c r="AE93" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AF93" s="3" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AG93" s="3" t="n">
-        <v>2.55</v>
+        <v>2.447</v>
       </c>
       <c r="AH93" s="3" t="n">
-        <v>2.278</v>
+        <v>2.235</v>
       </c>
       <c r="AI93" s="3" t="n">
-        <v>1.938</v>
+        <v>1.968</v>
       </c>
       <c r="AJ93" s="3" t="n">
-        <v>2.52</v>
+        <v>2.417</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>2.379</v>
+        <v>2.333</v>
       </c>
       <c r="AL93" s="3" t="n">
-        <v>2.275</v>
+        <v>2.202</v>
       </c>
       <c r="AM93" s="3" t="n">
-        <v>2.678</v>
+        <v>2.61</v>
       </c>
       <c r="AN93" s="3" t="n">
         <v>3.51</v>
       </c>
       <c r="AO93" s="3" t="n">
-        <v>3.48</v>
+        <v>3.377</v>
       </c>
       <c r="AP93" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AQ93" s="3" t="n">
-        <v>2.02</v>
+        <v>1.952</v>
       </c>
       <c r="AR93" s="3" t="n">
-        <v>2.4165</v>
+        <v>2.3135</v>
       </c>
       <c r="AS93" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8375</v>
       </c>
       <c r="AT93" s="3" t="n">
-        <v>2.014</v>
+        <v>1.911</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>2.3</v>
+        <v>2.197</v>
       </c>
       <c r="AV93" s="3" t="n">
-        <v>2.48</v>
+        <v>2.377</v>
       </c>
       <c r="AW93" s="3" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="AX93" s="3" t="n">
-        <v>2.34</v>
+        <v>2.237</v>
       </c>
       <c r="AY93" s="3" t="n">
-        <v>2.33</v>
+        <v>2.227</v>
       </c>
       <c r="AZ93" s="3" t="n">
-        <v>2.366</v>
+        <v>2.263</v>
       </c>
       <c r="BA93" s="3" t="n">
-        <v>2.123</v>
+        <v>2.077</v>
       </c>
       <c r="BB93" s="3" t="n">
-        <v>1.877</v>
+        <v>1.809</v>
       </c>
       <c r="BC93" s="3" t="n">
-        <v>2.3975</v>
+        <v>2.2945</v>
       </c>
       <c r="BD93" s="3" t="n">
-        <v>2.3355</v>
+        <v>2.2325</v>
       </c>
       <c r="BE93" s="3" t="n">
-        <v>2.4</v>
+        <v>2.297</v>
       </c>
       <c r="BF93" s="3" t="n">
-        <v>1.969</v>
+        <v>1.866</v>
       </c>
       <c r="BG93" s="3" t="n">
-        <v>2.35</v>
+        <v>2.247</v>
       </c>
       <c r="BH93" s="3" t="n">
-        <v>2.4635</v>
+        <v>2.3605</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>3.433</v>
+        <v>3.319</v>
       </c>
       <c r="BJ93" s="3" t="n">
-        <v>3.458</v>
+        <v>3.344</v>
       </c>
       <c r="BK93" s="3" t="n">
-        <v>1.85</v>
+        <v>1.747</v>
       </c>
       <c r="BL93" s="3" t="n">
-        <v>3.0865</v>
+        <v>2.9835</v>
       </c>
       <c r="BM93" s="3" t="n">
-        <v>3.067</v>
+        <v>2.85</v>
       </c>
       <c r="BN93" s="3" t="n">
-        <v>3.65</v>
+        <v>3.502</v>
       </c>
       <c r="BO93" s="3" t="n">
-        <v>1.996</v>
+        <v>1.893</v>
       </c>
       <c r="BP93" s="3" t="n">
-        <v>2.0855</v>
+        <v>1.9825</v>
       </c>
       <c r="BQ93" s="3" t="n">
-        <v>2.381</v>
+        <v>2.278</v>
       </c>
       <c r="BR93" s="3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -14792,211 +14792,211 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>2.4129</v>
+        <v>2.415</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2.3228</v>
+        <v>2.325</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>2.85</v>
+        <v>2.935</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2.3047</v>
+        <v>2.305</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>2.4066</v>
+        <v>2.405</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>2.2815</v>
+        <v>2.28</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>2.2922</v>
+        <v>2.29</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>2.3992</v>
+        <v>2.4</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>2.4005</v>
+        <v>2.4</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>2.0073</v>
+        <v>2.02</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>1.9269</v>
+        <v>1.925</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>2.3474</v>
+        <v>2.385</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>2.4825</v>
+        <v>2.455</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>3.3766</v>
+        <v>3.235</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>2.286</v>
+        <v>2.285</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>2.7268</v>
+        <v>2.725</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>2.5885</v>
+        <v>2.59</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>2.7031</v>
+        <v>2.72</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>2.2732</v>
+        <v>2.28</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>2.4002</v>
+        <v>2.77</v>
       </c>
       <c r="V67" s="3" t="n">
-        <v>2.3801</v>
+        <v>2.38</v>
       </c>
       <c r="W67" s="3" t="n">
-        <v>1.9065</v>
+        <v>1.905</v>
       </c>
       <c r="X67" s="3" t="n">
-        <v>2.3148</v>
+        <v>2.315</v>
       </c>
       <c r="Y67" s="3" t="n">
         <v>2.265</v>
       </c>
       <c r="Z67" s="3" t="n">
-        <v>2.3144</v>
+        <v>2.315</v>
       </c>
       <c r="AA67" s="3" t="n">
-        <v>2.3734</v>
+        <v>2.375</v>
       </c>
       <c r="AB67" s="3" t="n">
-        <v>2.3559</v>
+        <v>2.355</v>
       </c>
       <c r="AC67" s="3" t="n">
-        <v>2.415</v>
+        <v>2.41</v>
       </c>
       <c r="AD67" s="3" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AE67" s="3" t="n">
-        <v>2.2475</v>
+        <v>2.25</v>
       </c>
       <c r="AF67" s="3" t="n">
-        <v>2.9037</v>
+        <v>2.905</v>
       </c>
       <c r="AG67" s="3" t="n">
-        <v>2.4797</v>
+        <v>2.48</v>
       </c>
       <c r="AH67" s="3" t="n">
-        <v>2.2282</v>
+        <v>2.23</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>2.0287</v>
+        <v>2.02</v>
       </c>
       <c r="AJ67" s="3" t="n">
-        <v>2.4076</v>
+        <v>2.41</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>2.34</v>
+        <v>2.355</v>
       </c>
       <c r="AL67" s="3" t="n">
-        <v>2.2558</v>
+        <v>2.255</v>
       </c>
       <c r="AM67" s="3" t="n">
-        <v>2.7823</v>
+        <v>2.78</v>
       </c>
       <c r="AN67" s="3" t="n">
-        <v>3.6787</v>
+        <v>3.68</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>3.2083</v>
+        <v>3.21</v>
       </c>
       <c r="AP67" s="3" t="n">
-        <v>2.3072</v>
+        <v>2.305</v>
       </c>
       <c r="AQ67" s="3" t="n">
         <v>2.035</v>
       </c>
       <c r="AR67" s="3" t="n">
-        <v>2.4021</v>
+        <v>2.4</v>
       </c>
       <c r="AS67" s="3" t="n">
-        <v>2.012</v>
+        <v>2.01</v>
       </c>
       <c r="AT67" s="3" t="n">
         <v>2.12</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>2.2752</v>
+        <v>2.275</v>
       </c>
       <c r="AV67" s="3" t="n">
-        <v>2.3903</v>
+        <v>2.39</v>
       </c>
       <c r="AW67" s="3" t="n">
-        <v>3.1826</v>
+        <v>3.185</v>
       </c>
       <c r="AX67" s="3" t="n">
-        <v>2.3442</v>
+        <v>2.345</v>
       </c>
       <c r="AY67" s="3" t="n">
-        <v>2.2698</v>
+        <v>2.27</v>
       </c>
       <c r="AZ67" s="3" t="n">
-        <v>2.263</v>
+        <v>2.31</v>
       </c>
       <c r="BA67" s="3" t="n">
-        <v>2.1436</v>
+        <v>2.145</v>
       </c>
       <c r="BB67" s="3" t="n">
-        <v>1.8641</v>
+        <v>1.865</v>
       </c>
       <c r="BC67" s="3" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="BD67" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="BE67" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="BF67" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BG67" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="BH67" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="BI67" s="3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BJ67" s="3" t="n">
+        <v>3.225</v>
+      </c>
+      <c r="BK67" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="BL67" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BM67" s="3" t="n">
         <v>3.05</v>
       </c>
-      <c r="BD67" s="3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BE67" s="3" t="n">
-        <v>2.3448</v>
-      </c>
-      <c r="BF67" s="3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BG67" s="3" t="n">
-        <v>2.2662</v>
-      </c>
-      <c r="BH67" s="3" t="n">
-        <v>2.3855</v>
-      </c>
-      <c r="BI67" s="3" t="n">
-        <v>3.1971</v>
-      </c>
-      <c r="BJ67" s="3" t="n">
-        <v>3.2266</v>
-      </c>
-      <c r="BK67" s="3" t="n">
-        <v>1.9769</v>
-      </c>
-      <c r="BL67" s="3" t="n">
-        <v>3.2266</v>
-      </c>
-      <c r="BM67" s="3" t="n">
-        <v>3.3376</v>
-      </c>
       <c r="BN67" s="3" t="n">
-        <v>3.3376</v>
+        <v>3.34</v>
       </c>
       <c r="BO67" s="3" t="n">
-        <v>2.07</v>
+        <v>2.095</v>
       </c>
       <c r="BP67" s="3" t="n">
-        <v>2.1937</v>
+        <v>2.195</v>
       </c>
       <c r="BQ67" s="3" t="n">
-        <v>2.3137</v>
+        <v>2.315</v>
       </c>
       <c r="BR67" s="3" t="n">
-        <v>2.0128</v>
+        <v>2.015</v>
       </c>
     </row>
     <row r="68">
@@ -15006,211 +15006,211 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
+        <v>2.4013</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2.3396</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" s="3" t="n">
         <v>2.327</v>
       </c>
-      <c r="C68" s="3" t="n">
-        <v>2.246</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>2.247</v>
-      </c>
       <c r="F68" s="3" t="n">
-        <v>2.347</v>
+        <v>2.4163</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>2.183</v>
+        <v>2.2805</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>2.183</v>
+        <v>2.308</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2.37</v>
+        <v>2.4654</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>2.32</v>
+        <v>2.4777</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1.9055</v>
+        <v>2.0252</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>1.81</v>
+        <v>1.9243</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>2.257</v>
+        <v>2.3763</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>3.54</v>
+        <v>3.4409</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>2.3</v>
+        <v>2.2808</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>2.625</v>
+        <v>2.602</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.7916</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>2.417</v>
+        <v>3.2795</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.3078</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5466</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>2.388</v>
+        <v>2.4099</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>1.912</v>
+        <v>1.9242</v>
       </c>
       <c r="X68" s="3" t="n">
-        <v>2.247</v>
+        <v>2.332</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>2.247</v>
+        <v>2.287</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>2.33</v>
+        <v>2.3427</v>
       </c>
       <c r="AA68" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4138</v>
       </c>
       <c r="AB68" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4033</v>
       </c>
       <c r="AC68" s="3" t="n">
-        <v>2.325</v>
+        <v>2.575</v>
       </c>
       <c r="AD68" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE68" s="3" t="n">
-        <v>2.18</v>
+        <v>2.2745</v>
       </c>
       <c r="AF68" s="3" t="n">
-        <v>2.91</v>
+        <v>3.0367</v>
       </c>
       <c r="AG68" s="3" t="n">
-        <v>2.447</v>
+        <v>2.6526</v>
       </c>
       <c r="AH68" s="3" t="n">
-        <v>2.235</v>
+        <v>2.2682</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>1.968</v>
+        <v>2.0215</v>
       </c>
       <c r="AJ68" s="3" t="n">
-        <v>2.417</v>
+        <v>2.4241</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>2.333</v>
+        <v>2.4034</v>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2867</v>
       </c>
       <c r="AM68" s="3" t="n">
-        <v>2.61</v>
+        <v>3.0018</v>
       </c>
       <c r="AN68" s="3" t="n">
-        <v>3.51</v>
+        <v>3.8633</v>
       </c>
       <c r="AO68" s="3" t="n">
-        <v>3.377</v>
+        <v>3.2456</v>
       </c>
       <c r="AP68" s="3" t="n">
-        <v>2.197</v>
+        <v>2.3048</v>
       </c>
       <c r="AQ68" s="3" t="n">
-        <v>1.952</v>
+        <v>2.0138</v>
       </c>
       <c r="AR68" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.425</v>
       </c>
       <c r="AS68" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.9918</v>
       </c>
       <c r="AT68" s="3" t="n">
-        <v>1.911</v>
+        <v>2.1022</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>2.197</v>
+        <v>2.3054</v>
       </c>
       <c r="AV68" s="3" t="n">
-        <v>2.377</v>
+        <v>2.3988</v>
       </c>
       <c r="AW68" s="3" t="n">
-        <v>3.29</v>
+        <v>3.2773</v>
       </c>
       <c r="AX68" s="3" t="n">
-        <v>2.237</v>
+        <v>2.3431</v>
       </c>
       <c r="AY68" s="3" t="n">
-        <v>2.227</v>
+        <v>2.2521</v>
       </c>
       <c r="AZ68" s="3" t="n">
-        <v>2.263</v>
+        <v>2.35</v>
       </c>
       <c r="BA68" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0778</v>
       </c>
       <c r="BB68" s="3" t="n">
-        <v>1.809</v>
+        <v>1.7336</v>
       </c>
       <c r="BC68" s="3" t="n">
-        <v>2.2945</v>
+        <v>5.2</v>
       </c>
       <c r="BD68" s="3" t="n">
-        <v>2.2325</v>
+        <v>5</v>
       </c>
       <c r="BE68" s="3" t="n">
-        <v>2.297</v>
+        <v>2.3927</v>
       </c>
       <c r="BF68" s="3" t="n">
-        <v>1.866</v>
+        <v>2.1022</v>
       </c>
       <c r="BG68" s="3" t="n">
-        <v>2.247</v>
+        <v>2.3</v>
       </c>
       <c r="BH68" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.4206</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>3.319</v>
+        <v>3.287</v>
       </c>
       <c r="BJ68" s="3" t="n">
-        <v>3.344</v>
+        <v>3.2909</v>
       </c>
       <c r="BK68" s="3" t="n">
-        <v>1.747</v>
+        <v>1.8989</v>
       </c>
       <c r="BL68" s="3" t="n">
-        <v>2.9835</v>
+        <v>3.2909</v>
       </c>
       <c r="BM68" s="3" t="n">
-        <v>2.85</v>
+        <v>3.4047</v>
       </c>
       <c r="BN68" s="3" t="n">
-        <v>3.502</v>
+        <v>3.4047</v>
       </c>
       <c r="BO68" s="3" t="n">
-        <v>1.893</v>
+        <v>2.0522</v>
       </c>
       <c r="BP68" s="3" t="n">
-        <v>1.9825</v>
+        <v>2.2631</v>
       </c>
       <c r="BQ68" s="3" t="n">
-        <v>2.278</v>
+        <v>2.3694</v>
       </c>
       <c r="BR68" s="3" t="n">
-        <v>1.88</v>
+        <v>2.0278</v>
       </c>
     </row>
     <row r="69">
@@ -15220,40 +15220,40 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K69" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>2.46</v>
@@ -15268,25 +15268,25 @@
         <v>2.625</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T69" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y69" s="3" t="n">
         <v>2.247</v>
@@ -15295,28 +15295,28 @@
         <v>2.33</v>
       </c>
       <c r="AA69" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB69" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC69" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD69" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE69" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF69" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG69" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH69" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>1.968</v>
@@ -15325,28 +15325,28 @@
         <v>2.417</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL69" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM69" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN69" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP69" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ69" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR69" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS69" s="3" t="n">
         <v>1.8375</v>
@@ -15355,7 +15355,7 @@
         <v>1.911</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV69" s="3" t="n">
         <v>2.377</v>
@@ -15364,46 +15364,46 @@
         <v>3.29</v>
       </c>
       <c r="AX69" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY69" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ69" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA69" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB69" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC69" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD69" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE69" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF69" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG69" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH69" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ69" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK69" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL69" s="3" t="n">
         <v>2.9835</v>
@@ -15421,7 +15421,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ69" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR69" s="3" t="n">
         <v>1.88</v>
@@ -15434,40 +15434,40 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>2.46</v>
@@ -15482,25 +15482,25 @@
         <v>2.625</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T70" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X70" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y70" s="3" t="n">
         <v>2.247</v>
@@ -15509,28 +15509,28 @@
         <v>2.33</v>
       </c>
       <c r="AA70" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB70" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC70" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD70" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE70" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF70" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG70" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH70" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>1.968</v>
@@ -15539,28 +15539,28 @@
         <v>2.417</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL70" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM70" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN70" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP70" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ70" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR70" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS70" s="3" t="n">
         <v>1.8375</v>
@@ -15569,7 +15569,7 @@
         <v>1.911</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV70" s="3" t="n">
         <v>2.377</v>
@@ -15578,46 +15578,46 @@
         <v>3.29</v>
       </c>
       <c r="AX70" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY70" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ70" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA70" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB70" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC70" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD70" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE70" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF70" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG70" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH70" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ70" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK70" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL70" s="3" t="n">
         <v>2.9835</v>
@@ -15635,7 +15635,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ70" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR70" s="3" t="n">
         <v>1.88</v>
@@ -15648,40 +15648,40 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>2.46</v>
@@ -15696,25 +15696,25 @@
         <v>2.625</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T71" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y71" s="3" t="n">
         <v>2.247</v>
@@ -15723,28 +15723,28 @@
         <v>2.33</v>
       </c>
       <c r="AA71" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB71" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC71" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD71" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE71" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF71" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG71" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH71" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>1.968</v>
@@ -15753,28 +15753,28 @@
         <v>2.417</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL71" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN71" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP71" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ71" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR71" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS71" s="3" t="n">
         <v>1.8375</v>
@@ -15783,7 +15783,7 @@
         <v>1.911</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV71" s="3" t="n">
         <v>2.377</v>
@@ -15792,46 +15792,46 @@
         <v>3.29</v>
       </c>
       <c r="AX71" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY71" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ71" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA71" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB71" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC71" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD71" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE71" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF71" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG71" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH71" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ71" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK71" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL71" s="3" t="n">
         <v>2.9835</v>
@@ -15849,7 +15849,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ71" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR71" s="3" t="n">
         <v>1.88</v>
@@ -15862,40 +15862,40 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K72" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>2.46</v>
@@ -15910,25 +15910,25 @@
         <v>2.625</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T72" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y72" s="3" t="n">
         <v>2.247</v>
@@ -15937,28 +15937,28 @@
         <v>2.33</v>
       </c>
       <c r="AA72" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB72" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC72" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD72" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE72" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF72" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG72" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH72" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>1.968</v>
@@ -15967,28 +15967,28 @@
         <v>2.417</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL72" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN72" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP72" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ72" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR72" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS72" s="3" t="n">
         <v>1.8375</v>
@@ -15997,7 +15997,7 @@
         <v>1.911</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV72" s="3" t="n">
         <v>2.377</v>
@@ -16006,46 +16006,46 @@
         <v>3.29</v>
       </c>
       <c r="AX72" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY72" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ72" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA72" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB72" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC72" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD72" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE72" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF72" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG72" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH72" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ72" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK72" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL72" s="3" t="n">
         <v>2.9835</v>
@@ -16063,7 +16063,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ72" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR72" s="3" t="n">
         <v>1.88</v>
@@ -16076,40 +16076,40 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N73" s="3" t="n">
         <v>2.46</v>
@@ -16124,25 +16124,25 @@
         <v>2.625</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T73" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X73" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y73" s="3" t="n">
         <v>2.247</v>
@@ -16151,28 +16151,28 @@
         <v>2.33</v>
       </c>
       <c r="AA73" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB73" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC73" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD73" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE73" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF73" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG73" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH73" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>1.968</v>
@@ -16181,28 +16181,28 @@
         <v>2.417</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL73" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM73" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN73" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO73" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP73" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ73" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR73" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS73" s="3" t="n">
         <v>1.8375</v>
@@ -16211,7 +16211,7 @@
         <v>1.911</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV73" s="3" t="n">
         <v>2.377</v>
@@ -16220,46 +16220,46 @@
         <v>3.29</v>
       </c>
       <c r="AX73" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY73" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ73" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA73" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB73" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC73" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD73" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE73" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF73" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG73" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH73" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ73" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK73" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL73" s="3" t="n">
         <v>2.9835</v>
@@ -16277,7 +16277,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ73" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR73" s="3" t="n">
         <v>1.88</v>
@@ -16290,40 +16290,40 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K74" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>2.46</v>
@@ -16338,25 +16338,25 @@
         <v>2.625</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T74" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y74" s="3" t="n">
         <v>2.247</v>
@@ -16365,28 +16365,28 @@
         <v>2.33</v>
       </c>
       <c r="AA74" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB74" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC74" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD74" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE74" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF74" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG74" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH74" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>1.968</v>
@@ -16395,28 +16395,28 @@
         <v>2.417</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL74" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM74" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN74" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO74" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP74" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ74" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR74" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS74" s="3" t="n">
         <v>1.8375</v>
@@ -16425,7 +16425,7 @@
         <v>1.911</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV74" s="3" t="n">
         <v>2.377</v>
@@ -16434,46 +16434,46 @@
         <v>3.29</v>
       </c>
       <c r="AX74" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY74" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ74" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA74" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB74" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC74" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD74" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE74" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF74" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG74" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH74" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL74" s="3" t="n">
         <v>2.9835</v>
@@ -16491,7 +16491,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR74" s="3" t="n">
         <v>1.88</v>
@@ -16504,40 +16504,40 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>2.46</v>
@@ -16552,25 +16552,25 @@
         <v>2.625</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T75" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X75" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y75" s="3" t="n">
         <v>2.247</v>
@@ -16579,28 +16579,28 @@
         <v>2.33</v>
       </c>
       <c r="AA75" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB75" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC75" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD75" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE75" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF75" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG75" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH75" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>1.968</v>
@@ -16609,28 +16609,28 @@
         <v>2.417</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL75" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM75" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN75" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO75" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP75" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ75" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR75" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS75" s="3" t="n">
         <v>1.8375</v>
@@ -16639,7 +16639,7 @@
         <v>1.911</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV75" s="3" t="n">
         <v>2.377</v>
@@ -16648,46 +16648,46 @@
         <v>3.29</v>
       </c>
       <c r="AX75" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY75" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ75" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA75" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB75" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC75" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD75" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE75" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF75" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG75" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH75" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL75" s="3" t="n">
         <v>2.9835</v>
@@ -16705,7 +16705,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR75" s="3" t="n">
         <v>1.88</v>
@@ -16718,40 +16718,40 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K76" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>2.46</v>
@@ -16766,25 +16766,25 @@
         <v>2.625</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y76" s="3" t="n">
         <v>2.247</v>
@@ -16793,28 +16793,28 @@
         <v>2.33</v>
       </c>
       <c r="AA76" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB76" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC76" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD76" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE76" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF76" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG76" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH76" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>1.968</v>
@@ -16823,28 +16823,28 @@
         <v>2.417</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL76" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM76" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN76" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO76" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP76" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ76" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR76" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS76" s="3" t="n">
         <v>1.8375</v>
@@ -16853,7 +16853,7 @@
         <v>1.911</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV76" s="3" t="n">
         <v>2.377</v>
@@ -16862,46 +16862,46 @@
         <v>3.29</v>
       </c>
       <c r="AX76" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY76" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ76" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA76" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB76" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC76" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD76" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE76" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF76" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG76" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH76" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL76" s="3" t="n">
         <v>2.9835</v>
@@ -16919,7 +16919,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR76" s="3" t="n">
         <v>1.88</v>
@@ -16932,40 +16932,40 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K77" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>2.46</v>
@@ -16980,25 +16980,25 @@
         <v>2.625</v>
       </c>
       <c r="R77" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S77" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T77" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X77" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y77" s="3" t="n">
         <v>2.247</v>
@@ -17007,28 +17007,28 @@
         <v>2.33</v>
       </c>
       <c r="AA77" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB77" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC77" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD77" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE77" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF77" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG77" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH77" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>1.968</v>
@@ -17037,28 +17037,28 @@
         <v>2.417</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL77" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM77" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN77" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO77" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP77" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ77" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR77" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS77" s="3" t="n">
         <v>1.8375</v>
@@ -17067,7 +17067,7 @@
         <v>1.911</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV77" s="3" t="n">
         <v>2.377</v>
@@ -17076,46 +17076,46 @@
         <v>3.29</v>
       </c>
       <c r="AX77" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY77" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ77" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA77" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB77" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC77" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD77" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE77" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF77" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG77" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH77" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL77" s="3" t="n">
         <v>2.9835</v>
@@ -17133,7 +17133,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR77" s="3" t="n">
         <v>1.88</v>
@@ -17146,40 +17146,40 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K78" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N78" s="3" t="n">
         <v>2.46</v>
@@ -17194,25 +17194,25 @@
         <v>2.625</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T78" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X78" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y78" s="3" t="n">
         <v>2.247</v>
@@ -17221,28 +17221,28 @@
         <v>2.33</v>
       </c>
       <c r="AA78" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB78" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC78" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD78" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE78" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF78" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG78" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH78" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>1.968</v>
@@ -17251,28 +17251,28 @@
         <v>2.417</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL78" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM78" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN78" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO78" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP78" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ78" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR78" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS78" s="3" t="n">
         <v>1.8375</v>
@@ -17281,7 +17281,7 @@
         <v>1.911</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV78" s="3" t="n">
         <v>2.377</v>
@@ -17290,46 +17290,46 @@
         <v>3.29</v>
       </c>
       <c r="AX78" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY78" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ78" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA78" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB78" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC78" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD78" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE78" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF78" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG78" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH78" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL78" s="3" t="n">
         <v>2.9835</v>
@@ -17347,7 +17347,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR78" s="3" t="n">
         <v>1.88</v>
@@ -17360,40 +17360,40 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K79" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>2.46</v>
@@ -17408,25 +17408,25 @@
         <v>2.625</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y79" s="3" t="n">
         <v>2.247</v>
@@ -17435,28 +17435,28 @@
         <v>2.33</v>
       </c>
       <c r="AA79" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB79" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC79" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD79" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE79" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF79" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG79" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH79" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>1.968</v>
@@ -17465,28 +17465,28 @@
         <v>2.417</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL79" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM79" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN79" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO79" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP79" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ79" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR79" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS79" s="3" t="n">
         <v>1.8375</v>
@@ -17495,7 +17495,7 @@
         <v>1.911</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV79" s="3" t="n">
         <v>2.377</v>
@@ -17504,46 +17504,46 @@
         <v>3.29</v>
       </c>
       <c r="AX79" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY79" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ79" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA79" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB79" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC79" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD79" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE79" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF79" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG79" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH79" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL79" s="3" t="n">
         <v>2.9835</v>
@@ -17561,7 +17561,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR79" s="3" t="n">
         <v>1.88</v>
@@ -17574,40 +17574,40 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K80" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N80" s="3" t="n">
         <v>2.46</v>
@@ -17622,25 +17622,25 @@
         <v>2.625</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T80" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X80" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y80" s="3" t="n">
         <v>2.247</v>
@@ -17649,28 +17649,28 @@
         <v>2.33</v>
       </c>
       <c r="AA80" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB80" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC80" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD80" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE80" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF80" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG80" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH80" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>1.968</v>
@@ -17679,28 +17679,28 @@
         <v>2.417</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL80" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM80" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN80" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO80" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP80" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ80" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR80" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS80" s="3" t="n">
         <v>1.8375</v>
@@ -17709,7 +17709,7 @@
         <v>1.911</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV80" s="3" t="n">
         <v>2.377</v>
@@ -17718,46 +17718,46 @@
         <v>3.29</v>
       </c>
       <c r="AX80" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY80" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ80" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA80" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB80" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC80" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD80" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE80" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF80" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG80" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH80" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL80" s="3" t="n">
         <v>2.9835</v>
@@ -17775,7 +17775,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR80" s="3" t="n">
         <v>1.88</v>
@@ -17788,40 +17788,40 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K81" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N81" s="3" t="n">
         <v>2.46</v>
@@ -17836,25 +17836,25 @@
         <v>2.625</v>
       </c>
       <c r="R81" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S81" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T81" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X81" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y81" s="3" t="n">
         <v>2.247</v>
@@ -17863,28 +17863,28 @@
         <v>2.33</v>
       </c>
       <c r="AA81" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB81" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC81" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD81" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE81" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF81" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG81" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH81" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>1.968</v>
@@ -17893,28 +17893,28 @@
         <v>2.417</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL81" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM81" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN81" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO81" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP81" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ81" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR81" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS81" s="3" t="n">
         <v>1.8375</v>
@@ -17923,7 +17923,7 @@
         <v>1.911</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV81" s="3" t="n">
         <v>2.377</v>
@@ -17932,46 +17932,46 @@
         <v>3.29</v>
       </c>
       <c r="AX81" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY81" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ81" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA81" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB81" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC81" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD81" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE81" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF81" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG81" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH81" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL81" s="3" t="n">
         <v>2.9835</v>
@@ -17989,7 +17989,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR81" s="3" t="n">
         <v>1.88</v>
@@ -18002,40 +18002,40 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K82" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N82" s="3" t="n">
         <v>2.46</v>
@@ -18050,25 +18050,25 @@
         <v>2.625</v>
       </c>
       <c r="R82" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S82" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T82" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U82" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W82" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X82" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y82" s="3" t="n">
         <v>2.247</v>
@@ -18077,28 +18077,28 @@
         <v>2.33</v>
       </c>
       <c r="AA82" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB82" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC82" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD82" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE82" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF82" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG82" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH82" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI82" s="3" t="n">
         <v>1.968</v>
@@ -18107,28 +18107,28 @@
         <v>2.417</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL82" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM82" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN82" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO82" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP82" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ82" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR82" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS82" s="3" t="n">
         <v>1.8375</v>
@@ -18137,7 +18137,7 @@
         <v>1.911</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV82" s="3" t="n">
         <v>2.377</v>
@@ -18146,46 +18146,46 @@
         <v>3.29</v>
       </c>
       <c r="AX82" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY82" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ82" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA82" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB82" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC82" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD82" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE82" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF82" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG82" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH82" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL82" s="3" t="n">
         <v>2.9835</v>
@@ -18203,7 +18203,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR82" s="3" t="n">
         <v>1.88</v>
@@ -18216,40 +18216,40 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>2.46</v>
@@ -18264,25 +18264,25 @@
         <v>2.625</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T83" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W83" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X83" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y83" s="3" t="n">
         <v>2.247</v>
@@ -18291,28 +18291,28 @@
         <v>2.33</v>
       </c>
       <c r="AA83" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB83" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC83" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD83" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE83" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF83" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG83" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH83" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI83" s="3" t="n">
         <v>1.968</v>
@@ -18321,28 +18321,28 @@
         <v>2.417</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL83" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM83" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN83" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO83" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP83" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ83" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR83" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS83" s="3" t="n">
         <v>1.8375</v>
@@ -18351,7 +18351,7 @@
         <v>1.911</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV83" s="3" t="n">
         <v>2.377</v>
@@ -18360,46 +18360,46 @@
         <v>3.29</v>
       </c>
       <c r="AX83" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY83" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ83" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA83" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB83" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC83" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD83" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE83" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF83" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG83" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH83" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL83" s="3" t="n">
         <v>2.9835</v>
@@ -18417,7 +18417,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR83" s="3" t="n">
         <v>1.88</v>
@@ -18430,40 +18430,40 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K84" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>2.46</v>
@@ -18478,25 +18478,25 @@
         <v>2.625</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T84" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y84" s="3" t="n">
         <v>2.247</v>
@@ -18505,28 +18505,28 @@
         <v>2.33</v>
       </c>
       <c r="AA84" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB84" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC84" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD84" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE84" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF84" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG84" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH84" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI84" s="3" t="n">
         <v>1.968</v>
@@ -18535,28 +18535,28 @@
         <v>2.417</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL84" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM84" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN84" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO84" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP84" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ84" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR84" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS84" s="3" t="n">
         <v>1.8375</v>
@@ -18565,7 +18565,7 @@
         <v>1.911</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV84" s="3" t="n">
         <v>2.377</v>
@@ -18574,46 +18574,46 @@
         <v>3.29</v>
       </c>
       <c r="AX84" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY84" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ84" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA84" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB84" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC84" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD84" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE84" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF84" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG84" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH84" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL84" s="3" t="n">
         <v>2.9835</v>
@@ -18631,7 +18631,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR84" s="3" t="n">
         <v>1.88</v>
@@ -18644,40 +18644,40 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K85" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>2.46</v>
@@ -18692,25 +18692,25 @@
         <v>2.625</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T85" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X85" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y85" s="3" t="n">
         <v>2.247</v>
@@ -18719,28 +18719,28 @@
         <v>2.33</v>
       </c>
       <c r="AA85" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB85" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC85" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD85" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE85" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF85" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG85" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH85" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI85" s="3" t="n">
         <v>1.968</v>
@@ -18749,28 +18749,28 @@
         <v>2.417</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL85" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM85" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN85" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO85" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP85" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ85" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR85" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS85" s="3" t="n">
         <v>1.8375</v>
@@ -18779,7 +18779,7 @@
         <v>1.911</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV85" s="3" t="n">
         <v>2.377</v>
@@ -18788,46 +18788,46 @@
         <v>3.29</v>
       </c>
       <c r="AX85" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY85" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ85" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA85" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB85" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC85" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD85" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE85" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF85" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG85" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH85" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL85" s="3" t="n">
         <v>2.9835</v>
@@ -18845,7 +18845,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR85" s="3" t="n">
         <v>1.88</v>
@@ -18858,40 +18858,40 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K86" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N86" s="3" t="n">
         <v>2.46</v>
@@ -18906,25 +18906,25 @@
         <v>2.625</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T86" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y86" s="3" t="n">
         <v>2.247</v>
@@ -18933,28 +18933,28 @@
         <v>2.33</v>
       </c>
       <c r="AA86" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB86" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC86" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD86" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE86" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF86" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG86" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH86" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI86" s="3" t="n">
         <v>1.968</v>
@@ -18963,28 +18963,28 @@
         <v>2.417</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL86" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM86" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN86" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO86" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP86" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ86" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR86" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS86" s="3" t="n">
         <v>1.8375</v>
@@ -18993,7 +18993,7 @@
         <v>1.911</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV86" s="3" t="n">
         <v>2.377</v>
@@ -19002,46 +19002,46 @@
         <v>3.29</v>
       </c>
       <c r="AX86" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY86" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ86" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA86" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB86" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC86" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD86" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE86" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF86" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG86" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH86" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL86" s="3" t="n">
         <v>2.9835</v>
@@ -19059,7 +19059,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR86" s="3" t="n">
         <v>1.88</v>
@@ -19072,40 +19072,40 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K87" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N87" s="3" t="n">
         <v>2.46</v>
@@ -19120,25 +19120,25 @@
         <v>2.625</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T87" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W87" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X87" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y87" s="3" t="n">
         <v>2.247</v>
@@ -19147,28 +19147,28 @@
         <v>2.33</v>
       </c>
       <c r="AA87" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB87" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC87" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD87" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE87" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF87" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG87" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH87" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI87" s="3" t="n">
         <v>1.968</v>
@@ -19177,28 +19177,28 @@
         <v>2.417</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL87" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM87" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN87" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO87" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP87" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ87" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR87" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS87" s="3" t="n">
         <v>1.8375</v>
@@ -19207,7 +19207,7 @@
         <v>1.911</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV87" s="3" t="n">
         <v>2.377</v>
@@ -19216,46 +19216,46 @@
         <v>3.29</v>
       </c>
       <c r="AX87" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY87" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ87" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA87" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB87" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC87" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD87" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE87" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF87" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG87" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH87" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ87" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK87" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL87" s="3" t="n">
         <v>2.9835</v>
@@ -19273,7 +19273,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ87" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR87" s="3" t="n">
         <v>1.88</v>
@@ -19286,40 +19286,40 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N88" s="3" t="n">
         <v>2.46</v>
@@ -19334,25 +19334,25 @@
         <v>2.625</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T88" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W88" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X88" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y88" s="3" t="n">
         <v>2.247</v>
@@ -19361,28 +19361,28 @@
         <v>2.33</v>
       </c>
       <c r="AA88" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB88" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC88" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD88" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE88" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF88" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG88" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH88" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI88" s="3" t="n">
         <v>1.968</v>
@@ -19391,28 +19391,28 @@
         <v>2.417</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL88" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM88" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN88" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO88" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP88" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ88" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR88" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS88" s="3" t="n">
         <v>1.8375</v>
@@ -19421,7 +19421,7 @@
         <v>1.911</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV88" s="3" t="n">
         <v>2.377</v>
@@ -19430,46 +19430,46 @@
         <v>3.29</v>
       </c>
       <c r="AX88" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY88" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ88" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA88" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB88" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC88" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD88" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE88" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF88" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG88" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH88" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ88" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK88" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL88" s="3" t="n">
         <v>2.9835</v>
@@ -19487,7 +19487,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ88" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR88" s="3" t="n">
         <v>1.88</v>
@@ -19500,40 +19500,40 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K89" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N89" s="3" t="n">
         <v>2.46</v>
@@ -19548,25 +19548,25 @@
         <v>2.625</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T89" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y89" s="3" t="n">
         <v>2.247</v>
@@ -19575,28 +19575,28 @@
         <v>2.33</v>
       </c>
       <c r="AA89" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB89" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC89" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD89" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE89" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF89" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG89" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH89" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>1.968</v>
@@ -19605,28 +19605,28 @@
         <v>2.417</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL89" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM89" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN89" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO89" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP89" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ89" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR89" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS89" s="3" t="n">
         <v>1.8375</v>
@@ -19635,7 +19635,7 @@
         <v>1.911</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV89" s="3" t="n">
         <v>2.377</v>
@@ -19644,46 +19644,46 @@
         <v>3.29</v>
       </c>
       <c r="AX89" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY89" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ89" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA89" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB89" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC89" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD89" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE89" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF89" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG89" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH89" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ89" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK89" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL89" s="3" t="n">
         <v>2.9835</v>
@@ -19701,7 +19701,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ89" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR89" s="3" t="n">
         <v>1.88</v>
@@ -19714,40 +19714,40 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K90" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>2.46</v>
@@ -19762,25 +19762,25 @@
         <v>2.625</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T90" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y90" s="3" t="n">
         <v>2.247</v>
@@ -19789,28 +19789,28 @@
         <v>2.33</v>
       </c>
       <c r="AA90" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB90" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC90" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD90" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE90" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF90" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG90" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH90" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI90" s="3" t="n">
         <v>1.968</v>
@@ -19819,28 +19819,28 @@
         <v>2.417</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL90" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM90" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN90" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO90" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP90" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ90" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR90" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS90" s="3" t="n">
         <v>1.8375</v>
@@ -19849,7 +19849,7 @@
         <v>1.911</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV90" s="3" t="n">
         <v>2.377</v>
@@ -19858,46 +19858,46 @@
         <v>3.29</v>
       </c>
       <c r="AX90" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY90" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ90" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA90" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB90" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC90" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD90" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE90" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF90" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG90" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH90" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ90" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK90" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL90" s="3" t="n">
         <v>2.9835</v>
@@ -19915,7 +19915,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ90" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR90" s="3" t="n">
         <v>1.88</v>
@@ -19928,40 +19928,40 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>2.46</v>
@@ -19976,25 +19976,25 @@
         <v>2.625</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T91" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y91" s="3" t="n">
         <v>2.247</v>
@@ -20003,28 +20003,28 @@
         <v>2.33</v>
       </c>
       <c r="AA91" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB91" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC91" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD91" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE91" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF91" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG91" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH91" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI91" s="3" t="n">
         <v>1.968</v>
@@ -20033,28 +20033,28 @@
         <v>2.417</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL91" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM91" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN91" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO91" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP91" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ91" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR91" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS91" s="3" t="n">
         <v>1.8375</v>
@@ -20063,7 +20063,7 @@
         <v>1.911</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV91" s="3" t="n">
         <v>2.377</v>
@@ -20072,46 +20072,46 @@
         <v>3.29</v>
       </c>
       <c r="AX91" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY91" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ91" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA91" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB91" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC91" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD91" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE91" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF91" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG91" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH91" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ91" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK91" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL91" s="3" t="n">
         <v>2.9835</v>
@@ -20129,7 +20129,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ91" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR91" s="3" t="n">
         <v>1.88</v>
@@ -20142,40 +20142,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>2.46</v>
@@ -20190,25 +20190,25 @@
         <v>2.625</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T92" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W92" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X92" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y92" s="3" t="n">
         <v>2.247</v>
@@ -20217,28 +20217,28 @@
         <v>2.33</v>
       </c>
       <c r="AA92" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB92" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC92" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD92" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE92" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF92" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG92" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH92" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI92" s="3" t="n">
         <v>1.968</v>
@@ -20247,28 +20247,28 @@
         <v>2.417</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL92" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM92" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN92" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO92" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP92" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ92" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR92" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS92" s="3" t="n">
         <v>1.8375</v>
@@ -20277,7 +20277,7 @@
         <v>1.911</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV92" s="3" t="n">
         <v>2.377</v>
@@ -20286,46 +20286,46 @@
         <v>3.29</v>
       </c>
       <c r="AX92" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY92" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ92" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA92" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB92" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC92" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD92" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE92" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF92" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG92" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH92" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ92" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK92" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL92" s="3" t="n">
         <v>2.9835</v>
@@ -20343,7 +20343,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ92" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR92" s="3" t="n">
         <v>1.88</v>
@@ -20356,40 +20356,40 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>2.327</v>
+        <v>2.35</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.246</v>
+        <v>2.286</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2.247</v>
+        <v>2.25</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2.347</v>
+        <v>2.39</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.183</v>
+        <v>2.198</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>2.37</v>
+        <v>2.405</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>2.32</v>
+        <v>2.355</v>
       </c>
       <c r="K93" s="3" t="n">
         <v>1.9055</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>1.81</v>
+        <v>1.836</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>2.257</v>
+        <v>2.34</v>
       </c>
       <c r="N93" s="3" t="n">
         <v>2.46</v>
@@ -20404,25 +20404,25 @@
         <v>2.625</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>2.3495</v>
+        <v>2.3525</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>2.417</v>
+        <v>2.42</v>
       </c>
       <c r="T93" s="3" t="n">
         <v>2.3235</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>2.4775</v>
+        <v>2.5405</v>
       </c>
       <c r="V93" s="3" t="n">
-        <v>2.388</v>
+        <v>2.395</v>
       </c>
       <c r="W93" s="3" t="n">
-        <v>1.912</v>
+        <v>1.938</v>
       </c>
       <c r="X93" s="3" t="n">
-        <v>2.247</v>
+        <v>2.29</v>
       </c>
       <c r="Y93" s="3" t="n">
         <v>2.247</v>
@@ -20431,28 +20431,28 @@
         <v>2.33</v>
       </c>
       <c r="AA93" s="3" t="n">
-        <v>2.287</v>
+        <v>2.4</v>
       </c>
       <c r="AB93" s="3" t="n">
-        <v>2.297</v>
+        <v>2.4</v>
       </c>
       <c r="AC93" s="3" t="n">
-        <v>2.325</v>
+        <v>2.348</v>
       </c>
       <c r="AD93" s="3" t="n">
         <v>2.35</v>
       </c>
       <c r="AE93" s="3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF93" s="3" t="n">
         <v>2.91</v>
       </c>
       <c r="AG93" s="3" t="n">
-        <v>2.447</v>
+        <v>2.446</v>
       </c>
       <c r="AH93" s="3" t="n">
-        <v>2.235</v>
+        <v>2.275</v>
       </c>
       <c r="AI93" s="3" t="n">
         <v>1.968</v>
@@ -20461,28 +20461,28 @@
         <v>2.417</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>2.333</v>
+        <v>2.3465</v>
       </c>
       <c r="AL93" s="3" t="n">
         <v>2.202</v>
       </c>
       <c r="AM93" s="3" t="n">
-        <v>2.61</v>
+        <v>2.673</v>
       </c>
       <c r="AN93" s="3" t="n">
-        <v>3.51</v>
+        <v>3.567</v>
       </c>
       <c r="AO93" s="3" t="n">
-        <v>3.377</v>
+        <v>3.31</v>
       </c>
       <c r="AP93" s="3" t="n">
-        <v>2.197</v>
+        <v>2.26</v>
       </c>
       <c r="AQ93" s="3" t="n">
-        <v>1.952</v>
+        <v>1.978</v>
       </c>
       <c r="AR93" s="3" t="n">
-        <v>2.3135</v>
+        <v>2.35</v>
       </c>
       <c r="AS93" s="3" t="n">
         <v>1.8375</v>
@@ -20491,7 +20491,7 @@
         <v>1.911</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>2.197</v>
+        <v>2.25</v>
       </c>
       <c r="AV93" s="3" t="n">
         <v>2.377</v>
@@ -20500,46 +20500,46 @@
         <v>3.29</v>
       </c>
       <c r="AX93" s="3" t="n">
-        <v>2.237</v>
+        <v>2.28</v>
       </c>
       <c r="AY93" s="3" t="n">
         <v>2.227</v>
       </c>
       <c r="AZ93" s="3" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="BA93" s="3" t="n">
         <v>2.077</v>
       </c>
       <c r="BB93" s="3" t="n">
-        <v>1.809</v>
+        <v>1.835</v>
       </c>
       <c r="BC93" s="3" t="n">
-        <v>2.2945</v>
+        <v>2.2975</v>
       </c>
       <c r="BD93" s="3" t="n">
-        <v>2.2325</v>
+        <v>2.2355</v>
       </c>
       <c r="BE93" s="3" t="n">
-        <v>2.297</v>
+        <v>2.35</v>
       </c>
       <c r="BF93" s="3" t="n">
         <v>1.866</v>
       </c>
       <c r="BG93" s="3" t="n">
-        <v>2.247</v>
+        <v>2.27</v>
       </c>
       <c r="BH93" s="3" t="n">
         <v>2.3605</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>3.319</v>
+        <v>3.34</v>
       </c>
       <c r="BJ93" s="3" t="n">
-        <v>3.344</v>
+        <v>3.365</v>
       </c>
       <c r="BK93" s="3" t="n">
-        <v>1.747</v>
+        <v>1.79</v>
       </c>
       <c r="BL93" s="3" t="n">
         <v>2.9835</v>
@@ -20557,7 +20557,7 @@
         <v>1.9825</v>
       </c>
       <c r="BQ93" s="3" t="n">
-        <v>2.278</v>
+        <v>2.34</v>
       </c>
       <c r="BR93" s="3" t="n">
         <v>1.88</v>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -15006,211 +15006,211 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>2.4013</v>
+        <v>2.4</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2.3396</v>
+        <v>2.34</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>5</v>
+        <v>3.86</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2.327</v>
+        <v>2.325</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.4163</v>
+        <v>2.415</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>2.2805</v>
+        <v>2.28</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>2.308</v>
+        <v>2.31</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2.4654</v>
+        <v>2.465</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>2.4777</v>
+        <v>2.48</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>2.0252</v>
+        <v>2.025</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>1.9243</v>
+        <v>1.925</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>2.3763</v>
+        <v>2.375</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>2.52</v>
+        <v>2.495</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>3.4409</v>
+        <v>3.285</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>2.2808</v>
+        <v>2.28</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>2.602</v>
+        <v>2.6</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>2.7916</v>
+        <v>2.79</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>3.2795</v>
+        <v>3.29</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>2.3078</v>
+        <v>2.315</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>2.5466</v>
+        <v>3.025</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>2.4099</v>
+        <v>2.41</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>1.9242</v>
+        <v>1.925</v>
       </c>
       <c r="X68" s="3" t="n">
-        <v>2.332</v>
+        <v>2.33</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>2.287</v>
+        <v>2.285</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>2.3427</v>
+        <v>2.34</v>
       </c>
       <c r="AA68" s="3" t="n">
-        <v>2.4138</v>
+        <v>2.415</v>
       </c>
       <c r="AB68" s="3" t="n">
-        <v>2.4033</v>
+        <v>2.405</v>
       </c>
       <c r="AC68" s="3" t="n">
-        <v>2.575</v>
+        <v>2.535</v>
       </c>
       <c r="AD68" s="3" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="AE68" s="3" t="n">
-        <v>2.2745</v>
+        <v>2.28</v>
       </c>
       <c r="AF68" s="3" t="n">
-        <v>3.0367</v>
+        <v>3.035</v>
       </c>
       <c r="AG68" s="3" t="n">
-        <v>2.6526</v>
+        <v>2.655</v>
       </c>
       <c r="AH68" s="3" t="n">
-        <v>2.2682</v>
+        <v>2.27</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>2.0215</v>
+        <v>2.025</v>
       </c>
       <c r="AJ68" s="3" t="n">
-        <v>2.4241</v>
+        <v>2.425</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>2.4034</v>
+        <v>2.405</v>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>2.2867</v>
+        <v>2.285</v>
       </c>
       <c r="AM68" s="3" t="n">
-        <v>3.0018</v>
+        <v>2.99</v>
       </c>
       <c r="AN68" s="3" t="n">
-        <v>3.8633</v>
+        <v>3.865</v>
       </c>
       <c r="AO68" s="3" t="n">
-        <v>3.2456</v>
+        <v>3.245</v>
       </c>
       <c r="AP68" s="3" t="n">
-        <v>2.3048</v>
+        <v>2.305</v>
       </c>
       <c r="AQ68" s="3" t="n">
-        <v>2.0138</v>
+        <v>2.015</v>
       </c>
       <c r="AR68" s="3" t="n">
         <v>2.425</v>
       </c>
       <c r="AS68" s="3" t="n">
-        <v>1.9918</v>
+        <v>1.99</v>
       </c>
       <c r="AT68" s="3" t="n">
-        <v>2.1022</v>
+        <v>2.105</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>2.3054</v>
+        <v>2.305</v>
       </c>
       <c r="AV68" s="3" t="n">
-        <v>2.3988</v>
+        <v>2.4</v>
       </c>
       <c r="AW68" s="3" t="n">
-        <v>3.2773</v>
+        <v>3.275</v>
       </c>
       <c r="AX68" s="3" t="n">
-        <v>2.3431</v>
+        <v>2.345</v>
       </c>
       <c r="AY68" s="3" t="n">
-        <v>2.2521</v>
+        <v>2.25</v>
       </c>
       <c r="AZ68" s="3" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="BA68" s="3" t="n">
-        <v>2.0778</v>
+        <v>2.09</v>
       </c>
       <c r="BB68" s="3" t="n">
-        <v>1.7336</v>
+        <v>1.735</v>
       </c>
       <c r="BC68" s="3" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="BD68" s="3" t="n">
-        <v>5</v>
+        <v>3.395</v>
       </c>
       <c r="BE68" s="3" t="n">
-        <v>2.3927</v>
+        <v>2.395</v>
       </c>
       <c r="BF68" s="3" t="n">
-        <v>2.1022</v>
+        <v>2.115</v>
       </c>
       <c r="BG68" s="3" t="n">
-        <v>2.3</v>
+        <v>2.285</v>
       </c>
       <c r="BH68" s="3" t="n">
-        <v>2.4206</v>
+        <v>2.42</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>3.287</v>
+        <v>3.285</v>
       </c>
       <c r="BJ68" s="3" t="n">
-        <v>3.2909</v>
+        <v>3.29</v>
       </c>
       <c r="BK68" s="3" t="n">
-        <v>1.8989</v>
+        <v>1.9</v>
       </c>
       <c r="BL68" s="3" t="n">
-        <v>3.2909</v>
+        <v>2.865</v>
       </c>
       <c r="BM68" s="3" t="n">
-        <v>3.4047</v>
+        <v>2.79</v>
       </c>
       <c r="BN68" s="3" t="n">
-        <v>3.4047</v>
+        <v>3.405</v>
       </c>
       <c r="BO68" s="3" t="n">
-        <v>2.0522</v>
+        <v>2.115</v>
       </c>
       <c r="BP68" s="3" t="n">
-        <v>2.2631</v>
+        <v>2.265</v>
       </c>
       <c r="BQ68" s="3" t="n">
-        <v>2.3694</v>
+        <v>2.37</v>
       </c>
       <c r="BR68" s="3" t="n">
-        <v>2.0278</v>
+        <v>2.025</v>
       </c>
     </row>
     <row r="69">
@@ -15220,211 +15220,211 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
+        <v>2.3789</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2.2937</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2.4045</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>2.338</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>2.2967</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>2.4345</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>2.4398</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>1.9536</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>1.8327</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>3.4737</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>2.2295</v>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>2.5355</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>2.5576</v>
+      </c>
+      <c r="S69" s="3" t="n">
+        <v>2.9322</v>
+      </c>
+      <c r="T69" s="3" t="n">
+        <v>2.2865</v>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>2.4744</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>2.4079</v>
+      </c>
+      <c r="W69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>2.3302</v>
+      </c>
+      <c r="Y69" s="3" t="n">
+        <v>2.2753</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>2.3338</v>
+      </c>
+      <c r="AA69" s="3" t="n">
+        <v>2.4372</v>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>2.4323</v>
+      </c>
+      <c r="AC69" s="3" t="n">
+        <v>2.3154</v>
+      </c>
+      <c r="AD69" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE69" s="3" t="n">
+        <v>2.2377</v>
+      </c>
+      <c r="AF69" s="3" t="n">
+        <v>2.9243</v>
+      </c>
+      <c r="AG69" s="3" t="n">
+        <v>2.5747</v>
+      </c>
+      <c r="AH69" s="3" t="n">
+        <v>2.2478</v>
+      </c>
+      <c r="AI69" s="3" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="AJ69" s="3" t="n">
+        <v>2.4016</v>
+      </c>
+      <c r="AK69" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="C69" s="3" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>2.198</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>2.198</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>2.405</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>2.355</v>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>1.9055</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>1.836</v>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O69" s="3" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q69" s="3" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="R69" s="3" t="n">
-        <v>2.3525</v>
-      </c>
-      <c r="S69" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T69" s="3" t="n">
-        <v>2.3235</v>
-      </c>
-      <c r="U69" s="3" t="n">
-        <v>2.5405</v>
-      </c>
-      <c r="V69" s="3" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="W69" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="X69" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y69" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z69" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA69" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB69" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC69" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD69" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE69" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF69" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG69" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH69" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI69" s="3" t="n">
-        <v>1.968</v>
-      </c>
-      <c r="AJ69" s="3" t="n">
-        <v>2.417</v>
-      </c>
-      <c r="AK69" s="3" t="n">
-        <v>2.3465</v>
-      </c>
       <c r="AL69" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2157</v>
       </c>
       <c r="AM69" s="3" t="n">
-        <v>2.673</v>
+        <v>2.9857</v>
       </c>
       <c r="AN69" s="3" t="n">
-        <v>3.567</v>
+        <v>3.8509</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>3.31</v>
+        <v>3.1812</v>
       </c>
       <c r="AP69" s="3" t="n">
-        <v>2.26</v>
+        <v>2.3053</v>
       </c>
       <c r="AQ69" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR69" s="3" t="n">
-        <v>2.35</v>
+        <v>2.3638</v>
       </c>
       <c r="AS69" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.8511</v>
       </c>
       <c r="AT69" s="3" t="n">
-        <v>1.911</v>
+        <v>1.9483</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>2.25</v>
+        <v>2.2833</v>
       </c>
       <c r="AV69" s="3" t="n">
-        <v>2.377</v>
+        <v>2.3622</v>
       </c>
       <c r="AW69" s="3" t="n">
-        <v>3.29</v>
+        <v>3.062</v>
       </c>
       <c r="AX69" s="3" t="n">
-        <v>2.28</v>
+        <v>2.3335</v>
       </c>
       <c r="AY69" s="3" t="n">
-        <v>2.227</v>
+        <v>2.2668</v>
       </c>
       <c r="AZ69" s="3" t="n">
-        <v>2.306</v>
+        <v>2.3433</v>
       </c>
       <c r="BA69" s="3" t="n">
-        <v>2.077</v>
+        <v>2.1446</v>
       </c>
       <c r="BB69" s="3" t="n">
-        <v>1.835</v>
+        <v>1.9283</v>
       </c>
       <c r="BC69" s="3" t="n">
-        <v>2.2975</v>
+        <v>3.4</v>
       </c>
       <c r="BD69" s="3" t="n">
-        <v>2.2355</v>
+        <v>3.2</v>
       </c>
       <c r="BE69" s="3" t="n">
-        <v>2.35</v>
+        <v>2.3604</v>
       </c>
       <c r="BF69" s="3" t="n">
-        <v>1.866</v>
+        <v>1.9483</v>
       </c>
       <c r="BG69" s="3" t="n">
-        <v>2.27</v>
+        <v>2.2741</v>
       </c>
       <c r="BH69" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.4014</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>3.34</v>
+        <v>3.3148</v>
       </c>
       <c r="BJ69" s="3" t="n">
-        <v>3.365</v>
+        <v>3.3237</v>
       </c>
       <c r="BK69" s="3" t="n">
-        <v>1.79</v>
+        <v>1.9501</v>
       </c>
       <c r="BL69" s="3" t="n">
-        <v>2.9835</v>
+        <v>3.3237</v>
       </c>
       <c r="BM69" s="3" t="n">
-        <v>2.85</v>
+        <v>3.425</v>
       </c>
       <c r="BN69" s="3" t="n">
-        <v>3.502</v>
+        <v>3.425</v>
       </c>
       <c r="BO69" s="3" t="n">
-        <v>1.893</v>
+        <v>1.8983</v>
       </c>
       <c r="BP69" s="3" t="n">
-        <v>1.9825</v>
+        <v>2.0958</v>
       </c>
       <c r="BQ69" s="3" t="n">
-        <v>2.34</v>
+        <v>2.3407</v>
       </c>
       <c r="BR69" s="3" t="n">
-        <v>1.88</v>
+        <v>1.9487</v>
       </c>
     </row>
     <row r="70">
@@ -15434,211 +15434,211 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T70" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W70" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y70" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z70" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA70" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC70" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD70" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE70" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF70" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG70" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH70" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI70" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X70" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y70" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z70" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA70" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB70" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC70" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD70" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE70" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF70" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG70" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH70" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI70" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ70" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM70" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN70" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP70" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ70" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR70" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS70" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT70" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV70" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW70" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX70" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY70" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ70" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA70" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB70" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC70" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD70" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE70" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF70" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG70" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH70" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ70" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK70" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL70" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM70" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN70" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO70" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP70" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ70" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR70" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="71">
@@ -15648,211 +15648,211 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W71" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA71" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC71" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD71" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE71" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF71" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG71" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH71" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI71" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X71" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y71" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z71" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA71" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB71" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC71" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD71" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE71" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF71" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG71" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH71" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI71" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ71" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL71" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN71" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP71" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ71" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR71" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS71" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT71" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV71" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW71" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX71" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY71" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ71" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA71" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB71" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC71" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD71" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE71" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF71" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG71" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH71" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ71" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK71" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL71" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM71" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN71" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO71" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP71" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ71" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR71" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="72">
@@ -15862,211 +15862,211 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W72" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y72" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA72" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC72" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD72" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE72" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF72" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG72" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH72" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI72" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X72" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y72" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z72" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA72" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB72" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC72" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD72" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE72" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF72" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG72" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH72" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI72" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ72" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL72" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN72" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP72" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ72" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR72" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS72" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT72" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV72" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW72" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX72" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY72" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ72" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA72" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB72" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC72" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD72" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE72" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF72" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG72" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH72" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ72" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK72" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL72" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM72" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN72" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO72" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP72" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ72" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR72" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="73">
@@ -16076,211 +16076,211 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W73" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y73" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z73" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA73" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC73" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD73" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE73" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF73" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG73" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH73" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI73" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X73" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y73" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z73" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA73" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB73" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC73" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD73" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE73" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF73" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG73" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH73" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI73" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ73" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL73" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM73" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN73" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO73" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP73" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ73" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR73" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS73" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT73" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV73" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW73" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX73" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY73" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ73" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA73" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB73" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC73" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD73" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE73" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF73" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG73" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH73" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ73" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK73" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL73" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM73" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN73" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO73" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP73" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ73" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR73" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="74">
@@ -16290,211 +16290,211 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W74" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y74" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC74" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD74" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE74" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF74" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG74" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH74" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI74" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X74" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y74" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z74" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA74" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB74" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC74" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD74" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE74" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF74" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG74" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH74" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI74" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ74" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL74" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM74" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN74" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO74" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP74" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ74" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR74" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS74" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT74" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV74" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW74" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX74" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY74" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ74" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA74" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB74" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC74" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD74" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE74" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF74" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG74" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH74" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL74" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM74" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN74" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO74" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP74" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR74" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="75">
@@ -16504,211 +16504,211 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T75" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W75" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC75" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD75" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE75" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF75" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG75" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH75" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI75" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X75" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y75" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z75" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA75" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB75" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC75" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD75" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE75" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF75" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG75" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH75" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI75" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ75" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL75" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM75" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN75" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO75" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP75" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ75" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR75" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS75" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT75" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV75" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW75" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX75" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY75" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ75" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA75" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB75" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC75" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD75" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE75" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF75" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG75" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH75" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL75" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM75" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN75" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO75" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP75" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR75" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="76">
@@ -16718,211 +16718,211 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W76" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA76" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC76" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD76" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE76" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF76" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG76" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH76" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI76" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X76" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z76" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA76" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB76" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC76" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD76" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE76" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF76" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG76" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH76" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI76" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ76" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL76" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM76" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN76" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO76" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP76" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ76" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS76" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT76" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV76" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW76" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX76" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY76" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ76" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA76" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB76" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC76" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD76" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF76" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG76" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH76" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL76" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM76" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN76" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO76" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP76" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR76" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="77">
@@ -16932,211 +16932,211 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q77" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R77" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S77" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T77" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W77" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA77" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC77" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD77" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE77" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF77" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG77" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH77" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI77" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X77" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y77" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z77" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA77" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB77" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC77" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD77" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE77" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF77" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG77" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH77" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI77" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ77" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL77" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM77" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN77" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO77" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP77" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ77" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR77" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS77" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT77" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV77" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW77" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX77" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY77" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ77" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA77" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB77" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC77" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD77" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE77" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF77" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG77" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH77" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL77" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM77" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN77" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO77" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP77" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR77" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="78">
@@ -17146,211 +17146,211 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W78" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA78" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC78" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD78" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE78" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF78" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG78" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH78" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI78" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X78" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y78" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z78" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA78" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB78" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC78" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD78" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE78" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF78" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG78" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH78" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI78" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ78" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL78" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM78" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN78" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO78" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP78" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ78" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR78" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS78" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT78" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV78" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW78" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX78" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY78" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ78" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA78" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB78" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC78" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD78" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE78" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF78" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG78" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH78" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL78" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM78" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN78" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO78" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP78" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR78" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="79">
@@ -17360,211 +17360,211 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W79" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA79" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD79" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE79" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF79" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG79" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH79" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI79" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X79" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y79" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z79" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA79" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB79" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC79" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD79" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE79" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF79" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG79" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH79" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI79" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ79" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL79" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM79" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN79" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO79" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP79" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ79" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR79" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS79" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT79" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV79" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW79" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX79" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY79" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ79" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA79" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB79" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC79" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD79" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE79" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF79" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG79" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH79" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL79" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM79" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN79" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO79" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP79" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR79" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="80">
@@ -17574,211 +17574,211 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T80" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W80" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD80" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE80" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF80" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG80" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH80" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI80" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X80" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y80" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z80" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA80" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB80" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC80" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD80" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE80" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF80" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG80" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH80" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI80" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ80" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL80" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM80" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN80" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO80" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP80" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ80" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR80" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS80" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT80" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV80" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW80" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX80" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY80" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ80" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA80" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB80" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC80" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD80" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE80" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF80" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG80" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH80" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL80" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM80" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN80" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO80" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP80" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR80" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="81">
@@ -17788,211 +17788,211 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P81" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R81" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S81" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T81" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W81" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA81" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD81" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE81" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF81" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG81" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH81" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI81" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X81" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y81" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z81" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA81" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB81" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC81" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD81" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE81" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF81" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG81" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH81" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI81" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ81" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL81" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM81" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN81" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO81" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP81" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ81" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR81" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS81" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT81" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV81" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW81" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX81" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY81" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ81" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA81" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB81" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC81" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD81" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE81" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF81" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG81" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH81" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL81" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM81" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN81" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO81" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP81" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR81" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="82">
@@ -18002,211 +18002,211 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P82" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R82" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S82" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T82" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U82" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W82" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA82" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD82" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE82" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF82" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG82" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH82" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI82" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X82" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y82" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z82" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA82" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB82" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC82" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD82" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE82" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF82" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG82" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH82" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI82" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ82" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL82" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM82" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN82" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO82" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP82" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ82" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR82" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS82" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT82" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV82" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW82" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX82" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY82" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ82" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA82" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB82" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC82" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD82" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE82" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF82" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG82" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH82" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL82" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM82" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN82" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO82" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP82" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR82" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="83">
@@ -18216,211 +18216,211 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P83" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W83" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA83" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC83" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD83" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE83" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF83" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG83" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH83" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI83" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X83" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y83" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z83" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA83" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB83" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC83" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD83" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE83" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF83" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG83" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH83" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI83" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ83" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM83" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN83" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO83" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP83" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ83" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR83" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS83" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT83" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV83" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW83" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX83" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY83" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ83" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA83" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB83" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC83" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD83" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE83" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF83" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG83" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH83" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL83" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM83" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN83" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO83" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP83" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR83" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="84">
@@ -18430,211 +18430,211 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W84" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA84" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB84" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC84" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD84" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE84" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF84" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG84" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH84" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI84" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X84" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y84" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z84" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA84" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB84" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC84" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD84" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE84" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF84" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG84" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH84" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI84" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ84" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL84" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM84" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN84" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO84" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP84" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ84" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR84" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS84" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT84" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV84" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW84" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX84" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY84" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ84" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA84" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB84" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC84" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD84" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE84" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF84" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG84" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH84" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL84" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM84" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN84" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO84" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP84" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR84" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="85">
@@ -18644,211 +18644,211 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W85" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y85" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA85" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC85" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD85" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE85" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF85" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG85" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH85" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI85" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X85" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y85" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z85" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA85" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB85" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC85" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD85" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE85" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF85" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG85" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH85" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI85" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ85" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM85" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN85" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO85" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP85" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ85" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR85" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS85" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT85" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV85" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW85" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX85" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY85" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ85" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA85" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB85" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC85" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD85" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE85" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF85" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG85" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH85" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL85" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM85" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN85" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO85" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP85" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR85" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="86">
@@ -18858,211 +18858,211 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W86" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y86" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z86" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA86" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC86" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD86" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE86" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF86" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG86" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH86" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI86" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X86" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y86" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z86" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA86" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB86" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC86" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD86" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE86" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF86" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG86" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH86" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI86" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ86" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM86" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN86" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO86" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP86" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ86" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR86" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS86" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT86" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV86" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW86" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX86" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY86" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ86" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA86" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB86" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC86" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD86" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE86" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF86" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG86" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH86" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL86" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM86" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN86" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO86" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP86" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR86" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="87">
@@ -19072,211 +19072,211 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P87" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W87" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y87" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA87" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB87" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC87" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD87" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE87" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF87" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG87" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH87" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI87" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X87" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y87" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z87" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA87" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB87" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC87" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD87" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE87" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF87" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG87" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH87" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI87" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ87" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM87" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN87" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO87" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP87" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ87" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR87" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS87" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT87" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV87" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW87" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX87" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY87" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ87" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA87" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB87" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC87" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD87" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE87" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF87" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG87" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH87" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ87" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK87" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL87" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM87" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN87" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO87" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP87" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ87" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR87" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="88">
@@ -19286,211 +19286,211 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W88" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y88" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z88" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA88" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB88" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC88" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD88" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE88" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF88" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG88" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH88" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI88" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X88" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y88" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z88" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA88" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB88" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC88" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD88" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE88" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF88" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG88" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH88" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI88" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ88" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL88" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM88" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN88" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO88" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP88" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ88" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR88" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS88" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT88" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV88" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW88" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX88" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY88" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ88" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA88" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB88" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC88" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD88" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE88" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF88" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG88" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH88" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ88" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK88" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL88" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM88" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN88" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO88" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP88" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ88" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR88" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="89">
@@ -19500,211 +19500,211 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W89" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y89" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA89" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB89" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC89" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD89" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE89" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF89" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG89" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH89" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI89" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X89" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y89" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z89" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA89" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB89" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC89" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD89" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE89" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF89" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG89" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH89" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI89" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ89" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL89" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM89" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN89" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO89" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP89" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ89" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR89" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS89" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT89" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV89" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW89" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX89" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY89" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ89" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA89" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB89" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC89" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD89" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE89" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF89" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG89" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH89" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ89" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK89" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL89" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM89" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN89" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO89" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP89" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ89" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR89" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="90">
@@ -19714,211 +19714,211 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W90" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y90" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z90" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA90" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC90" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD90" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE90" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF90" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG90" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH90" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI90" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X90" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y90" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z90" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA90" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB90" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC90" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD90" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE90" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF90" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG90" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH90" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI90" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ90" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL90" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM90" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN90" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO90" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP90" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ90" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR90" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS90" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT90" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV90" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW90" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX90" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY90" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ90" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA90" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB90" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC90" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD90" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE90" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF90" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG90" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH90" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ90" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK90" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL90" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM90" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN90" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO90" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP90" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ90" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR90" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="91">
@@ -19928,211 +19928,211 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W91" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y91" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA91" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB91" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC91" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD91" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE91" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF91" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG91" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH91" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI91" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X91" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y91" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z91" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA91" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB91" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC91" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD91" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE91" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF91" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG91" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH91" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI91" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ91" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL91" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM91" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN91" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO91" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP91" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ91" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR91" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS91" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT91" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV91" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW91" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX91" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY91" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ91" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA91" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB91" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC91" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD91" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE91" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF91" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG91" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH91" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ91" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK91" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL91" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM91" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN91" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO91" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP91" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ91" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR91" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="92">
@@ -20142,211 +20142,211 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W92" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y92" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z92" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA92" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB92" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC92" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD92" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE92" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF92" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG92" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH92" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI92" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X92" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y92" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z92" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA92" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB92" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC92" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD92" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE92" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF92" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG92" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH92" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI92" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ92" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL92" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM92" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN92" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO92" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP92" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ92" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR92" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS92" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT92" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV92" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW92" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX92" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY92" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ92" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA92" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB92" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC92" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD92" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE92" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF92" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG92" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH92" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ92" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK92" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL92" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM92" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN92" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO92" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP92" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ92" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR92" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="93">
@@ -20356,211 +20356,211 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.286</v>
+        <v>2.231</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2.29</v>
+        <v>2.235</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2.39</v>
+        <v>2.335</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.198</v>
+        <v>2.18</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>2.405</v>
+        <v>2.38</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>2.355</v>
+        <v>2.33</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>1.9055</v>
+        <v>1.8755</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>1.836</v>
+        <v>1.795</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>2.46</v>
+        <v>2.445</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>2.3</v>
+        <v>2.265</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>2.625</v>
+        <v>2.57</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.2975</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>2.42</v>
+        <v>2.365</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>2.3235</v>
+        <v>2.2885</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>2.5405</v>
+        <v>2.4735</v>
       </c>
       <c r="V93" s="3" t="n">
-        <v>2.395</v>
+        <v>2.37</v>
       </c>
       <c r="W93" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="Y93" s="3" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AA93" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AB93" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AC93" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD93" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AE93" s="3" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="AF93" s="3" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AG93" s="3" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="AH93" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI93" s="3" t="n">
         <v>1.938</v>
       </c>
-      <c r="X93" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y93" s="3" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="Z93" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA93" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB93" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC93" s="3" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="AD93" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE93" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF93" s="3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG93" s="3" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="AH93" s="3" t="n">
-        <v>2.275</v>
-      </c>
-      <c r="AI93" s="3" t="n">
-        <v>1.968</v>
-      </c>
       <c r="AJ93" s="3" t="n">
-        <v>2.417</v>
+        <v>2.362</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>2.3465</v>
+        <v>2.345</v>
       </c>
       <c r="AL93" s="3" t="n">
-        <v>2.202</v>
+        <v>2.2</v>
       </c>
       <c r="AM93" s="3" t="n">
-        <v>2.673</v>
+        <v>2.606</v>
       </c>
       <c r="AN93" s="3" t="n">
-        <v>3.567</v>
+        <v>3.5</v>
       </c>
       <c r="AO93" s="3" t="n">
-        <v>3.31</v>
+        <v>3.255</v>
       </c>
       <c r="AP93" s="3" t="n">
-        <v>2.26</v>
+        <v>2.205</v>
       </c>
       <c r="AQ93" s="3" t="n">
-        <v>1.978</v>
+        <v>1.937</v>
       </c>
       <c r="AR93" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="AS93" s="3" t="n">
-        <v>1.8375</v>
+        <v>1.7965</v>
       </c>
       <c r="AT93" s="3" t="n">
-        <v>1.911</v>
+        <v>1.856</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>2.25</v>
+        <v>2.195</v>
       </c>
       <c r="AV93" s="3" t="n">
-        <v>2.377</v>
+        <v>2.322</v>
       </c>
       <c r="AW93" s="3" t="n">
-        <v>3.29</v>
+        <v>3.255</v>
       </c>
       <c r="AX93" s="3" t="n">
-        <v>2.28</v>
+        <v>2.225</v>
       </c>
       <c r="AY93" s="3" t="n">
-        <v>2.227</v>
+        <v>2.24</v>
       </c>
       <c r="AZ93" s="3" t="n">
-        <v>2.306</v>
+        <v>2.251</v>
       </c>
       <c r="BA93" s="3" t="n">
-        <v>2.077</v>
+        <v>2.0755</v>
       </c>
       <c r="BB93" s="3" t="n">
-        <v>1.835</v>
+        <v>1.794</v>
       </c>
       <c r="BC93" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.2425</v>
       </c>
       <c r="BD93" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.1805</v>
       </c>
       <c r="BE93" s="3" t="n">
-        <v>2.35</v>
+        <v>2.295</v>
       </c>
       <c r="BF93" s="3" t="n">
-        <v>1.866</v>
+        <v>1.811</v>
       </c>
       <c r="BG93" s="3" t="n">
-        <v>2.27</v>
+        <v>2.215</v>
       </c>
       <c r="BH93" s="3" t="n">
-        <v>2.3605</v>
+        <v>2.3055</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="BJ93" s="3" t="n">
-        <v>3.365</v>
+        <v>3.295</v>
       </c>
       <c r="BK93" s="3" t="n">
-        <v>1.79</v>
+        <v>1.735</v>
       </c>
       <c r="BL93" s="3" t="n">
-        <v>2.9835</v>
+        <v>2.9285</v>
       </c>
       <c r="BM93" s="3" t="n">
-        <v>2.85</v>
+        <v>2.765</v>
       </c>
       <c r="BN93" s="3" t="n">
-        <v>3.502</v>
+        <v>3.417</v>
       </c>
       <c r="BO93" s="3" t="n">
-        <v>1.893</v>
+        <v>1.838</v>
       </c>
       <c r="BP93" s="3" t="n">
-        <v>1.9825</v>
+        <v>1.9275</v>
       </c>
       <c r="BQ93" s="3" t="n">
-        <v>2.34</v>
+        <v>2.285</v>
       </c>
       <c r="BR93" s="3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -15220,211 +15220,211 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>2.3789</v>
+        <v>2.38</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>2.33</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>3.2</v>
+        <v>2.835</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2.2937</v>
+        <v>2.295</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2.4045</v>
+        <v>2.405</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>2.338</v>
+        <v>2.34</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>2.2967</v>
+        <v>2.295</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>2.4345</v>
+        <v>2.43</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>2.4398</v>
+        <v>2.44</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>1.9536</v>
+        <v>1.96</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>1.8327</v>
+        <v>1.835</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>2.38</v>
+        <v>2.375</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>2.49</v>
+        <v>2.475</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>3.4737</v>
+        <v>3.315</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>2.2295</v>
+        <v>2.23</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>2.5355</v>
+        <v>2.535</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>2.5576</v>
+        <v>2.555</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>2.9322</v>
+        <v>2.92</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>2.2865</v>
+        <v>2.295</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>2.4744</v>
+        <v>2.935</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>2.4079</v>
+        <v>2.41</v>
       </c>
       <c r="W69" s="3" t="n">
         <v>2</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>2.3302</v>
+        <v>2.33</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>2.2753</v>
+        <v>2.275</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>2.3338</v>
+        <v>2.33</v>
       </c>
       <c r="AA69" s="3" t="n">
-        <v>2.4372</v>
+        <v>2.435</v>
       </c>
       <c r="AB69" s="3" t="n">
-        <v>2.4323</v>
+        <v>2.43</v>
       </c>
       <c r="AC69" s="3" t="n">
-        <v>2.3154</v>
+        <v>2.515</v>
       </c>
       <c r="AD69" s="3" t="n">
-        <v>2.295</v>
+        <v>2.475</v>
       </c>
       <c r="AE69" s="3" t="n">
-        <v>2.2377</v>
+        <v>2.24</v>
       </c>
       <c r="AF69" s="3" t="n">
-        <v>2.9243</v>
+        <v>2.925</v>
       </c>
       <c r="AG69" s="3" t="n">
-        <v>2.5747</v>
+        <v>2.57</v>
       </c>
       <c r="AH69" s="3" t="n">
-        <v>2.2478</v>
+        <v>2.25</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>1.973</v>
+        <v>1.96</v>
       </c>
       <c r="AJ69" s="3" t="n">
-        <v>2.4016</v>
+        <v>2.4</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>2.2157</v>
+        <v>2.22</v>
       </c>
       <c r="AM69" s="3" t="n">
-        <v>2.9857</v>
+        <v>2.975</v>
       </c>
       <c r="AN69" s="3" t="n">
-        <v>3.8509</v>
+        <v>3.85</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>3.1812</v>
+        <v>3.18</v>
       </c>
       <c r="AP69" s="3" t="n">
-        <v>2.3053</v>
+        <v>2.305</v>
       </c>
       <c r="AQ69" s="3" t="n">
-        <v>1.937</v>
+        <v>1.935</v>
       </c>
       <c r="AR69" s="3" t="n">
-        <v>2.3638</v>
+        <v>2.365</v>
       </c>
       <c r="AS69" s="3" t="n">
-        <v>1.8511</v>
+        <v>1.85</v>
       </c>
       <c r="AT69" s="3" t="n">
-        <v>1.9483</v>
+        <v>1.95</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>2.2833</v>
+        <v>2.285</v>
       </c>
       <c r="AV69" s="3" t="n">
-        <v>2.3622</v>
+        <v>2.36</v>
       </c>
       <c r="AW69" s="3" t="n">
-        <v>3.062</v>
+        <v>3.06</v>
       </c>
       <c r="AX69" s="3" t="n">
-        <v>2.3335</v>
+        <v>2.335</v>
       </c>
       <c r="AY69" s="3" t="n">
-        <v>2.2668</v>
+        <v>2.265</v>
       </c>
       <c r="AZ69" s="3" t="n">
-        <v>2.3433</v>
+        <v>2.385</v>
       </c>
       <c r="BA69" s="3" t="n">
-        <v>2.1446</v>
+        <v>2.14</v>
       </c>
       <c r="BB69" s="3" t="n">
-        <v>1.9283</v>
+        <v>1.93</v>
       </c>
       <c r="BC69" s="3" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="BD69" s="3" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BE69" s="3" t="n">
-        <v>2.3604</v>
+        <v>2.36</v>
       </c>
       <c r="BF69" s="3" t="n">
-        <v>1.9483</v>
+        <v>1.98</v>
       </c>
       <c r="BG69" s="3" t="n">
-        <v>2.2741</v>
+        <v>2.275</v>
       </c>
       <c r="BH69" s="3" t="n">
-        <v>2.4014</v>
+        <v>2.4</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>3.3148</v>
+        <v>3.315</v>
       </c>
       <c r="BJ69" s="3" t="n">
-        <v>3.3237</v>
+        <v>3.325</v>
       </c>
       <c r="BK69" s="3" t="n">
-        <v>1.9501</v>
+        <v>1.95</v>
       </c>
       <c r="BL69" s="3" t="n">
-        <v>3.3237</v>
+        <v>3.01</v>
       </c>
       <c r="BM69" s="3" t="n">
-        <v>3.425</v>
+        <v>2.815</v>
       </c>
       <c r="BN69" s="3" t="n">
         <v>3.425</v>
       </c>
       <c r="BO69" s="3" t="n">
-        <v>1.8983</v>
+        <v>1.96</v>
       </c>
       <c r="BP69" s="3" t="n">
-        <v>2.0958</v>
+        <v>2.11</v>
       </c>
       <c r="BQ69" s="3" t="n">
-        <v>2.3407</v>
+        <v>2.34</v>
       </c>
       <c r="BR69" s="3" t="n">
-        <v>1.9487</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="70">
@@ -15434,211 +15434,211 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2.295</v>
+        <v>2.4451</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2.231</v>
+        <v>2.3725</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2.195</v>
+        <v>2.8</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2.235</v>
+        <v>2.3092</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2.335</v>
+        <v>2.411</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2.18</v>
+        <v>2.3976</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>2.18</v>
+        <v>2.3532</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2.38</v>
+        <v>2.5009</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>2.33</v>
+        <v>2.4954</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>1.8755</v>
+        <v>1.8292</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>1.795</v>
+        <v>1.9664</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>2.285</v>
+        <v>2.3806</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>2.445</v>
+        <v>2.5</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>3.34</v>
+        <v>3.4198</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>2.265</v>
+        <v>2.2326</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>2.57</v>
+        <v>2.556</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.5889</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>2.365</v>
+        <v>3.0381</v>
       </c>
       <c r="T70" s="3" t="n">
-        <v>2.2885</v>
+        <v>2.2517</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>2.4735</v>
+        <v>2.4085</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>2.37</v>
+        <v>2.4003</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>1.897</v>
+        <v>2.0484</v>
       </c>
       <c r="X70" s="3" t="n">
-        <v>2.235</v>
+        <v>2.375</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>2.192</v>
+        <v>2.2835</v>
       </c>
       <c r="Z70" s="3" t="n">
+        <v>2.3746</v>
+      </c>
+      <c r="AA70" s="3" t="n">
+        <v>2.4323</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>2.4269</v>
+      </c>
+      <c r="AC70" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD70" s="3" t="n">
         <v>2.315</v>
       </c>
-      <c r="AA70" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB70" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC70" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD70" s="3" t="n">
-        <v>2.295</v>
-      </c>
       <c r="AE70" s="3" t="n">
-        <v>2.195</v>
+        <v>2.2382</v>
       </c>
       <c r="AF70" s="3" t="n">
-        <v>2.855</v>
+        <v>2.8832</v>
       </c>
       <c r="AG70" s="3" t="n">
-        <v>2.421</v>
+        <v>2.5393</v>
       </c>
       <c r="AH70" s="3" t="n">
-        <v>2.22</v>
+        <v>2.2968</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>1.938</v>
+        <v>1.8302</v>
       </c>
       <c r="AJ70" s="3" t="n">
-        <v>2.362</v>
+        <v>2.442</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>2.345</v>
+        <v>2.4244</v>
       </c>
       <c r="AL70" s="3" t="n">
+        <v>2.1272</v>
+      </c>
+      <c r="AM70" s="3" t="n">
+        <v>2.9615</v>
+      </c>
+      <c r="AN70" s="3" t="n">
+        <v>3.8352</v>
+      </c>
+      <c r="AO70" s="3" t="n">
+        <v>3.1687</v>
+      </c>
+      <c r="AP70" s="3" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="AQ70" s="3" t="n">
+        <v>2.0785</v>
+      </c>
+      <c r="AR70" s="3" t="n">
+        <v>2.3996</v>
+      </c>
+      <c r="AS70" s="3" t="n">
+        <v>2.0524</v>
+      </c>
+      <c r="AT70" s="3" t="n">
+        <v>2.1638</v>
+      </c>
+      <c r="AU70" s="3" t="n">
+        <v>2.2864</v>
+      </c>
+      <c r="AV70" s="3" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="AW70" s="3" t="n">
+        <v>3.0313</v>
+      </c>
+      <c r="AX70" s="3" t="n">
+        <v>2.3234</v>
+      </c>
+      <c r="AY70" s="3" t="n">
+        <v>2.2751</v>
+      </c>
+      <c r="AZ70" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA70" s="3" t="n">
+        <v>2.2824</v>
+      </c>
+      <c r="BB70" s="3" t="n">
+        <v>2.0322</v>
+      </c>
+      <c r="BC70" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD70" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE70" s="3" t="n">
+        <v>2.3814</v>
+      </c>
+      <c r="BF70" s="3" t="n">
+        <v>2.1638</v>
+      </c>
+      <c r="BG70" s="3" t="n">
+        <v>2.2756</v>
+      </c>
+      <c r="BH70" s="3" t="n">
+        <v>2.4209</v>
+      </c>
+      <c r="BI70" s="3" t="n">
+        <v>3.2598</v>
+      </c>
+      <c r="BJ70" s="3" t="n">
+        <v>3.2698</v>
+      </c>
+      <c r="BK70" s="3" t="n">
+        <v>2.0814</v>
+      </c>
+      <c r="BL70" s="3" t="n">
+        <v>3.2698</v>
+      </c>
+      <c r="BM70" s="3" t="n">
+        <v>3.4584</v>
+      </c>
+      <c r="BN70" s="3" t="n">
+        <v>3.4584</v>
+      </c>
+      <c r="BO70" s="3" t="n">
+        <v>2.1138</v>
+      </c>
+      <c r="BP70" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM70" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN70" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO70" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP70" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ70" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR70" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS70" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT70" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU70" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV70" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW70" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX70" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY70" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ70" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA70" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB70" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC70" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD70" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE70" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF70" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG70" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="BH70" s="3" t="n">
-        <v>2.3055</v>
-      </c>
-      <c r="BI70" s="3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BJ70" s="3" t="n">
-        <v>3.295</v>
-      </c>
-      <c r="BK70" s="3" t="n">
-        <v>1.735</v>
-      </c>
-      <c r="BL70" s="3" t="n">
-        <v>2.9285</v>
-      </c>
-      <c r="BM70" s="3" t="n">
-        <v>2.765</v>
-      </c>
-      <c r="BN70" s="3" t="n">
-        <v>3.417</v>
-      </c>
-      <c r="BO70" s="3" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="BP70" s="3" t="n">
-        <v>1.9275</v>
-      </c>
       <c r="BQ70" s="3" t="n">
-        <v>2.285</v>
+        <v>2.3553</v>
       </c>
       <c r="BR70" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8417</v>
       </c>
     </row>
     <row r="71">
@@ -15648,211 +15648,211 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.295</v>
+        <v>2.4451</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.231</v>
+        <v>2.3725</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.195</v>
+        <v>2.8</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.235</v>
+        <v>2.3092</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.335</v>
+        <v>2.411</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.18</v>
+        <v>2.3976</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.18</v>
+        <v>2.3532</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.38</v>
+        <v>2.5009</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.33</v>
+        <v>2.4954</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.8755</v>
+        <v>1.8292</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.795</v>
+        <v>1.9664</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.285</v>
+        <v>2.3806</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.445</v>
+        <v>2.5</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.34</v>
+        <v>3.4198</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.265</v>
+        <v>2.2326</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.57</v>
+        <v>2.556</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.5889</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.365</v>
+        <v>3.0381</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.2885</v>
+        <v>2.2517</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.4735</v>
+        <v>2.4085</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.37</v>
+        <v>2.4003</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.897</v>
+        <v>2.0484</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.235</v>
+        <v>2.375</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.192</v>
+        <v>2.2835</v>
       </c>
       <c r="Z71" s="3" t="n">
+        <v>2.3746</v>
+      </c>
+      <c r="AA71" s="3" t="n">
+        <v>2.4323</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>2.4269</v>
+      </c>
+      <c r="AC71" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD71" s="3" t="n">
         <v>2.315</v>
       </c>
-      <c r="AA71" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB71" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC71" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD71" s="3" t="n">
-        <v>2.295</v>
-      </c>
       <c r="AE71" s="3" t="n">
-        <v>2.195</v>
+        <v>2.2382</v>
       </c>
       <c r="AF71" s="3" t="n">
-        <v>2.855</v>
+        <v>2.8832</v>
       </c>
       <c r="AG71" s="3" t="n">
-        <v>2.421</v>
+        <v>2.5393</v>
       </c>
       <c r="AH71" s="3" t="n">
-        <v>2.22</v>
+        <v>2.2968</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>1.938</v>
+        <v>1.8302</v>
       </c>
       <c r="AJ71" s="3" t="n">
-        <v>2.362</v>
+        <v>2.442</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>2.345</v>
+        <v>2.4244</v>
       </c>
       <c r="AL71" s="3" t="n">
+        <v>2.1272</v>
+      </c>
+      <c r="AM71" s="3" t="n">
+        <v>2.9615</v>
+      </c>
+      <c r="AN71" s="3" t="n">
+        <v>3.8352</v>
+      </c>
+      <c r="AO71" s="3" t="n">
+        <v>3.1687</v>
+      </c>
+      <c r="AP71" s="3" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="AQ71" s="3" t="n">
+        <v>2.0785</v>
+      </c>
+      <c r="AR71" s="3" t="n">
+        <v>2.3996</v>
+      </c>
+      <c r="AS71" s="3" t="n">
+        <v>2.0524</v>
+      </c>
+      <c r="AT71" s="3" t="n">
+        <v>2.1638</v>
+      </c>
+      <c r="AU71" s="3" t="n">
+        <v>2.2864</v>
+      </c>
+      <c r="AV71" s="3" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="AW71" s="3" t="n">
+        <v>3.0313</v>
+      </c>
+      <c r="AX71" s="3" t="n">
+        <v>2.3234</v>
+      </c>
+      <c r="AY71" s="3" t="n">
+        <v>2.2751</v>
+      </c>
+      <c r="AZ71" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA71" s="3" t="n">
+        <v>2.2824</v>
+      </c>
+      <c r="BB71" s="3" t="n">
+        <v>2.0322</v>
+      </c>
+      <c r="BC71" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD71" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE71" s="3" t="n">
+        <v>2.3814</v>
+      </c>
+      <c r="BF71" s="3" t="n">
+        <v>2.1638</v>
+      </c>
+      <c r="BG71" s="3" t="n">
+        <v>2.2756</v>
+      </c>
+      <c r="BH71" s="3" t="n">
+        <v>2.4209</v>
+      </c>
+      <c r="BI71" s="3" t="n">
+        <v>3.2598</v>
+      </c>
+      <c r="BJ71" s="3" t="n">
+        <v>3.2698</v>
+      </c>
+      <c r="BK71" s="3" t="n">
+        <v>2.0814</v>
+      </c>
+      <c r="BL71" s="3" t="n">
+        <v>3.2698</v>
+      </c>
+      <c r="BM71" s="3" t="n">
+        <v>3.4584</v>
+      </c>
+      <c r="BN71" s="3" t="n">
+        <v>3.4584</v>
+      </c>
+      <c r="BO71" s="3" t="n">
+        <v>2.1138</v>
+      </c>
+      <c r="BP71" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM71" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN71" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO71" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP71" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ71" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR71" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS71" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT71" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU71" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV71" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW71" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX71" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY71" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ71" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA71" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB71" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC71" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD71" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE71" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF71" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG71" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="BH71" s="3" t="n">
-        <v>2.3055</v>
-      </c>
-      <c r="BI71" s="3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BJ71" s="3" t="n">
-        <v>3.295</v>
-      </c>
-      <c r="BK71" s="3" t="n">
-        <v>1.735</v>
-      </c>
-      <c r="BL71" s="3" t="n">
-        <v>2.9285</v>
-      </c>
-      <c r="BM71" s="3" t="n">
-        <v>2.765</v>
-      </c>
-      <c r="BN71" s="3" t="n">
-        <v>3.417</v>
-      </c>
-      <c r="BO71" s="3" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="BP71" s="3" t="n">
-        <v>1.9275</v>
-      </c>
       <c r="BQ71" s="3" t="n">
-        <v>2.285</v>
+        <v>2.3553</v>
       </c>
       <c r="BR71" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8417</v>
       </c>
     </row>
     <row r="72">
@@ -15862,211 +15862,211 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.295</v>
+        <v>2.4451</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>2.231</v>
+        <v>2.3725</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2.195</v>
+        <v>2.8</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2.235</v>
+        <v>2.3092</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2.335</v>
+        <v>2.411</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2.18</v>
+        <v>2.3976</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.18</v>
+        <v>2.3532</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2.38</v>
+        <v>2.5009</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2.33</v>
+        <v>2.4954</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>1.8755</v>
+        <v>1.8292</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>1.795</v>
+        <v>1.9664</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>2.285</v>
+        <v>2.3806</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>2.445</v>
+        <v>2.5</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>3.34</v>
+        <v>3.4198</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>2.265</v>
+        <v>2.2326</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>2.57</v>
+        <v>2.556</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.5889</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>2.365</v>
+        <v>3.0381</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>2.2885</v>
+        <v>2.2517</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>2.4735</v>
+        <v>2.4085</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>2.37</v>
+        <v>2.4003</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>1.897</v>
+        <v>2.0484</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>2.235</v>
+        <v>2.375</v>
       </c>
       <c r="Y72" s="3" t="n">
-        <v>2.192</v>
+        <v>2.2835</v>
       </c>
       <c r="Z72" s="3" t="n">
+        <v>2.3746</v>
+      </c>
+      <c r="AA72" s="3" t="n">
+        <v>2.4323</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>2.4269</v>
+      </c>
+      <c r="AC72" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD72" s="3" t="n">
         <v>2.315</v>
       </c>
-      <c r="AA72" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB72" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC72" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD72" s="3" t="n">
-        <v>2.295</v>
-      </c>
       <c r="AE72" s="3" t="n">
-        <v>2.195</v>
+        <v>2.2382</v>
       </c>
       <c r="AF72" s="3" t="n">
-        <v>2.855</v>
+        <v>2.8832</v>
       </c>
       <c r="AG72" s="3" t="n">
-        <v>2.421</v>
+        <v>2.5393</v>
       </c>
       <c r="AH72" s="3" t="n">
-        <v>2.22</v>
+        <v>2.2968</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>1.938</v>
+        <v>1.8302</v>
       </c>
       <c r="AJ72" s="3" t="n">
-        <v>2.362</v>
+        <v>2.442</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>2.345</v>
+        <v>2.4244</v>
       </c>
       <c r="AL72" s="3" t="n">
+        <v>2.1272</v>
+      </c>
+      <c r="AM72" s="3" t="n">
+        <v>2.9615</v>
+      </c>
+      <c r="AN72" s="3" t="n">
+        <v>3.8352</v>
+      </c>
+      <c r="AO72" s="3" t="n">
+        <v>3.1687</v>
+      </c>
+      <c r="AP72" s="3" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="AQ72" s="3" t="n">
+        <v>2.0785</v>
+      </c>
+      <c r="AR72" s="3" t="n">
+        <v>2.3996</v>
+      </c>
+      <c r="AS72" s="3" t="n">
+        <v>2.0524</v>
+      </c>
+      <c r="AT72" s="3" t="n">
+        <v>2.1638</v>
+      </c>
+      <c r="AU72" s="3" t="n">
+        <v>2.2864</v>
+      </c>
+      <c r="AV72" s="3" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="AW72" s="3" t="n">
+        <v>3.0313</v>
+      </c>
+      <c r="AX72" s="3" t="n">
+        <v>2.3234</v>
+      </c>
+      <c r="AY72" s="3" t="n">
+        <v>2.2751</v>
+      </c>
+      <c r="AZ72" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA72" s="3" t="n">
+        <v>2.2824</v>
+      </c>
+      <c r="BB72" s="3" t="n">
+        <v>2.0322</v>
+      </c>
+      <c r="BC72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD72" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE72" s="3" t="n">
+        <v>2.3814</v>
+      </c>
+      <c r="BF72" s="3" t="n">
+        <v>2.1638</v>
+      </c>
+      <c r="BG72" s="3" t="n">
+        <v>2.2756</v>
+      </c>
+      <c r="BH72" s="3" t="n">
+        <v>2.4209</v>
+      </c>
+      <c r="BI72" s="3" t="n">
+        <v>3.2598</v>
+      </c>
+      <c r="BJ72" s="3" t="n">
+        <v>3.2698</v>
+      </c>
+      <c r="BK72" s="3" t="n">
+        <v>2.0814</v>
+      </c>
+      <c r="BL72" s="3" t="n">
+        <v>3.2698</v>
+      </c>
+      <c r="BM72" s="3" t="n">
+        <v>3.4584</v>
+      </c>
+      <c r="BN72" s="3" t="n">
+        <v>3.4584</v>
+      </c>
+      <c r="BO72" s="3" t="n">
+        <v>2.1138</v>
+      </c>
+      <c r="BP72" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM72" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN72" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO72" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP72" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ72" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR72" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS72" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT72" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU72" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV72" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW72" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX72" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY72" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ72" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA72" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB72" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC72" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD72" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE72" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF72" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG72" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="BH72" s="3" t="n">
-        <v>2.3055</v>
-      </c>
-      <c r="BI72" s="3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BJ72" s="3" t="n">
-        <v>3.295</v>
-      </c>
-      <c r="BK72" s="3" t="n">
-        <v>1.735</v>
-      </c>
-      <c r="BL72" s="3" t="n">
-        <v>2.9285</v>
-      </c>
-      <c r="BM72" s="3" t="n">
-        <v>2.765</v>
-      </c>
-      <c r="BN72" s="3" t="n">
-        <v>3.417</v>
-      </c>
-      <c r="BO72" s="3" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="BP72" s="3" t="n">
-        <v>1.9275</v>
-      </c>
       <c r="BQ72" s="3" t="n">
-        <v>2.285</v>
+        <v>2.3553</v>
       </c>
       <c r="BR72" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8417</v>
       </c>
     </row>
     <row r="73">
@@ -16076,211 +16076,211 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E73" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S73" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T73" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V73" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W73" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y73" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z73" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA73" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC73" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD73" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE73" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF73" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG73" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH73" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI73" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ73" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK73" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL73" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM73" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN73" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO73" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP73" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ73" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR73" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS73" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT73" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU73" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV73" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW73" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX73" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY73" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ73" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA73" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB73" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC73" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD73" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE73" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF73" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG73" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F73" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N73" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O73" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P73" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q73" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R73" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S73" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T73" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U73" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V73" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W73" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X73" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y73" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z73" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA73" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB73" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC73" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD73" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE73" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF73" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG73" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH73" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI73" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ73" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK73" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL73" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM73" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN73" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO73" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP73" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ73" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR73" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS73" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT73" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU73" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV73" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW73" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX73" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY73" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ73" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA73" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB73" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC73" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD73" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE73" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF73" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG73" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH73" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ73" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK73" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL73" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM73" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN73" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO73" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP73" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ73" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR73" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="74">
@@ -16290,211 +16290,211 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E74" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S74" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T74" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y74" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC74" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD74" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE74" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF74" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG74" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH74" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI74" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ74" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK74" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL74" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM74" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN74" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO74" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP74" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ74" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR74" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS74" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT74" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU74" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV74" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW74" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX74" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY74" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ74" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA74" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB74" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC74" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD74" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE74" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF74" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG74" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F74" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N74" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O74" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P74" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q74" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R74" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S74" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T74" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U74" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V74" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W74" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X74" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y74" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z74" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA74" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB74" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC74" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD74" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE74" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF74" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG74" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH74" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI74" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ74" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK74" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL74" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM74" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN74" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO74" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP74" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ74" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR74" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS74" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT74" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU74" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV74" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW74" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX74" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY74" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ74" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA74" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB74" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC74" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD74" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE74" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF74" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG74" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH74" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL74" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM74" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN74" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO74" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP74" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR74" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="75">
@@ -16504,211 +16504,211 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E75" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S75" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC75" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD75" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE75" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF75" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG75" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH75" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI75" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ75" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL75" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM75" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN75" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO75" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP75" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ75" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR75" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS75" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT75" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU75" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV75" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW75" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX75" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY75" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ75" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA75" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB75" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC75" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD75" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE75" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF75" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG75" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F75" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J75" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M75" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N75" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O75" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P75" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q75" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R75" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S75" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T75" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U75" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V75" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W75" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X75" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y75" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z75" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA75" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB75" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC75" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD75" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE75" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF75" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG75" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH75" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI75" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ75" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK75" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL75" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM75" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN75" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO75" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP75" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ75" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR75" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS75" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT75" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU75" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV75" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW75" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX75" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY75" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ75" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA75" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB75" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC75" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD75" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE75" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF75" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG75" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH75" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL75" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM75" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN75" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO75" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP75" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR75" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="76">
@@ -16718,211 +16718,211 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E76" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA76" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC76" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD76" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE76" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF76" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG76" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH76" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI76" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ76" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL76" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM76" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN76" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO76" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP76" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ76" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR76" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS76" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT76" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU76" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV76" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW76" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX76" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY76" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ76" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA76" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB76" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC76" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD76" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE76" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF76" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG76" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F76" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z76" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA76" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB76" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC76" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD76" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE76" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF76" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG76" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH76" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI76" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ76" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK76" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL76" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM76" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN76" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO76" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP76" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ76" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR76" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS76" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT76" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU76" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV76" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW76" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX76" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY76" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ76" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA76" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB76" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC76" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD76" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE76" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF76" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG76" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH76" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL76" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM76" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN76" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO76" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP76" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR76" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="77">
@@ -16932,211 +16932,211 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E77" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S77" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA77" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC77" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD77" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE77" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF77" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG77" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH77" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI77" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ77" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK77" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL77" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM77" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN77" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO77" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP77" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ77" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR77" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS77" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT77" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU77" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV77" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW77" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX77" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY77" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ77" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA77" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB77" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC77" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD77" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE77" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF77" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG77" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F77" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M77" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N77" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O77" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P77" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q77" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R77" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S77" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T77" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U77" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V77" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W77" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X77" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y77" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z77" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA77" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB77" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC77" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD77" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE77" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF77" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG77" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH77" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI77" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ77" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK77" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL77" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM77" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN77" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO77" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP77" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ77" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR77" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS77" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT77" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU77" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV77" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW77" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX77" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY77" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ77" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA77" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB77" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC77" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD77" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE77" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF77" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG77" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH77" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL77" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM77" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN77" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO77" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP77" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR77" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="78">
@@ -17146,211 +17146,211 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E78" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S78" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA78" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC78" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD78" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE78" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF78" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG78" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH78" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI78" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ78" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK78" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL78" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM78" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN78" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO78" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP78" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ78" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR78" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS78" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT78" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU78" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV78" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW78" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX78" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY78" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ78" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA78" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB78" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC78" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD78" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE78" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF78" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG78" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F78" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N78" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O78" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P78" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q78" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R78" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S78" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T78" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U78" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V78" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W78" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X78" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y78" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z78" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA78" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB78" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC78" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD78" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE78" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF78" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG78" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH78" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI78" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ78" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK78" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL78" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM78" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN78" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO78" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP78" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ78" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR78" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS78" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT78" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU78" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV78" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW78" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX78" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY78" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ78" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA78" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB78" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC78" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD78" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE78" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF78" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG78" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH78" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL78" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM78" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN78" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO78" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP78" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR78" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="79">
@@ -17360,211 +17360,211 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E79" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA79" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD79" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE79" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF79" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG79" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH79" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI79" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ79" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK79" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL79" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM79" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN79" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO79" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP79" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ79" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR79" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS79" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT79" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU79" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV79" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW79" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX79" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY79" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ79" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA79" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB79" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC79" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD79" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE79" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF79" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG79" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F79" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H79" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T79" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U79" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V79" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W79" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X79" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y79" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z79" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA79" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB79" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC79" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD79" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE79" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF79" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG79" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH79" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI79" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ79" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK79" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL79" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM79" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN79" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO79" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP79" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ79" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR79" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS79" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT79" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU79" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV79" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW79" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX79" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY79" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ79" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA79" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB79" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC79" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD79" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE79" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF79" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG79" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH79" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL79" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM79" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN79" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO79" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP79" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR79" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="80">
@@ -17574,211 +17574,211 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E80" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD80" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE80" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF80" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG80" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH80" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI80" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ80" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK80" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL80" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM80" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN80" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO80" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP80" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ80" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR80" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS80" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT80" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU80" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV80" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW80" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX80" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY80" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ80" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA80" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB80" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC80" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD80" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE80" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF80" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG80" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F80" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H80" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N80" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O80" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P80" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q80" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R80" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S80" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T80" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U80" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V80" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W80" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X80" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y80" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z80" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA80" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB80" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC80" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD80" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE80" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF80" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG80" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH80" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI80" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ80" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK80" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL80" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM80" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN80" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO80" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP80" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ80" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR80" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS80" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT80" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU80" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV80" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW80" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX80" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY80" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ80" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA80" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB80" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC80" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD80" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE80" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF80" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG80" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH80" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL80" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM80" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN80" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO80" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP80" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR80" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="81">
@@ -17788,211 +17788,211 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E81" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S81" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA81" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD81" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE81" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF81" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG81" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH81" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI81" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ81" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK81" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL81" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM81" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN81" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO81" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP81" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ81" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR81" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS81" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT81" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU81" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV81" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW81" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX81" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY81" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ81" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA81" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB81" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC81" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD81" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE81" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF81" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG81" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F81" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M81" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N81" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O81" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P81" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q81" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R81" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S81" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T81" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U81" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V81" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W81" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X81" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y81" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z81" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA81" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB81" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC81" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD81" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE81" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF81" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG81" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH81" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI81" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ81" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK81" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL81" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM81" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN81" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO81" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP81" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ81" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR81" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS81" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT81" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU81" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV81" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW81" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX81" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY81" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ81" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA81" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB81" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC81" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD81" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE81" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF81" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG81" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH81" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL81" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM81" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN81" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO81" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP81" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR81" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="82">
@@ -18002,211 +18002,211 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E82" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S82" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA82" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD82" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE82" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF82" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG82" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH82" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI82" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ82" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK82" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL82" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM82" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN82" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO82" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP82" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ82" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR82" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS82" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT82" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU82" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV82" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW82" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX82" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY82" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ82" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA82" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB82" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC82" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD82" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE82" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF82" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG82" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F82" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N82" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O82" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P82" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q82" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R82" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S82" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T82" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U82" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V82" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W82" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X82" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y82" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z82" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA82" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB82" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC82" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD82" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE82" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF82" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG82" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH82" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI82" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ82" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK82" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL82" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM82" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN82" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO82" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP82" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ82" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR82" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS82" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT82" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU82" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV82" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW82" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX82" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY82" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ82" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA82" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB82" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC82" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD82" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE82" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF82" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG82" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH82" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL82" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM82" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN82" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO82" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP82" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR82" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="83">
@@ -18216,211 +18216,211 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E83" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S83" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA83" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC83" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD83" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE83" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF83" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG83" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH83" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI83" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ83" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK83" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL83" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM83" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN83" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO83" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP83" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ83" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR83" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS83" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT83" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU83" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV83" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW83" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX83" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY83" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ83" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA83" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB83" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC83" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD83" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE83" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF83" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG83" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F83" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N83" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O83" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P83" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q83" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R83" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S83" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T83" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U83" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V83" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W83" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X83" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y83" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z83" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA83" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB83" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC83" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD83" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE83" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF83" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG83" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH83" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI83" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ83" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK83" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL83" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM83" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN83" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO83" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP83" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ83" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR83" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS83" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT83" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU83" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV83" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW83" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX83" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY83" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ83" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA83" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB83" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC83" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD83" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE83" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF83" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG83" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH83" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL83" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM83" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN83" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO83" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP83" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR83" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="84">
@@ -18430,211 +18430,211 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E84" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA84" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB84" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC84" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD84" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE84" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF84" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG84" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH84" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI84" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ84" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK84" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL84" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM84" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN84" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO84" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP84" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ84" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR84" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS84" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT84" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU84" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV84" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW84" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX84" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY84" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ84" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA84" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB84" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC84" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD84" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE84" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF84" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG84" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F84" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N84" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O84" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q84" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R84" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S84" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T84" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U84" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V84" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W84" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X84" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y84" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z84" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA84" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB84" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC84" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD84" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE84" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF84" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG84" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH84" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI84" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ84" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK84" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL84" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM84" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN84" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO84" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP84" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ84" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR84" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS84" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT84" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU84" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV84" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW84" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX84" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY84" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ84" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA84" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB84" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC84" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD84" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE84" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF84" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG84" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH84" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL84" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM84" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN84" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO84" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP84" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR84" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="85">
@@ -18644,211 +18644,211 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E85" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S85" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T85" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W85" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y85" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA85" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC85" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD85" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE85" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF85" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG85" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH85" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI85" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ85" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK85" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL85" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM85" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN85" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO85" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP85" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ85" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR85" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS85" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT85" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU85" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV85" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW85" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX85" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY85" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ85" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA85" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB85" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC85" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD85" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE85" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF85" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG85" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F85" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M85" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N85" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O85" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P85" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q85" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R85" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S85" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T85" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U85" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V85" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W85" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X85" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y85" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z85" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA85" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB85" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC85" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD85" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE85" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF85" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG85" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH85" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI85" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ85" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK85" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL85" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM85" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN85" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO85" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP85" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ85" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR85" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS85" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT85" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU85" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV85" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW85" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX85" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY85" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ85" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA85" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB85" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC85" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD85" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE85" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF85" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG85" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH85" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL85" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM85" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN85" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO85" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP85" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR85" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="86">
@@ -18858,211 +18858,211 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E86" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y86" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z86" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA86" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC86" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD86" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE86" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF86" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG86" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH86" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI86" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ86" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK86" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL86" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM86" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN86" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO86" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP86" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ86" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR86" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS86" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT86" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU86" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV86" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW86" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX86" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY86" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ86" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA86" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB86" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC86" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD86" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE86" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF86" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG86" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F86" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T86" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U86" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V86" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W86" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X86" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y86" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z86" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA86" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB86" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC86" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD86" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE86" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF86" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG86" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH86" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI86" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ86" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK86" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL86" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM86" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN86" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO86" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP86" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ86" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR86" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS86" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT86" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU86" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV86" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW86" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX86" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY86" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ86" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA86" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB86" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC86" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD86" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE86" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF86" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG86" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH86" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL86" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM86" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN86" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO86" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP86" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR86" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="87">
@@ -19072,211 +19072,211 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E87" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S87" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T87" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W87" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y87" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA87" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB87" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC87" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD87" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE87" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF87" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG87" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH87" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI87" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ87" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK87" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL87" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM87" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN87" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO87" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP87" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ87" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR87" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS87" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT87" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU87" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV87" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW87" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX87" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY87" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ87" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA87" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB87" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC87" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD87" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE87" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF87" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG87" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F87" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N87" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O87" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q87" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R87" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S87" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T87" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U87" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V87" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W87" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X87" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y87" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z87" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA87" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB87" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC87" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD87" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE87" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF87" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG87" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH87" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI87" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ87" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK87" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL87" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM87" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN87" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO87" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP87" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ87" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR87" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS87" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT87" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU87" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV87" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW87" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX87" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY87" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ87" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA87" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB87" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC87" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD87" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE87" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF87" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG87" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH87" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ87" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK87" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL87" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM87" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN87" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO87" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP87" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ87" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR87" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="88">
@@ -19286,211 +19286,211 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E88" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q88" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S88" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T88" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W88" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y88" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z88" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA88" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB88" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC88" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD88" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE88" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF88" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG88" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH88" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI88" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ88" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK88" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL88" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM88" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN88" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO88" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP88" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ88" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR88" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS88" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT88" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU88" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV88" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW88" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX88" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY88" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ88" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA88" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB88" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC88" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD88" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE88" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF88" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG88" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F88" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N88" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O88" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P88" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q88" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R88" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S88" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T88" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U88" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V88" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W88" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X88" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y88" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z88" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA88" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB88" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC88" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD88" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE88" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF88" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG88" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH88" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI88" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ88" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK88" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL88" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM88" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN88" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO88" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP88" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ88" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR88" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS88" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT88" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU88" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV88" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW88" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX88" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY88" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ88" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA88" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB88" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC88" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD88" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE88" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF88" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG88" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH88" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ88" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK88" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL88" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM88" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN88" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO88" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP88" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ88" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR88" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="89">
@@ -19500,211 +19500,211 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E89" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S89" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T89" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W89" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y89" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA89" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB89" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC89" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD89" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE89" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF89" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG89" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH89" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI89" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ89" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK89" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL89" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM89" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN89" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO89" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP89" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ89" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR89" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS89" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT89" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU89" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV89" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW89" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX89" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY89" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ89" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA89" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB89" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC89" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD89" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE89" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF89" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG89" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F89" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N89" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O89" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P89" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q89" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R89" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S89" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T89" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U89" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V89" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W89" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X89" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y89" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z89" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA89" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB89" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC89" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD89" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE89" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF89" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG89" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH89" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI89" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ89" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK89" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL89" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM89" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN89" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO89" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP89" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ89" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR89" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS89" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT89" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU89" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV89" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW89" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX89" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY89" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ89" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA89" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB89" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC89" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD89" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE89" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF89" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG89" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH89" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ89" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK89" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL89" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM89" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN89" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO89" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP89" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ89" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR89" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="90">
@@ -19714,211 +19714,211 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E90" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q90" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S90" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W90" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y90" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z90" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA90" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC90" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD90" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE90" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF90" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG90" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH90" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI90" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ90" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK90" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL90" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM90" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN90" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO90" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP90" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ90" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR90" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS90" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT90" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU90" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV90" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW90" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX90" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY90" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ90" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA90" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB90" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC90" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD90" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE90" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF90" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG90" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M90" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N90" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O90" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P90" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q90" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R90" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S90" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T90" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U90" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V90" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W90" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X90" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y90" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z90" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA90" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB90" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC90" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD90" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE90" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF90" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG90" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH90" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI90" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ90" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK90" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL90" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM90" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN90" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO90" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP90" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ90" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR90" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS90" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT90" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU90" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV90" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW90" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX90" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY90" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ90" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA90" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB90" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC90" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD90" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE90" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF90" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG90" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH90" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ90" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK90" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL90" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM90" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN90" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO90" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP90" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ90" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR90" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="91">
@@ -19928,211 +19928,211 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E91" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y91" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA91" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB91" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC91" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD91" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE91" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF91" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG91" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH91" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI91" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ91" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK91" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL91" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM91" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN91" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO91" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP91" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ91" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR91" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS91" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT91" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU91" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV91" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW91" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX91" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY91" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ91" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA91" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB91" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC91" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD91" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE91" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF91" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG91" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F91" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U91" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X91" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y91" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z91" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA91" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB91" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC91" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD91" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE91" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF91" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG91" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH91" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI91" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ91" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK91" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL91" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM91" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN91" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO91" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP91" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ91" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR91" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS91" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT91" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU91" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV91" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW91" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX91" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY91" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ91" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA91" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB91" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC91" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD91" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE91" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF91" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG91" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH91" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ91" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK91" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL91" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM91" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN91" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO91" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP91" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ91" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR91" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="92">
@@ -20142,211 +20142,211 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E92" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q92" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S92" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W92" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y92" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z92" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA92" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB92" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC92" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD92" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE92" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF92" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG92" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH92" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI92" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ92" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK92" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL92" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM92" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN92" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO92" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP92" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ92" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR92" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS92" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT92" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU92" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV92" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW92" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX92" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY92" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ92" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA92" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB92" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC92" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD92" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE92" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF92" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG92" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F92" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M92" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N92" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O92" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P92" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q92" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R92" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S92" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T92" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U92" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V92" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W92" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X92" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y92" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z92" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA92" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB92" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC92" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD92" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE92" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF92" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG92" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH92" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI92" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ92" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK92" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL92" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM92" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN92" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO92" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP92" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ92" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR92" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS92" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT92" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU92" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV92" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW92" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX92" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY92" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ92" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA92" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB92" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC92" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD92" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE92" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF92" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG92" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH92" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ92" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK92" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL92" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM92" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN92" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO92" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP92" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ92" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR92" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="93">
@@ -20356,211 +20356,211 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>2.295</v>
+        <v>2.315</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.231</v>
+        <v>2.251</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2.195</v>
+        <v>2.215</v>
       </c>
       <c r="E93" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>1.8255</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="Q93" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>2.3175</v>
+      </c>
+      <c r="S93" s="3" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>2.2985</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="Y93" s="3" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AA93" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB93" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC93" s="3" t="n">
+        <v>2.399</v>
+      </c>
+      <c r="AD93" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AE93" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AF93" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG93" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH93" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AI93" s="3" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="AJ93" s="3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="AK93" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="AL93" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM93" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AN93" s="3" t="n">
+        <v>3.629</v>
+      </c>
+      <c r="AO93" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AP93" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="AQ93" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AR93" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AS93" s="3" t="n">
+        <v>1.8285</v>
+      </c>
+      <c r="AT93" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AU93" s="3" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AV93" s="3" t="n">
+        <v>2.342</v>
+      </c>
+      <c r="AW93" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AX93" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="AY93" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ93" s="3" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="BA93" s="3" t="n">
+        <v>2.0955</v>
+      </c>
+      <c r="BB93" s="3" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="BC93" s="3" t="n">
+        <v>2.2625</v>
+      </c>
+      <c r="BD93" s="3" t="n">
+        <v>2.2005</v>
+      </c>
+      <c r="BE93" s="3" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="BF93" s="3" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="BG93" s="3" t="n">
         <v>2.235</v>
       </c>
-      <c r="F93" s="3" t="n">
-        <v>2.335</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>1.8755</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="N93" s="3" t="n">
-        <v>2.445</v>
-      </c>
-      <c r="O93" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P93" s="3" t="n">
-        <v>2.265</v>
-      </c>
-      <c r="Q93" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R93" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="S93" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="T93" s="3" t="n">
-        <v>2.2885</v>
-      </c>
-      <c r="U93" s="3" t="n">
-        <v>2.4735</v>
-      </c>
-      <c r="V93" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W93" s="3" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="X93" s="3" t="n">
-        <v>2.235</v>
-      </c>
-      <c r="Y93" s="3" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z93" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AA93" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AB93" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AC93" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD93" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AE93" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AF93" s="3" t="n">
-        <v>2.855</v>
-      </c>
-      <c r="AG93" s="3" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="AH93" s="3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI93" s="3" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="AJ93" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AK93" s="3" t="n">
-        <v>2.345</v>
-      </c>
-      <c r="AL93" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM93" s="3" t="n">
-        <v>2.606</v>
-      </c>
-      <c r="AN93" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO93" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AP93" s="3" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="AQ93" s="3" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="AR93" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AS93" s="3" t="n">
-        <v>1.7965</v>
-      </c>
-      <c r="AT93" s="3" t="n">
-        <v>1.856</v>
-      </c>
-      <c r="AU93" s="3" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="AV93" s="3" t="n">
-        <v>2.322</v>
-      </c>
-      <c r="AW93" s="3" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="AX93" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AY93" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ93" s="3" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="BA93" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="BB93" s="3" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="BC93" s="3" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="BD93" s="3" t="n">
-        <v>2.1805</v>
-      </c>
-      <c r="BE93" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="BF93" s="3" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="BG93" s="3" t="n">
-        <v>2.215</v>
-      </c>
       <c r="BH93" s="3" t="n">
-        <v>2.3055</v>
+        <v>2.3255</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>3.27</v>
+        <v>3.305</v>
       </c>
       <c r="BJ93" s="3" t="n">
-        <v>3.295</v>
+        <v>3.33</v>
       </c>
       <c r="BK93" s="3" t="n">
-        <v>1.735</v>
+        <v>1.755</v>
       </c>
       <c r="BL93" s="3" t="n">
-        <v>2.9285</v>
+        <v>2.9485</v>
       </c>
       <c r="BM93" s="3" t="n">
-        <v>2.765</v>
+        <v>2.785</v>
       </c>
       <c r="BN93" s="3" t="n">
-        <v>3.417</v>
+        <v>3.437</v>
       </c>
       <c r="BO93" s="3" t="n">
-        <v>1.838</v>
+        <v>1.858</v>
       </c>
       <c r="BP93" s="3" t="n">
-        <v>1.9275</v>
+        <v>1.9475</v>
       </c>
       <c r="BQ93" s="3" t="n">
-        <v>2.285</v>
+        <v>2.305</v>
       </c>
       <c r="BR93" s="3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -15434,211 +15434,211 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2.4451</v>
+        <v>2.445</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2.3725</v>
+        <v>2.375</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2.3092</v>
+        <v>2.31</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2.411</v>
+        <v>2.41</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2.3976</v>
+        <v>2.4</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>2.3532</v>
+        <v>2.355</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2.5009</v>
+        <v>2.505</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>2.4954</v>
+        <v>2.495</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>1.8292</v>
+        <v>1.83</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>1.9664</v>
+        <v>1.965</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>2.3806</v>
+        <v>2.37</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>2.5</v>
+        <v>2.495</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>3.4198</v>
+        <v>3.265</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>2.2326</v>
+        <v>2.235</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>2.556</v>
+        <v>2.555</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>2.5889</v>
+        <v>2.59</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>3.0381</v>
+        <v>3.04</v>
       </c>
       <c r="T70" s="3" t="n">
-        <v>2.2517</v>
+        <v>2.26</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>2.4085</v>
+        <v>2.945</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>2.4003</v>
+        <v>2.4</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>2.0484</v>
+        <v>2.05</v>
       </c>
       <c r="X70" s="3" t="n">
         <v>2.375</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>2.2835</v>
+        <v>2.285</v>
       </c>
       <c r="Z70" s="3" t="n">
-        <v>2.3746</v>
+        <v>2.37</v>
       </c>
       <c r="AA70" s="3" t="n">
-        <v>2.4323</v>
+        <v>2.43</v>
       </c>
       <c r="AB70" s="3" t="n">
-        <v>2.4269</v>
+        <v>2.425</v>
       </c>
       <c r="AC70" s="3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD70" s="3" t="n">
-        <v>2.315</v>
+        <v>2.48</v>
       </c>
       <c r="AE70" s="3" t="n">
-        <v>2.2382</v>
+        <v>2.24</v>
       </c>
       <c r="AF70" s="3" t="n">
-        <v>2.8832</v>
+        <v>2.885</v>
       </c>
       <c r="AG70" s="3" t="n">
-        <v>2.5393</v>
+        <v>2.54</v>
       </c>
       <c r="AH70" s="3" t="n">
-        <v>2.2968</v>
+        <v>2.295</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>1.8302</v>
+        <v>1.83</v>
       </c>
       <c r="AJ70" s="3" t="n">
-        <v>2.442</v>
+        <v>2.44</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>2.4244</v>
+        <v>2.425</v>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>2.1272</v>
+        <v>2.125</v>
       </c>
       <c r="AM70" s="3" t="n">
-        <v>2.9615</v>
+        <v>2.96</v>
       </c>
       <c r="AN70" s="3" t="n">
-        <v>3.8352</v>
+        <v>3.835</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>3.1687</v>
+        <v>3.17</v>
       </c>
       <c r="AP70" s="3" t="n">
-        <v>2.318</v>
+        <v>2.32</v>
       </c>
       <c r="AQ70" s="3" t="n">
-        <v>2.0785</v>
+        <v>2.08</v>
       </c>
       <c r="AR70" s="3" t="n">
-        <v>2.3996</v>
+        <v>2.4</v>
       </c>
       <c r="AS70" s="3" t="n">
-        <v>2.0524</v>
+        <v>2.05</v>
       </c>
       <c r="AT70" s="3" t="n">
-        <v>2.1638</v>
+        <v>2.165</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>2.2864</v>
+        <v>2.285</v>
       </c>
       <c r="AV70" s="3" t="n">
-        <v>2.389</v>
+        <v>2.39</v>
       </c>
       <c r="AW70" s="3" t="n">
-        <v>3.0313</v>
+        <v>3.03</v>
       </c>
       <c r="AX70" s="3" t="n">
-        <v>2.3234</v>
+        <v>2.325</v>
       </c>
       <c r="AY70" s="3" t="n">
-        <v>2.2751</v>
+        <v>2.275</v>
       </c>
       <c r="AZ70" s="3" t="n">
-        <v>2.271</v>
+        <v>2.38</v>
       </c>
       <c r="BA70" s="3" t="n">
-        <v>2.2824</v>
+        <v>2.285</v>
       </c>
       <c r="BB70" s="3" t="n">
-        <v>2.0322</v>
+        <v>2.03</v>
       </c>
       <c r="BC70" s="3" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BD70" s="3" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="BE70" s="3" t="n">
-        <v>2.3814</v>
+        <v>2.385</v>
       </c>
       <c r="BF70" s="3" t="n">
-        <v>2.1638</v>
+        <v>2.215</v>
       </c>
       <c r="BG70" s="3" t="n">
-        <v>2.2756</v>
+        <v>2.275</v>
       </c>
       <c r="BH70" s="3" t="n">
-        <v>2.4209</v>
+        <v>2.42</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>3.2598</v>
+        <v>3.26</v>
       </c>
       <c r="BJ70" s="3" t="n">
-        <v>3.2698</v>
+        <v>3.27</v>
       </c>
       <c r="BK70" s="3" t="n">
-        <v>2.0814</v>
+        <v>2.08</v>
       </c>
       <c r="BL70" s="3" t="n">
-        <v>3.2698</v>
+        <v>2.87</v>
       </c>
       <c r="BM70" s="3" t="n">
-        <v>3.4584</v>
+        <v>3.195</v>
       </c>
       <c r="BN70" s="3" t="n">
-        <v>3.4584</v>
+        <v>3.46</v>
       </c>
       <c r="BO70" s="3" t="n">
-        <v>2.1138</v>
+        <v>2.115</v>
       </c>
       <c r="BP70" s="3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BQ70" s="3" t="n">
-        <v>2.3553</v>
+        <v>2.355</v>
       </c>
       <c r="BR70" s="3" t="n">
-        <v>1.8417</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="71">
@@ -15648,211 +15648,211 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.4451</v>
+        <v>2.445</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.3725</v>
+        <v>2.375</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.3092</v>
+        <v>2.31</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.411</v>
+        <v>2.41</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.3976</v>
+        <v>2.4</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.3532</v>
+        <v>2.355</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.5009</v>
+        <v>2.505</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.4954</v>
+        <v>2.495</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.8292</v>
+        <v>1.83</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.9664</v>
+        <v>1.965</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.3806</v>
+        <v>2.37</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.5</v>
+        <v>2.495</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.4198</v>
+        <v>3.265</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.2326</v>
+        <v>2.235</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.556</v>
+        <v>2.555</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.5889</v>
+        <v>2.59</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>3.0381</v>
+        <v>3.04</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.2517</v>
+        <v>2.26</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.4085</v>
+        <v>2.945</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.4003</v>
+        <v>2.4</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.0484</v>
+        <v>2.05</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>2.375</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.2835</v>
+        <v>2.285</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.3746</v>
+        <v>2.37</v>
       </c>
       <c r="AA71" s="3" t="n">
-        <v>2.4323</v>
+        <v>2.43</v>
       </c>
       <c r="AB71" s="3" t="n">
-        <v>2.4269</v>
+        <v>2.425</v>
       </c>
       <c r="AC71" s="3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD71" s="3" t="n">
-        <v>2.315</v>
+        <v>2.48</v>
       </c>
       <c r="AE71" s="3" t="n">
-        <v>2.2382</v>
+        <v>2.24</v>
       </c>
       <c r="AF71" s="3" t="n">
-        <v>2.8832</v>
+        <v>2.885</v>
       </c>
       <c r="AG71" s="3" t="n">
-        <v>2.5393</v>
+        <v>2.54</v>
       </c>
       <c r="AH71" s="3" t="n">
-        <v>2.2968</v>
+        <v>2.295</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>1.8302</v>
+        <v>1.83</v>
       </c>
       <c r="AJ71" s="3" t="n">
-        <v>2.442</v>
+        <v>2.44</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>2.4244</v>
+        <v>2.425</v>
       </c>
       <c r="AL71" s="3" t="n">
-        <v>2.1272</v>
+        <v>2.125</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>2.9615</v>
+        <v>2.96</v>
       </c>
       <c r="AN71" s="3" t="n">
-        <v>3.8352</v>
+        <v>3.835</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>3.1687</v>
+        <v>3.17</v>
       </c>
       <c r="AP71" s="3" t="n">
-        <v>2.318</v>
+        <v>2.32</v>
       </c>
       <c r="AQ71" s="3" t="n">
-        <v>2.0785</v>
+        <v>2.08</v>
       </c>
       <c r="AR71" s="3" t="n">
-        <v>2.3996</v>
+        <v>2.4</v>
       </c>
       <c r="AS71" s="3" t="n">
-        <v>2.0524</v>
+        <v>2.05</v>
       </c>
       <c r="AT71" s="3" t="n">
-        <v>2.1638</v>
+        <v>2.165</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>2.2864</v>
+        <v>2.285</v>
       </c>
       <c r="AV71" s="3" t="n">
-        <v>2.389</v>
+        <v>2.39</v>
       </c>
       <c r="AW71" s="3" t="n">
-        <v>3.0313</v>
+        <v>3.03</v>
       </c>
       <c r="AX71" s="3" t="n">
-        <v>2.3234</v>
+        <v>2.325</v>
       </c>
       <c r="AY71" s="3" t="n">
-        <v>2.2751</v>
+        <v>2.275</v>
       </c>
       <c r="AZ71" s="3" t="n">
-        <v>2.271</v>
+        <v>2.38</v>
       </c>
       <c r="BA71" s="3" t="n">
-        <v>2.2824</v>
+        <v>2.285</v>
       </c>
       <c r="BB71" s="3" t="n">
-        <v>2.0322</v>
+        <v>2.03</v>
       </c>
       <c r="BC71" s="3" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BD71" s="3" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="BE71" s="3" t="n">
-        <v>2.3814</v>
+        <v>2.385</v>
       </c>
       <c r="BF71" s="3" t="n">
-        <v>2.1638</v>
+        <v>2.215</v>
       </c>
       <c r="BG71" s="3" t="n">
-        <v>2.2756</v>
+        <v>2.275</v>
       </c>
       <c r="BH71" s="3" t="n">
-        <v>2.4209</v>
+        <v>2.42</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>3.2598</v>
+        <v>3.26</v>
       </c>
       <c r="BJ71" s="3" t="n">
-        <v>3.2698</v>
+        <v>3.27</v>
       </c>
       <c r="BK71" s="3" t="n">
-        <v>2.0814</v>
+        <v>2.08</v>
       </c>
       <c r="BL71" s="3" t="n">
-        <v>3.2698</v>
+        <v>2.87</v>
       </c>
       <c r="BM71" s="3" t="n">
-        <v>3.4584</v>
+        <v>3.195</v>
       </c>
       <c r="BN71" s="3" t="n">
-        <v>3.4584</v>
+        <v>3.46</v>
       </c>
       <c r="BO71" s="3" t="n">
-        <v>2.1138</v>
+        <v>2.115</v>
       </c>
       <c r="BP71" s="3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BQ71" s="3" t="n">
-        <v>2.3553</v>
+        <v>2.355</v>
       </c>
       <c r="BR71" s="3" t="n">
-        <v>1.8417</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="72">
@@ -15862,211 +15862,211 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.4451</v>
+        <v>2.445</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>2.3725</v>
+        <v>2.375</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2.3092</v>
+        <v>2.31</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2.411</v>
+        <v>2.41</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2.3976</v>
+        <v>2.4</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.3532</v>
+        <v>2.355</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2.5009</v>
+        <v>2.505</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2.4954</v>
+        <v>2.495</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>1.8292</v>
+        <v>1.83</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>1.9664</v>
+        <v>1.965</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>2.3806</v>
+        <v>2.37</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>2.5</v>
+        <v>2.495</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>3.4198</v>
+        <v>3.265</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>2.2326</v>
+        <v>2.235</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>2.556</v>
+        <v>2.555</v>
       </c>
       <c r="R72" s="3" t="n">
-        <v>2.5889</v>
+        <v>2.59</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>3.0381</v>
+        <v>3.04</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>2.2517</v>
+        <v>2.26</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>2.4085</v>
+        <v>2.945</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>2.4003</v>
+        <v>2.4</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>2.0484</v>
+        <v>2.05</v>
       </c>
       <c r="X72" s="3" t="n">
         <v>2.375</v>
       </c>
       <c r="Y72" s="3" t="n">
-        <v>2.2835</v>
+        <v>2.285</v>
       </c>
       <c r="Z72" s="3" t="n">
-        <v>2.3746</v>
+        <v>2.37</v>
       </c>
       <c r="AA72" s="3" t="n">
-        <v>2.4323</v>
+        <v>2.43</v>
       </c>
       <c r="AB72" s="3" t="n">
-        <v>2.4269</v>
+        <v>2.425</v>
       </c>
       <c r="AC72" s="3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD72" s="3" t="n">
-        <v>2.315</v>
+        <v>2.48</v>
       </c>
       <c r="AE72" s="3" t="n">
-        <v>2.2382</v>
+        <v>2.24</v>
       </c>
       <c r="AF72" s="3" t="n">
-        <v>2.8832</v>
+        <v>2.885</v>
       </c>
       <c r="AG72" s="3" t="n">
-        <v>2.5393</v>
+        <v>2.54</v>
       </c>
       <c r="AH72" s="3" t="n">
-        <v>2.2968</v>
+        <v>2.295</v>
       </c>
       <c r="AI72" s="3" t="n">
-        <v>1.8302</v>
+        <v>1.83</v>
       </c>
       <c r="AJ72" s="3" t="n">
-        <v>2.442</v>
+        <v>2.44</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>2.4244</v>
+        <v>2.425</v>
       </c>
       <c r="AL72" s="3" t="n">
-        <v>2.1272</v>
+        <v>2.125</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>2.9615</v>
+        <v>2.96</v>
       </c>
       <c r="AN72" s="3" t="n">
-        <v>3.8352</v>
+        <v>3.835</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>3.1687</v>
+        <v>3.17</v>
       </c>
       <c r="AP72" s="3" t="n">
-        <v>2.318</v>
+        <v>2.32</v>
       </c>
       <c r="AQ72" s="3" t="n">
-        <v>2.0785</v>
+        <v>2.08</v>
       </c>
       <c r="AR72" s="3" t="n">
-        <v>2.3996</v>
+        <v>2.4</v>
       </c>
       <c r="AS72" s="3" t="n">
-        <v>2.0524</v>
+        <v>2.05</v>
       </c>
       <c r="AT72" s="3" t="n">
-        <v>2.1638</v>
+        <v>2.165</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>2.2864</v>
+        <v>2.285</v>
       </c>
       <c r="AV72" s="3" t="n">
-        <v>2.389</v>
+        <v>2.39</v>
       </c>
       <c r="AW72" s="3" t="n">
-        <v>3.0313</v>
+        <v>3.03</v>
       </c>
       <c r="AX72" s="3" t="n">
-        <v>2.3234</v>
+        <v>2.325</v>
       </c>
       <c r="AY72" s="3" t="n">
-        <v>2.2751</v>
+        <v>2.275</v>
       </c>
       <c r="AZ72" s="3" t="n">
-        <v>2.271</v>
+        <v>2.38</v>
       </c>
       <c r="BA72" s="3" t="n">
-        <v>2.2824</v>
+        <v>2.285</v>
       </c>
       <c r="BB72" s="3" t="n">
-        <v>2.0322</v>
+        <v>2.03</v>
       </c>
       <c r="BC72" s="3" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BD72" s="3" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="BE72" s="3" t="n">
-        <v>2.3814</v>
+        <v>2.385</v>
       </c>
       <c r="BF72" s="3" t="n">
-        <v>2.1638</v>
+        <v>2.215</v>
       </c>
       <c r="BG72" s="3" t="n">
-        <v>2.2756</v>
+        <v>2.275</v>
       </c>
       <c r="BH72" s="3" t="n">
-        <v>2.4209</v>
+        <v>2.42</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>3.2598</v>
+        <v>3.26</v>
       </c>
       <c r="BJ72" s="3" t="n">
-        <v>3.2698</v>
+        <v>3.27</v>
       </c>
       <c r="BK72" s="3" t="n">
-        <v>2.0814</v>
+        <v>2.08</v>
       </c>
       <c r="BL72" s="3" t="n">
-        <v>3.2698</v>
+        <v>2.87</v>
       </c>
       <c r="BM72" s="3" t="n">
-        <v>3.4584</v>
+        <v>3.195</v>
       </c>
       <c r="BN72" s="3" t="n">
-        <v>3.4584</v>
+        <v>3.46</v>
       </c>
       <c r="BO72" s="3" t="n">
-        <v>2.1138</v>
+        <v>2.115</v>
       </c>
       <c r="BP72" s="3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BQ72" s="3" t="n">
-        <v>2.3553</v>
+        <v>2.355</v>
       </c>
       <c r="BR72" s="3" t="n">
-        <v>1.8417</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="73">
@@ -16076,211 +16076,211 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2.315</v>
+        <v>2.5596</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2.251</v>
+        <v>2.4275</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2.215</v>
+        <v>2.4</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2.255</v>
+        <v>2.4077</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2.355</v>
+        <v>2.548</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>2.23</v>
+        <v>2.435</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>2.415</v>
+        <v>2.5357</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>2.365</v>
+        <v>2.5991</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>1.8255</v>
+        <v>2.0907</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>1.827</v>
+        <v>2.1024</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>2.305</v>
+        <v>2.55</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>3.4</v>
+        <v>3.7172</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>2.275</v>
+        <v>2.3414</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>2.59</v>
+        <v>2.7125</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.61</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>2.385</v>
+        <v>3.43</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.3856</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6205</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>2.405</v>
+        <v>2.522</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>1.929</v>
+        <v>2.1526</v>
       </c>
       <c r="X73" s="3" t="n">
-        <v>2.255</v>
+        <v>2.3982</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>2.212</v>
+        <v>2.378</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>2.345</v>
+        <v>2.4291</v>
       </c>
       <c r="AA73" s="3" t="n">
-        <v>2.42</v>
+        <v>2.5651</v>
       </c>
       <c r="AB73" s="3" t="n">
-        <v>2.42</v>
+        <v>2.5733</v>
       </c>
       <c r="AC73" s="3" t="n">
-        <v>2.399</v>
+        <v>2.5002</v>
       </c>
       <c r="AD73" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE73" s="3" t="n">
-        <v>2.215</v>
+        <v>2.2847</v>
       </c>
       <c r="AF73" s="3" t="n">
-        <v>2.875</v>
+        <v>3.0691</v>
       </c>
       <c r="AG73" s="3" t="n">
-        <v>2.5</v>
+        <v>2.7697</v>
       </c>
       <c r="AH73" s="3" t="n">
-        <v>2.24</v>
+        <v>2.328</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>1.888</v>
+        <v>2.0791</v>
       </c>
       <c r="AJ73" s="3" t="n">
-        <v>2.382</v>
+        <v>2.5675</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>2.365</v>
+        <v>2.5049</v>
       </c>
       <c r="AL73" s="3" t="n">
-        <v>2.16</v>
+        <v>2.4983</v>
       </c>
       <c r="AM73" s="3" t="n">
-        <v>2.735</v>
+        <v>2.9773</v>
       </c>
       <c r="AN73" s="3" t="n">
-        <v>3.629</v>
+        <v>3.8547</v>
       </c>
       <c r="AO73" s="3" t="n">
-        <v>3.275</v>
+        <v>3.4742</v>
       </c>
       <c r="AP73" s="3" t="n">
-        <v>2.225</v>
+        <v>2.4246</v>
       </c>
       <c r="AQ73" s="3" t="n">
-        <v>1.969</v>
+        <v>2.1655</v>
       </c>
       <c r="AR73" s="3" t="n">
-        <v>2.315</v>
+        <v>2.5089</v>
       </c>
       <c r="AS73" s="3" t="n">
-        <v>1.8285</v>
+        <v>2.1124</v>
       </c>
       <c r="AT73" s="3" t="n">
-        <v>1.876</v>
+        <v>2.2299</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>2.215</v>
+        <v>2.4267</v>
       </c>
       <c r="AV73" s="3" t="n">
-        <v>2.342</v>
+        <v>2.5417</v>
       </c>
       <c r="AW73" s="3" t="n">
-        <v>3.275</v>
+        <v>3.4529</v>
       </c>
       <c r="AX73" s="3" t="n">
-        <v>2.245</v>
+        <v>2.5131</v>
       </c>
       <c r="AY73" s="3" t="n">
-        <v>2.26</v>
+        <v>2.3721</v>
       </c>
       <c r="AZ73" s="3" t="n">
-        <v>2.271</v>
+        <v>2.52</v>
       </c>
       <c r="BA73" s="3" t="n">
-        <v>2.0955</v>
+        <v>2.2515</v>
       </c>
       <c r="BB73" s="3" t="n">
-        <v>1.826</v>
+        <v>2.1122</v>
       </c>
       <c r="BC73" s="3" t="n">
-        <v>2.2625</v>
+        <v>2.6</v>
       </c>
       <c r="BD73" s="3" t="n">
-        <v>2.2005</v>
+        <v>2.4</v>
       </c>
       <c r="BE73" s="3" t="n">
-        <v>2.315</v>
+        <v>2.5157</v>
       </c>
       <c r="BF73" s="3" t="n">
-        <v>1.831</v>
+        <v>2.2299</v>
       </c>
       <c r="BG73" s="3" t="n">
-        <v>2.235</v>
+        <v>2.3797</v>
       </c>
       <c r="BH73" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.5553</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>3.305</v>
+        <v>3.5362</v>
       </c>
       <c r="BJ73" s="3" t="n">
-        <v>3.33</v>
+        <v>3.5672</v>
       </c>
       <c r="BK73" s="3" t="n">
-        <v>1.755</v>
+        <v>2.1943</v>
       </c>
       <c r="BL73" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.5672</v>
       </c>
       <c r="BM73" s="3" t="n">
-        <v>2.785</v>
+        <v>3.8195</v>
       </c>
       <c r="BN73" s="3" t="n">
-        <v>3.437</v>
+        <v>3.8195</v>
       </c>
       <c r="BO73" s="3" t="n">
-        <v>1.858</v>
+        <v>2.1799</v>
       </c>
       <c r="BP73" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.375</v>
       </c>
       <c r="BQ73" s="3" t="n">
-        <v>2.305</v>
+        <v>2.5083</v>
       </c>
       <c r="BR73" s="3" t="n">
-        <v>1.8</v>
+        <v>2.0148</v>
       </c>
     </row>
     <row r="74">
@@ -16290,211 +16290,211 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA74" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB74" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC74" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD74" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE74" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF74" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG74" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH74" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ74" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK74" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL74" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM74" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN74" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO74" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP74" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ74" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR74" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS74" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT74" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU74" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV74" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW74" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX74" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY74" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ74" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA74" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB74" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC74" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD74" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE74" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF74" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG74" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK74" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL74" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM74" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN74" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO74" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP74" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ74" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR74" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS74" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT74" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU74" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV74" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW74" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX74" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY74" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ74" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA74" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB74" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC74" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD74" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE74" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF74" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG74" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH74" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL74" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM74" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN74" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO74" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP74" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR74" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="75">
@@ -16504,211 +16504,211 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T75" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X75" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y75" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z75" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA75" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB75" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC75" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD75" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE75" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF75" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG75" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH75" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ75" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL75" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM75" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN75" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO75" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP75" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ75" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR75" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS75" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT75" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU75" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV75" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW75" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX75" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY75" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ75" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA75" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB75" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC75" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD75" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE75" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF75" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG75" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK75" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL75" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM75" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN75" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO75" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP75" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ75" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR75" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS75" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT75" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU75" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV75" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW75" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX75" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY75" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ75" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA75" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB75" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC75" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD75" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE75" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF75" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG75" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH75" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL75" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM75" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN75" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO75" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP75" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR75" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="76">
@@ -16718,211 +16718,211 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA76" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB76" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC76" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD76" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE76" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF76" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG76" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH76" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ76" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL76" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM76" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN76" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO76" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP76" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ76" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR76" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS76" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT76" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU76" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV76" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW76" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX76" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY76" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ76" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA76" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB76" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC76" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD76" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE76" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF76" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG76" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK76" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL76" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM76" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN76" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO76" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP76" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ76" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR76" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS76" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT76" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU76" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV76" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW76" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX76" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY76" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ76" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA76" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB76" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC76" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD76" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE76" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF76" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG76" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH76" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL76" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM76" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN76" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO76" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP76" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR76" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="77">
@@ -16932,211 +16932,211 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q77" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R77" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S77" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T77" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X77" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y77" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z77" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA77" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB77" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC77" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD77" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE77" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF77" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG77" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH77" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ77" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK77" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL77" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM77" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN77" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO77" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP77" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ77" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR77" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS77" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT77" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU77" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV77" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW77" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX77" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY77" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ77" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA77" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB77" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC77" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD77" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE77" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF77" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG77" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK77" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL77" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM77" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN77" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO77" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP77" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ77" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR77" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS77" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT77" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU77" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV77" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW77" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX77" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY77" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ77" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA77" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB77" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC77" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD77" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE77" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF77" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG77" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH77" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL77" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM77" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN77" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO77" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP77" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR77" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="78">
@@ -17146,211 +17146,211 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X78" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y78" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA78" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB78" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC78" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD78" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE78" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF78" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG78" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH78" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ78" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK78" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL78" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM78" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN78" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO78" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP78" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ78" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR78" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS78" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT78" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU78" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV78" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW78" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX78" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY78" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ78" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA78" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB78" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC78" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD78" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE78" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF78" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG78" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK78" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL78" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM78" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN78" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO78" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP78" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ78" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR78" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS78" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT78" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU78" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV78" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW78" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX78" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY78" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ78" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA78" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB78" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC78" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD78" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE78" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF78" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG78" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH78" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL78" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM78" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN78" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO78" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP78" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR78" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="79">
@@ -17360,211 +17360,211 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA79" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB79" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC79" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD79" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE79" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF79" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG79" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH79" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ79" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK79" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL79" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM79" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN79" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO79" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP79" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ79" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR79" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS79" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT79" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU79" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV79" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW79" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX79" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY79" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ79" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA79" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB79" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC79" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD79" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE79" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF79" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG79" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK79" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL79" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM79" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN79" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO79" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP79" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ79" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR79" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS79" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT79" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU79" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV79" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW79" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX79" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY79" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ79" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA79" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB79" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC79" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD79" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE79" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF79" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG79" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH79" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL79" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM79" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN79" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO79" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP79" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR79" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="80">
@@ -17574,211 +17574,211 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T80" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X80" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y80" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z80" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA80" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB80" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC80" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD80" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE80" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF80" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG80" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH80" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ80" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK80" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL80" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM80" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN80" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO80" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP80" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ80" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR80" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS80" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT80" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU80" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV80" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW80" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX80" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY80" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ80" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA80" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB80" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC80" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD80" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE80" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF80" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG80" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK80" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL80" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM80" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN80" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO80" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP80" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ80" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR80" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS80" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT80" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU80" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV80" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW80" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX80" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY80" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ80" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA80" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB80" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC80" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD80" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE80" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF80" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG80" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH80" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL80" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM80" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN80" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO80" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP80" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR80" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="81">
@@ -17788,211 +17788,211 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P81" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R81" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S81" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T81" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X81" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA81" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB81" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC81" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD81" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE81" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF81" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG81" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH81" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ81" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK81" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL81" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM81" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN81" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO81" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP81" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ81" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR81" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS81" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT81" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU81" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV81" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW81" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX81" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY81" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ81" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA81" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB81" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC81" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD81" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE81" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF81" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG81" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK81" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL81" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM81" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN81" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO81" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP81" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ81" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR81" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS81" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT81" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU81" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV81" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW81" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX81" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY81" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ81" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA81" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB81" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC81" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD81" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE81" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF81" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG81" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH81" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL81" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM81" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN81" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO81" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP81" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR81" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="82">
@@ -18002,211 +18002,211 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P82" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R82" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S82" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T82" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U82" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W82" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X82" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y82" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA82" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB82" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC82" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD82" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE82" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF82" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG82" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH82" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ82" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK82" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL82" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM82" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN82" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO82" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP82" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ82" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR82" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS82" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT82" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU82" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV82" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW82" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX82" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY82" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ82" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA82" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB82" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC82" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD82" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE82" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF82" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG82" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK82" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL82" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM82" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN82" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO82" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP82" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ82" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR82" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS82" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT82" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU82" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV82" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW82" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX82" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY82" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ82" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA82" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB82" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC82" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD82" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE82" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF82" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG82" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH82" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL82" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM82" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN82" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO82" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP82" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR82" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="83">
@@ -18216,211 +18216,211 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P83" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W83" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X83" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y83" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA83" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB83" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC83" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD83" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE83" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF83" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG83" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH83" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ83" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK83" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL83" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM83" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN83" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO83" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP83" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ83" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR83" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS83" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT83" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU83" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV83" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW83" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX83" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY83" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ83" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA83" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB83" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC83" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD83" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE83" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF83" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG83" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK83" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL83" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM83" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN83" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO83" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP83" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ83" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR83" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS83" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT83" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU83" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV83" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW83" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX83" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY83" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ83" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA83" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB83" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC83" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD83" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE83" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF83" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG83" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH83" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL83" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM83" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN83" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO83" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP83" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR83" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="84">
@@ -18430,211 +18430,211 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA84" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB84" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC84" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD84" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE84" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF84" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG84" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH84" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ84" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK84" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL84" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM84" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN84" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO84" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP84" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ84" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR84" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS84" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT84" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU84" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV84" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW84" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX84" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY84" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ84" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA84" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB84" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC84" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD84" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE84" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF84" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG84" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK84" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL84" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM84" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN84" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO84" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP84" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ84" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR84" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS84" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT84" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU84" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV84" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW84" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX84" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY84" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ84" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA84" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB84" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC84" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD84" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE84" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF84" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG84" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH84" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL84" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM84" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN84" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO84" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP84" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR84" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="85">
@@ -18644,211 +18644,211 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X85" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA85" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB85" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC85" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD85" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE85" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF85" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG85" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH85" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ85" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK85" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL85" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM85" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN85" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO85" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP85" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ85" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR85" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS85" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT85" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU85" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV85" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW85" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX85" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY85" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ85" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA85" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB85" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC85" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD85" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE85" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF85" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG85" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK85" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL85" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM85" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN85" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO85" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP85" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ85" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR85" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS85" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT85" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU85" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV85" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW85" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX85" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY85" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ85" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA85" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB85" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC85" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD85" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE85" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF85" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG85" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH85" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL85" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM85" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN85" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO85" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP85" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR85" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="86">
@@ -18858,211 +18858,211 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA86" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB86" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC86" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD86" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE86" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF86" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG86" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH86" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ86" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK86" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL86" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM86" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN86" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO86" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP86" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ86" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR86" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS86" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT86" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU86" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV86" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW86" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX86" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY86" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ86" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA86" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB86" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC86" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD86" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE86" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF86" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG86" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK86" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL86" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM86" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN86" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO86" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP86" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ86" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR86" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS86" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT86" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU86" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV86" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW86" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX86" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY86" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ86" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA86" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB86" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC86" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD86" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE86" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF86" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG86" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH86" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL86" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM86" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN86" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO86" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP86" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR86" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="87">
@@ -19072,211 +19072,211 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P87" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W87" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X87" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z87" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA87" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB87" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC87" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD87" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE87" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF87" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG87" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH87" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ87" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK87" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL87" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM87" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN87" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO87" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP87" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ87" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR87" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS87" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT87" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU87" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV87" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW87" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX87" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY87" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ87" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA87" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB87" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC87" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD87" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE87" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF87" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG87" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK87" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL87" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM87" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN87" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO87" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP87" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ87" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR87" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS87" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT87" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU87" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV87" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW87" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX87" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY87" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ87" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA87" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB87" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC87" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD87" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE87" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF87" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG87" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH87" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ87" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK87" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL87" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM87" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN87" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO87" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP87" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ87" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR87" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="88">
@@ -19286,211 +19286,211 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W88" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X88" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y88" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA88" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB88" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC88" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD88" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE88" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF88" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG88" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH88" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ88" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK88" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL88" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM88" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN88" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO88" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP88" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ88" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR88" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS88" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT88" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU88" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV88" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW88" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX88" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY88" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ88" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA88" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB88" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC88" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD88" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE88" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF88" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG88" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK88" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL88" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM88" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN88" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO88" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP88" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ88" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR88" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS88" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT88" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU88" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV88" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW88" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX88" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY88" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ88" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA88" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB88" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC88" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD88" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE88" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF88" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG88" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH88" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ88" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK88" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL88" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM88" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN88" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO88" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP88" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ88" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR88" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="89">
@@ -19500,211 +19500,211 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA89" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB89" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC89" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD89" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE89" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF89" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG89" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH89" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI89" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ89" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK89" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL89" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM89" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN89" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO89" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP89" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ89" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR89" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS89" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT89" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU89" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV89" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW89" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX89" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY89" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ89" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA89" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB89" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC89" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD89" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE89" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF89" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG89" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK89" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL89" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM89" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN89" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO89" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP89" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ89" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR89" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS89" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT89" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU89" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV89" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW89" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX89" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY89" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ89" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA89" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB89" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC89" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD89" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE89" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF89" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG89" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH89" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ89" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK89" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL89" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM89" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN89" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO89" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP89" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ89" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR89" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="90">
@@ -19714,211 +19714,211 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA90" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB90" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC90" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD90" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE90" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF90" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG90" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH90" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI90" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ90" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK90" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL90" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM90" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN90" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO90" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP90" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ90" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR90" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS90" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT90" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU90" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV90" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW90" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX90" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY90" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ90" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA90" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB90" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC90" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD90" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE90" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF90" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG90" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK90" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL90" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM90" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN90" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO90" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP90" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ90" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR90" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS90" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT90" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU90" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV90" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW90" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX90" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY90" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ90" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA90" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB90" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC90" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD90" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE90" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF90" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG90" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH90" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ90" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK90" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL90" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM90" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN90" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO90" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP90" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ90" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR90" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="91">
@@ -19928,211 +19928,211 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA91" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB91" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC91" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD91" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE91" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF91" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG91" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH91" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI91" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ91" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK91" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL91" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM91" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN91" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO91" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP91" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ91" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR91" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS91" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT91" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU91" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV91" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW91" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX91" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY91" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ91" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA91" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB91" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC91" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD91" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE91" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF91" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG91" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK91" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL91" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM91" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN91" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO91" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP91" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ91" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR91" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS91" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT91" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU91" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV91" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW91" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX91" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY91" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ91" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA91" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB91" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC91" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD91" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE91" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF91" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG91" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH91" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ91" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK91" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL91" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM91" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN91" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO91" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP91" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ91" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR91" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="92">
@@ -20142,211 +20142,211 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W92" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X92" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA92" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB92" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC92" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD92" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE92" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF92" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG92" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH92" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI92" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ92" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK92" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL92" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM92" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN92" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO92" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP92" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ92" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR92" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS92" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT92" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU92" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV92" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW92" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX92" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY92" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ92" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA92" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB92" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC92" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD92" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE92" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF92" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG92" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK92" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL92" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM92" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN92" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO92" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP92" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ92" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR92" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS92" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT92" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU92" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV92" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW92" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX92" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY92" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ92" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA92" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB92" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC92" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD92" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE92" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF92" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG92" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH92" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ92" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK92" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL92" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM92" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN92" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO92" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP92" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ92" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR92" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
     <row r="93">
@@ -20356,211 +20356,211 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.251</v>
+        <v>2.368</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2.355</v>
+        <v>2.502</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.23</v>
+        <v>2.347</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>2.415</v>
+        <v>2.562</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>2.365</v>
+        <v>2.512</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>1.8255</v>
+        <v>1.9745</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>1.827</v>
+        <v>1.961</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>3.4</v>
+        <v>3.823</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>2.275</v>
+        <v>2.392</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>2.59</v>
+        <v>2.737</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>2.3175</v>
+        <v>2.4645</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>2.385</v>
+        <v>2.532</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>2.2985</v>
+        <v>2.4155</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>2.6025</v>
+        <v>2.6975</v>
       </c>
       <c r="V93" s="3" t="n">
-        <v>2.405</v>
+        <v>2.5</v>
       </c>
       <c r="W93" s="3" t="n">
-        <v>1.929</v>
+        <v>2.063</v>
       </c>
       <c r="X93" s="3" t="n">
-        <v>2.255</v>
+        <v>2.402</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>2.212</v>
+        <v>2.359</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>2.345</v>
+        <v>2.497</v>
       </c>
       <c r="AA93" s="3" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AB93" s="3" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC93" s="3" t="n">
-        <v>2.399</v>
+        <v>2.51</v>
       </c>
       <c r="AD93" s="3" t="n">
-        <v>2.315</v>
+        <v>2.462</v>
       </c>
       <c r="AE93" s="3" t="n">
-        <v>2.215</v>
+        <v>2.362</v>
       </c>
       <c r="AF93" s="3" t="n">
-        <v>2.875</v>
+        <v>3.065</v>
       </c>
       <c r="AG93" s="3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AH93" s="3" t="n">
-        <v>2.24</v>
+        <v>2.357</v>
       </c>
       <c r="AI93" s="3" t="n">
-        <v>1.888</v>
+        <v>2.037</v>
       </c>
       <c r="AJ93" s="3" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="AK93" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AL93" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM93" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN93" s="3" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="AO93" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AP93" s="3" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="AQ93" s="3" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="AR93" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="AS93" s="3" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="AT93" s="3" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="AU93" s="3" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="AV93" s="3" t="n">
+        <v>2.489</v>
+      </c>
+      <c r="AW93" s="3" t="n">
+        <v>3.587</v>
+      </c>
+      <c r="AX93" s="3" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="AY93" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="AZ93" s="3" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="BA93" s="3" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="BB93" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BC93" s="3" t="n">
+        <v>2.4095</v>
+      </c>
+      <c r="BD93" s="3" t="n">
+        <v>2.3475</v>
+      </c>
+      <c r="BE93" s="3" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="BF93" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="BG93" s="3" t="n">
         <v>2.382</v>
       </c>
-      <c r="AK93" s="3" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="AL93" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM93" s="3" t="n">
-        <v>2.735</v>
-      </c>
-      <c r="AN93" s="3" t="n">
-        <v>3.629</v>
-      </c>
-      <c r="AO93" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AP93" s="3" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="AQ93" s="3" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="AR93" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="AS93" s="3" t="n">
-        <v>1.8285</v>
-      </c>
-      <c r="AT93" s="3" t="n">
-        <v>1.876</v>
-      </c>
-      <c r="AU93" s="3" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="AV93" s="3" t="n">
-        <v>2.342</v>
-      </c>
-      <c r="AW93" s="3" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="AX93" s="3" t="n">
-        <v>2.245</v>
-      </c>
-      <c r="AY93" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ93" s="3" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="BA93" s="3" t="n">
-        <v>2.0955</v>
-      </c>
-      <c r="BB93" s="3" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="BC93" s="3" t="n">
-        <v>2.2625</v>
-      </c>
-      <c r="BD93" s="3" t="n">
-        <v>2.2005</v>
-      </c>
-      <c r="BE93" s="3" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="BF93" s="3" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="BG93" s="3" t="n">
-        <v>2.235</v>
-      </c>
       <c r="BH93" s="3" t="n">
-        <v>2.3255</v>
+        <v>2.4725</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>3.305</v>
+        <v>3.764</v>
       </c>
       <c r="BJ93" s="3" t="n">
-        <v>3.33</v>
+        <v>3.789</v>
       </c>
       <c r="BK93" s="3" t="n">
-        <v>1.755</v>
+        <v>1.902</v>
       </c>
       <c r="BL93" s="3" t="n">
-        <v>2.9485</v>
+        <v>3.0955</v>
       </c>
       <c r="BM93" s="3" t="n">
-        <v>2.785</v>
+        <v>3.213</v>
       </c>
       <c r="BN93" s="3" t="n">
-        <v>3.437</v>
+        <v>3.865</v>
       </c>
       <c r="BO93" s="3" t="n">
-        <v>1.858</v>
+        <v>2.005</v>
       </c>
       <c r="BP93" s="3" t="n">
-        <v>1.9475</v>
+        <v>2.0945</v>
       </c>
       <c r="BQ93" s="3" t="n">
-        <v>2.305</v>
+        <v>2.452</v>
       </c>
       <c r="BR93" s="3" t="n">
-        <v>1.8</v>
+        <v>1.949</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -16076,19 +16076,19 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2.5596</v>
+        <v>2.56</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2.4275</v>
+        <v>2.43</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2.4</v>
+        <v>2.455</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2.4077</v>
+        <v>2.41</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2.548</v>
+        <v>2.55</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>2.46</v>
@@ -16097,190 +16097,190 @@
         <v>2.435</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>2.5357</v>
+        <v>2.54</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>2.5991</v>
+        <v>2.6</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>2.0907</v>
+        <v>2.085</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>2.1024</v>
+        <v>2.1</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>3.7172</v>
+        <v>3.595</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>2.3414</v>
+        <v>2.34</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>2.7125</v>
+        <v>2.71</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>2.61</v>
+        <v>2.615</v>
       </c>
       <c r="S73" s="3" t="n">
         <v>3.43</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>2.3856</v>
+        <v>2.39</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>2.6205</v>
+        <v>2.99</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>2.522</v>
+        <v>2.52</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>2.1526</v>
+        <v>2.155</v>
       </c>
       <c r="X73" s="3" t="n">
-        <v>2.3982</v>
+        <v>2.4</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>2.378</v>
+        <v>2.38</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>2.4291</v>
+        <v>2.43</v>
       </c>
       <c r="AA73" s="3" t="n">
-        <v>2.5651</v>
+        <v>2.565</v>
       </c>
       <c r="AB73" s="3" t="n">
-        <v>2.5733</v>
+        <v>2.575</v>
       </c>
       <c r="AC73" s="3" t="n">
-        <v>2.5002</v>
+        <v>2.645</v>
       </c>
       <c r="AD73" s="3" t="n">
-        <v>2.462</v>
+        <v>2.705</v>
       </c>
       <c r="AE73" s="3" t="n">
-        <v>2.2847</v>
+        <v>2.285</v>
       </c>
       <c r="AF73" s="3" t="n">
-        <v>3.0691</v>
+        <v>3.07</v>
       </c>
       <c r="AG73" s="3" t="n">
-        <v>2.7697</v>
+        <v>2.755</v>
       </c>
       <c r="AH73" s="3" t="n">
-        <v>2.328</v>
+        <v>2.33</v>
       </c>
       <c r="AI73" s="3" t="n">
-        <v>2.0791</v>
+        <v>2.09</v>
       </c>
       <c r="AJ73" s="3" t="n">
-        <v>2.5675</v>
+        <v>2.57</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>2.5049</v>
+        <v>2.505</v>
       </c>
       <c r="AL73" s="3" t="n">
-        <v>2.4983</v>
+        <v>2.5</v>
       </c>
       <c r="AM73" s="3" t="n">
-        <v>2.9773</v>
+        <v>2.97</v>
       </c>
       <c r="AN73" s="3" t="n">
-        <v>3.8547</v>
+        <v>3.855</v>
       </c>
       <c r="AO73" s="3" t="n">
-        <v>3.4742</v>
+        <v>3.475</v>
       </c>
       <c r="AP73" s="3" t="n">
-        <v>2.4246</v>
+        <v>2.425</v>
       </c>
       <c r="AQ73" s="3" t="n">
-        <v>2.1655</v>
+        <v>2.165</v>
       </c>
       <c r="AR73" s="3" t="n">
-        <v>2.5089</v>
+        <v>2.51</v>
       </c>
       <c r="AS73" s="3" t="n">
-        <v>2.1124</v>
+        <v>2.115</v>
       </c>
       <c r="AT73" s="3" t="n">
-        <v>2.2299</v>
+        <v>2.23</v>
       </c>
       <c r="AU73" s="3" t="n">
-        <v>2.4267</v>
+        <v>2.425</v>
       </c>
       <c r="AV73" s="3" t="n">
-        <v>2.5417</v>
+        <v>2.54</v>
       </c>
       <c r="AW73" s="3" t="n">
-        <v>3.4529</v>
+        <v>3.455</v>
       </c>
       <c r="AX73" s="3" t="n">
-        <v>2.5131</v>
+        <v>2.515</v>
       </c>
       <c r="AY73" s="3" t="n">
-        <v>2.3721</v>
+        <v>2.37</v>
       </c>
       <c r="AZ73" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA73" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB73" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BC73" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BD73" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BE73" s="3" t="n">
         <v>2.52</v>
       </c>
-      <c r="BA73" s="3" t="n">
-        <v>2.2515</v>
-      </c>
-      <c r="BB73" s="3" t="n">
-        <v>2.1122</v>
-      </c>
-      <c r="BC73" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BD73" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BE73" s="3" t="n">
-        <v>2.5157</v>
-      </c>
       <c r="BF73" s="3" t="n">
-        <v>2.2299</v>
+        <v>2.215</v>
       </c>
       <c r="BG73" s="3" t="n">
-        <v>2.3797</v>
+        <v>2.385</v>
       </c>
       <c r="BH73" s="3" t="n">
-        <v>2.5553</v>
+        <v>2.52</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>3.5362</v>
+        <v>3.525</v>
       </c>
       <c r="BJ73" s="3" t="n">
-        <v>3.5672</v>
+        <v>3.565</v>
       </c>
       <c r="BK73" s="3" t="n">
-        <v>2.1943</v>
+        <v>2.195</v>
       </c>
       <c r="BL73" s="3" t="n">
-        <v>3.5672</v>
+        <v>3.315</v>
       </c>
       <c r="BM73" s="3" t="n">
-        <v>3.8195</v>
+        <v>3.49</v>
       </c>
       <c r="BN73" s="3" t="n">
-        <v>3.8195</v>
+        <v>3.82</v>
       </c>
       <c r="BO73" s="3" t="n">
-        <v>2.1799</v>
+        <v>2.215</v>
       </c>
       <c r="BP73" s="3" t="n">
         <v>2.375</v>
       </c>
       <c r="BQ73" s="3" t="n">
-        <v>2.5083</v>
+        <v>2.51</v>
       </c>
       <c r="BR73" s="3" t="n">
-        <v>2.0148</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="74">
@@ -16290,211 +16290,211 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.462</v>
+        <v>2.6113</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.368</v>
+        <v>2.4977</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.362</v>
+        <v>2.15</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.402</v>
+        <v>2.4811</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2.502</v>
+        <v>2.599</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2.347</v>
+        <v>2.5107</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2.347</v>
+        <v>2.4628</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.562</v>
+        <v>2.5917</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>2.512</v>
+        <v>2.5824</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>1.9745</v>
+        <v>2.219</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>1.961</v>
+        <v>1.9867</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>2.452</v>
+        <v>2.52</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>2.59</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>3.823</v>
+        <v>4.0836</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>2.392</v>
+        <v>2.3662</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>2.737</v>
+        <v>2.7849</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>2.4645</v>
+        <v>2.6247</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>2.532</v>
+        <v>2.7606</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>2.4155</v>
+        <v>2.3986</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>2.6975</v>
+        <v>2.6078</v>
       </c>
       <c r="V74" s="3" t="n">
+        <v>2.5378</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>1.9459</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>2.4721</v>
+      </c>
+      <c r="Y74" s="3" t="n">
+        <v>2.3913</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>2.4979</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>2.5786</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="AC74" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AD74" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE74" s="3" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="AF74" s="3" t="n">
+        <v>3.1571</v>
+      </c>
+      <c r="AG74" s="3" t="n">
+        <v>2.6231</v>
+      </c>
+      <c r="AH74" s="3" t="n">
+        <v>2.3547</v>
+      </c>
+      <c r="AI74" s="3" t="n">
+        <v>2.2057</v>
+      </c>
+      <c r="AJ74" s="3" t="n">
+        <v>2.5677</v>
+      </c>
+      <c r="AK74" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="W74" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X74" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y74" s="3" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="Z74" s="3" t="n">
-        <v>2.497</v>
-      </c>
-      <c r="AA74" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB74" s="3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC74" s="3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD74" s="3" t="n">
-        <v>2.462</v>
-      </c>
-      <c r="AE74" s="3" t="n">
-        <v>2.362</v>
-      </c>
-      <c r="AF74" s="3" t="n">
-        <v>3.065</v>
-      </c>
-      <c r="AG74" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH74" s="3" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="AI74" s="3" t="n">
-        <v>2.037</v>
-      </c>
-      <c r="AJ74" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK74" s="3" t="n">
-        <v>2.485</v>
-      </c>
       <c r="AL74" s="3" t="n">
-        <v>2.4</v>
+        <v>2.627</v>
       </c>
       <c r="AM74" s="3" t="n">
-        <v>2.83</v>
+        <v>2.974</v>
       </c>
       <c r="AN74" s="3" t="n">
-        <v>3.724</v>
+        <v>3.87</v>
       </c>
       <c r="AO74" s="3" t="n">
-        <v>3.587</v>
+        <v>3.788</v>
       </c>
       <c r="AP74" s="3" t="n">
-        <v>2.372</v>
+        <v>2.4662</v>
       </c>
       <c r="AQ74" s="3" t="n">
-        <v>2.103</v>
+        <v>2.0401</v>
       </c>
       <c r="AR74" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5498</v>
       </c>
       <c r="AS74" s="3" t="n">
-        <v>1.9855</v>
+        <v>2.0374</v>
       </c>
       <c r="AT74" s="3" t="n">
-        <v>2.023</v>
+        <v>2.0692</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>2.362</v>
+        <v>2.4488</v>
       </c>
       <c r="AV74" s="3" t="n">
-        <v>2.489</v>
+        <v>2.5684</v>
       </c>
       <c r="AW74" s="3" t="n">
-        <v>3.587</v>
+        <v>3.7067</v>
       </c>
       <c r="AX74" s="3" t="n">
-        <v>2.392</v>
+        <v>2.4863</v>
       </c>
       <c r="AY74" s="3" t="n">
-        <v>2.407</v>
+        <v>2.3993</v>
       </c>
       <c r="AZ74" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA74" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.0496</v>
       </c>
       <c r="BB74" s="3" t="n">
-        <v>1.96</v>
+        <v>1.8727</v>
       </c>
       <c r="BC74" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.35</v>
       </c>
       <c r="BD74" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.15</v>
       </c>
       <c r="BE74" s="3" t="n">
-        <v>2.462</v>
+        <v>2.545</v>
       </c>
       <c r="BF74" s="3" t="n">
-        <v>1.978</v>
+        <v>2.0692</v>
       </c>
       <c r="BG74" s="3" t="n">
-        <v>2.382</v>
+        <v>2.4261</v>
       </c>
       <c r="BH74" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.5888</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.764</v>
+        <v>3.6912</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.789</v>
+        <v>3.9336</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>1.902</v>
+        <v>2.0017</v>
       </c>
       <c r="BL74" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.9336</v>
       </c>
       <c r="BM74" s="3" t="n">
-        <v>3.213</v>
+        <v>4.0705</v>
       </c>
       <c r="BN74" s="3" t="n">
-        <v>3.865</v>
+        <v>4.0705</v>
       </c>
       <c r="BO74" s="3" t="n">
-        <v>2.005</v>
+        <v>2.0192</v>
       </c>
       <c r="BP74" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0624</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.452</v>
+        <v>2.5242</v>
       </c>
       <c r="BR74" s="3" t="n">
-        <v>1.949</v>
+        <v>2.1499</v>
       </c>
     </row>
     <row r="75">
@@ -16504,211 +16504,211 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G75" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S75" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y75" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H75" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J75" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M75" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N75" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O75" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P75" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q75" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R75" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S75" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T75" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U75" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V75" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W75" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X75" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y75" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z75" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA75" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB75" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC75" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD75" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE75" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF75" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG75" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH75" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI75" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ75" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL75" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM75" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN75" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO75" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP75" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ75" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ75" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK75" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL75" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM75" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN75" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO75" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP75" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ75" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR75" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS75" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT75" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV75" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW75" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX75" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY75" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ75" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA75" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB75" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC75" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD75" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE75" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF75" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG75" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH75" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL75" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM75" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN75" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO75" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP75" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR75" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="76">
@@ -16718,211 +16718,211 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G76" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y76" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H76" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z76" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA76" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB76" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC76" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD76" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE76" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF76" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG76" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH76" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI76" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ76" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL76" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM76" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN76" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO76" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP76" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ76" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ76" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK76" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL76" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM76" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN76" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO76" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP76" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ76" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR76" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS76" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT76" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV76" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW76" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX76" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY76" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ76" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA76" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB76" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC76" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD76" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE76" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF76" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG76" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH76" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL76" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM76" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN76" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO76" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP76" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR76" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="77">
@@ -16932,211 +16932,211 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G77" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S77" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y77" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H77" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M77" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N77" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O77" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P77" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q77" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R77" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S77" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T77" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U77" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V77" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W77" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X77" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y77" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z77" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA77" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB77" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC77" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD77" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE77" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF77" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG77" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH77" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI77" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ77" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK77" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL77" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM77" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN77" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO77" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP77" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ77" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ77" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK77" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL77" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM77" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN77" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO77" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP77" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ77" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR77" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS77" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT77" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV77" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW77" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX77" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY77" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ77" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA77" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB77" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC77" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD77" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE77" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF77" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG77" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH77" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL77" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM77" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN77" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO77" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP77" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR77" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="78">
@@ -17146,211 +17146,211 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G78" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S78" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y78" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H78" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N78" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O78" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P78" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q78" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R78" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S78" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T78" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U78" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V78" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W78" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X78" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y78" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z78" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA78" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB78" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC78" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD78" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE78" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF78" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG78" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH78" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI78" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ78" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK78" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL78" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM78" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN78" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO78" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP78" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ78" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ78" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK78" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL78" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM78" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN78" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO78" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP78" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ78" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR78" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS78" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT78" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV78" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW78" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX78" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY78" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ78" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA78" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB78" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC78" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD78" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE78" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF78" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG78" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH78" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL78" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM78" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN78" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO78" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP78" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR78" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="79">
@@ -17360,211 +17360,211 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G79" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y79" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H79" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T79" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U79" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V79" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W79" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X79" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y79" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z79" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA79" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB79" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC79" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD79" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE79" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF79" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG79" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH79" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI79" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ79" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK79" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL79" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM79" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN79" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO79" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP79" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ79" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ79" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK79" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL79" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM79" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN79" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO79" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP79" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ79" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR79" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS79" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT79" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV79" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW79" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX79" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY79" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ79" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA79" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB79" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC79" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD79" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE79" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF79" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG79" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH79" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL79" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM79" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN79" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO79" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP79" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR79" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="80">
@@ -17574,211 +17574,211 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G80" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y80" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H80" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N80" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O80" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P80" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q80" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R80" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S80" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T80" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U80" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V80" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W80" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X80" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y80" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z80" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA80" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB80" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC80" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD80" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE80" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF80" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG80" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH80" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI80" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ80" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK80" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL80" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM80" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN80" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO80" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP80" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ80" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ80" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK80" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL80" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM80" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN80" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO80" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP80" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ80" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR80" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS80" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT80" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV80" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW80" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX80" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY80" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ80" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA80" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB80" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC80" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD80" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE80" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF80" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG80" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH80" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL80" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM80" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN80" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO80" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP80" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR80" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="81">
@@ -17788,211 +17788,211 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G81" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S81" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y81" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H81" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M81" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N81" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O81" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P81" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q81" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R81" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S81" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T81" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U81" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V81" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W81" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X81" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y81" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z81" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA81" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB81" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC81" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD81" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE81" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF81" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG81" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH81" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI81" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ81" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK81" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL81" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM81" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN81" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO81" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP81" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ81" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ81" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK81" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL81" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM81" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN81" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO81" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP81" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ81" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR81" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS81" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT81" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV81" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW81" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX81" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY81" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ81" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA81" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB81" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC81" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD81" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE81" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF81" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG81" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH81" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL81" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM81" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN81" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO81" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP81" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR81" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="82">
@@ -18002,211 +18002,211 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G82" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S82" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y82" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H82" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N82" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O82" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P82" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q82" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R82" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S82" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T82" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U82" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V82" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W82" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X82" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y82" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z82" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA82" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB82" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC82" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD82" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE82" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF82" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG82" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH82" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI82" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ82" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK82" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL82" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM82" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN82" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO82" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP82" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ82" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ82" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK82" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL82" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM82" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN82" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO82" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP82" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ82" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR82" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS82" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT82" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV82" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW82" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX82" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY82" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ82" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA82" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB82" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC82" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD82" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE82" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF82" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG82" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH82" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL82" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM82" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN82" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO82" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP82" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR82" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="83">
@@ -18216,211 +18216,211 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G83" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S83" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y83" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H83" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N83" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O83" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P83" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q83" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R83" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S83" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T83" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U83" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V83" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W83" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X83" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y83" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z83" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA83" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB83" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC83" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD83" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE83" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF83" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG83" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH83" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI83" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ83" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK83" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL83" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM83" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN83" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO83" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP83" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ83" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ83" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK83" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL83" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM83" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN83" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO83" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP83" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ83" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR83" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS83" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT83" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV83" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW83" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX83" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY83" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ83" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA83" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB83" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC83" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD83" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE83" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF83" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG83" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH83" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL83" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM83" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN83" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO83" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP83" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR83" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="84">
@@ -18430,211 +18430,211 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G84" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y84" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H84" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N84" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O84" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q84" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R84" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S84" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T84" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U84" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V84" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W84" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X84" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y84" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z84" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA84" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB84" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC84" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD84" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE84" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF84" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG84" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH84" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI84" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ84" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK84" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL84" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM84" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN84" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO84" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP84" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ84" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ84" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK84" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL84" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM84" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN84" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO84" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP84" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ84" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR84" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS84" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT84" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV84" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW84" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX84" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY84" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ84" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA84" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB84" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC84" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD84" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE84" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF84" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG84" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH84" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL84" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM84" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN84" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO84" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP84" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR84" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="85">
@@ -18644,211 +18644,211 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G85" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S85" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T85" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W85" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y85" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H85" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M85" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N85" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O85" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P85" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q85" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R85" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S85" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T85" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U85" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V85" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W85" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X85" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y85" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z85" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA85" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB85" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC85" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD85" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE85" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF85" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG85" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH85" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI85" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ85" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK85" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL85" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM85" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN85" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO85" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP85" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ85" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ85" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK85" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL85" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM85" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN85" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO85" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP85" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ85" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR85" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS85" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT85" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV85" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW85" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX85" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY85" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ85" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA85" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB85" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC85" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD85" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE85" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF85" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG85" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH85" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL85" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM85" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN85" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO85" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP85" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR85" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="86">
@@ -18858,211 +18858,211 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G86" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y86" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H86" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T86" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U86" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V86" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W86" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X86" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y86" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z86" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA86" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB86" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC86" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD86" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE86" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF86" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG86" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH86" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI86" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ86" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK86" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL86" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM86" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN86" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO86" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP86" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ86" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ86" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK86" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL86" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM86" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN86" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO86" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP86" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ86" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR86" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS86" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT86" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV86" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW86" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX86" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY86" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ86" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA86" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB86" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC86" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD86" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE86" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF86" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG86" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH86" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL86" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM86" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN86" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO86" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP86" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR86" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="87">
@@ -19072,211 +19072,211 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G87" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S87" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T87" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W87" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y87" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H87" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N87" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O87" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q87" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R87" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S87" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T87" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U87" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V87" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W87" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X87" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y87" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z87" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA87" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB87" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC87" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD87" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE87" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF87" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG87" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH87" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI87" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ87" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK87" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL87" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM87" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN87" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO87" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP87" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ87" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ87" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK87" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL87" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM87" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN87" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO87" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP87" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ87" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR87" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS87" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT87" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV87" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW87" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX87" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY87" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ87" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA87" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB87" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC87" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD87" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE87" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF87" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG87" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH87" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ87" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK87" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL87" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM87" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN87" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO87" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP87" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ87" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR87" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="88">
@@ -19286,211 +19286,211 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G88" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q88" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S88" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T88" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W88" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y88" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H88" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N88" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O88" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P88" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q88" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R88" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S88" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T88" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U88" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V88" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W88" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X88" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y88" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z88" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA88" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB88" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC88" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD88" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE88" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF88" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG88" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH88" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI88" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ88" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK88" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL88" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM88" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN88" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO88" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP88" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ88" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ88" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK88" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL88" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM88" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN88" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO88" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP88" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ88" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR88" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS88" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT88" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV88" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW88" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX88" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY88" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ88" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA88" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB88" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC88" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD88" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE88" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF88" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG88" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH88" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ88" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK88" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL88" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM88" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN88" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO88" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP88" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ88" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR88" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="89">
@@ -19500,211 +19500,211 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G89" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S89" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T89" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W89" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y89" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H89" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N89" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O89" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P89" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q89" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R89" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S89" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T89" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U89" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V89" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W89" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X89" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y89" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z89" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA89" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB89" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC89" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD89" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE89" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF89" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG89" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH89" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI89" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ89" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK89" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL89" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM89" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN89" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO89" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP89" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ89" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ89" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK89" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL89" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM89" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN89" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO89" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP89" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ89" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR89" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS89" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT89" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV89" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW89" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX89" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY89" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ89" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA89" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB89" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC89" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD89" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE89" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF89" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG89" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH89" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ89" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK89" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL89" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM89" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN89" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO89" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP89" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ89" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR89" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="90">
@@ -19714,211 +19714,211 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G90" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q90" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S90" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W90" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y90" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H90" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M90" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N90" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O90" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P90" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q90" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R90" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S90" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T90" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U90" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V90" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W90" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X90" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y90" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z90" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA90" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB90" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC90" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD90" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE90" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF90" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG90" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH90" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI90" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ90" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK90" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL90" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM90" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN90" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO90" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP90" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ90" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ90" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK90" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL90" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM90" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN90" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO90" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP90" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ90" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR90" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS90" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT90" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV90" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW90" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX90" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY90" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ90" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA90" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB90" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC90" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD90" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE90" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF90" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG90" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH90" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ90" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK90" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL90" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM90" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN90" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO90" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP90" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ90" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR90" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="91">
@@ -19928,211 +19928,211 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G91" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y91" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H91" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U91" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X91" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y91" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z91" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA91" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB91" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC91" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD91" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE91" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF91" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG91" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH91" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI91" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ91" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK91" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL91" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM91" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN91" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO91" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP91" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ91" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ91" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK91" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL91" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM91" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN91" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO91" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP91" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ91" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR91" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS91" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT91" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV91" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW91" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX91" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY91" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ91" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA91" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB91" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC91" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD91" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE91" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF91" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG91" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH91" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ91" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK91" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL91" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM91" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN91" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO91" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP91" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ91" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR91" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="92">
@@ -20142,211 +20142,211 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G92" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q92" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S92" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W92" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y92" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H92" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M92" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N92" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O92" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P92" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q92" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R92" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S92" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T92" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U92" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V92" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W92" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X92" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y92" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z92" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA92" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB92" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC92" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD92" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE92" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF92" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG92" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH92" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI92" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ92" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK92" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL92" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM92" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN92" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO92" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP92" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ92" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ92" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK92" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL92" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM92" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN92" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO92" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP92" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ92" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR92" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS92" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT92" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV92" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW92" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX92" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY92" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ92" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA92" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB92" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC92" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD92" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE92" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF92" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG92" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH92" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ92" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK92" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL92" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM92" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN92" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO92" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP92" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ92" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR92" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="93">
@@ -20356,211 +20356,211 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>2.462</v>
+        <v>2.5</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.368</v>
+        <v>2.306</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2.402</v>
+        <v>2.39</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2.502</v>
+        <v>2.49</v>
       </c>
       <c r="G93" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>2.0755</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q93" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="S93" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>2.3735</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>2.6915</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y93" s="3" t="n">
         <v>2.347</v>
       </c>
-      <c r="H93" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>1.9745</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>1.961</v>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>2.452</v>
-      </c>
-      <c r="N93" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O93" s="3" t="n">
-        <v>3.823</v>
-      </c>
-      <c r="P93" s="3" t="n">
-        <v>2.392</v>
-      </c>
-      <c r="Q93" s="3" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="R93" s="3" t="n">
-        <v>2.4645</v>
-      </c>
-      <c r="S93" s="3" t="n">
-        <v>2.532</v>
-      </c>
-      <c r="T93" s="3" t="n">
-        <v>2.4155</v>
-      </c>
-      <c r="U93" s="3" t="n">
-        <v>2.6975</v>
-      </c>
-      <c r="V93" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W93" s="3" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="X93" s="3" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="Y93" s="3" t="n">
-        <v>2.359</v>
-      </c>
       <c r="Z93" s="3" t="n">
-        <v>2.497</v>
+        <v>2.46</v>
       </c>
       <c r="AA93" s="3" t="n">
-        <v>2.54</v>
+        <v>2.545</v>
       </c>
       <c r="AB93" s="3" t="n">
-        <v>2.55</v>
+        <v>2.545</v>
       </c>
       <c r="AC93" s="3" t="n">
-        <v>2.51</v>
+        <v>2.524</v>
       </c>
       <c r="AD93" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AE93" s="3" t="n">
-        <v>2.362</v>
+        <v>2.3</v>
       </c>
       <c r="AF93" s="3" t="n">
-        <v>3.065</v>
+        <v>3.075</v>
       </c>
       <c r="AG93" s="3" t="n">
-        <v>2.65</v>
+        <v>2.638</v>
       </c>
       <c r="AH93" s="3" t="n">
-        <v>2.357</v>
+        <v>2.295</v>
       </c>
       <c r="AI93" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="AJ93" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="AK93" s="3" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="AL93" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM93" s="3" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="AN93" s="3" t="n">
+        <v>3.718</v>
+      </c>
+      <c r="AO93" s="3" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="AP93" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ93" s="3" t="n">
         <v>2.037</v>
       </c>
-      <c r="AJ93" s="3" t="n">
-        <v>2.529</v>
-      </c>
-      <c r="AK93" s="3" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="AL93" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM93" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AN93" s="3" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="AO93" s="3" t="n">
-        <v>3.587</v>
-      </c>
-      <c r="AP93" s="3" t="n">
-        <v>2.372</v>
-      </c>
-      <c r="AQ93" s="3" t="n">
-        <v>2.103</v>
-      </c>
       <c r="AR93" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="AS93" s="3" t="n">
-        <v>1.9855</v>
+        <v>1.9735</v>
       </c>
       <c r="AT93" s="3" t="n">
-        <v>2.023</v>
+        <v>2.011</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>2.362</v>
+        <v>2.35</v>
       </c>
       <c r="AV93" s="3" t="n">
-        <v>2.489</v>
+        <v>2.477</v>
       </c>
       <c r="AW93" s="3" t="n">
-        <v>3.587</v>
+        <v>3.65</v>
       </c>
       <c r="AX93" s="3" t="n">
-        <v>2.392</v>
+        <v>2.38</v>
       </c>
       <c r="AY93" s="3" t="n">
-        <v>2.407</v>
+        <v>2.395</v>
       </c>
       <c r="AZ93" s="3" t="n">
-        <v>2.418</v>
+        <v>2.406</v>
       </c>
       <c r="BA93" s="3" t="n">
-        <v>2.2425</v>
+        <v>2.2305</v>
       </c>
       <c r="BB93" s="3" t="n">
-        <v>1.96</v>
+        <v>1.894</v>
       </c>
       <c r="BC93" s="3" t="n">
-        <v>2.4095</v>
+        <v>2.2975</v>
       </c>
       <c r="BD93" s="3" t="n">
-        <v>2.3475</v>
+        <v>2.2355</v>
       </c>
       <c r="BE93" s="3" t="n">
-        <v>2.462</v>
+        <v>2.45</v>
       </c>
       <c r="BF93" s="3" t="n">
-        <v>1.978</v>
+        <v>1.966</v>
       </c>
       <c r="BG93" s="3" t="n">
-        <v>2.382</v>
+        <v>2.37</v>
       </c>
       <c r="BH93" s="3" t="n">
-        <v>2.4725</v>
+        <v>2.4605</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>3.764</v>
+        <v>3.9</v>
       </c>
       <c r="BJ93" s="3" t="n">
-        <v>3.789</v>
+        <v>3.925</v>
       </c>
       <c r="BK93" s="3" t="n">
-        <v>1.902</v>
+        <v>1.89</v>
       </c>
       <c r="BL93" s="3" t="n">
-        <v>3.0955</v>
+        <v>3.0835</v>
       </c>
       <c r="BM93" s="3" t="n">
-        <v>3.213</v>
+        <v>3.334</v>
       </c>
       <c r="BN93" s="3" t="n">
-        <v>3.865</v>
+        <v>3.986</v>
       </c>
       <c r="BO93" s="3" t="n">
-        <v>2.005</v>
+        <v>1.993</v>
       </c>
       <c r="BP93" s="3" t="n">
-        <v>2.0945</v>
+        <v>2.0825</v>
       </c>
       <c r="BQ93" s="3" t="n">
-        <v>2.452</v>
+        <v>2.44</v>
       </c>
       <c r="BR93" s="3" t="n">
-        <v>1.949</v>
+        <v>2.05</v>
       </c>
     </row>
   </sheetData>

--- a/master/master_ng_swing_gdd_v2.xlsx
+++ b/master/master_ng_swing_gdd_v2.xlsx
@@ -16290,211 +16290,211 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.6113</v>
+        <v>2.61</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2.4977</v>
+        <v>2.5</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2.15</v>
+        <v>2.145</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.4811</v>
+        <v>2.48</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2.599</v>
+        <v>2.59</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2.5107</v>
+        <v>2.51</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2.4628</v>
+        <v>2.465</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2.5917</v>
+        <v>2.595</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>2.5824</v>
+        <v>2.58</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>2.219</v>
+        <v>2.215</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>1.9867</v>
+        <v>1.985</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>2.52</v>
+        <v>2.565</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>2.59</v>
+        <v>2.595</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>4.0836</v>
+        <v>3.92</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>2.3662</v>
+        <v>2.365</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>2.7849</v>
+        <v>2.785</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>2.6247</v>
+        <v>2.625</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>2.7606</v>
+        <v>2.76</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>2.3986</v>
+        <v>2.405</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>2.6078</v>
+        <v>2.925</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>2.5378</v>
+        <v>2.54</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>1.9459</v>
+        <v>1.945</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>2.4721</v>
+        <v>2.47</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>2.3913</v>
+        <v>2.39</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>2.4979</v>
+        <v>2.5</v>
       </c>
       <c r="AA74" s="3" t="n">
-        <v>2.5786</v>
+        <v>2.58</v>
       </c>
       <c r="AB74" s="3" t="n">
-        <v>2.597</v>
+        <v>2.595</v>
       </c>
       <c r="AC74" s="3" t="n">
         <v>2.625</v>
       </c>
       <c r="AD74" s="3" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AE74" s="3" t="n">
-        <v>2.294</v>
+        <v>2.295</v>
       </c>
       <c r="AF74" s="3" t="n">
-        <v>3.1571</v>
+        <v>3.155</v>
       </c>
       <c r="AG74" s="3" t="n">
-        <v>2.6231</v>
+        <v>2.63</v>
       </c>
       <c r="AH74" s="3" t="n">
-        <v>2.3547</v>
+        <v>2.355</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>2.2057</v>
+        <v>2.215</v>
       </c>
       <c r="AJ74" s="3" t="n">
-        <v>2.5677</v>
+        <v>2.57</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL74" s="3" t="n">
-        <v>2.627</v>
+        <v>2.625</v>
       </c>
       <c r="AM74" s="3" t="n">
-        <v>2.974</v>
+        <v>2.975</v>
       </c>
       <c r="AN74" s="3" t="n">
         <v>3.87</v>
       </c>
       <c r="AO74" s="3" t="n">
-        <v>3.788</v>
+        <v>3.79</v>
       </c>
       <c r="AP74" s="3" t="n">
-        <v>2.4662</v>
+        <v>2.465</v>
       </c>
       <c r="AQ74" s="3" t="n">
-        <v>2.0401</v>
+        <v>2.04</v>
       </c>
       <c r="AR74" s="3" t="n">
-        <v>2.5498</v>
+        <v>2.55</v>
       </c>
       <c r="AS74" s="3" t="n">
-        <v>2.0374</v>
+        <v>2.035</v>
       </c>
       <c r="AT74" s="3" t="n">
-        <v>2.0692</v>
+        <v>2.07</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>2.4488</v>
+        <v>2.45</v>
       </c>
       <c r="AV74" s="3" t="n">
-        <v>2.5684</v>
+        <v>2.57</v>
       </c>
       <c r="AW74" s="3" t="n">
-        <v>3.7067</v>
+        <v>3.705</v>
       </c>
       <c r="AX74" s="3" t="n">
-        <v>2.4863</v>
+        <v>2.485</v>
       </c>
       <c r="AY74" s="3" t="n">
-        <v>2.3993</v>
+        <v>2.4</v>
       </c>
       <c r="AZ74" s="3" t="n">
-        <v>2.406</v>
+        <v>2.51</v>
       </c>
       <c r="BA74" s="3" t="n">
-        <v>2.0496</v>
+        <v>2.05</v>
       </c>
       <c r="BB74" s="3" t="n">
-        <v>1.8727</v>
+        <v>1.875</v>
       </c>
       <c r="BC74" s="3" t="n">
-        <v>2.35</v>
+        <v>2.305</v>
       </c>
       <c r="BD74" s="3" t="n">
         <v>2.15</v>
       </c>
       <c r="BE74" s="3" t="n">
-        <v>2.545</v>
+        <v>2.55</v>
       </c>
       <c r="BF74" s="3" t="n">
-        <v>2.0692</v>
+        <v>2.015</v>
       </c>
       <c r="BG74" s="3" t="n">
-        <v>2.4261</v>
+        <v>2.425</v>
       </c>
       <c r="BH74" s="3" t="n">
-        <v>2.5888</v>
+        <v>2.59</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>3.6912</v>
+        <v>3.69</v>
       </c>
       <c r="BJ74" s="3" t="n">
-        <v>3.9336</v>
+        <v>3.935</v>
       </c>
       <c r="BK74" s="3" t="n">
-        <v>2.0017</v>
+        <v>2</v>
       </c>
       <c r="BL74" s="3" t="n">
-        <v>3.9336</v>
+        <v>3.385</v>
       </c>
       <c r="BM74" s="3" t="n">
-        <v>4.0705</v>
+        <v>3.57</v>
       </c>
       <c r="BN74" s="3" t="n">
-        <v>4.0705</v>
+        <v>4.075</v>
       </c>
       <c r="BO74" s="3" t="n">
-        <v>2.0192</v>
+        <v>2.035</v>
       </c>
       <c r="BP74" s="3" t="n">
-        <v>2.0624</v>
+        <v>2.06</v>
       </c>
       <c r="BQ74" s="3" t="n">
-        <v>2.5242</v>
+        <v>2.525</v>
       </c>
       <c r="BR74" s="3" t="n">
-        <v>2.1499</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="75">
@@ -16504,211 +16504,211 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
+        <v>2.5831</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2.4244</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>2.5209</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2.6085</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>2.3884</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>2.5549</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>2.5611</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>2.2207</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>1.8439</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>2.5268</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>2.6025</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>4.6959</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>2.4231</v>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>2.8187</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>2.6459</v>
+      </c>
+      <c r="S75" s="3" t="n">
+        <v>2.747</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>2.4447</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>2.4248</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>2.5367</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>1.8444</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>2.4165</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>2.4358</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>2.4768</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>2.5048</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>2.5039</v>
+      </c>
+      <c r="AC75" s="3" t="n">
+        <v>2.3763</v>
+      </c>
+      <c r="AD75" s="3" t="n">
+        <v>2.518</v>
+      </c>
+      <c r="AE75" s="3" t="n">
+        <v>2.361</v>
+      </c>
+      <c r="AF75" s="3" t="n">
+        <v>3.1399</v>
+      </c>
+      <c r="AG75" s="3" t="n">
+        <v>2.4227</v>
+      </c>
+      <c r="AH75" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AI75" s="3" t="n">
+        <v>2.2432</v>
+      </c>
+      <c r="AJ75" s="3" t="n">
+        <v>2.5908</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>2.5035</v>
+      </c>
+      <c r="AL75" s="3" t="n">
+        <v>2.4252</v>
+      </c>
+      <c r="AM75" s="3" t="n">
+        <v>2.8581</v>
+      </c>
+      <c r="AN75" s="3" t="n">
+        <v>3.7754</v>
+      </c>
+      <c r="AO75" s="3" t="n">
+        <v>4.3916</v>
+      </c>
+      <c r="AP75" s="3" t="n">
+        <v>2.4984</v>
+      </c>
+      <c r="AQ75" s="3" t="n">
+        <v>1.9833</v>
+      </c>
+      <c r="AR75" s="3" t="n">
+        <v>2.5936</v>
+      </c>
+      <c r="AS75" s="3" t="n">
+        <v>1.8477</v>
+      </c>
+      <c r="AT75" s="3" t="n">
+        <v>1.9413</v>
+      </c>
+      <c r="AU75" s="3" t="n">
+        <v>2.4416</v>
+      </c>
+      <c r="AV75" s="3" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="AW75" s="3" t="n">
+        <v>4.2338</v>
+      </c>
+      <c r="AX75" s="3" t="n">
+        <v>2.5251</v>
+      </c>
+      <c r="AY75" s="3" t="n">
+        <v>2.4258</v>
+      </c>
+      <c r="AZ75" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="C75" s="3" t="n">
-        <v>2.306</v>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>2.379</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>2.379</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J75" s="3" t="n">
+      <c r="BA75" s="3" t="n">
+        <v>1.9642</v>
+      </c>
+      <c r="BB75" s="3" t="n">
+        <v>1.8363</v>
+      </c>
+      <c r="BC75" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BD75" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BE75" s="3" t="n">
+        <v>2.5311</v>
+      </c>
+      <c r="BF75" s="3" t="n">
+        <v>1.9413</v>
+      </c>
+      <c r="BG75" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="K75" s="3" t="n">
-        <v>2.0755</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="M75" s="3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N75" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O75" s="3" t="n">
-        <v>3.925</v>
-      </c>
-      <c r="P75" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q75" s="3" t="n">
-        <v>2.725</v>
-      </c>
-      <c r="R75" s="3" t="n">
-        <v>2.3525</v>
-      </c>
-      <c r="S75" s="3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T75" s="3" t="n">
-        <v>2.3735</v>
-      </c>
-      <c r="U75" s="3" t="n">
-        <v>2.6915</v>
-      </c>
-      <c r="V75" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W75" s="3" t="n">
-        <v>1.997</v>
-      </c>
-      <c r="X75" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y75" s="3" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="Z75" s="3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA75" s="3" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="AB75" s="3" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="AC75" s="3" t="n">
-        <v>2.524</v>
-      </c>
-      <c r="AD75" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE75" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF75" s="3" t="n">
-        <v>3.075</v>
-      </c>
-      <c r="AG75" s="3" t="n">
-        <v>2.638</v>
-      </c>
-      <c r="AH75" s="3" t="n">
-        <v>2.295</v>
-      </c>
-      <c r="AI75" s="3" t="n">
-        <v>2.138</v>
-      </c>
-      <c r="AJ75" s="3" t="n">
-        <v>2.517</v>
-      </c>
-      <c r="AK75" s="3" t="n">
-        <v>2.493</v>
-      </c>
-      <c r="AL75" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM75" s="3" t="n">
-        <v>2.824</v>
-      </c>
-      <c r="AN75" s="3" t="n">
-        <v>3.718</v>
-      </c>
-      <c r="AO75" s="3" t="n">
-        <v>3.695</v>
-      </c>
-      <c r="AP75" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ75" s="3" t="n">
-        <v>2.037</v>
-      </c>
-      <c r="AR75" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AS75" s="3" t="n">
-        <v>1.9735</v>
-      </c>
-      <c r="AT75" s="3" t="n">
-        <v>2.011</v>
-      </c>
-      <c r="AU75" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AV75" s="3" t="n">
-        <v>2.477</v>
-      </c>
-      <c r="AW75" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX75" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AY75" s="3" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="AZ75" s="3" t="n">
-        <v>2.406</v>
-      </c>
-      <c r="BA75" s="3" t="n">
-        <v>2.2305</v>
-      </c>
-      <c r="BB75" s="3" t="n">
-        <v>1.894</v>
-      </c>
-      <c r="BC75" s="3" t="n">
-        <v>2.2975</v>
-      </c>
-      <c r="BD75" s="3" t="n">
-        <v>2.2355</v>
-      </c>
-      <c r="BE75" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BF75" s="3" t="n">
-        <v>1.966</v>
-      </c>
-      <c r="BG75" s="3" t="n">
-        <v>2.37</v>
-      </c>
       <c r="BH75" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5801</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>3.9</v>
+        <v>4.0129</v>
       </c>
       <c r="BJ75" s="3" t="n">
-        <v>3.925</v>
+        <v>4.5459</v>
       </c>
       <c r="BK75" s="3" t="n">
-        <v>1.89</v>
+        <v>1.8986</v>
       </c>
       <c r="BL75" s="3" t="n">
-        <v>3.0835</v>
+        <v>4.5459</v>
       </c>
       <c r="BM75" s="3" t="n">
-        <v>3.334</v>
+        <v>4.7288</v>
       </c>
       <c r="BN75" s="3" t="n">
-        <v>3.986</v>
+        <v>4.7288</v>
       </c>
       <c r="BO75" s="3" t="n">
-        <v>1.993</v>
+        <v>1.8913</v>
       </c>
       <c r="BP75" s="3" t="n">
-        <v>2.0825</v>
+        <v>2.04</v>
       </c>
       <c r="BQ75" s="3" t="n">
-        <v>2.44</v>
+        <v>2.5066</v>
       </c>
       <c r="BR75" s="3" t="n">
-        <v>2.05</v>
+        <v>2.2283</v>
       </c>
     </row>
     <row r="76">
@@ -16718,199 +16718,199 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA76" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB76" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC76" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD76" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE76" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF76" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG76" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH76" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ76" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL76" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM76" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN76" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO76" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP76" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ76" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR76" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS76" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT76" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV76" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW76" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX76" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY76" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ76" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA76" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB76" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC76" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD76" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE76" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF76" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG76" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH76" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ76" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK76" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL76" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM76" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN76" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO76" s="3" t="n">
         <v>1.993</v>
@@ -16919,10 +16919,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ76" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR76" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="77">
@@ -16932,199 +16932,199 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q77" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R77" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S77" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T77" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X77" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y77" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z77" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA77" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB77" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC77" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD77" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE77" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF77" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG77" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH77" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ77" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL77" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM77" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN77" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO77" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP77" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ77" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR77" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS77" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT77" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV77" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW77" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX77" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY77" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ77" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA77" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB77" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC77" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD77" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE77" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF77" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG77" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH77" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ77" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK77" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL77" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM77" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN77" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO77" s="3" t="n">
         <v>1.993</v>
@@ -17133,10 +17133,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ77" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR77" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="78">
@@ -17146,199 +17146,199 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X78" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y78" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA78" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB78" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC78" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD78" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE78" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF78" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG78" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH78" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ78" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL78" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM78" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN78" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO78" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP78" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ78" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR78" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS78" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT78" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV78" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW78" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX78" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY78" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ78" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA78" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB78" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC78" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD78" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE78" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF78" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG78" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH78" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ78" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK78" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL78" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM78" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN78" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO78" s="3" t="n">
         <v>1.993</v>
@@ -17347,10 +17347,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ78" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR78" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="79">
@@ -17360,199 +17360,199 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA79" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB79" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC79" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD79" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE79" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF79" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG79" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH79" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ79" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL79" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM79" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN79" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO79" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP79" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ79" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR79" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS79" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT79" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV79" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW79" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX79" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY79" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ79" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA79" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB79" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC79" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD79" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE79" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF79" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG79" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH79" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ79" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK79" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL79" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM79" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN79" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO79" s="3" t="n">
         <v>1.993</v>
@@ -17561,10 +17561,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ79" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR79" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="80">
@@ -17574,199 +17574,199 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T80" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X80" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y80" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z80" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA80" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB80" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC80" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD80" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE80" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF80" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG80" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH80" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ80" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK80" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL80" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM80" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN80" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO80" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP80" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ80" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR80" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS80" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT80" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV80" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW80" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX80" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY80" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ80" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA80" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB80" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC80" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD80" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE80" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF80" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG80" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH80" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ80" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK80" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL80" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM80" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN80" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO80" s="3" t="n">
         <v>1.993</v>
@@ -17775,10 +17775,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ80" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR80" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="81">
@@ -17788,199 +17788,199 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P81" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R81" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S81" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T81" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X81" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA81" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB81" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC81" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD81" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE81" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF81" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG81" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH81" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI81" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ81" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL81" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM81" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN81" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO81" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP81" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ81" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR81" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS81" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT81" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV81" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW81" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX81" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY81" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ81" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA81" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB81" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC81" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD81" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE81" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF81" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG81" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH81" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ81" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK81" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL81" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM81" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN81" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO81" s="3" t="n">
         <v>1.993</v>
@@ -17989,10 +17989,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ81" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR81" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="82">
@@ -18002,199 +18002,199 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P82" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R82" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S82" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T82" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U82" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W82" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X82" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y82" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA82" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB82" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC82" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD82" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE82" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF82" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG82" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH82" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI82" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ82" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK82" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL82" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM82" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN82" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO82" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP82" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ82" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR82" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS82" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT82" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV82" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW82" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX82" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY82" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ82" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA82" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB82" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC82" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD82" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE82" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF82" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG82" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH82" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ82" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK82" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL82" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM82" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN82" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO82" s="3" t="n">
         <v>1.993</v>
@@ -18203,10 +18203,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ82" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR82" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="83">
@@ -18216,199 +18216,199 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P83" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W83" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X83" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y83" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA83" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB83" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC83" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD83" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE83" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF83" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG83" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH83" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI83" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ83" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK83" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM83" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN83" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO83" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP83" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ83" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR83" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS83" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT83" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV83" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW83" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX83" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY83" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ83" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA83" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB83" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC83" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD83" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE83" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF83" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG83" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH83" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ83" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK83" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL83" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM83" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN83" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO83" s="3" t="n">
         <v>1.993</v>
@@ -18417,10 +18417,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ83" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR83" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="84">
@@ -18430,199 +18430,199 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA84" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB84" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC84" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD84" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE84" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF84" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG84" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH84" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI84" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ84" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL84" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM84" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN84" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO84" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP84" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ84" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR84" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS84" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT84" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV84" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW84" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX84" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY84" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ84" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA84" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB84" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC84" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD84" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE84" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF84" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG84" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH84" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ84" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK84" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL84" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM84" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN84" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO84" s="3" t="n">
         <v>1.993</v>
@@ -18631,10 +18631,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ84" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR84" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="85">
@@ -18644,199 +18644,199 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X85" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA85" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB85" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC85" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD85" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE85" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF85" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG85" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH85" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ85" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK85" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL85" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM85" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN85" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO85" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP85" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ85" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR85" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS85" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT85" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV85" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW85" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX85" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY85" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ85" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA85" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB85" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC85" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD85" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE85" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF85" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG85" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH85" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ85" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK85" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL85" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM85" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN85" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO85" s="3" t="n">
         <v>1.993</v>
@@ -18845,10 +18845,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ85" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR85" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="86">
@@ -18858,199 +18858,199 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA86" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB86" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC86" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD86" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE86" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF86" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG86" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH86" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ86" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK86" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM86" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN86" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO86" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c>
       <c r="AP86" s="3" t="n">
-        <v>2.36</v>
+        <v>2.428</v>
       </c>
       <c r="AQ86" s="3" t="n">
-        <v>2.037</v>
+        <v>1.985</v>
       </c>
       <c r="AR86" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AS86" s="3" t="n">
-        <v>1.9735</v>
+        <v>1.9215</v>
       </c>
       <c r="AT86" s="3" t="n">
         <v>2.011</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="AV86" s="3" t="n">
-        <v>2.477</v>
+        <v>2.545</v>
       </c>
       <c r="AW86" s="3" t="n">
-        <v>3.65</v>
+        <v>4.158</v>
       </c>
       <c r="AX86" s="3" t="n">
-        <v>2.38</v>
+        <v>2.448</v>
       </c>
       <c r="AY86" s="3" t="n">
-        <v>2.395</v>
+        <v>2.463</v>
       </c>
       <c r="AZ86" s="3" t="n">
-        <v>2.406</v>
+        <v>2.474</v>
       </c>
       <c r="BA86" s="3" t="n">
         <v>2.2305</v>
       </c>
       <c r="BB86" s="3" t="n">
-        <v>1.894</v>
+        <v>1.842</v>
       </c>
       <c r="BC86" s="3" t="n">
-        <v>2.2975</v>
+        <v>2.3655</v>
       </c>
       <c r="BD86" s="3" t="n">
-        <v>2.2355</v>
+        <v>2.3035</v>
       </c>
       <c r="BE86" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="BF86" s="3" t="n">
-        <v>1.966</v>
+        <v>2.034</v>
       </c>
       <c r="BG86" s="3" t="n">
-        <v>2.37</v>
+        <v>2.438</v>
       </c>
       <c r="BH86" s="3" t="n">
-        <v>2.4605</v>
+        <v>2.5285</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>3.9</v>
+        <v>4.385</v>
       </c>
       <c r="BJ86" s="3" t="n">
-        <v>3.925</v>
+        <v>4.41</v>
       </c>
       <c r="BK86" s="3" t="n">
-        <v>1.89</v>
+        <v>1.958</v>
       </c>
       <c r="BL86" s="3" t="n">
-        <v>3.0835</v>
+        <v>3.1515</v>
       </c>
       <c r="BM86" s="3" t="n">
-        <v>3.334</v>
+        <v>3.402</v>
       </c>
       <c r="BN86" s="3" t="n">
-        <v>3.986</v>
+        <v>4.054</v>
       </c>
       <c r="BO86" s="3" t="n">
         <v>1.993</v>
@@ -19059,10 +19059,10 @@
         <v>2.0825</v>
       </c>
       <c r="BQ86" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="BR86" s="3" t="n">
-        <v>2.05</v>
+        <v>2.095</v>
       </c>
     </row>
     <row r="87">
@@ -19072,199 +19072,199 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2.306</v>
+        <v>2.374</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2.49</v>
+        <v>2.558</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2.379</v>
+        <v>2.37</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>2.5</v>
+        <v>2.568</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>2.0755</v>
+        <v>2.1205</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>1.895</v>
+        <v>1.843</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>2.44</v>
+        <v>2.508</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>3.925</v>
+        <v>4.2</v>
       </c>
       <c r="P87" s="3" t="n">
-        <v>2.35</v>
+        <v>2.418</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>2.725</v>
+        <v>2.793</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>2.3525</v>
+        <v>2.4205</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>2.42</v>
+        <v>2.488</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>2.3735</v>
+        <v>2.4415</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>2.6915</v>
+        <v>2.7105</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>2.52</v>
+        <v>2.588</v>
       </c>
       <c r="W87" s="3" t="n">
-        <v>1.997</v>
+        <v>1.945</v>
       </c>
       <c r="X87" s="3" t="n">
-        <v>2.39</v>
+        <v>2.458</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>2.347</v>
+        <v>2.415</v>
       </c>
       <c r="Z87" s="3" t="n">
-        <v>2.46</v>
+        <v>2.528</v>
       </c>
       <c r="AA87" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AB87" s="3" t="n">
-        <v>2.545</v>
+        <v>2.613</v>
       </c>
       <c r="AC87" s="3" t="n">
-        <v>2.524</v>
+        <v>2.543</v>
       </c>
       <c r="AD87" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AE87" s="3" t="n">
-        <v>2.3</v>
+        <v>2.368</v>
       </c>
       <c r="AF87" s="3" t="n">
-        <v>3.075</v>
+        <v>3.143</v>
       </c>
       <c r="AG87" s="3" t="n">
-        <v>2.638</v>
+        <v>2.706</v>
       </c>
       <c r="AH87" s="3" t="n">
-        <v>2.295</v>
+        <v>2.363</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>2.138</v>
+        <v>2.183</v>
       </c>
       <c r="AJ87" s="3" t="n">
-        <v>2.517</v>
+        <v>2.585</v>
       </c>
       <c r="AK87" s="3" t="n">
         <v>2.493</v>
       </c>
       <c r="AL87" s="3" t="n">
-        <v>2.45</v>
+        <v>2.518</v>
       </c>
       <c r="AM87" s="3" t="n">
-        <v>2.824</v>
+        <v>2.843</v>
       </c>
       <c r="AN87" s="3" t="n">
-        <v>3.718</v>
+        <v>3.737</v>
       </c>
       <c r="AO87" s="3" t="n">
-        <v>3.695</v>
+        <v>4.22</v>
       </c